--- a/dados-catalago-pcm-interno/relatorio.xlsx
+++ b/dados-catalago-pcm-interno/relatorio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amaggicombr-my.sharepoint.com/personal/hiago_andre_amaggi_com_br/Documents/Área de Trabalho/codigos/catalogoPecasPCM/dados-catalago-pcm-interno/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="58" documentId="11_FD86FE4AC4094E4AB971B8A5A011EE841C83CB4A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6135BD73-5016-4859-9A7C-A25BA8757E28}"/>
+  <xr:revisionPtr revIDLastSave="60" documentId="11_FD86FE4AC4094E4AB971B8A5A011EE841C83CB4A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C23EAEF6-8282-46BC-9E68-2F1E358A0310}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5187" uniqueCount="1629">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5187" uniqueCount="1627">
   <si>
     <t/>
   </si>
@@ -3190,12 +3190,6 @@
     <t>RETROREFLETOR ESQ CARR RANDON/210107635P</t>
   </si>
   <si>
-    <t>1040096343</t>
-  </si>
-  <si>
-    <t>RODA LIBRELATO: 9701161</t>
-  </si>
-  <si>
     <t>1010056523</t>
   </si>
   <si>
@@ -3946,9 +3940,6 @@
     <t>SUPORTE RANDON: 260000443-OF</t>
   </si>
   <si>
-    <t>307</t>
-  </si>
-  <si>
     <t>1010064887</t>
   </si>
   <si>
@@ -4027,9 +4018,6 @@
     <t>530</t>
   </si>
   <si>
-    <t>157,950</t>
-  </si>
-  <si>
     <t>1030000490</t>
   </si>
   <si>
@@ -4045,9 +4033,6 @@
     <t>VALVULA RED CURV 45MM STEELS/ST102369211</t>
   </si>
   <si>
-    <t>103</t>
-  </si>
-  <si>
     <t>1010026864</t>
   </si>
   <si>
@@ -4285,18 +4270,12 @@
     <t>314</t>
   </si>
   <si>
-    <t>245</t>
-  </si>
-  <si>
     <t>1010084519</t>
   </si>
   <si>
     <t>SUPORTE CJ DIREITA CARRETA FADO/FF0253</t>
   </si>
   <si>
-    <t>70</t>
-  </si>
-  <si>
     <t>1010084767</t>
   </si>
   <si>
@@ -4480,9 +4459,6 @@
     <t>ROLAMENTO FIX ESF;30X72X19MM;AC;6306ZZC3</t>
   </si>
   <si>
-    <t>116</t>
-  </si>
-  <si>
     <t>1040100107</t>
   </si>
   <si>
@@ -4558,9 +4534,6 @@
     <t>102</t>
   </si>
   <si>
-    <t>162</t>
-  </si>
-  <si>
     <t>460</t>
   </si>
   <si>
@@ -4570,15 +4543,9 @@
     <t>227</t>
   </si>
   <si>
-    <t>253</t>
-  </si>
-  <si>
     <t>176</t>
   </si>
   <si>
-    <t>2.740</t>
-  </si>
-  <si>
     <t>94</t>
   </si>
   <si>
@@ -4606,9 +4573,6 @@
     <t>150</t>
   </si>
   <si>
-    <t>86</t>
-  </si>
-  <si>
     <t>330</t>
   </si>
   <si>
@@ -4633,27 +4597,12 @@
     <t>ARRUELA RANDON: R81000024</t>
   </si>
   <si>
-    <t>485</t>
-  </si>
-  <si>
-    <t>167</t>
-  </si>
-  <si>
     <t>173</t>
   </si>
   <si>
-    <t>128</t>
-  </si>
-  <si>
-    <t>1.101</t>
-  </si>
-  <si>
     <t>191</t>
   </si>
   <si>
-    <t>155,500</t>
-  </si>
-  <si>
     <t>77</t>
   </si>
   <si>
@@ -4663,9 +4612,6 @@
     <t>53</t>
   </si>
   <si>
-    <t>356</t>
-  </si>
-  <si>
     <t>255</t>
   </si>
   <si>
@@ -4675,15 +4621,6 @@
     <t>SUPORTE DIANT ESQ CARRETA FADO/FF0253A</t>
   </si>
   <si>
-    <t>1.070</t>
-  </si>
-  <si>
-    <t>236</t>
-  </si>
-  <si>
-    <t>5.497</t>
-  </si>
-  <si>
     <t>1010077386</t>
   </si>
   <si>
@@ -4723,18 +4660,12 @@
     <t>112</t>
   </si>
   <si>
-    <t>172</t>
-  </si>
-  <si>
     <t>190</t>
   </si>
   <si>
     <t>101</t>
   </si>
   <si>
-    <t>329</t>
-  </si>
-  <si>
     <t>160</t>
   </si>
   <si>
@@ -4753,9 +4684,6 @@
     <t>COXIM RANDON: AD00342J00</t>
   </si>
   <si>
-    <t>293</t>
-  </si>
-  <si>
     <t>1010084109</t>
   </si>
   <si>
@@ -4768,36 +4696,15 @@
     <t>171</t>
   </si>
   <si>
-    <t>615</t>
-  </si>
-  <si>
-    <t>1.233</t>
-  </si>
-  <si>
     <t>435</t>
   </si>
   <si>
     <t>186</t>
   </si>
   <si>
-    <t>416</t>
-  </si>
-  <si>
-    <t>467</t>
-  </si>
-  <si>
     <t>111</t>
   </si>
   <si>
-    <t>355</t>
-  </si>
-  <si>
-    <t>133</t>
-  </si>
-  <si>
-    <t>334</t>
-  </si>
-  <si>
     <t>83,500</t>
   </si>
   <si>
@@ -4813,9 +4720,6 @@
     <t>359</t>
   </si>
   <si>
-    <t>2.100</t>
-  </si>
-  <si>
     <t>1.923</t>
   </si>
   <si>
@@ -4855,24 +4759,15 @@
     <t>1.080</t>
   </si>
   <si>
-    <t>214</t>
-  </si>
-  <si>
     <t>408</t>
   </si>
   <si>
     <t>3.969,830</t>
   </si>
   <si>
-    <t>26.390</t>
-  </si>
-  <si>
     <t>924</t>
   </si>
   <si>
-    <t>74</t>
-  </si>
-  <si>
     <t>365</t>
   </si>
   <si>
@@ -4885,28 +4780,127 @@
     <t>232</t>
   </si>
   <si>
-    <t>569</t>
-  </si>
-  <si>
-    <t>145</t>
-  </si>
-  <si>
     <t>210</t>
   </si>
   <si>
-    <t>131.229,950</t>
-  </si>
-  <si>
-    <t>10.411,450</t>
-  </si>
-  <si>
-    <t>1.399</t>
-  </si>
-  <si>
-    <t>8.419</t>
-  </si>
-  <si>
     <t>126.229,500</t>
+  </si>
+  <si>
+    <t>5.477</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>473</t>
+  </si>
+  <si>
+    <t>165</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>154</t>
+  </si>
+  <si>
+    <t>297</t>
+  </si>
+  <si>
+    <t>290</t>
+  </si>
+  <si>
+    <t>166</t>
+  </si>
+  <si>
+    <t>241</t>
+  </si>
+  <si>
+    <t>595</t>
+  </si>
+  <si>
+    <t>1.153</t>
+  </si>
+  <si>
+    <t>1.089</t>
+  </si>
+  <si>
+    <t>295</t>
+  </si>
+  <si>
+    <t>411</t>
+  </si>
+  <si>
+    <t>459</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>152</t>
+  </si>
+  <si>
+    <t>152,500</t>
+  </si>
+  <si>
+    <t>333</t>
+  </si>
+  <si>
+    <t>151,450</t>
+  </si>
+  <si>
+    <t>2.020</t>
+  </si>
+  <si>
+    <t>2.728</t>
+  </si>
+  <si>
+    <t>204</t>
+  </si>
+  <si>
+    <t>350</t>
+  </si>
+  <si>
+    <t>207</t>
+  </si>
+  <si>
+    <t>282</t>
+  </si>
+  <si>
+    <t>26.000</t>
+  </si>
+  <si>
+    <t>135</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>1.058</t>
+  </si>
+  <si>
+    <t>557</t>
+  </si>
+  <si>
+    <t>141</t>
+  </si>
+  <si>
+    <t>131.149,950</t>
+  </si>
+  <si>
+    <t>10.384,950</t>
+  </si>
+  <si>
+    <t>1.393</t>
+  </si>
+  <si>
+    <t>8.381</t>
+  </si>
+  <si>
+    <t>125.370,500</t>
   </si>
 </sst>
 </file>
@@ -4975,10 +4969,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5315,19 +5305,19 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="G1" t="s">
         <v>3</v>
@@ -5370,7 +5360,7 @@
         <v>7</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1553</v>
+        <v>1588</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>9</v>
@@ -5416,7 +5406,7 @@
         <v>7</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>146</v>
+        <v>8</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>9</v>
@@ -5568,16 +5558,16 @@
         <v>4</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1491</v>
+        <v>1483</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1492</v>
+        <v>1484</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1493</v>
+        <v>1485</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>428</v>
@@ -5637,10 +5627,10 @@
         <v>4</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1554</v>
+        <v>1533</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1555</v>
+        <v>1534</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>7</v>
@@ -5739,7 +5729,7 @@
         <v>7</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>1509</v>
+        <v>1501</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>9</v>
@@ -5762,7 +5752,7 @@
         <v>7</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1456</v>
+        <v>1449</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>9</v>
@@ -5831,7 +5821,7 @@
         <v>7</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>1510</v>
+        <v>1502</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>9</v>
@@ -5877,7 +5867,7 @@
         <v>7</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>1420</v>
+        <v>1415</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>9</v>
@@ -5900,7 +5890,7 @@
         <v>7</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>1431</v>
+        <v>1424</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>9</v>
@@ -5937,10 +5927,10 @@
         <v>4</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>7</v>
@@ -5992,7 +5982,7 @@
         <v>7</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>86</v>
+        <v>317</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>9</v>
@@ -6075,10 +6065,10 @@
         <v>4</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>1556</v>
+        <v>1535</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>1557</v>
+        <v>1536</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>7</v>
@@ -6107,7 +6097,7 @@
         <v>7</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>1558</v>
+        <v>1537</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>9</v>
@@ -6130,7 +6120,7 @@
         <v>7</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>1559</v>
+        <v>1538</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>9</v>
@@ -6153,7 +6143,7 @@
         <v>7</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>242</v>
+        <v>1589</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>9</v>
@@ -6199,7 +6189,7 @@
         <v>7</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>1388</v>
+        <v>1383</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>9</v>
@@ -6222,7 +6212,7 @@
         <v>7</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>1457</v>
+        <v>1450</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>100</v>
@@ -6259,16 +6249,16 @@
         <v>4</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>1356</v>
+        <v>1351</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>1357</v>
+        <v>1352</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>1458</v>
+        <v>1451</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>9</v>
@@ -6291,7 +6281,7 @@
         <v>7</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>1560</v>
+        <v>1539</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>9</v>
@@ -6314,7 +6304,7 @@
         <v>7</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>1381</v>
+        <v>1376</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>9</v>
@@ -6337,7 +6327,7 @@
         <v>7</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>1494</v>
+        <v>1486</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>9</v>
@@ -6351,16 +6341,16 @@
         <v>4</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>1535</v>
+        <v>1523</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>1536</v>
+        <v>1524</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>1561</v>
+        <v>1540</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>9</v>
@@ -6383,7 +6373,7 @@
         <v>7</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>1537</v>
+        <v>1590</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>9</v>
@@ -6406,7 +6396,7 @@
         <v>7</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>1460</v>
+        <v>1453</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>9</v>
@@ -6452,7 +6442,7 @@
         <v>7</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>1562</v>
+        <v>1541</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>9</v>
@@ -6489,10 +6479,10 @@
         <v>4</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>1495</v>
+        <v>1487</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>1496</v>
+        <v>1488</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>40</v>
@@ -6535,10 +6525,10 @@
         <v>4</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>1461</v>
+        <v>1454</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>1462</v>
+        <v>1455</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>7</v>
@@ -6788,16 +6778,16 @@
         <v>4</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>1563</v>
+        <v>1542</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>1564</v>
+        <v>1543</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>146</v>
+        <v>8</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>9</v>
@@ -6889,7 +6879,7 @@
         <v>7</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>523</v>
+        <v>216</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>9</v>
@@ -7248,10 +7238,10 @@
         <v>4</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>40</v>
@@ -7478,10 +7468,10 @@
         <v>4</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>40</v>
@@ -7823,10 +7813,10 @@
         <v>4</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>1389</v>
+        <v>1384</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>7</v>
@@ -7846,10 +7836,10 @@
         <v>4</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>1391</v>
+        <v>1386</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>1392</v>
+        <v>1387</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>7</v>
@@ -7869,16 +7859,16 @@
         <v>4</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>1393</v>
+        <v>1388</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>1394</v>
+        <v>1389</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>1400</v>
+        <v>1395</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>9</v>
@@ -7892,10 +7882,10 @@
         <v>4</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1395</v>
+        <v>1390</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>1396</v>
+        <v>1391</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>7</v>
@@ -7924,7 +7914,7 @@
         <v>7</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>9</v>
@@ -7970,7 +7960,7 @@
         <v>7</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>1497</v>
+        <v>1489</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>9</v>
@@ -8016,7 +8006,7 @@
         <v>7</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>1434</v>
+        <v>1427</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>9</v>
@@ -8039,7 +8029,7 @@
         <v>7</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>1382</v>
+        <v>1377</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>9</v>
@@ -8062,7 +8052,7 @@
         <v>7</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>1565</v>
+        <v>1544</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>9</v>
@@ -8223,7 +8213,7 @@
         <v>7</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>1066</v>
+        <v>523</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>265</v>
@@ -8237,10 +8227,10 @@
         <v>4</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>1397</v>
+        <v>1392</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>1398</v>
+        <v>1393</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>7</v>
@@ -8269,7 +8259,7 @@
         <v>19</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>1347</v>
+        <v>1342</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>265</v>
@@ -8283,10 +8273,10 @@
         <v>4</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>1418</v>
+        <v>1413</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>1419</v>
+        <v>1414</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>7</v>
@@ -8338,7 +8328,7 @@
         <v>7</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>30</v>
+        <v>149</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>9</v>
@@ -8361,7 +8351,7 @@
         <v>19</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>1360</v>
+        <v>1355</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>9</v>
@@ -8384,7 +8374,7 @@
         <v>7</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>146</v>
+        <v>8</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>9</v>
@@ -8591,7 +8581,7 @@
         <v>7</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>1348</v>
+        <v>1343</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>9</v>
@@ -8628,10 +8618,10 @@
         <v>4</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>1318</v>
+        <v>1315</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>1319</v>
+        <v>1316</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>277</v>
@@ -8720,10 +8710,10 @@
         <v>4</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>1321</v>
+        <v>1318</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>277</v>
@@ -8766,10 +8756,10 @@
         <v>4</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>1322</v>
+        <v>1319</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>1323</v>
+        <v>1320</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>277</v>
@@ -8789,10 +8779,10 @@
         <v>4</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>1324</v>
+        <v>1321</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>1325</v>
+        <v>1322</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>277</v>
@@ -8812,10 +8802,10 @@
         <v>4</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>1326</v>
+        <v>1323</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>277</v>
@@ -8858,10 +8848,10 @@
         <v>4</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>1328</v>
+        <v>1325</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>277</v>
@@ -8890,7 +8880,7 @@
         <v>277</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>1498</v>
+        <v>1490</v>
       </c>
       <c r="F156" s="2" t="s">
         <v>9</v>
@@ -8973,10 +8963,10 @@
         <v>4</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>1330</v>
+        <v>1327</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>1331</v>
+        <v>1328</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>277</v>
@@ -8996,10 +8986,10 @@
         <v>4</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>1332</v>
+        <v>1329</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>1333</v>
+        <v>1330</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>277</v>
@@ -9019,10 +9009,10 @@
         <v>4</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>1309</v>
+        <v>1306</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>1310</v>
+        <v>1307</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>277</v>
@@ -9042,10 +9032,10 @@
         <v>4</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>1312</v>
+        <v>1309</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>277</v>
@@ -9065,10 +9055,10 @@
         <v>4</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>1313</v>
+        <v>1310</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>1314</v>
+        <v>1311</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>277</v>
@@ -9088,10 +9078,10 @@
         <v>4</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>277</v>
@@ -9189,7 +9179,7 @@
         <v>277</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>1354</v>
+        <v>1349</v>
       </c>
       <c r="F169" s="2" t="s">
         <v>9</v>
@@ -9212,7 +9202,7 @@
         <v>277</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
       <c r="F170" s="2" t="s">
         <v>9</v>
@@ -9235,7 +9225,7 @@
         <v>277</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>1538</v>
+        <v>1591</v>
       </c>
       <c r="F171" s="2" t="s">
         <v>9</v>
@@ -9258,7 +9248,7 @@
         <v>19</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>1338</v>
+        <v>1334</v>
       </c>
       <c r="F172" s="2" t="s">
         <v>9</v>
@@ -9281,7 +9271,7 @@
         <v>277</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>1486</v>
+        <v>1592</v>
       </c>
       <c r="F173" s="2" t="s">
         <v>9</v>
@@ -9304,7 +9294,7 @@
         <v>19</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>1399</v>
+        <v>1394</v>
       </c>
       <c r="F174" s="2" t="s">
         <v>9</v>
@@ -9327,7 +9317,7 @@
         <v>277</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="F175" s="2" t="s">
         <v>9</v>
@@ -9373,7 +9363,7 @@
         <v>277</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="F177" s="2" t="s">
         <v>9</v>
@@ -9419,7 +9409,7 @@
         <v>277</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>1566</v>
+        <v>1545</v>
       </c>
       <c r="F179" s="2" t="s">
         <v>9</v>
@@ -9465,7 +9455,7 @@
         <v>277</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>1406</v>
+        <v>1401</v>
       </c>
       <c r="F181" s="2" t="s">
         <v>9</v>
@@ -9534,7 +9524,7 @@
         <v>277</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>1567</v>
+        <v>1557</v>
       </c>
       <c r="F184" s="2" t="s">
         <v>9</v>
@@ -9672,7 +9662,7 @@
         <v>7</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="F190" s="2" t="s">
         <v>9</v>
@@ -9695,7 +9685,7 @@
         <v>7</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>1568</v>
+        <v>1546</v>
       </c>
       <c r="F191" s="2" t="s">
         <v>9</v>
@@ -9718,7 +9708,7 @@
         <v>7</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>1569</v>
+        <v>1547</v>
       </c>
       <c r="F192" s="2" t="s">
         <v>9</v>
@@ -9833,7 +9823,7 @@
         <v>40</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="F197" s="2" t="s">
         <v>9</v>
@@ -9879,7 +9869,7 @@
         <v>7</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>216</v>
+        <v>143</v>
       </c>
       <c r="F199" s="2" t="s">
         <v>9</v>
@@ -9916,16 +9906,16 @@
         <v>4</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>1432</v>
+        <v>1425</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>1433</v>
+        <v>1426</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>156</v>
+        <v>42</v>
       </c>
       <c r="F201" s="2" t="s">
         <v>9</v>
@@ -9971,7 +9961,7 @@
         <v>7</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="F203" s="2" t="s">
         <v>9</v>
@@ -10040,7 +10030,7 @@
         <v>7</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>1570</v>
+        <v>1501</v>
       </c>
       <c r="F206" s="2" t="s">
         <v>9</v>
@@ -10063,7 +10053,7 @@
         <v>7</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>1571</v>
+        <v>1548</v>
       </c>
       <c r="F207" s="2" t="s">
         <v>9</v>
@@ -10376,10 +10366,10 @@
         <v>4</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>1464</v>
+        <v>1457</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>1465</v>
+        <v>1458</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>40</v>
@@ -10431,7 +10421,7 @@
         <v>40</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>1511</v>
+        <v>1503</v>
       </c>
       <c r="F223" s="2" t="s">
         <v>9</v>
@@ -10454,7 +10444,7 @@
         <v>7</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="F224" s="2" t="s">
         <v>9</v>
@@ -10477,7 +10467,7 @@
         <v>427</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>1572</v>
+        <v>1549</v>
       </c>
       <c r="F225" s="2" t="s">
         <v>428</v>
@@ -10546,7 +10536,7 @@
         <v>7</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>1511</v>
+        <v>1593</v>
       </c>
       <c r="F228" s="2" t="s">
         <v>100</v>
@@ -10592,7 +10582,7 @@
         <v>7</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>1512</v>
+        <v>1594</v>
       </c>
       <c r="F230" s="2" t="s">
         <v>9</v>
@@ -10661,7 +10651,7 @@
         <v>7</v>
       </c>
       <c r="E233" s="2" t="s">
-        <v>1505</v>
+        <v>1497</v>
       </c>
       <c r="F233" s="2" t="s">
         <v>9</v>
@@ -10822,7 +10812,7 @@
         <v>7</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>1499</v>
+        <v>1491</v>
       </c>
       <c r="F240" s="2" t="s">
         <v>265</v>
@@ -10882,16 +10872,16 @@
         <v>4</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>1573</v>
+        <v>1550</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>1574</v>
+        <v>1551</v>
       </c>
       <c r="D243" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="F243" s="2" t="s">
         <v>528</v>
@@ -10914,7 +10904,7 @@
         <v>7</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>20</v>
+        <v>1350</v>
       </c>
       <c r="F244" s="2" t="s">
         <v>9</v>
@@ -10937,7 +10927,7 @@
         <v>19</v>
       </c>
       <c r="E245" s="2" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
       <c r="F245" s="2" t="s">
         <v>9</v>
@@ -10960,7 +10950,7 @@
         <v>7</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>1308</v>
+        <v>1595</v>
       </c>
       <c r="F246" s="2" t="s">
         <v>9</v>
@@ -10997,10 +10987,10 @@
         <v>4</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>1466</v>
+        <v>1459</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>1467</v>
+        <v>1460</v>
       </c>
       <c r="D248" s="2" t="s">
         <v>7</v>
@@ -11020,10 +11010,10 @@
         <v>4</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>1575</v>
+        <v>1552</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>1576</v>
+        <v>1553</v>
       </c>
       <c r="D249" s="2" t="s">
         <v>7</v>
@@ -11098,7 +11088,7 @@
         <v>7</v>
       </c>
       <c r="E252" s="2" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="F252" s="2" t="s">
         <v>9</v>
@@ -11259,7 +11249,7 @@
         <v>33</v>
       </c>
       <c r="E259" s="2" t="s">
-        <v>1456</v>
+        <v>1560</v>
       </c>
       <c r="F259" s="2" t="s">
         <v>9</v>
@@ -11305,7 +11295,7 @@
         <v>7</v>
       </c>
       <c r="E261" s="2" t="s">
-        <v>1508</v>
+        <v>1500</v>
       </c>
       <c r="F261" s="2" t="s">
         <v>9</v>
@@ -11328,7 +11318,7 @@
         <v>19</v>
       </c>
       <c r="E262" s="2" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="F262" s="2" t="s">
         <v>9</v>
@@ -11351,7 +11341,7 @@
         <v>7</v>
       </c>
       <c r="E263" s="2" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
       <c r="F263" s="2" t="s">
         <v>9</v>
@@ -11443,7 +11433,7 @@
         <v>7</v>
       </c>
       <c r="E267" s="2" t="s">
-        <v>1409</v>
+        <v>1404</v>
       </c>
       <c r="F267" s="2" t="s">
         <v>9</v>
@@ -11466,7 +11456,7 @@
         <v>7</v>
       </c>
       <c r="E268" s="2" t="s">
-        <v>1435</v>
+        <v>1428</v>
       </c>
       <c r="F268" s="2" t="s">
         <v>9</v>
@@ -11526,10 +11516,10 @@
         <v>4</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>1468</v>
+        <v>1461</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>1469</v>
+        <v>1462</v>
       </c>
       <c r="D271" s="2" t="s">
         <v>7</v>
@@ -11558,7 +11548,7 @@
         <v>7</v>
       </c>
       <c r="E272" s="2" t="s">
-        <v>1456</v>
+        <v>1449</v>
       </c>
       <c r="F272" s="2" t="s">
         <v>9</v>
@@ -11572,16 +11562,16 @@
         <v>4</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>1364</v>
+        <v>1359</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>1365</v>
+        <v>1360</v>
       </c>
       <c r="D273" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>1354</v>
+        <v>1349</v>
       </c>
       <c r="F273" s="2" t="s">
         <v>9</v>
@@ -11742,7 +11732,7 @@
         <v>7</v>
       </c>
       <c r="E280" s="2" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="F280" s="2" t="s">
         <v>9</v>
@@ -11825,10 +11815,10 @@
         <v>4</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>1470</v>
+        <v>1463</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>1471</v>
+        <v>1464</v>
       </c>
       <c r="D284" s="2" t="s">
         <v>7</v>
@@ -11894,10 +11884,10 @@
         <v>4</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>1366</v>
+        <v>1361</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>1367</v>
+        <v>1362</v>
       </c>
       <c r="D287" s="2" t="s">
         <v>7</v>
@@ -11972,7 +11962,7 @@
         <v>7</v>
       </c>
       <c r="E290" s="2" t="s">
-        <v>1577</v>
+        <v>1596</v>
       </c>
       <c r="F290" s="2" t="s">
         <v>100</v>
@@ -11986,10 +11976,10 @@
         <v>4</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>1578</v>
+        <v>1554</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>1579</v>
+        <v>1555</v>
       </c>
       <c r="D291" s="2" t="s">
         <v>7</v>
@@ -12041,7 +12031,7 @@
         <v>7</v>
       </c>
       <c r="E293" s="2" t="s">
-        <v>1580</v>
+        <v>1556</v>
       </c>
       <c r="F293" s="2" t="s">
         <v>9</v>
@@ -12133,7 +12123,7 @@
         <v>7</v>
       </c>
       <c r="E297" s="2" t="s">
-        <v>1581</v>
+        <v>1597</v>
       </c>
       <c r="F297" s="2" t="s">
         <v>9</v>
@@ -12202,7 +12192,7 @@
         <v>7</v>
       </c>
       <c r="E300" s="2" t="s">
-        <v>1539</v>
+        <v>1525</v>
       </c>
       <c r="F300" s="2" t="s">
         <v>9</v>
@@ -12225,7 +12215,7 @@
         <v>7</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>1514</v>
+        <v>1505</v>
       </c>
       <c r="F301" s="2" t="s">
         <v>9</v>
@@ -12248,7 +12238,7 @@
         <v>7</v>
       </c>
       <c r="E302" s="2" t="s">
-        <v>1381</v>
+        <v>1376</v>
       </c>
       <c r="F302" s="2" t="s">
         <v>9</v>
@@ -12271,7 +12261,7 @@
         <v>7</v>
       </c>
       <c r="E303" s="2" t="s">
-        <v>216</v>
+        <v>103</v>
       </c>
       <c r="F303" s="2" t="s">
         <v>9</v>
@@ -12317,7 +12307,7 @@
         <v>7</v>
       </c>
       <c r="E305" s="2" t="s">
-        <v>211</v>
+        <v>104</v>
       </c>
       <c r="F305" s="2" t="s">
         <v>9</v>
@@ -12340,7 +12330,7 @@
         <v>7</v>
       </c>
       <c r="E306" s="2" t="s">
-        <v>127</v>
+        <v>211</v>
       </c>
       <c r="F306" s="2" t="s">
         <v>9</v>
@@ -12455,7 +12445,7 @@
         <v>7</v>
       </c>
       <c r="E311" s="2" t="s">
-        <v>1431</v>
+        <v>1598</v>
       </c>
       <c r="F311" s="2" t="s">
         <v>9</v>
@@ -12570,7 +12560,7 @@
         <v>7</v>
       </c>
       <c r="E316" s="2" t="s">
-        <v>1582</v>
+        <v>1599</v>
       </c>
       <c r="F316" s="2" t="s">
         <v>9</v>
@@ -12607,10 +12597,10 @@
         <v>4</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>1500</v>
+        <v>1492</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>1501</v>
+        <v>1493</v>
       </c>
       <c r="D318" s="2" t="s">
         <v>33</v>
@@ -12639,7 +12629,7 @@
         <v>7</v>
       </c>
       <c r="E319" s="2" t="s">
-        <v>571</v>
+        <v>23</v>
       </c>
       <c r="F319" s="2" t="s">
         <v>9</v>
@@ -12653,16 +12643,16 @@
         <v>4</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>1436</v>
+        <v>1429</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>1437</v>
+        <v>1430</v>
       </c>
       <c r="D320" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E320" s="2" t="s">
-        <v>1382</v>
+        <v>1377</v>
       </c>
       <c r="F320" s="2" t="s">
         <v>100</v>
@@ -12708,7 +12698,7 @@
         <v>7</v>
       </c>
       <c r="E322" s="2" t="s">
-        <v>1348</v>
+        <v>1343</v>
       </c>
       <c r="F322" s="2" t="s">
         <v>9</v>
@@ -12731,7 +12721,7 @@
         <v>7</v>
       </c>
       <c r="E323" s="2" t="s">
-        <v>1540</v>
+        <v>1239</v>
       </c>
       <c r="F323" s="2" t="s">
         <v>9</v>
@@ -12754,7 +12744,7 @@
         <v>7</v>
       </c>
       <c r="E324" s="2" t="s">
-        <v>1513</v>
+        <v>1504</v>
       </c>
       <c r="F324" s="2" t="s">
         <v>9</v>
@@ -12823,7 +12813,7 @@
         <v>7</v>
       </c>
       <c r="E327" s="2" t="s">
-        <v>1583</v>
+        <v>1600</v>
       </c>
       <c r="F327" s="2" t="s">
         <v>9</v>
@@ -12846,7 +12836,7 @@
         <v>19</v>
       </c>
       <c r="E328" s="2" t="s">
-        <v>1502</v>
+        <v>1494</v>
       </c>
       <c r="F328" s="2" t="s">
         <v>9</v>
@@ -12906,10 +12896,10 @@
         <v>4</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>1473</v>
+        <v>1466</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>1474</v>
+        <v>1467</v>
       </c>
       <c r="D331" s="2" t="s">
         <v>7</v>
@@ -12961,7 +12951,7 @@
         <v>7</v>
       </c>
       <c r="E333" s="2" t="s">
-        <v>1414</v>
+        <v>1409</v>
       </c>
       <c r="F333" s="2" t="s">
         <v>9</v>
@@ -12984,7 +12974,7 @@
         <v>7</v>
       </c>
       <c r="E334" s="2" t="s">
-        <v>1434</v>
+        <v>1427</v>
       </c>
       <c r="F334" s="2" t="s">
         <v>9</v>
@@ -12998,10 +12988,10 @@
         <v>4</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>1475</v>
+        <v>1468</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>1476</v>
+        <v>1469</v>
       </c>
       <c r="D335" s="2" t="s">
         <v>7</v>
@@ -13030,7 +13020,7 @@
         <v>33</v>
       </c>
       <c r="E336" s="2" t="s">
-        <v>1482</v>
+        <v>518</v>
       </c>
       <c r="F336" s="2" t="s">
         <v>9</v>
@@ -13076,7 +13066,7 @@
         <v>7</v>
       </c>
       <c r="E338" s="2" t="s">
-        <v>292</v>
+        <v>864</v>
       </c>
       <c r="F338" s="2" t="s">
         <v>9</v>
@@ -13099,7 +13089,7 @@
         <v>7</v>
       </c>
       <c r="E339" s="2" t="s">
-        <v>37</v>
+        <v>375</v>
       </c>
       <c r="F339" s="2" t="s">
         <v>9</v>
@@ -13168,7 +13158,7 @@
         <v>7</v>
       </c>
       <c r="E342" s="2" t="s">
-        <v>1412</v>
+        <v>1407</v>
       </c>
       <c r="F342" s="2" t="s">
         <v>100</v>
@@ -13214,7 +13204,7 @@
         <v>7</v>
       </c>
       <c r="E344" s="2" t="s">
-        <v>1413</v>
+        <v>1408</v>
       </c>
       <c r="F344" s="2" t="s">
         <v>9</v>
@@ -13228,16 +13218,16 @@
         <v>4</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>1477</v>
+        <v>1470</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>1478</v>
+        <v>1471</v>
       </c>
       <c r="D345" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E345" s="2" t="s">
-        <v>1584</v>
+        <v>1558</v>
       </c>
       <c r="F345" s="2" t="s">
         <v>9</v>
@@ -13260,7 +13250,7 @@
         <v>7</v>
       </c>
       <c r="E346" s="2" t="s">
-        <v>1541</v>
+        <v>1601</v>
       </c>
       <c r="F346" s="2" t="s">
         <v>9</v>
@@ -13283,7 +13273,7 @@
         <v>7</v>
       </c>
       <c r="E347" s="2" t="s">
-        <v>1509</v>
+        <v>1501</v>
       </c>
       <c r="F347" s="2" t="s">
         <v>9</v>
@@ -13297,16 +13287,16 @@
         <v>4</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>1361</v>
+        <v>1356</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>1362</v>
+        <v>1357</v>
       </c>
       <c r="D348" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E348" s="2" t="s">
-        <v>1514</v>
+        <v>1602</v>
       </c>
       <c r="F348" s="2" t="s">
         <v>9</v>
@@ -13375,7 +13365,7 @@
         <v>7</v>
       </c>
       <c r="E351" s="2" t="s">
-        <v>1585</v>
+        <v>1559</v>
       </c>
       <c r="F351" s="2" t="s">
         <v>9</v>
@@ -13398,7 +13388,7 @@
         <v>7</v>
       </c>
       <c r="E352" s="2" t="s">
-        <v>1586</v>
+        <v>1603</v>
       </c>
       <c r="F352" s="2" t="s">
         <v>9</v>
@@ -13421,7 +13411,7 @@
         <v>7</v>
       </c>
       <c r="E353" s="2" t="s">
-        <v>1587</v>
+        <v>1604</v>
       </c>
       <c r="F353" s="2" t="s">
         <v>9</v>
@@ -13444,7 +13434,7 @@
         <v>7</v>
       </c>
       <c r="E354" s="2" t="s">
-        <v>1588</v>
+        <v>1205</v>
       </c>
       <c r="F354" s="2" t="s">
         <v>9</v>
@@ -13467,7 +13457,7 @@
         <v>7</v>
       </c>
       <c r="E355" s="2" t="s">
-        <v>1589</v>
+        <v>1453</v>
       </c>
       <c r="F355" s="2" t="s">
         <v>100</v>
@@ -13513,7 +13503,7 @@
         <v>7</v>
       </c>
       <c r="E357" s="2" t="s">
-        <v>1530</v>
+        <v>1605</v>
       </c>
       <c r="F357" s="2" t="s">
         <v>9</v>
@@ -13536,7 +13526,7 @@
         <v>7</v>
       </c>
       <c r="E358" s="2" t="s">
-        <v>1542</v>
+        <v>1526</v>
       </c>
       <c r="F358" s="2" t="s">
         <v>9</v>
@@ -13582,7 +13572,7 @@
         <v>7</v>
       </c>
       <c r="E360" s="2" t="s">
-        <v>1590</v>
+        <v>1437</v>
       </c>
       <c r="F360" s="2" t="s">
         <v>9</v>
@@ -13605,7 +13595,7 @@
         <v>7</v>
       </c>
       <c r="E361" s="2" t="s">
-        <v>1571</v>
+        <v>1606</v>
       </c>
       <c r="F361" s="2" t="s">
         <v>9</v>
@@ -13628,7 +13618,7 @@
         <v>19</v>
       </c>
       <c r="E362" s="2" t="s">
-        <v>1515</v>
+        <v>1506</v>
       </c>
       <c r="F362" s="2" t="s">
         <v>9</v>
@@ -13651,7 +13641,7 @@
         <v>7</v>
       </c>
       <c r="E363" s="2" t="s">
-        <v>1526</v>
+        <v>1515</v>
       </c>
       <c r="F363" s="2" t="s">
         <v>9</v>
@@ -13697,7 +13687,7 @@
         <v>7</v>
       </c>
       <c r="E365" s="2" t="s">
-        <v>1412</v>
+        <v>1407</v>
       </c>
       <c r="F365" s="2" t="s">
         <v>9</v>
@@ -13720,7 +13710,7 @@
         <v>7</v>
       </c>
       <c r="E366" s="2" t="s">
-        <v>1408</v>
+        <v>1403</v>
       </c>
       <c r="F366" s="2" t="s">
         <v>9</v>
@@ -13803,10 +13793,10 @@
         <v>4</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>1438</v>
+        <v>1431</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>1439</v>
+        <v>1432</v>
       </c>
       <c r="D370" s="2" t="s">
         <v>7</v>
@@ -14065,7 +14055,7 @@
         <v>7</v>
       </c>
       <c r="E381" s="2" t="s">
-        <v>1530</v>
+        <v>1518</v>
       </c>
       <c r="F381" s="2" t="s">
         <v>100</v>
@@ -14088,7 +14078,7 @@
         <v>7</v>
       </c>
       <c r="E382" s="2" t="s">
-        <v>1317</v>
+        <v>1314</v>
       </c>
       <c r="F382" s="2" t="s">
         <v>9</v>
@@ -14111,7 +14101,7 @@
         <v>7</v>
       </c>
       <c r="E383" s="2" t="s">
-        <v>1543</v>
+        <v>1607</v>
       </c>
       <c r="F383" s="2" t="s">
         <v>9</v>
@@ -14203,7 +14193,7 @@
         <v>19</v>
       </c>
       <c r="E387" s="2" t="s">
-        <v>731</v>
+        <v>1529</v>
       </c>
       <c r="F387" s="2" t="s">
         <v>9</v>
@@ -14364,7 +14354,7 @@
         <v>40</v>
       </c>
       <c r="E394" s="2" t="s">
-        <v>1360</v>
+        <v>1355</v>
       </c>
       <c r="F394" s="2" t="s">
         <v>172</v>
@@ -14387,7 +14377,7 @@
         <v>40</v>
       </c>
       <c r="E395" s="2" t="s">
-        <v>242</v>
+        <v>1355</v>
       </c>
       <c r="F395" s="2" t="s">
         <v>172</v>
@@ -14456,7 +14446,7 @@
         <v>40</v>
       </c>
       <c r="E398" s="2" t="s">
-        <v>81</v>
+        <v>1104</v>
       </c>
       <c r="F398" s="2" t="s">
         <v>172</v>
@@ -14470,10 +14460,10 @@
         <v>4</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>1368</v>
+        <v>1363</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>1369</v>
+        <v>1364</v>
       </c>
       <c r="D399" s="2" t="s">
         <v>40</v>
@@ -14548,7 +14538,7 @@
         <v>40</v>
       </c>
       <c r="E402" s="2" t="s">
-        <v>1591</v>
+        <v>1608</v>
       </c>
       <c r="F402" s="2" t="s">
         <v>172</v>
@@ -14723,10 +14713,10 @@
         <v>4</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>1479</v>
+        <v>1472</v>
       </c>
       <c r="C410" s="2" t="s">
-        <v>1480</v>
+        <v>1473</v>
       </c>
       <c r="D410" s="2" t="s">
         <v>7</v>
@@ -14801,7 +14791,7 @@
         <v>7</v>
       </c>
       <c r="E413" s="2" t="s">
-        <v>1335</v>
+        <v>1609</v>
       </c>
       <c r="F413" s="2" t="s">
         <v>265</v>
@@ -14824,7 +14814,7 @@
         <v>7</v>
       </c>
       <c r="E414" s="2" t="s">
-        <v>1592</v>
+        <v>1561</v>
       </c>
       <c r="F414" s="2" t="s">
         <v>265</v>
@@ -14847,7 +14837,7 @@
         <v>19</v>
       </c>
       <c r="E415" s="2" t="s">
-        <v>1472</v>
+        <v>1465</v>
       </c>
       <c r="F415" s="2" t="s">
         <v>265</v>
@@ -14870,7 +14860,7 @@
         <v>7</v>
       </c>
       <c r="E416" s="2" t="s">
-        <v>1453</v>
+        <v>1446</v>
       </c>
       <c r="F416" s="2" t="s">
         <v>9</v>
@@ -14884,10 +14874,10 @@
         <v>4</v>
       </c>
       <c r="B417" s="2" t="s">
-        <v>1440</v>
+        <v>1433</v>
       </c>
       <c r="C417" s="2" t="s">
-        <v>1441</v>
+        <v>1434</v>
       </c>
       <c r="D417" s="2" t="s">
         <v>7</v>
@@ -14953,16 +14943,16 @@
         <v>4</v>
       </c>
       <c r="B420" s="2" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="C420" s="2" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="D420" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E420" s="2" t="s">
-        <v>1544</v>
+        <v>1527</v>
       </c>
       <c r="F420" s="2" t="s">
         <v>9</v>
@@ -14985,7 +14975,7 @@
         <v>7</v>
       </c>
       <c r="E421" s="2" t="s">
-        <v>1593</v>
+        <v>1562</v>
       </c>
       <c r="F421" s="2" t="s">
         <v>9</v>
@@ -15008,7 +14998,7 @@
         <v>7</v>
       </c>
       <c r="E422" s="2" t="s">
-        <v>1594</v>
+        <v>1563</v>
       </c>
       <c r="F422" s="2" t="s">
         <v>9</v>
@@ -15022,10 +15012,10 @@
         <v>4</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>1531</v>
+        <v>1519</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>1532</v>
+        <v>1520</v>
       </c>
       <c r="D423" s="2" t="s">
         <v>7</v>
@@ -15160,16 +15150,16 @@
         <v>4</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>1442</v>
+        <v>1435</v>
       </c>
       <c r="C429" s="2" t="s">
-        <v>1443</v>
+        <v>1436</v>
       </c>
       <c r="D429" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E429" s="2" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="F429" s="2" t="s">
         <v>9</v>
@@ -15215,7 +15205,7 @@
         <v>7</v>
       </c>
       <c r="E431" s="2" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="F431" s="2" t="s">
         <v>9</v>
@@ -15238,7 +15228,7 @@
         <v>19</v>
       </c>
       <c r="E432" s="2" t="s">
-        <v>1463</v>
+        <v>1456</v>
       </c>
       <c r="F432" s="2" t="s">
         <v>9</v>
@@ -15284,7 +15274,7 @@
         <v>7</v>
       </c>
       <c r="E434" s="2" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="F434" s="2" t="s">
         <v>9</v>
@@ -15330,7 +15320,7 @@
         <v>7</v>
       </c>
       <c r="E436" s="2" t="s">
-        <v>1595</v>
+        <v>1564</v>
       </c>
       <c r="F436" s="2" t="s">
         <v>9</v>
@@ -15376,7 +15366,7 @@
         <v>40</v>
       </c>
       <c r="E438" s="2" t="s">
-        <v>1400</v>
+        <v>1395</v>
       </c>
       <c r="F438" s="2" t="s">
         <v>9</v>
@@ -15399,7 +15389,7 @@
         <v>40</v>
       </c>
       <c r="E439" s="2" t="s">
-        <v>1504</v>
+        <v>1496</v>
       </c>
       <c r="F439" s="2" t="s">
         <v>9</v>
@@ -15422,7 +15412,7 @@
         <v>40</v>
       </c>
       <c r="E440" s="2" t="s">
-        <v>1527</v>
+        <v>1516</v>
       </c>
       <c r="F440" s="2" t="s">
         <v>9</v>
@@ -15445,7 +15435,7 @@
         <v>40</v>
       </c>
       <c r="E441" s="2" t="s">
-        <v>1596</v>
+        <v>1565</v>
       </c>
       <c r="F441" s="2" t="s">
         <v>9</v>
@@ -15468,7 +15458,7 @@
         <v>33</v>
       </c>
       <c r="E442" s="2" t="s">
-        <v>1597</v>
+        <v>1610</v>
       </c>
       <c r="F442" s="2" t="s">
         <v>428</v>
@@ -15505,10 +15495,10 @@
         <v>4</v>
       </c>
       <c r="B444" s="2" t="s">
-        <v>1415</v>
+        <v>1410</v>
       </c>
       <c r="C444" s="2" t="s">
-        <v>1416</v>
+        <v>1411</v>
       </c>
       <c r="D444" s="2" t="s">
         <v>7</v>
@@ -15859,7 +15849,7 @@
         <v>7</v>
       </c>
       <c r="E459" s="2" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
       <c r="F459" s="2" t="s">
         <v>9</v>
@@ -15905,7 +15895,7 @@
         <v>7</v>
       </c>
       <c r="E461" s="2" t="s">
-        <v>1516</v>
+        <v>1366</v>
       </c>
       <c r="F461" s="2" t="s">
         <v>100</v>
@@ -15951,7 +15941,7 @@
         <v>7</v>
       </c>
       <c r="E463" s="2" t="s">
-        <v>1370</v>
+        <v>1365</v>
       </c>
       <c r="F463" s="2" t="s">
         <v>9</v>
@@ -15974,7 +15964,7 @@
         <v>7</v>
       </c>
       <c r="E464" s="2" t="s">
-        <v>1363</v>
+        <v>1358</v>
       </c>
       <c r="F464" s="2" t="s">
         <v>9</v>
@@ -15997,7 +15987,7 @@
         <v>7</v>
       </c>
       <c r="E465" s="2" t="s">
-        <v>1598</v>
+        <v>1566</v>
       </c>
       <c r="F465" s="2" t="s">
         <v>9</v>
@@ -16020,7 +16010,7 @@
         <v>7</v>
       </c>
       <c r="E466" s="2" t="s">
-        <v>1599</v>
+        <v>1567</v>
       </c>
       <c r="F466" s="2" t="s">
         <v>9</v>
@@ -16043,7 +16033,7 @@
         <v>7</v>
       </c>
       <c r="E467" s="2" t="s">
-        <v>1459</v>
+        <v>1452</v>
       </c>
       <c r="F467" s="2" t="s">
         <v>9</v>
@@ -16089,7 +16079,7 @@
         <v>7</v>
       </c>
       <c r="E469" s="2" t="s">
-        <v>1454</v>
+        <v>1447</v>
       </c>
       <c r="F469" s="2" t="s">
         <v>100</v>
@@ -16112,7 +16102,7 @@
         <v>7</v>
       </c>
       <c r="E470" s="2" t="s">
-        <v>1545</v>
+        <v>1528</v>
       </c>
       <c r="F470" s="2" t="s">
         <v>100</v>
@@ -16172,10 +16162,10 @@
         <v>4</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>1342</v>
+        <v>1337</v>
       </c>
       <c r="C473" s="2" t="s">
-        <v>1343</v>
+        <v>1338</v>
       </c>
       <c r="D473" s="2" t="s">
         <v>7</v>
@@ -16204,7 +16194,7 @@
         <v>7</v>
       </c>
       <c r="E474" s="2" t="s">
-        <v>1600</v>
+        <v>1568</v>
       </c>
       <c r="F474" s="2" t="s">
         <v>9</v>
@@ -16227,7 +16217,7 @@
         <v>7</v>
       </c>
       <c r="E475" s="2" t="s">
-        <v>1409</v>
+        <v>1404</v>
       </c>
       <c r="F475" s="2" t="s">
         <v>9</v>
@@ -16250,7 +16240,7 @@
         <v>7</v>
       </c>
       <c r="E476" s="2" t="s">
-        <v>1517</v>
+        <v>1507</v>
       </c>
       <c r="F476" s="2" t="s">
         <v>9</v>
@@ -16296,7 +16286,7 @@
         <v>7</v>
       </c>
       <c r="E478" s="2" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="F478" s="2" t="s">
         <v>9</v>
@@ -16310,10 +16300,10 @@
         <v>4</v>
       </c>
       <c r="B479" s="2" t="s">
-        <v>1601</v>
+        <v>1569</v>
       </c>
       <c r="C479" s="2" t="s">
-        <v>1602</v>
+        <v>1570</v>
       </c>
       <c r="D479" s="2" t="s">
         <v>7</v>
@@ -16365,7 +16355,7 @@
         <v>7</v>
       </c>
       <c r="E481" s="2" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="F481" s="2" t="s">
         <v>9</v>
@@ -16379,10 +16369,10 @@
         <v>4</v>
       </c>
       <c r="B482" s="2" t="s">
-        <v>1401</v>
+        <v>1396</v>
       </c>
       <c r="C482" s="2" t="s">
-        <v>1402</v>
+        <v>1397</v>
       </c>
       <c r="D482" s="2" t="s">
         <v>7</v>
@@ -16434,7 +16424,7 @@
         <v>7</v>
       </c>
       <c r="E484" s="2" t="s">
-        <v>1371</v>
+        <v>1366</v>
       </c>
       <c r="F484" s="2" t="s">
         <v>9</v>
@@ -16457,7 +16447,7 @@
         <v>7</v>
       </c>
       <c r="E485" s="2" t="s">
-        <v>1403</v>
+        <v>1398</v>
       </c>
       <c r="F485" s="2" t="s">
         <v>9</v>
@@ -16480,7 +16470,7 @@
         <v>7</v>
       </c>
       <c r="E486" s="2" t="s">
-        <v>1383</v>
+        <v>1378</v>
       </c>
       <c r="F486" s="2" t="s">
         <v>9</v>
@@ -16503,7 +16493,7 @@
         <v>7</v>
       </c>
       <c r="E487" s="2" t="s">
-        <v>1603</v>
+        <v>1571</v>
       </c>
       <c r="F487" s="2" t="s">
         <v>9</v>
@@ -16526,7 +16516,7 @@
         <v>7</v>
       </c>
       <c r="E488" s="2" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="F488" s="2" t="s">
         <v>9</v>
@@ -16540,16 +16530,16 @@
         <v>4</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>1404</v>
+        <v>1399</v>
       </c>
       <c r="C489" s="2" t="s">
-        <v>1405</v>
+        <v>1400</v>
       </c>
       <c r="D489" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E489" s="2" t="s">
-        <v>1066</v>
+        <v>200</v>
       </c>
       <c r="F489" s="2" t="s">
         <v>9</v>
@@ -16572,7 +16562,7 @@
         <v>7</v>
       </c>
       <c r="E490" s="2" t="s">
-        <v>1303</v>
+        <v>1495</v>
       </c>
       <c r="F490" s="2" t="s">
         <v>9</v>
@@ -16595,7 +16585,7 @@
         <v>7</v>
       </c>
       <c r="E491" s="2" t="s">
-        <v>1604</v>
+        <v>1572</v>
       </c>
       <c r="F491" s="2" t="s">
         <v>9</v>
@@ -16618,7 +16608,7 @@
         <v>7</v>
       </c>
       <c r="E492" s="2" t="s">
-        <v>1417</v>
+        <v>1412</v>
       </c>
       <c r="F492" s="2" t="s">
         <v>9</v>
@@ -16641,7 +16631,7 @@
         <v>7</v>
       </c>
       <c r="E493" s="2" t="s">
-        <v>1605</v>
+        <v>1573</v>
       </c>
       <c r="F493" s="2" t="s">
         <v>9</v>
@@ -16664,7 +16654,7 @@
         <v>7</v>
       </c>
       <c r="E494" s="2" t="s">
-        <v>1355</v>
+        <v>1350</v>
       </c>
       <c r="F494" s="2" t="s">
         <v>9</v>
@@ -16710,7 +16700,7 @@
         <v>7</v>
       </c>
       <c r="E496" s="2" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="F496" s="2" t="s">
         <v>9</v>
@@ -16756,7 +16746,7 @@
         <v>7</v>
       </c>
       <c r="E498" s="2" t="s">
-        <v>1518</v>
+        <v>1611</v>
       </c>
       <c r="F498" s="2" t="s">
         <v>9</v>
@@ -16825,7 +16815,7 @@
         <v>7</v>
       </c>
       <c r="E501" s="2" t="s">
-        <v>1606</v>
+        <v>580</v>
       </c>
       <c r="F501" s="2" t="s">
         <v>9</v>
@@ -16894,7 +16884,7 @@
         <v>7</v>
       </c>
       <c r="E504" s="2" t="s">
-        <v>1546</v>
+        <v>1529</v>
       </c>
       <c r="F504" s="2" t="s">
         <v>9</v>
@@ -17032,7 +17022,7 @@
         <v>7</v>
       </c>
       <c r="E510" s="2" t="s">
-        <v>1519</v>
+        <v>1508</v>
       </c>
       <c r="F510" s="2" t="s">
         <v>9</v>
@@ -17101,7 +17091,7 @@
         <v>7</v>
       </c>
       <c r="E513" s="2" t="s">
-        <v>195</v>
+        <v>292</v>
       </c>
       <c r="F513" s="2" t="s">
         <v>9</v>
@@ -17147,7 +17137,7 @@
         <v>7</v>
       </c>
       <c r="E515" s="2" t="s">
-        <v>1444</v>
+        <v>1437</v>
       </c>
       <c r="F515" s="2" t="s">
         <v>9</v>
@@ -17170,7 +17160,7 @@
         <v>7</v>
       </c>
       <c r="E516" s="2" t="s">
-        <v>1421</v>
+        <v>1366</v>
       </c>
       <c r="F516" s="2" t="s">
         <v>9</v>
@@ -17193,7 +17183,7 @@
         <v>952</v>
       </c>
       <c r="E517" s="2" t="s">
-        <v>731</v>
+        <v>23</v>
       </c>
       <c r="F517" s="2" t="s">
         <v>9</v>
@@ -17239,7 +17229,7 @@
         <v>952</v>
       </c>
       <c r="E519" s="2" t="s">
-        <v>840</v>
+        <v>1612</v>
       </c>
       <c r="F519" s="2" t="s">
         <v>9</v>
@@ -17253,10 +17243,10 @@
         <v>4</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>1384</v>
+        <v>1379</v>
       </c>
       <c r="C520" s="2" t="s">
-        <v>1385</v>
+        <v>1380</v>
       </c>
       <c r="D520" s="2" t="s">
         <v>955</v>
@@ -17276,16 +17266,16 @@
         <v>4</v>
       </c>
       <c r="B521" s="2" t="s">
-        <v>1350</v>
+        <v>1345</v>
       </c>
       <c r="C521" s="2" t="s">
-        <v>1351</v>
+        <v>1346</v>
       </c>
       <c r="D521" s="2" t="s">
         <v>955</v>
       </c>
       <c r="E521" s="2" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="F521" s="2" t="s">
         <v>9</v>
@@ -17299,10 +17289,10 @@
         <v>4</v>
       </c>
       <c r="B522" s="2" t="s">
-        <v>1520</v>
+        <v>1509</v>
       </c>
       <c r="C522" s="2" t="s">
-        <v>1521</v>
+        <v>1510</v>
       </c>
       <c r="D522" s="2" t="s">
         <v>955</v>
@@ -17322,10 +17312,10 @@
         <v>4</v>
       </c>
       <c r="B523" s="2" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="C523" s="2" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="D523" s="2" t="s">
         <v>955</v>
@@ -17345,10 +17335,10 @@
         <v>4</v>
       </c>
       <c r="B524" s="2" t="s">
-        <v>1336</v>
+        <v>1332</v>
       </c>
       <c r="C524" s="2" t="s">
-        <v>1337</v>
+        <v>1333</v>
       </c>
       <c r="D524" s="2" t="s">
         <v>955</v>
@@ -17368,10 +17358,10 @@
         <v>4</v>
       </c>
       <c r="B525" s="2" t="s">
-        <v>1607</v>
+        <v>1575</v>
       </c>
       <c r="C525" s="2" t="s">
-        <v>1608</v>
+        <v>1576</v>
       </c>
       <c r="D525" s="2" t="s">
         <v>955</v>
@@ -17391,10 +17381,10 @@
         <v>4</v>
       </c>
       <c r="B526" s="2" t="s">
-        <v>1522</v>
+        <v>1511</v>
       </c>
       <c r="C526" s="2" t="s">
-        <v>1523</v>
+        <v>1512</v>
       </c>
       <c r="D526" s="2" t="s">
         <v>7</v>
@@ -17414,10 +17404,10 @@
         <v>4</v>
       </c>
       <c r="B527" s="2" t="s">
-        <v>1522</v>
+        <v>1511</v>
       </c>
       <c r="C527" s="2" t="s">
-        <v>1523</v>
+        <v>1512</v>
       </c>
       <c r="D527" s="2" t="s">
         <v>19</v>
@@ -17446,7 +17436,7 @@
         <v>7</v>
       </c>
       <c r="E528" s="2" t="s">
-        <v>81</v>
+        <v>1064</v>
       </c>
       <c r="F528" s="2" t="s">
         <v>9</v>
@@ -17492,7 +17482,7 @@
         <v>7</v>
       </c>
       <c r="E530" s="2" t="s">
-        <v>1372</v>
+        <v>1367</v>
       </c>
       <c r="F530" s="2" t="s">
         <v>100</v>
@@ -17584,7 +17574,7 @@
         <v>7</v>
       </c>
       <c r="E534" s="2" t="s">
-        <v>1609</v>
+        <v>1577</v>
       </c>
       <c r="F534" s="2" t="s">
         <v>9</v>
@@ -17630,7 +17620,7 @@
         <v>7</v>
       </c>
       <c r="E536" s="2" t="s">
-        <v>1434</v>
+        <v>1427</v>
       </c>
       <c r="F536" s="2" t="s">
         <v>9</v>
@@ -17653,7 +17643,7 @@
         <v>7</v>
       </c>
       <c r="E537" s="2" t="s">
-        <v>1610</v>
+        <v>1578</v>
       </c>
       <c r="F537" s="2" t="s">
         <v>9</v>
@@ -17699,7 +17689,7 @@
         <v>7</v>
       </c>
       <c r="E539" s="2" t="s">
-        <v>1482</v>
+        <v>1475</v>
       </c>
       <c r="F539" s="2" t="s">
         <v>9</v>
@@ -17722,7 +17712,7 @@
         <v>7</v>
       </c>
       <c r="E540" s="2" t="s">
-        <v>1445</v>
+        <v>1438</v>
       </c>
       <c r="F540" s="2" t="s">
         <v>9</v>
@@ -17736,16 +17726,16 @@
         <v>4</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>1524</v>
+        <v>1513</v>
       </c>
       <c r="C541" s="2" t="s">
-        <v>1525</v>
+        <v>1514</v>
       </c>
       <c r="D541" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E541" s="2" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="F541" s="2" t="s">
         <v>9</v>
@@ -17791,7 +17781,7 @@
         <v>7</v>
       </c>
       <c r="E543" s="2" t="s">
-        <v>1547</v>
+        <v>1613</v>
       </c>
       <c r="F543" s="2" t="s">
         <v>9</v>
@@ -17814,7 +17804,7 @@
         <v>7</v>
       </c>
       <c r="E544" s="2" t="s">
-        <v>1611</v>
+        <v>1614</v>
       </c>
       <c r="F544" s="2" t="s">
         <v>9</v>
@@ -17837,7 +17827,7 @@
         <v>7</v>
       </c>
       <c r="E545" s="2" t="s">
-        <v>1526</v>
+        <v>1615</v>
       </c>
       <c r="F545" s="2" t="s">
         <v>9</v>
@@ -17860,7 +17850,7 @@
         <v>7</v>
       </c>
       <c r="E546" s="2" t="s">
-        <v>1505</v>
+        <v>1497</v>
       </c>
       <c r="F546" s="2" t="s">
         <v>100</v>
@@ -17883,7 +17873,7 @@
         <v>7</v>
       </c>
       <c r="E547" s="2" t="s">
-        <v>1612</v>
+        <v>1579</v>
       </c>
       <c r="F547" s="2" t="s">
         <v>9</v>
@@ -17975,7 +17965,7 @@
         <v>7</v>
       </c>
       <c r="E551" s="2" t="s">
-        <v>1408</v>
+        <v>1403</v>
       </c>
       <c r="F551" s="2" t="s">
         <v>9</v>
@@ -17989,10 +17979,10 @@
         <v>4</v>
       </c>
       <c r="B552" s="2" t="s">
-        <v>1506</v>
+        <v>1498</v>
       </c>
       <c r="C552" s="2" t="s">
-        <v>1507</v>
+        <v>1499</v>
       </c>
       <c r="D552" s="2" t="s">
         <v>40</v>
@@ -18021,7 +18011,7 @@
         <v>40</v>
       </c>
       <c r="E553" s="2" t="s">
-        <v>1566</v>
+        <v>1545</v>
       </c>
       <c r="F553" s="2" t="s">
         <v>9</v>
@@ -18090,7 +18080,7 @@
         <v>19</v>
       </c>
       <c r="E556" s="2" t="s">
-        <v>1317</v>
+        <v>1314</v>
       </c>
       <c r="F556" s="2" t="s">
         <v>9</v>
@@ -18136,7 +18126,7 @@
         <v>427</v>
       </c>
       <c r="E558" s="2" t="s">
-        <v>1613</v>
+        <v>1580</v>
       </c>
       <c r="F558" s="2" t="s">
         <v>428</v>
@@ -18159,7 +18149,7 @@
         <v>7</v>
       </c>
       <c r="E559" s="2" t="s">
-        <v>1614</v>
+        <v>1616</v>
       </c>
       <c r="F559" s="2" t="s">
         <v>9</v>
@@ -18228,7 +18218,7 @@
         <v>7</v>
       </c>
       <c r="E562" s="2" t="s">
-        <v>1381</v>
+        <v>551</v>
       </c>
       <c r="F562" s="2" t="s">
         <v>9</v>
@@ -18320,7 +18310,7 @@
         <v>7</v>
       </c>
       <c r="E566" s="2" t="s">
-        <v>1349</v>
+        <v>1344</v>
       </c>
       <c r="F566" s="2" t="s">
         <v>9</v>
@@ -18481,7 +18471,7 @@
         <v>7</v>
       </c>
       <c r="E573" s="2" t="s">
-        <v>1548</v>
+        <v>1530</v>
       </c>
       <c r="F573" s="2" t="s">
         <v>100</v>
@@ -18564,16 +18554,16 @@
         <v>4</v>
       </c>
       <c r="B577" s="2" t="s">
-        <v>1373</v>
+        <v>1368</v>
       </c>
       <c r="C577" s="2" t="s">
-        <v>1374</v>
+        <v>1369</v>
       </c>
       <c r="D577" s="2" t="s">
         <v>40</v>
       </c>
       <c r="E577" s="2" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="F577" s="2" t="s">
         <v>9</v>
@@ -18587,16 +18577,16 @@
         <v>4</v>
       </c>
       <c r="B578" s="2" t="s">
-        <v>1373</v>
+        <v>1368</v>
       </c>
       <c r="C578" s="2" t="s">
-        <v>1374</v>
+        <v>1369</v>
       </c>
       <c r="D578" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E578" s="2" t="s">
-        <v>1483</v>
+        <v>1476</v>
       </c>
       <c r="F578" s="2" t="s">
         <v>9</v>
@@ -18619,7 +18609,7 @@
         <v>7</v>
       </c>
       <c r="E579" s="2" t="s">
-        <v>1241</v>
+        <v>1560</v>
       </c>
       <c r="F579" s="2" t="s">
         <v>9</v>
@@ -18642,7 +18632,7 @@
         <v>19</v>
       </c>
       <c r="E580" s="2" t="s">
-        <v>1615</v>
+        <v>1581</v>
       </c>
       <c r="F580" s="2" t="s">
         <v>9</v>
@@ -18665,7 +18655,7 @@
         <v>7</v>
       </c>
       <c r="E581" s="2" t="s">
-        <v>1616</v>
+        <v>1295</v>
       </c>
       <c r="F581" s="2" t="s">
         <v>9</v>
@@ -18688,7 +18678,7 @@
         <v>7</v>
       </c>
       <c r="E582" s="2" t="s">
-        <v>1546</v>
+        <v>1343</v>
       </c>
       <c r="F582" s="2" t="s">
         <v>9</v>
@@ -18711,7 +18701,7 @@
         <v>7</v>
       </c>
       <c r="E583" s="2" t="s">
-        <v>67</v>
+        <v>580</v>
       </c>
       <c r="F583" s="2" t="s">
         <v>9</v>
@@ -18748,16 +18738,16 @@
         <v>4</v>
       </c>
       <c r="B585" s="2" t="s">
-        <v>1060</v>
+        <v>1477</v>
       </c>
       <c r="C585" s="2" t="s">
-        <v>1061</v>
+        <v>1478</v>
       </c>
       <c r="D585" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E585" s="2" t="s">
-        <v>580</v>
+        <v>146</v>
       </c>
       <c r="F585" s="2" t="s">
         <v>9</v>
@@ -18771,16 +18761,16 @@
         <v>4</v>
       </c>
       <c r="B586" s="2" t="s">
-        <v>1484</v>
+        <v>1060</v>
       </c>
       <c r="C586" s="2" t="s">
-        <v>1485</v>
+        <v>1061</v>
       </c>
       <c r="D586" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E586" s="2" t="s">
-        <v>146</v>
+        <v>431</v>
       </c>
       <c r="F586" s="2" t="s">
         <v>9</v>
@@ -18794,16 +18784,16 @@
         <v>4</v>
       </c>
       <c r="B587" s="2" t="s">
-        <v>1062</v>
+        <v>1479</v>
       </c>
       <c r="C587" s="2" t="s">
-        <v>1063</v>
+        <v>1480</v>
       </c>
       <c r="D587" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E587" s="2" t="s">
-        <v>1341</v>
+        <v>1474</v>
       </c>
       <c r="F587" s="2" t="s">
         <v>9</v>
@@ -18817,16 +18807,16 @@
         <v>4</v>
       </c>
       <c r="B588" s="2" t="s">
-        <v>1487</v>
+        <v>1062</v>
       </c>
       <c r="C588" s="2" t="s">
-        <v>1488</v>
+        <v>1063</v>
       </c>
       <c r="D588" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E588" s="2" t="s">
-        <v>1481</v>
+        <v>86</v>
       </c>
       <c r="F588" s="2" t="s">
         <v>9</v>
@@ -18840,16 +18830,16 @@
         <v>4</v>
       </c>
       <c r="B589" s="2" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="C589" s="2" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="D589" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E589" s="2" t="s">
-        <v>86</v>
+        <v>1617</v>
       </c>
       <c r="F589" s="2" t="s">
         <v>9</v>
@@ -18872,7 +18862,7 @@
         <v>7</v>
       </c>
       <c r="E590" s="2" t="s">
-        <v>1346</v>
+        <v>235</v>
       </c>
       <c r="F590" s="2" t="s">
         <v>9</v>
@@ -18892,13 +18882,13 @@
         <v>1070</v>
       </c>
       <c r="D591" s="2" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="E591" s="2" t="s">
-        <v>235</v>
+        <v>67</v>
       </c>
       <c r="F591" s="2" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="G591" s="2" t="s">
         <v>10</v>
@@ -18918,7 +18908,7 @@
         <v>40</v>
       </c>
       <c r="E592" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="F592" s="2" t="s">
         <v>172</v>
@@ -18941,7 +18931,7 @@
         <v>40</v>
       </c>
       <c r="E593" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="F593" s="2" t="s">
         <v>172</v>
@@ -18955,16 +18945,16 @@
         <v>4</v>
       </c>
       <c r="B594" s="2" t="s">
-        <v>1075</v>
+        <v>194</v>
       </c>
       <c r="C594" s="2" t="s">
-        <v>1076</v>
+        <v>1481</v>
       </c>
       <c r="D594" s="2" t="s">
         <v>40</v>
       </c>
       <c r="E594" s="2" t="s">
-        <v>67</v>
+        <v>195</v>
       </c>
       <c r="F594" s="2" t="s">
         <v>172</v>
@@ -18978,16 +18968,16 @@
         <v>4</v>
       </c>
       <c r="B595" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C595" s="2" t="s">
-        <v>1489</v>
+        <v>1481</v>
       </c>
       <c r="D595" s="2" t="s">
         <v>40</v>
       </c>
       <c r="E595" s="2" t="s">
-        <v>195</v>
+        <v>76</v>
       </c>
       <c r="F595" s="2" t="s">
         <v>172</v>
@@ -19004,13 +18994,13 @@
         <v>198</v>
       </c>
       <c r="C596" s="2" t="s">
-        <v>1489</v>
+        <v>1481</v>
       </c>
       <c r="D596" s="2" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="E596" s="2" t="s">
-        <v>76</v>
+        <v>134</v>
       </c>
       <c r="F596" s="2" t="s">
         <v>172</v>
@@ -19024,16 +19014,16 @@
         <v>4</v>
       </c>
       <c r="B597" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C597" s="2" t="s">
-        <v>1489</v>
+        <v>1481</v>
       </c>
       <c r="D597" s="2" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="E597" s="2" t="s">
-        <v>134</v>
+        <v>1404</v>
       </c>
       <c r="F597" s="2" t="s">
         <v>172</v>
@@ -19047,16 +19037,16 @@
         <v>4</v>
       </c>
       <c r="B598" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C598" s="2" t="s">
-        <v>1489</v>
+        <v>1481</v>
       </c>
       <c r="D598" s="2" t="s">
         <v>40</v>
       </c>
       <c r="E598" s="2" t="s">
-        <v>1409</v>
+        <v>1104</v>
       </c>
       <c r="F598" s="2" t="s">
         <v>172</v>
@@ -19070,16 +19060,16 @@
         <v>4</v>
       </c>
       <c r="B599" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C599" s="2" t="s">
-        <v>1489</v>
+        <v>1481</v>
       </c>
       <c r="D599" s="2" t="s">
         <v>40</v>
       </c>
       <c r="E599" s="2" t="s">
-        <v>1106</v>
+        <v>76</v>
       </c>
       <c r="F599" s="2" t="s">
         <v>172</v>
@@ -19093,16 +19083,16 @@
         <v>4</v>
       </c>
       <c r="B600" s="2" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C600" s="2" t="s">
-        <v>1489</v>
+        <v>1481</v>
       </c>
       <c r="D600" s="2" t="s">
         <v>40</v>
       </c>
       <c r="E600" s="2" t="s">
-        <v>47</v>
+        <v>134</v>
       </c>
       <c r="F600" s="2" t="s">
         <v>172</v>
@@ -19119,13 +19109,13 @@
         <v>202</v>
       </c>
       <c r="C601" s="2" t="s">
-        <v>1489</v>
+        <v>1481</v>
       </c>
       <c r="D601" s="2" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="E601" s="2" t="s">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="F601" s="2" t="s">
         <v>172</v>
@@ -19139,16 +19129,16 @@
         <v>4</v>
       </c>
       <c r="B602" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C602" s="2" t="s">
-        <v>1489</v>
+        <v>1481</v>
       </c>
       <c r="D602" s="2" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="E602" s="2" t="s">
-        <v>103</v>
+        <v>159</v>
       </c>
       <c r="F602" s="2" t="s">
         <v>172</v>
@@ -19162,16 +19152,16 @@
         <v>4</v>
       </c>
       <c r="B603" s="2" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="C603" s="2" t="s">
-        <v>1489</v>
+        <v>1481</v>
       </c>
       <c r="D603" s="2" t="s">
         <v>40</v>
       </c>
       <c r="E603" s="2" t="s">
-        <v>159</v>
+        <v>580</v>
       </c>
       <c r="F603" s="2" t="s">
         <v>172</v>
@@ -19185,16 +19175,16 @@
         <v>4</v>
       </c>
       <c r="B604" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C604" s="2" t="s">
-        <v>1489</v>
+        <v>1481</v>
       </c>
       <c r="D604" s="2" t="s">
         <v>40</v>
       </c>
       <c r="E604" s="2" t="s">
-        <v>580</v>
+        <v>292</v>
       </c>
       <c r="F604" s="2" t="s">
         <v>172</v>
@@ -19208,16 +19198,16 @@
         <v>4</v>
       </c>
       <c r="B605" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C605" s="2" t="s">
-        <v>1489</v>
+        <v>1481</v>
       </c>
       <c r="D605" s="2" t="s">
         <v>40</v>
       </c>
       <c r="E605" s="2" t="s">
-        <v>292</v>
+        <v>103</v>
       </c>
       <c r="F605" s="2" t="s">
         <v>172</v>
@@ -19231,16 +19221,16 @@
         <v>4</v>
       </c>
       <c r="B606" s="2" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C606" s="2" t="s">
-        <v>1489</v>
+        <v>1481</v>
       </c>
       <c r="D606" s="2" t="s">
         <v>40</v>
       </c>
       <c r="E606" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F606" s="2" t="s">
         <v>172</v>
@@ -19254,16 +19244,16 @@
         <v>4</v>
       </c>
       <c r="B607" s="2" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="C607" s="2" t="s">
-        <v>1489</v>
+        <v>1481</v>
       </c>
       <c r="D607" s="2" t="s">
         <v>40</v>
       </c>
       <c r="E607" s="2" t="s">
-        <v>104</v>
+        <v>149</v>
       </c>
       <c r="F607" s="2" t="s">
         <v>172</v>
@@ -19277,19 +19267,19 @@
         <v>4</v>
       </c>
       <c r="B608" s="2" t="s">
-        <v>193</v>
+        <v>1075</v>
       </c>
       <c r="C608" s="2" t="s">
-        <v>1489</v>
+        <v>1076</v>
       </c>
       <c r="D608" s="2" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="E608" s="2" t="s">
-        <v>149</v>
+        <v>1077</v>
       </c>
       <c r="F608" s="2" t="s">
-        <v>172</v>
+        <v>9</v>
       </c>
       <c r="G608" s="2" t="s">
         <v>10</v>
@@ -19300,16 +19290,16 @@
         <v>4</v>
       </c>
       <c r="B609" s="2" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C609" s="2" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="D609" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E609" s="2" t="s">
-        <v>1079</v>
+        <v>134</v>
       </c>
       <c r="F609" s="2" t="s">
         <v>9</v>
@@ -19332,10 +19322,10 @@
         <v>7</v>
       </c>
       <c r="E610" s="2" t="s">
-        <v>134</v>
+        <v>59</v>
       </c>
       <c r="F610" s="2" t="s">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="G610" s="2" t="s">
         <v>10</v>
@@ -19355,10 +19345,10 @@
         <v>7</v>
       </c>
       <c r="E611" s="2" t="s">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="F611" s="2" t="s">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="G611" s="2" t="s">
         <v>10</v>
@@ -19375,10 +19365,10 @@
         <v>1085</v>
       </c>
       <c r="D612" s="2" t="s">
-        <v>7</v>
+        <v>1208</v>
       </c>
       <c r="E612" s="2" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="F612" s="2" t="s">
         <v>9</v>
@@ -19398,10 +19388,10 @@
         <v>1087</v>
       </c>
       <c r="D613" s="2" t="s">
-        <v>1210</v>
+        <v>7</v>
       </c>
       <c r="E613" s="2" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="F613" s="2" t="s">
         <v>9</v>
@@ -19424,7 +19414,7 @@
         <v>7</v>
       </c>
       <c r="E614" s="2" t="s">
-        <v>143</v>
+        <v>41</v>
       </c>
       <c r="F614" s="2" t="s">
         <v>9</v>
@@ -19447,7 +19437,7 @@
         <v>7</v>
       </c>
       <c r="E615" s="2" t="s">
-        <v>41</v>
+        <v>216</v>
       </c>
       <c r="F615" s="2" t="s">
         <v>9</v>
@@ -19470,7 +19460,7 @@
         <v>7</v>
       </c>
       <c r="E616" s="2" t="s">
-        <v>216</v>
+        <v>503</v>
       </c>
       <c r="F616" s="2" t="s">
         <v>9</v>
@@ -19493,7 +19483,7 @@
         <v>7</v>
       </c>
       <c r="E617" s="2" t="s">
-        <v>503</v>
+        <v>30</v>
       </c>
       <c r="F617" s="2" t="s">
         <v>9</v>
@@ -19507,16 +19497,16 @@
         <v>4</v>
       </c>
       <c r="B618" s="2" t="s">
-        <v>1096</v>
+        <v>1416</v>
       </c>
       <c r="C618" s="2" t="s">
-        <v>1097</v>
+        <v>1417</v>
       </c>
       <c r="D618" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E618" s="2" t="s">
-        <v>30</v>
+        <v>104</v>
       </c>
       <c r="F618" s="2" t="s">
         <v>9</v>
@@ -19530,16 +19520,16 @@
         <v>4</v>
       </c>
       <c r="B619" s="2" t="s">
-        <v>1422</v>
+        <v>1096</v>
       </c>
       <c r="C619" s="2" t="s">
-        <v>1423</v>
+        <v>1097</v>
       </c>
       <c r="D619" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E619" s="2" t="s">
-        <v>104</v>
+        <v>195</v>
       </c>
       <c r="F619" s="2" t="s">
         <v>9</v>
@@ -19562,7 +19552,7 @@
         <v>7</v>
       </c>
       <c r="E620" s="2" t="s">
-        <v>195</v>
+        <v>317</v>
       </c>
       <c r="F620" s="2" t="s">
         <v>9</v>
@@ -19576,16 +19566,16 @@
         <v>4</v>
       </c>
       <c r="B621" s="2" t="s">
-        <v>1100</v>
+        <v>1439</v>
       </c>
       <c r="C621" s="2" t="s">
-        <v>1101</v>
+        <v>1440</v>
       </c>
       <c r="D621" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E621" s="2" t="s">
-        <v>317</v>
+        <v>146</v>
       </c>
       <c r="F621" s="2" t="s">
         <v>9</v>
@@ -19599,10 +19589,10 @@
         <v>4</v>
       </c>
       <c r="B622" s="2" t="s">
-        <v>1446</v>
+        <v>1531</v>
       </c>
       <c r="C622" s="2" t="s">
-        <v>1447</v>
+        <v>1532</v>
       </c>
       <c r="D622" s="2" t="s">
         <v>7</v>
@@ -19622,10 +19612,10 @@
         <v>4</v>
       </c>
       <c r="B623" s="2" t="s">
-        <v>1549</v>
+        <v>1100</v>
       </c>
       <c r="C623" s="2" t="s">
-        <v>1550</v>
+        <v>1101</v>
       </c>
       <c r="D623" s="2" t="s">
         <v>7</v>
@@ -19654,7 +19644,7 @@
         <v>7</v>
       </c>
       <c r="E624" s="2" t="s">
-        <v>146</v>
+        <v>1104</v>
       </c>
       <c r="F624" s="2" t="s">
         <v>9</v>
@@ -19668,16 +19658,16 @@
         <v>4</v>
       </c>
       <c r="B625" s="2" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="C625" s="2" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="D625" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E625" s="2" t="s">
-        <v>1106</v>
+        <v>317</v>
       </c>
       <c r="F625" s="2" t="s">
         <v>9</v>
@@ -19700,7 +19690,7 @@
         <v>7</v>
       </c>
       <c r="E626" s="2" t="s">
-        <v>317</v>
+        <v>1343</v>
       </c>
       <c r="F626" s="2" t="s">
         <v>9</v>
@@ -19723,7 +19713,7 @@
         <v>7</v>
       </c>
       <c r="E627" s="2" t="s">
-        <v>1348</v>
+        <v>42</v>
       </c>
       <c r="F627" s="2" t="s">
         <v>9</v>
@@ -19737,16 +19727,16 @@
         <v>4</v>
       </c>
       <c r="B628" s="2" t="s">
-        <v>1111</v>
+        <v>1370</v>
       </c>
       <c r="C628" s="2" t="s">
-        <v>1112</v>
+        <v>1371</v>
       </c>
       <c r="D628" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E628" s="2" t="s">
-        <v>42</v>
+        <v>211</v>
       </c>
       <c r="F628" s="2" t="s">
         <v>9</v>
@@ -19760,16 +19750,16 @@
         <v>4</v>
       </c>
       <c r="B629" s="2" t="s">
-        <v>1375</v>
+        <v>1111</v>
       </c>
       <c r="C629" s="2" t="s">
-        <v>1376</v>
+        <v>1112</v>
       </c>
       <c r="D629" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E629" s="2" t="s">
-        <v>211</v>
+        <v>59</v>
       </c>
       <c r="F629" s="2" t="s">
         <v>9</v>
@@ -19792,7 +19782,7 @@
         <v>7</v>
       </c>
       <c r="E630" s="2" t="s">
-        <v>59</v>
+        <v>1314</v>
       </c>
       <c r="F630" s="2" t="s">
         <v>9</v>
@@ -19815,7 +19805,7 @@
         <v>7</v>
       </c>
       <c r="E631" s="2" t="s">
-        <v>1317</v>
+        <v>67</v>
       </c>
       <c r="F631" s="2" t="s">
         <v>9</v>
@@ -19829,16 +19819,16 @@
         <v>4</v>
       </c>
       <c r="B632" s="2" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="C632" s="2" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="D632" s="2" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E632" s="2" t="s">
-        <v>67</v>
+        <v>104</v>
       </c>
       <c r="F632" s="2" t="s">
         <v>9</v>
@@ -19858,10 +19848,10 @@
         <v>1118</v>
       </c>
       <c r="D633" s="2" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E633" s="2" t="s">
-        <v>104</v>
+        <v>23</v>
       </c>
       <c r="F633" s="2" t="s">
         <v>9</v>
@@ -19884,7 +19874,7 @@
         <v>7</v>
       </c>
       <c r="E634" s="2" t="s">
-        <v>23</v>
+        <v>156</v>
       </c>
       <c r="F634" s="2" t="s">
         <v>9</v>
@@ -19898,16 +19888,16 @@
         <v>4</v>
       </c>
       <c r="B635" s="2" t="s">
-        <v>1121</v>
+        <v>1372</v>
       </c>
       <c r="C635" s="2" t="s">
-        <v>1122</v>
+        <v>1373</v>
       </c>
       <c r="D635" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E635" s="2" t="s">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="F635" s="2" t="s">
         <v>9</v>
@@ -19921,16 +19911,16 @@
         <v>4</v>
       </c>
       <c r="B636" s="2" t="s">
-        <v>1377</v>
+        <v>1304</v>
       </c>
       <c r="C636" s="2" t="s">
-        <v>1378</v>
+        <v>1305</v>
       </c>
       <c r="D636" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E636" s="2" t="s">
-        <v>41</v>
+        <v>1343</v>
       </c>
       <c r="F636" s="2" t="s">
         <v>9</v>
@@ -19944,16 +19934,16 @@
         <v>4</v>
       </c>
       <c r="B637" s="2" t="s">
-        <v>1306</v>
+        <v>1121</v>
       </c>
       <c r="C637" s="2" t="s">
-        <v>1307</v>
+        <v>1122</v>
       </c>
       <c r="D637" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E637" s="2" t="s">
-        <v>1348</v>
+        <v>62</v>
       </c>
       <c r="F637" s="2" t="s">
         <v>9</v>
@@ -19976,7 +19966,7 @@
         <v>7</v>
       </c>
       <c r="E638" s="2" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="F638" s="2" t="s">
         <v>9</v>
@@ -19999,7 +19989,7 @@
         <v>7</v>
       </c>
       <c r="E639" s="2" t="s">
-        <v>47</v>
+        <v>731</v>
       </c>
       <c r="F639" s="2" t="s">
         <v>9</v>
@@ -20022,7 +20012,7 @@
         <v>7</v>
       </c>
       <c r="E640" s="2" t="s">
-        <v>731</v>
+        <v>42</v>
       </c>
       <c r="F640" s="2" t="s">
         <v>9</v>
@@ -20045,7 +20035,7 @@
         <v>7</v>
       </c>
       <c r="E641" s="2" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="F641" s="2" t="s">
         <v>9</v>
@@ -20068,7 +20058,7 @@
         <v>7</v>
       </c>
       <c r="E642" s="2" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="F642" s="2" t="s">
         <v>9</v>
@@ -20088,10 +20078,10 @@
         <v>1134</v>
       </c>
       <c r="D643" s="2" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E643" s="2" t="s">
-        <v>67</v>
+        <v>1448</v>
       </c>
       <c r="F643" s="2" t="s">
         <v>9</v>
@@ -20111,10 +20101,10 @@
         <v>1136</v>
       </c>
       <c r="D644" s="2" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="E644" s="2" t="s">
-        <v>1455</v>
+        <v>67</v>
       </c>
       <c r="F644" s="2" t="s">
         <v>9</v>
@@ -20128,16 +20118,16 @@
         <v>4</v>
       </c>
       <c r="B645" s="2" t="s">
-        <v>1137</v>
+        <v>1347</v>
       </c>
       <c r="C645" s="2" t="s">
-        <v>1138</v>
+        <v>1348</v>
       </c>
       <c r="D645" s="2" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="E645" s="2" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="F645" s="2" t="s">
         <v>9</v>
@@ -20151,16 +20141,16 @@
         <v>4</v>
       </c>
       <c r="B646" s="2" t="s">
-        <v>1352</v>
+        <v>1137</v>
       </c>
       <c r="C646" s="2" t="s">
-        <v>1353</v>
+        <v>1138</v>
       </c>
       <c r="D646" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E646" s="2" t="s">
-        <v>47</v>
+        <v>156</v>
       </c>
       <c r="F646" s="2" t="s">
         <v>9</v>
@@ -20183,7 +20173,7 @@
         <v>7</v>
       </c>
       <c r="E647" s="2" t="s">
-        <v>156</v>
+        <v>18</v>
       </c>
       <c r="F647" s="2" t="s">
         <v>9</v>
@@ -20206,7 +20196,7 @@
         <v>7</v>
       </c>
       <c r="E648" s="2" t="s">
-        <v>18</v>
+        <v>195</v>
       </c>
       <c r="F648" s="2" t="s">
         <v>9</v>
@@ -20220,16 +20210,16 @@
         <v>4</v>
       </c>
       <c r="B649" s="2" t="s">
-        <v>1143</v>
+        <v>1521</v>
       </c>
       <c r="C649" s="2" t="s">
-        <v>1144</v>
+        <v>1522</v>
       </c>
       <c r="D649" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E649" s="2" t="s">
-        <v>195</v>
+        <v>18</v>
       </c>
       <c r="F649" s="2" t="s">
         <v>9</v>
@@ -20243,16 +20233,16 @@
         <v>4</v>
       </c>
       <c r="B650" s="2" t="s">
-        <v>1533</v>
+        <v>1143</v>
       </c>
       <c r="C650" s="2" t="s">
-        <v>1534</v>
+        <v>1144</v>
       </c>
       <c r="D650" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E650" s="2" t="s">
-        <v>18</v>
+        <v>195</v>
       </c>
       <c r="F650" s="2" t="s">
         <v>9</v>
@@ -20275,7 +20265,7 @@
         <v>7</v>
       </c>
       <c r="E651" s="2" t="s">
-        <v>195</v>
+        <v>86</v>
       </c>
       <c r="F651" s="2" t="s">
         <v>9</v>
@@ -20298,7 +20288,7 @@
         <v>7</v>
       </c>
       <c r="E652" s="2" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="F652" s="2" t="s">
         <v>9</v>
@@ -20312,16 +20302,16 @@
         <v>4</v>
       </c>
       <c r="B653" s="2" t="s">
-        <v>1149</v>
+        <v>1353</v>
       </c>
       <c r="C653" s="2" t="s">
-        <v>1150</v>
+        <v>1354</v>
       </c>
       <c r="D653" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E653" s="2" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="F653" s="2" t="s">
         <v>9</v>
@@ -20335,16 +20325,16 @@
         <v>4</v>
       </c>
       <c r="B654" s="2" t="s">
-        <v>1358</v>
+        <v>1149</v>
       </c>
       <c r="C654" s="2" t="s">
-        <v>1359</v>
+        <v>1150</v>
       </c>
       <c r="D654" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E654" s="2" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="F654" s="2" t="s">
         <v>9</v>
@@ -20367,7 +20357,7 @@
         <v>7</v>
       </c>
       <c r="E655" s="2" t="s">
-        <v>76</v>
+        <v>216</v>
       </c>
       <c r="F655" s="2" t="s">
         <v>9</v>
@@ -20390,7 +20380,7 @@
         <v>7</v>
       </c>
       <c r="E656" s="2" t="s">
-        <v>216</v>
+        <v>1501</v>
       </c>
       <c r="F656" s="2" t="s">
         <v>9</v>
@@ -20413,7 +20403,7 @@
         <v>7</v>
       </c>
       <c r="E657" s="2" t="s">
-        <v>1509</v>
+        <v>1582</v>
       </c>
       <c r="F657" s="2" t="s">
         <v>9</v>
@@ -20436,7 +20426,7 @@
         <v>7</v>
       </c>
       <c r="E658" s="2" t="s">
-        <v>1617</v>
+        <v>86</v>
       </c>
       <c r="F658" s="2" t="s">
         <v>9</v>
@@ -20459,7 +20449,7 @@
         <v>7</v>
       </c>
       <c r="E659" s="2" t="s">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="F659" s="2" t="s">
         <v>9</v>
@@ -20482,7 +20472,7 @@
         <v>7</v>
       </c>
       <c r="E660" s="2" t="s">
-        <v>18</v>
+        <v>1583</v>
       </c>
       <c r="F660" s="2" t="s">
         <v>9</v>
@@ -20505,7 +20495,7 @@
         <v>7</v>
       </c>
       <c r="E661" s="2" t="s">
-        <v>1618</v>
+        <v>1165</v>
       </c>
       <c r="F661" s="2" t="s">
         <v>9</v>
@@ -20519,16 +20509,16 @@
         <v>4</v>
       </c>
       <c r="B662" s="2" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="C662" s="2" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="D662" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E662" s="2" t="s">
-        <v>1167</v>
+        <v>42</v>
       </c>
       <c r="F662" s="2" t="s">
         <v>9</v>
@@ -20542,16 +20532,16 @@
         <v>4</v>
       </c>
       <c r="B663" s="2" t="s">
-        <v>1168</v>
+        <v>1441</v>
       </c>
       <c r="C663" s="2" t="s">
-        <v>1169</v>
+        <v>1442</v>
       </c>
       <c r="D663" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E663" s="2" t="s">
-        <v>42</v>
+        <v>1574</v>
       </c>
       <c r="F663" s="2" t="s">
         <v>9</v>
@@ -20565,16 +20555,16 @@
         <v>4</v>
       </c>
       <c r="B664" s="2" t="s">
-        <v>1448</v>
+        <v>1168</v>
       </c>
       <c r="C664" s="2" t="s">
-        <v>1449</v>
+        <v>1169</v>
       </c>
       <c r="D664" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E664" s="2" t="s">
-        <v>1606</v>
+        <v>1446</v>
       </c>
       <c r="F664" s="2" t="s">
         <v>9</v>
@@ -20597,7 +20587,7 @@
         <v>7</v>
       </c>
       <c r="E665" s="2" t="s">
-        <v>1528</v>
+        <v>416</v>
       </c>
       <c r="F665" s="2" t="s">
         <v>9</v>
@@ -20611,16 +20601,16 @@
         <v>4</v>
       </c>
       <c r="B666" s="2" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="C666" s="2" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="D666" s="2" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E666" s="2" t="s">
-        <v>416</v>
+        <v>609</v>
       </c>
       <c r="F666" s="2" t="s">
         <v>9</v>
@@ -20640,13 +20630,13 @@
         <v>1173</v>
       </c>
       <c r="D667" s="2" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E667" s="2" t="s">
-        <v>609</v>
+        <v>431</v>
       </c>
       <c r="F667" s="2" t="s">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="G667" s="2" t="s">
         <v>10</v>
@@ -20666,7 +20656,7 @@
         <v>7</v>
       </c>
       <c r="E668" s="2" t="s">
-        <v>431</v>
+        <v>104</v>
       </c>
       <c r="F668" s="2" t="s">
         <v>100</v>
@@ -20689,10 +20679,10 @@
         <v>7</v>
       </c>
       <c r="E669" s="2" t="s">
-        <v>104</v>
+        <v>149</v>
       </c>
       <c r="F669" s="2" t="s">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="G669" s="2" t="s">
         <v>10</v>
@@ -20712,7 +20702,7 @@
         <v>7</v>
       </c>
       <c r="E670" s="2" t="s">
-        <v>149</v>
+        <v>1618</v>
       </c>
       <c r="F670" s="2" t="s">
         <v>9</v>
@@ -20735,7 +20725,7 @@
         <v>7</v>
       </c>
       <c r="E671" s="2" t="s">
-        <v>1424</v>
+        <v>146</v>
       </c>
       <c r="F671" s="2" t="s">
         <v>9</v>
@@ -20758,7 +20748,7 @@
         <v>7</v>
       </c>
       <c r="E672" s="2" t="s">
-        <v>146</v>
+        <v>1584</v>
       </c>
       <c r="F672" s="2" t="s">
         <v>9</v>
@@ -20781,7 +20771,7 @@
         <v>7</v>
       </c>
       <c r="E673" s="2" t="s">
-        <v>1619</v>
+        <v>1021</v>
       </c>
       <c r="F673" s="2" t="s">
         <v>9</v>
@@ -20804,7 +20794,7 @@
         <v>7</v>
       </c>
       <c r="E674" s="2" t="s">
-        <v>1503</v>
+        <v>431</v>
       </c>
       <c r="F674" s="2" t="s">
         <v>9</v>
@@ -20827,7 +20817,7 @@
         <v>7</v>
       </c>
       <c r="E675" s="2" t="s">
-        <v>431</v>
+        <v>274</v>
       </c>
       <c r="F675" s="2" t="s">
         <v>9</v>
@@ -20850,7 +20840,7 @@
         <v>7</v>
       </c>
       <c r="E676" s="2" t="s">
-        <v>274</v>
+        <v>18</v>
       </c>
       <c r="F676" s="2" t="s">
         <v>9</v>
@@ -20873,7 +20863,7 @@
         <v>7</v>
       </c>
       <c r="E677" s="2" t="s">
-        <v>47</v>
+        <v>1194</v>
       </c>
       <c r="F677" s="2" t="s">
         <v>9</v>
@@ -20887,16 +20877,16 @@
         <v>4</v>
       </c>
       <c r="B678" s="2" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="C678" s="2" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="D678" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E678" s="2" t="s">
-        <v>1196</v>
+        <v>431</v>
       </c>
       <c r="F678" s="2" t="s">
         <v>9</v>
@@ -20919,7 +20909,7 @@
         <v>7</v>
       </c>
       <c r="E679" s="2" t="s">
-        <v>431</v>
+        <v>1334</v>
       </c>
       <c r="F679" s="2" t="s">
         <v>9</v>
@@ -20942,7 +20932,7 @@
         <v>7</v>
       </c>
       <c r="E680" s="2" t="s">
-        <v>1338</v>
+        <v>18</v>
       </c>
       <c r="F680" s="2" t="s">
         <v>9</v>
@@ -20965,7 +20955,7 @@
         <v>7</v>
       </c>
       <c r="E681" s="2" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="F681" s="2" t="s">
         <v>9</v>
@@ -20979,16 +20969,16 @@
         <v>4</v>
       </c>
       <c r="B682" s="2" t="s">
-        <v>1203</v>
+        <v>1418</v>
       </c>
       <c r="C682" s="2" t="s">
-        <v>1204</v>
+        <v>1419</v>
       </c>
       <c r="D682" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E682" s="2" t="s">
-        <v>103</v>
+        <v>864</v>
       </c>
       <c r="F682" s="2" t="s">
         <v>9</v>
@@ -21002,16 +20992,16 @@
         <v>4</v>
       </c>
       <c r="B683" s="2" t="s">
-        <v>1425</v>
+        <v>1203</v>
       </c>
       <c r="C683" s="2" t="s">
-        <v>1426</v>
+        <v>1204</v>
       </c>
       <c r="D683" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E683" s="2" t="s">
-        <v>864</v>
+        <v>1205</v>
       </c>
       <c r="F683" s="2" t="s">
         <v>9</v>
@@ -21025,16 +21015,16 @@
         <v>4</v>
       </c>
       <c r="B684" s="2" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="C684" s="2" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="D684" s="2" t="s">
-        <v>7</v>
+        <v>1208</v>
       </c>
       <c r="E684" s="2" t="s">
-        <v>1207</v>
+        <v>134</v>
       </c>
       <c r="F684" s="2" t="s">
         <v>9</v>
@@ -21048,16 +21038,16 @@
         <v>4</v>
       </c>
       <c r="B685" s="2" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C685" s="2" t="s">
+        <v>1210</v>
+      </c>
+      <c r="D685" s="2" t="s">
         <v>1208</v>
       </c>
-      <c r="C685" s="2" t="s">
-        <v>1209</v>
-      </c>
-      <c r="D685" s="2" t="s">
-        <v>1210</v>
-      </c>
       <c r="E685" s="2" t="s">
-        <v>134</v>
+        <v>1021</v>
       </c>
       <c r="F685" s="2" t="s">
         <v>9</v>
@@ -21077,10 +21067,10 @@
         <v>1212</v>
       </c>
       <c r="D686" s="2" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="E686" s="2" t="s">
-        <v>1021</v>
+        <v>1585</v>
       </c>
       <c r="F686" s="2" t="s">
         <v>9</v>
@@ -21100,10 +21090,10 @@
         <v>1214</v>
       </c>
       <c r="D687" s="2" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="E687" s="2" t="s">
-        <v>1620</v>
+        <v>42</v>
       </c>
       <c r="F687" s="2" t="s">
         <v>9</v>
@@ -21123,10 +21113,10 @@
         <v>1216</v>
       </c>
       <c r="D688" s="2" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="E688" s="2" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="F688" s="2" t="s">
         <v>9</v>
@@ -21146,10 +21136,10 @@
         <v>1218</v>
       </c>
       <c r="D689" s="2" t="s">
-        <v>1210</v>
+        <v>7</v>
       </c>
       <c r="E689" s="2" t="s">
-        <v>59</v>
+        <v>523</v>
       </c>
       <c r="F689" s="2" t="s">
         <v>9</v>
@@ -21163,19 +21153,19 @@
         <v>4</v>
       </c>
       <c r="B690" s="2" t="s">
-        <v>1219</v>
+        <v>1339</v>
       </c>
       <c r="C690" s="2" t="s">
-        <v>1220</v>
+        <v>1340</v>
       </c>
       <c r="D690" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E690" s="2" t="s">
-        <v>523</v>
+        <v>143</v>
       </c>
       <c r="F690" s="2" t="s">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="G690" s="2" t="s">
         <v>10</v>
@@ -21186,19 +21176,19 @@
         <v>4</v>
       </c>
       <c r="B691" s="2" t="s">
-        <v>1344</v>
+        <v>1219</v>
       </c>
       <c r="C691" s="2" t="s">
-        <v>1345</v>
+        <v>1220</v>
       </c>
       <c r="D691" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E691" s="2" t="s">
-        <v>62</v>
+        <v>216</v>
       </c>
       <c r="F691" s="2" t="s">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="G691" s="2" t="s">
         <v>10</v>
@@ -21218,7 +21208,7 @@
         <v>7</v>
       </c>
       <c r="E692" s="2" t="s">
-        <v>523</v>
+        <v>42</v>
       </c>
       <c r="F692" s="2" t="s">
         <v>9</v>
@@ -21232,16 +21222,16 @@
         <v>4</v>
       </c>
       <c r="B693" s="2" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="C693" s="2" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="D693" s="2" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E693" s="2" t="s">
-        <v>146</v>
+        <v>457</v>
       </c>
       <c r="F693" s="2" t="s">
         <v>9</v>
@@ -21261,10 +21251,10 @@
         <v>1224</v>
       </c>
       <c r="D694" s="2" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E694" s="2" t="s">
-        <v>457</v>
+        <v>1404</v>
       </c>
       <c r="F694" s="2" t="s">
         <v>9</v>
@@ -21287,7 +21277,7 @@
         <v>7</v>
       </c>
       <c r="E695" s="2" t="s">
-        <v>1348</v>
+        <v>1619</v>
       </c>
       <c r="F695" s="2" t="s">
         <v>9</v>
@@ -21310,7 +21300,7 @@
         <v>7</v>
       </c>
       <c r="E696" s="2" t="s">
-        <v>1551</v>
+        <v>1446</v>
       </c>
       <c r="F696" s="2" t="s">
         <v>9</v>
@@ -21333,7 +21323,7 @@
         <v>7</v>
       </c>
       <c r="E697" s="2" t="s">
-        <v>1453</v>
+        <v>1620</v>
       </c>
       <c r="F697" s="2" t="s">
         <v>9</v>
@@ -21359,7 +21349,7 @@
         <v>1621</v>
       </c>
       <c r="F698" s="2" t="s">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="G698" s="2" t="s">
         <v>10</v>
@@ -21379,10 +21369,10 @@
         <v>7</v>
       </c>
       <c r="E699" s="2" t="s">
-        <v>1622</v>
+        <v>195</v>
       </c>
       <c r="F699" s="2" t="s">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="G699" s="2" t="s">
         <v>10</v>
@@ -21402,7 +21392,7 @@
         <v>7</v>
       </c>
       <c r="E700" s="2" t="s">
-        <v>195</v>
+        <v>1537</v>
       </c>
       <c r="F700" s="2" t="s">
         <v>9</v>
@@ -21425,7 +21415,7 @@
         <v>7</v>
       </c>
       <c r="E701" s="2" t="s">
-        <v>1558</v>
+        <v>1239</v>
       </c>
       <c r="F701" s="2" t="s">
         <v>9</v>
@@ -21439,19 +21429,19 @@
         <v>4</v>
       </c>
       <c r="B702" s="2" t="s">
-        <v>1239</v>
+        <v>1374</v>
       </c>
       <c r="C702" s="2" t="s">
-        <v>1240</v>
+        <v>1375</v>
       </c>
       <c r="D702" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E702" s="2" t="s">
-        <v>1241</v>
+        <v>1482</v>
       </c>
       <c r="F702" s="2" t="s">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="G702" s="2" t="s">
         <v>10</v>
@@ -21462,19 +21452,19 @@
         <v>4</v>
       </c>
       <c r="B703" s="2" t="s">
-        <v>1379</v>
+        <v>1240</v>
       </c>
       <c r="C703" s="2" t="s">
-        <v>1380</v>
+        <v>1241</v>
       </c>
       <c r="D703" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E703" s="2" t="s">
-        <v>1490</v>
+        <v>59</v>
       </c>
       <c r="F703" s="2" t="s">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="G703" s="2" t="s">
         <v>10</v>
@@ -21485,16 +21475,16 @@
         <v>4</v>
       </c>
       <c r="B704" s="2" t="s">
-        <v>1242</v>
+        <v>1443</v>
       </c>
       <c r="C704" s="2" t="s">
-        <v>1243</v>
+        <v>1444</v>
       </c>
       <c r="D704" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E704" s="2" t="s">
-        <v>59</v>
+        <v>143</v>
       </c>
       <c r="F704" s="2" t="s">
         <v>9</v>
@@ -21508,16 +21498,16 @@
         <v>4</v>
       </c>
       <c r="B705" s="2" t="s">
-        <v>1450</v>
+        <v>1242</v>
       </c>
       <c r="C705" s="2" t="s">
-        <v>1451</v>
+        <v>1243</v>
       </c>
       <c r="D705" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E705" s="2" t="s">
-        <v>143</v>
+        <v>249</v>
       </c>
       <c r="F705" s="2" t="s">
         <v>9</v>
@@ -21540,7 +21530,7 @@
         <v>7</v>
       </c>
       <c r="E706" s="2" t="s">
-        <v>249</v>
+        <v>1104</v>
       </c>
       <c r="F706" s="2" t="s">
         <v>9</v>
@@ -21563,10 +21553,10 @@
         <v>7</v>
       </c>
       <c r="E707" s="2" t="s">
-        <v>81</v>
+        <v>1517</v>
       </c>
       <c r="F707" s="2" t="s">
-        <v>9</v>
+        <v>265</v>
       </c>
       <c r="G707" s="2" t="s">
         <v>10</v>
@@ -21586,7 +21576,7 @@
         <v>7</v>
       </c>
       <c r="E708" s="2" t="s">
-        <v>1529</v>
+        <v>1250</v>
       </c>
       <c r="F708" s="2" t="s">
         <v>265</v>
@@ -21600,19 +21590,19 @@
         <v>4</v>
       </c>
       <c r="B709" s="2" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="C709" s="2" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="D709" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E709" s="2" t="s">
-        <v>1252</v>
+        <v>67</v>
       </c>
       <c r="F709" s="2" t="s">
-        <v>265</v>
+        <v>100</v>
       </c>
       <c r="G709" s="2" t="s">
         <v>10</v>
@@ -21632,7 +21622,7 @@
         <v>7</v>
       </c>
       <c r="E710" s="2" t="s">
-        <v>67</v>
+        <v>1344</v>
       </c>
       <c r="F710" s="2" t="s">
         <v>100</v>
@@ -21646,19 +21636,19 @@
         <v>4</v>
       </c>
       <c r="B711" s="2" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="C711" s="2" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="D711" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E711" s="2" t="s">
-        <v>1349</v>
+        <v>843</v>
       </c>
       <c r="F711" s="2" t="s">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="G711" s="2" t="s">
         <v>10</v>
@@ -21669,16 +21659,16 @@
         <v>4</v>
       </c>
       <c r="B712" s="2" t="s">
-        <v>1258</v>
+        <v>1381</v>
       </c>
       <c r="C712" s="2" t="s">
-        <v>1259</v>
+        <v>1382</v>
       </c>
       <c r="D712" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E712" s="2" t="s">
-        <v>843</v>
+        <v>1021</v>
       </c>
       <c r="F712" s="2" t="s">
         <v>9</v>
@@ -21692,16 +21682,16 @@
         <v>4</v>
       </c>
       <c r="B713" s="2" t="s">
-        <v>1386</v>
+        <v>1258</v>
       </c>
       <c r="C713" s="2" t="s">
-        <v>1387</v>
+        <v>1259</v>
       </c>
       <c r="D713" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E713" s="2" t="s">
-        <v>1021</v>
+        <v>109</v>
       </c>
       <c r="F713" s="2" t="s">
         <v>9</v>
@@ -21724,7 +21714,7 @@
         <v>7</v>
       </c>
       <c r="E714" s="2" t="s">
-        <v>109</v>
+        <v>149</v>
       </c>
       <c r="F714" s="2" t="s">
         <v>9</v>
@@ -21747,7 +21737,7 @@
         <v>7</v>
       </c>
       <c r="E715" s="2" t="s">
-        <v>149</v>
+        <v>30</v>
       </c>
       <c r="F715" s="2" t="s">
         <v>9</v>
@@ -21761,16 +21751,16 @@
         <v>4</v>
       </c>
       <c r="B716" s="2" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C716" s="2" t="s">
+        <v>1263</v>
+      </c>
+      <c r="D716" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E716" s="2" t="s">
         <v>1264</v>
-      </c>
-      <c r="C716" s="2" t="s">
-        <v>1265</v>
-      </c>
-      <c r="D716" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E716" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="F716" s="2" t="s">
         <v>9</v>
@@ -21784,16 +21774,16 @@
         <v>4</v>
       </c>
       <c r="B717" s="2" t="s">
-        <v>1264</v>
+        <v>1420</v>
       </c>
       <c r="C717" s="2" t="s">
-        <v>1265</v>
+        <v>1421</v>
       </c>
       <c r="D717" s="2" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E717" s="2" t="s">
-        <v>1266</v>
+        <v>41</v>
       </c>
       <c r="F717" s="2" t="s">
         <v>9</v>
@@ -21807,10 +21797,10 @@
         <v>4</v>
       </c>
       <c r="B718" s="2" t="s">
-        <v>1427</v>
+        <v>1422</v>
       </c>
       <c r="C718" s="2" t="s">
-        <v>1428</v>
+        <v>1423</v>
       </c>
       <c r="D718" s="2" t="s">
         <v>7</v>
@@ -21830,16 +21820,16 @@
         <v>4</v>
       </c>
       <c r="B719" s="2" t="s">
-        <v>1429</v>
+        <v>1265</v>
       </c>
       <c r="C719" s="2" t="s">
-        <v>1430</v>
+        <v>1266</v>
       </c>
       <c r="D719" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E719" s="2" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="F719" s="2" t="s">
         <v>9</v>
@@ -21862,7 +21852,7 @@
         <v>7</v>
       </c>
       <c r="E720" s="2" t="s">
-        <v>76</v>
+        <v>8</v>
       </c>
       <c r="F720" s="2" t="s">
         <v>9</v>
@@ -21885,7 +21875,7 @@
         <v>7</v>
       </c>
       <c r="E721" s="2" t="s">
-        <v>8</v>
+        <v>1495</v>
       </c>
       <c r="F721" s="2" t="s">
         <v>9</v>
@@ -21908,7 +21898,7 @@
         <v>7</v>
       </c>
       <c r="E722" s="2" t="s">
-        <v>1503</v>
+        <v>1366</v>
       </c>
       <c r="F722" s="2" t="s">
         <v>9</v>
@@ -21931,7 +21921,7 @@
         <v>7</v>
       </c>
       <c r="E723" s="2" t="s">
-        <v>1552</v>
+        <v>41</v>
       </c>
       <c r="F723" s="2" t="s">
         <v>9</v>
@@ -21954,7 +21944,7 @@
         <v>7</v>
       </c>
       <c r="E724" s="2" t="s">
-        <v>41</v>
+        <v>1427</v>
       </c>
       <c r="F724" s="2" t="s">
         <v>9</v>
@@ -21977,7 +21967,7 @@
         <v>7</v>
       </c>
       <c r="E725" s="2" t="s">
-        <v>1348</v>
+        <v>156</v>
       </c>
       <c r="F725" s="2" t="s">
         <v>9</v>
@@ -21991,16 +21981,16 @@
         <v>4</v>
       </c>
       <c r="B726" s="2" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="C726" s="2" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="D726" s="2" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E726" s="2" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F726" s="2" t="s">
         <v>9</v>
@@ -22020,10 +22010,10 @@
         <v>1280</v>
       </c>
       <c r="D727" s="2" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E727" s="2" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="F727" s="2" t="s">
         <v>9</v>
@@ -22037,16 +22027,16 @@
         <v>4</v>
       </c>
       <c r="B728" s="2" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="C728" s="2" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="D728" s="2" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E728" s="2" t="s">
-        <v>87</v>
+        <v>431</v>
       </c>
       <c r="F728" s="2" t="s">
         <v>9</v>
@@ -22066,10 +22056,10 @@
         <v>1282</v>
       </c>
       <c r="D729" s="2" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E729" s="2" t="s">
-        <v>431</v>
+        <v>146</v>
       </c>
       <c r="F729" s="2" t="s">
         <v>9</v>
@@ -22083,16 +22073,16 @@
         <v>4</v>
       </c>
       <c r="B730" s="2" t="s">
-        <v>1283</v>
+        <v>1335</v>
       </c>
       <c r="C730" s="2" t="s">
-        <v>1284</v>
+        <v>1336</v>
       </c>
       <c r="D730" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E730" s="2" t="s">
-        <v>149</v>
+        <v>571</v>
       </c>
       <c r="F730" s="2" t="s">
         <v>9</v>
@@ -22106,16 +22096,16 @@
         <v>4</v>
       </c>
       <c r="B731" s="2" t="s">
-        <v>1339</v>
+        <v>1283</v>
       </c>
       <c r="C731" s="2" t="s">
-        <v>1340</v>
+        <v>1284</v>
       </c>
       <c r="D731" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E731" s="2" t="s">
-        <v>571</v>
+        <v>375</v>
       </c>
       <c r="F731" s="2" t="s">
         <v>9</v>
@@ -22129,16 +22119,16 @@
         <v>4</v>
       </c>
       <c r="B732" s="2" t="s">
-        <v>1285</v>
+        <v>1405</v>
       </c>
       <c r="C732" s="2" t="s">
-        <v>1286</v>
+        <v>1406</v>
       </c>
       <c r="D732" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E732" s="2" t="s">
-        <v>375</v>
+        <v>146</v>
       </c>
       <c r="F732" s="2" t="s">
         <v>9</v>
@@ -22152,16 +22142,16 @@
         <v>4</v>
       </c>
       <c r="B733" s="2" t="s">
-        <v>1410</v>
+        <v>1285</v>
       </c>
       <c r="C733" s="2" t="s">
-        <v>1411</v>
+        <v>1286</v>
       </c>
       <c r="D733" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E733" s="2" t="s">
-        <v>146</v>
+        <v>1064</v>
       </c>
       <c r="F733" s="2" t="s">
         <v>9</v>
@@ -22172,25 +22162,25 @@
     </row>
     <row r="734" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A734" s="2" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B734" s="2" t="s">
-        <v>1287</v>
+        <v>0</v>
       </c>
       <c r="C734" s="2" t="s">
-        <v>1288</v>
+        <v>0</v>
       </c>
       <c r="D734" s="2" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E734" s="2" t="s">
-        <v>1066</v>
+        <v>0</v>
       </c>
       <c r="F734" s="2" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G734" s="2" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="735" spans="1:7" x14ac:dyDescent="0.2">
@@ -22207,13 +22197,13 @@
         <v>0</v>
       </c>
       <c r="E735" s="2" t="s">
-        <v>0</v>
+        <v>1586</v>
       </c>
       <c r="F735" s="2" t="s">
-        <v>0</v>
+        <v>528</v>
       </c>
       <c r="G735" s="2" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="736" spans="1:7" x14ac:dyDescent="0.2">
@@ -22230,10 +22220,10 @@
         <v>0</v>
       </c>
       <c r="E736" s="2" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="F736" s="2" t="s">
-        <v>528</v>
+        <v>428</v>
       </c>
       <c r="G736" s="2" t="s">
         <v>10</v>
@@ -22253,10 +22243,10 @@
         <v>0</v>
       </c>
       <c r="E737" s="2" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="F737" s="2" t="s">
-        <v>428</v>
+        <v>265</v>
       </c>
       <c r="G737" s="2" t="s">
         <v>10</v>
@@ -22276,13 +22266,13 @@
         <v>0</v>
       </c>
       <c r="E738" s="2" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="F738" s="2" t="s">
-        <v>265</v>
+        <v>172</v>
       </c>
       <c r="G738" s="2" t="s">
-        <v>10</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="739" spans="1:7" x14ac:dyDescent="0.2">
@@ -22299,13 +22289,13 @@
         <v>0</v>
       </c>
       <c r="E739" s="2" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="F739" s="2" t="s">
-        <v>172</v>
+        <v>100</v>
       </c>
       <c r="G739" s="2" t="s">
-        <v>1452</v>
+        <v>10</v>
       </c>
     </row>
     <row r="740" spans="1:7" x14ac:dyDescent="0.2">
@@ -22322,10 +22312,10 @@
         <v>0</v>
       </c>
       <c r="E740" s="2" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="F740" s="2" t="s">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="G740" s="2" t="s">
         <v>10</v>
@@ -22345,7 +22335,7 @@
         <v>0</v>
       </c>
       <c r="E741" s="2" t="s">
-        <v>1628</v>
+        <v>1587</v>
       </c>
       <c r="F741" s="2" t="s">
         <v>9</v>

--- a/dados-catalago-pcm-interno/relatorio.xlsx
+++ b/dados-catalago-pcm-interno/relatorio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amaggicombr-my.sharepoint.com/personal/hiago_andre_amaggi_com_br/Documents/Área de Trabalho/codigos/catalogoPecasPCM/dados-catalago-pcm-interno/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="60" documentId="11_FD86FE4AC4094E4AB971B8A5A011EE841C83CB4A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C23EAEF6-8282-46BC-9E68-2F1E358A0310}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="11_FD86FE4AC4094E4AB971B8A5A011EE841C83CB4A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17F379CA-D6FE-4A41-AA93-C1A6DF3190CC}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5187" uniqueCount="1627">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5187" uniqueCount="1618">
   <si>
     <t/>
   </si>
@@ -2725,9 +2725,6 @@
     <t>PARAFUSO SEXT;M20X2,50;100MM;8,8;RP</t>
   </si>
   <si>
-    <t>56</t>
-  </si>
-  <si>
     <t>1010011379</t>
   </si>
   <si>
@@ -4363,9 +4360,6 @@
     <t>82</t>
   </si>
   <si>
-    <t>437</t>
-  </si>
-  <si>
     <t>72</t>
   </si>
   <si>
@@ -4378,12 +4372,6 @@
     <t>321</t>
   </si>
   <si>
-    <t>780</t>
-  </si>
-  <si>
-    <t>353</t>
-  </si>
-  <si>
     <t>1010047190</t>
   </si>
   <si>
@@ -4417,9 +4405,6 @@
     <t>EMBREAGEM CJ CAM FH4 SACHS/3400700601</t>
   </si>
   <si>
-    <t>250</t>
-  </si>
-  <si>
     <t>1010046976</t>
   </si>
   <si>
@@ -4468,9 +4453,6 @@
     <t>SAPATO SEG P/ELETR BOMPEL/SP900ELAA00615</t>
   </si>
   <si>
-    <t>161</t>
-  </si>
-  <si>
     <t>1010084644</t>
   </si>
   <si>
@@ -4510,9 +4492,6 @@
     <t>61</t>
   </si>
   <si>
-    <t>360</t>
-  </si>
-  <si>
     <t>159</t>
   </si>
   <si>
@@ -4522,21 +4501,12 @@
     <t>PROTETOR AURIC TP CONCH HONEYWELL/VS110D</t>
   </si>
   <si>
-    <t>126</t>
-  </si>
-  <si>
     <t>319</t>
   </si>
   <si>
     <t>380</t>
   </si>
   <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>460</t>
-  </si>
-  <si>
     <t>301</t>
   </si>
   <si>
@@ -4600,15 +4570,9 @@
     <t>173</t>
   </si>
   <si>
-    <t>191</t>
-  </si>
-  <si>
     <t>77</t>
   </si>
   <si>
-    <t>1.885</t>
-  </si>
-  <si>
     <t>53</t>
   </si>
   <si>
@@ -4639,15 +4603,9 @@
     <t>592</t>
   </si>
   <si>
-    <t>670</t>
-  </si>
-  <si>
     <t>997</t>
   </si>
   <si>
-    <t>1.124</t>
-  </si>
-  <si>
     <t>1010083462</t>
   </si>
   <si>
@@ -4666,9 +4624,6 @@
     <t>101</t>
   </si>
   <si>
-    <t>160</t>
-  </si>
-  <si>
     <t>124.841,120</t>
   </si>
   <si>
@@ -4690,30 +4645,15 @@
     <t>ENGATE REB CAM FH 540 RKTDIESEL/21313876</t>
   </si>
   <si>
-    <t>196</t>
-  </si>
-  <si>
     <t>171</t>
   </si>
   <si>
     <t>435</t>
   </si>
   <si>
-    <t>186</t>
-  </si>
-  <si>
     <t>111</t>
   </si>
   <si>
-    <t>83,500</t>
-  </si>
-  <si>
-    <t>849</t>
-  </si>
-  <si>
-    <t>158</t>
-  </si>
-  <si>
     <t>3.700</t>
   </si>
   <si>
@@ -4723,9 +4663,6 @@
     <t>1.923</t>
   </si>
   <si>
-    <t>127</t>
-  </si>
-  <si>
     <t>81</t>
   </si>
   <si>
@@ -4738,12 +4675,6 @@
     <t>509</t>
   </si>
   <si>
-    <t>613</t>
-  </si>
-  <si>
-    <t>771</t>
-  </si>
-  <si>
     <t>32</t>
   </si>
   <si>
@@ -4756,9 +4687,6 @@
     <t>502</t>
   </si>
   <si>
-    <t>1.080</t>
-  </si>
-  <si>
     <t>408</t>
   </si>
   <si>
@@ -4780,15 +4708,9 @@
     <t>232</t>
   </si>
   <si>
-    <t>210</t>
-  </si>
-  <si>
     <t>126.229,500</t>
   </si>
   <si>
-    <t>5.477</t>
-  </si>
-  <si>
     <t>59</t>
   </si>
   <si>
@@ -4813,45 +4735,12 @@
     <t>290</t>
   </si>
   <si>
-    <t>166</t>
-  </si>
-  <si>
-    <t>241</t>
-  </si>
-  <si>
-    <t>595</t>
-  </si>
-  <si>
-    <t>1.153</t>
-  </si>
-  <si>
     <t>1.089</t>
   </si>
   <si>
-    <t>295</t>
-  </si>
-  <si>
-    <t>411</t>
-  </si>
-  <si>
-    <t>459</t>
-  </si>
-  <si>
-    <t>83</t>
-  </si>
-  <si>
-    <t>152</t>
-  </si>
-  <si>
     <t>152,500</t>
   </si>
   <si>
-    <t>333</t>
-  </si>
-  <si>
-    <t>151,450</t>
-  </si>
-  <si>
     <t>2.020</t>
   </si>
   <si>
@@ -4861,9 +4750,6 @@
     <t>204</t>
   </si>
   <si>
-    <t>350</t>
-  </si>
-  <si>
     <t>207</t>
   </si>
   <si>
@@ -4891,16 +4777,103 @@
     <t>131.149,950</t>
   </si>
   <si>
-    <t>10.384,950</t>
-  </si>
-  <si>
-    <t>1.393</t>
-  </si>
-  <si>
-    <t>8.381</t>
-  </si>
-  <si>
-    <t>125.370,500</t>
+    <t>5.467</t>
+  </si>
+  <si>
+    <t>648</t>
+  </si>
+  <si>
+    <t>345</t>
+  </si>
+  <si>
+    <t>1.106</t>
+  </si>
+  <si>
+    <t>155</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>194</t>
+  </si>
+  <si>
+    <t>239</t>
+  </si>
+  <si>
+    <t>594</t>
+  </si>
+  <si>
+    <t>1.113</t>
+  </si>
+  <si>
+    <t>294</t>
+  </si>
+  <si>
+    <t>184</t>
+  </si>
+  <si>
+    <t>406</t>
+  </si>
+  <si>
+    <t>352</t>
+  </si>
+  <si>
+    <t>188</t>
+  </si>
+  <si>
+    <t>144</t>
+  </si>
+  <si>
+    <t>148,250</t>
+  </si>
+  <si>
+    <t>133,500</t>
+  </si>
+  <si>
+    <t>847</t>
+  </si>
+  <si>
+    <t>157</t>
+  </si>
+  <si>
+    <t>358</t>
+  </si>
+  <si>
+    <t>522</t>
+  </si>
+  <si>
+    <t>772</t>
+  </si>
+  <si>
+    <t>1.877</t>
+  </si>
+  <si>
+    <t>604</t>
+  </si>
+  <si>
+    <t>763</t>
+  </si>
+  <si>
+    <t>1.062</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>185</t>
+  </si>
+  <si>
+    <t>10.376,750</t>
+  </si>
+  <si>
+    <t>1.388</t>
+  </si>
+  <si>
+    <t>8.368</t>
+  </si>
+  <si>
+    <t>125.031,500</t>
   </si>
 </sst>
 </file>
@@ -4969,6 +4942,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5305,19 +5282,19 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="G1" t="s">
         <v>3</v>
@@ -5360,7 +5337,7 @@
         <v>7</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1588</v>
+        <v>1585</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>9</v>
@@ -5558,16 +5535,16 @@
         <v>4</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1483</v>
+        <v>1477</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1484</v>
+        <v>1478</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1485</v>
+        <v>1479</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>428</v>
@@ -5627,10 +5604,10 @@
         <v>4</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1533</v>
+        <v>1521</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1534</v>
+        <v>1522</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>7</v>
@@ -5729,7 +5706,7 @@
         <v>7</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>1501</v>
+        <v>1493</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>9</v>
@@ -5752,7 +5729,7 @@
         <v>7</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>9</v>
@@ -5821,7 +5798,7 @@
         <v>7</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>1502</v>
+        <v>1494</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>9</v>
@@ -5867,7 +5844,7 @@
         <v>7</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>9</v>
@@ -5890,7 +5867,7 @@
         <v>7</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>9</v>
@@ -5927,10 +5904,10 @@
         <v>4</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>1291</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>1292</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>7</v>
@@ -6028,7 +6005,7 @@
         <v>7</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>901</v>
+        <v>731</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>9</v>
@@ -6065,16 +6042,16 @@
         <v>4</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>1535</v>
+        <v>1523</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>1536</v>
+        <v>1524</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>27</v>
+        <v>1426</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>9</v>
@@ -6097,7 +6074,7 @@
         <v>7</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>1537</v>
+        <v>1525</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>9</v>
@@ -6120,7 +6097,7 @@
         <v>7</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>1538</v>
+        <v>1526</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>9</v>
@@ -6143,7 +6120,7 @@
         <v>7</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>1589</v>
+        <v>1563</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>9</v>
@@ -6189,7 +6166,7 @@
         <v>7</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>9</v>
@@ -6212,7 +6189,7 @@
         <v>7</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>100</v>
@@ -6249,16 +6226,16 @@
         <v>4</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>1350</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>1351</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>1352</v>
-      </c>
       <c r="D42" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>9</v>
@@ -6281,7 +6258,7 @@
         <v>7</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>1539</v>
+        <v>1586</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>9</v>
@@ -6304,7 +6281,7 @@
         <v>7</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>9</v>
@@ -6327,7 +6304,7 @@
         <v>7</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>9</v>
@@ -6341,16 +6318,16 @@
         <v>4</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>1523</v>
+        <v>1513</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>1524</v>
+        <v>1514</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>1540</v>
+        <v>1527</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>9</v>
@@ -6373,7 +6350,7 @@
         <v>7</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>1590</v>
+        <v>1564</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>9</v>
@@ -6396,7 +6373,7 @@
         <v>7</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>1453</v>
+        <v>1587</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>9</v>
@@ -6442,7 +6419,7 @@
         <v>7</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>1541</v>
+        <v>1588</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>9</v>
@@ -6479,10 +6456,10 @@
         <v>4</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>1488</v>
+        <v>1482</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>40</v>
@@ -6525,10 +6502,10 @@
         <v>4</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>1454</v>
+        <v>1450</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>1455</v>
+        <v>1451</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>7</v>
@@ -6778,16 +6755,16 @@
         <v>4</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>1542</v>
+        <v>1528</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>1543</v>
+        <v>1529</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>9</v>
@@ -6810,7 +6787,7 @@
         <v>7</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>76</v>
+        <v>156</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>9</v>
@@ -7238,10 +7215,10 @@
         <v>4</v>
       </c>
       <c r="B85" s="2" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C85" s="2" t="s">
         <v>1296</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>1297</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>40</v>
@@ -7468,10 +7445,10 @@
         <v>4</v>
       </c>
       <c r="B95" s="2" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C95" s="2" t="s">
         <v>1299</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>1300</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>40</v>
@@ -7813,10 +7790,10 @@
         <v>4</v>
       </c>
       <c r="B110" s="2" t="s">
+        <v>1383</v>
+      </c>
+      <c r="C110" s="2" t="s">
         <v>1384</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>1385</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>7</v>
@@ -7836,10 +7813,10 @@
         <v>4</v>
       </c>
       <c r="B111" s="2" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C111" s="2" t="s">
         <v>1386</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>1387</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>7</v>
@@ -7859,16 +7836,16 @@
         <v>4</v>
       </c>
       <c r="B112" s="2" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C112" s="2" t="s">
         <v>1388</v>
       </c>
-      <c r="C112" s="2" t="s">
-        <v>1389</v>
-      </c>
       <c r="D112" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>9</v>
@@ -7882,10 +7859,10 @@
         <v>4</v>
       </c>
       <c r="B113" s="2" t="s">
+        <v>1389</v>
+      </c>
+      <c r="C113" s="2" t="s">
         <v>1390</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>1391</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>7</v>
@@ -7914,7 +7891,7 @@
         <v>7</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>9</v>
@@ -7960,7 +7937,7 @@
         <v>7</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>1489</v>
+        <v>1483</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>9</v>
@@ -8006,7 +7983,7 @@
         <v>7</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>1427</v>
+        <v>1470</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>9</v>
@@ -8029,7 +8006,7 @@
         <v>7</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>9</v>
@@ -8052,7 +8029,7 @@
         <v>7</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>1544</v>
+        <v>1530</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>9</v>
@@ -8213,7 +8190,7 @@
         <v>7</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>523</v>
+        <v>50</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>265</v>
@@ -8227,10 +8204,10 @@
         <v>4</v>
       </c>
       <c r="B128" s="2" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C128" s="2" t="s">
         <v>1392</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>1393</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>7</v>
@@ -8259,7 +8236,7 @@
         <v>19</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>265</v>
@@ -8273,10 +8250,10 @@
         <v>4</v>
       </c>
       <c r="B130" s="2" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C130" s="2" t="s">
         <v>1413</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>1414</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>7</v>
@@ -8328,7 +8305,7 @@
         <v>7</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>149</v>
+        <v>104</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>9</v>
@@ -8351,7 +8328,7 @@
         <v>19</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>1355</v>
+        <v>159</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>9</v>
@@ -8374,7 +8351,7 @@
         <v>7</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>8</v>
+        <v>104</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>9</v>
@@ -8397,7 +8374,7 @@
         <v>19</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>242</v>
+        <v>1470</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>9</v>
@@ -8581,7 +8558,7 @@
         <v>7</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>9</v>
@@ -8618,10 +8595,10 @@
         <v>4</v>
       </c>
       <c r="B145" s="2" t="s">
+        <v>1314</v>
+      </c>
+      <c r="C145" s="2" t="s">
         <v>1315</v>
-      </c>
-      <c r="C145" s="2" t="s">
-        <v>1316</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>277</v>
@@ -8710,10 +8687,10 @@
         <v>4</v>
       </c>
       <c r="B149" s="2" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C149" s="2" t="s">
         <v>1317</v>
-      </c>
-      <c r="C149" s="2" t="s">
-        <v>1318</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>277</v>
@@ -8756,10 +8733,10 @@
         <v>4</v>
       </c>
       <c r="B151" s="2" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C151" s="2" t="s">
         <v>1319</v>
-      </c>
-      <c r="C151" s="2" t="s">
-        <v>1320</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>277</v>
@@ -8779,10 +8756,10 @@
         <v>4</v>
       </c>
       <c r="B152" s="2" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C152" s="2" t="s">
         <v>1321</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>1322</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>277</v>
@@ -8802,10 +8779,10 @@
         <v>4</v>
       </c>
       <c r="B153" s="2" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C153" s="2" t="s">
         <v>1323</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>1324</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>277</v>
@@ -8848,10 +8825,10 @@
         <v>4</v>
       </c>
       <c r="B155" s="2" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C155" s="2" t="s">
         <v>1325</v>
-      </c>
-      <c r="C155" s="2" t="s">
-        <v>1326</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>277</v>
@@ -8880,7 +8857,7 @@
         <v>277</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
       <c r="F156" s="2" t="s">
         <v>9</v>
@@ -8963,10 +8940,10 @@
         <v>4</v>
       </c>
       <c r="B160" s="2" t="s">
+        <v>1326</v>
+      </c>
+      <c r="C160" s="2" t="s">
         <v>1327</v>
-      </c>
-      <c r="C160" s="2" t="s">
-        <v>1328</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>277</v>
@@ -8986,10 +8963,10 @@
         <v>4</v>
       </c>
       <c r="B161" s="2" t="s">
+        <v>1328</v>
+      </c>
+      <c r="C161" s="2" t="s">
         <v>1329</v>
-      </c>
-      <c r="C161" s="2" t="s">
-        <v>1330</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>277</v>
@@ -9009,10 +8986,10 @@
         <v>4</v>
       </c>
       <c r="B162" s="2" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C162" s="2" t="s">
         <v>1306</v>
-      </c>
-      <c r="C162" s="2" t="s">
-        <v>1307</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>277</v>
@@ -9032,10 +9009,10 @@
         <v>4</v>
       </c>
       <c r="B163" s="2" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C163" s="2" t="s">
         <v>1308</v>
-      </c>
-      <c r="C163" s="2" t="s">
-        <v>1309</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>277</v>
@@ -9055,10 +9032,10 @@
         <v>4</v>
       </c>
       <c r="B164" s="2" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C164" s="2" t="s">
         <v>1310</v>
-      </c>
-      <c r="C164" s="2" t="s">
-        <v>1311</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>277</v>
@@ -9078,10 +9055,10 @@
         <v>4</v>
       </c>
       <c r="B165" s="2" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C165" s="2" t="s">
         <v>1312</v>
-      </c>
-      <c r="C165" s="2" t="s">
-        <v>1313</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>277</v>
@@ -9179,7 +9156,7 @@
         <v>277</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="F169" s="2" t="s">
         <v>9</v>
@@ -9202,7 +9179,7 @@
         <v>277</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="F170" s="2" t="s">
         <v>9</v>
@@ -9225,7 +9202,7 @@
         <v>277</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>1591</v>
+        <v>1565</v>
       </c>
       <c r="F171" s="2" t="s">
         <v>9</v>
@@ -9248,7 +9225,7 @@
         <v>19</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="F172" s="2" t="s">
         <v>9</v>
@@ -9271,7 +9248,7 @@
         <v>277</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>1592</v>
+        <v>1566</v>
       </c>
       <c r="F173" s="2" t="s">
         <v>9</v>
@@ -9294,7 +9271,7 @@
         <v>19</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="F174" s="2" t="s">
         <v>9</v>
@@ -9317,7 +9294,7 @@
         <v>277</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="F175" s="2" t="s">
         <v>9</v>
@@ -9363,7 +9340,7 @@
         <v>277</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="F177" s="2" t="s">
         <v>9</v>
@@ -9409,7 +9386,7 @@
         <v>277</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>1545</v>
+        <v>1531</v>
       </c>
       <c r="F179" s="2" t="s">
         <v>9</v>
@@ -9455,7 +9432,7 @@
         <v>277</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="F181" s="2" t="s">
         <v>9</v>
@@ -9524,7 +9501,7 @@
         <v>277</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>1557</v>
+        <v>1541</v>
       </c>
       <c r="F184" s="2" t="s">
         <v>9</v>
@@ -9662,7 +9639,7 @@
         <v>7</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>1104</v>
+        <v>317</v>
       </c>
       <c r="F190" s="2" t="s">
         <v>9</v>
@@ -9685,7 +9662,7 @@
         <v>7</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>1546</v>
+        <v>1532</v>
       </c>
       <c r="F191" s="2" t="s">
         <v>9</v>
@@ -9708,7 +9685,7 @@
         <v>7</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>1547</v>
+        <v>1533</v>
       </c>
       <c r="F192" s="2" t="s">
         <v>9</v>
@@ -9869,7 +9846,7 @@
         <v>7</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>143</v>
+        <v>50</v>
       </c>
       <c r="F199" s="2" t="s">
         <v>9</v>
@@ -9906,10 +9883,10 @@
         <v>4</v>
       </c>
       <c r="B201" s="2" t="s">
+        <v>1424</v>
+      </c>
+      <c r="C201" s="2" t="s">
         <v>1425</v>
-      </c>
-      <c r="C201" s="2" t="s">
-        <v>1426</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>7</v>
@@ -9961,7 +9938,7 @@
         <v>7</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="F203" s="2" t="s">
         <v>9</v>
@@ -10030,7 +10007,7 @@
         <v>7</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>1501</v>
+        <v>1493</v>
       </c>
       <c r="F206" s="2" t="s">
         <v>9</v>
@@ -10053,7 +10030,7 @@
         <v>7</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>1548</v>
+        <v>1589</v>
       </c>
       <c r="F207" s="2" t="s">
         <v>9</v>
@@ -10366,10 +10343,10 @@
         <v>4</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>1457</v>
+        <v>1453</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>1458</v>
+        <v>1454</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>40</v>
@@ -10421,7 +10398,7 @@
         <v>40</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>1503</v>
+        <v>1533</v>
       </c>
       <c r="F223" s="2" t="s">
         <v>9</v>
@@ -10444,7 +10421,7 @@
         <v>7</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="F224" s="2" t="s">
         <v>9</v>
@@ -10467,7 +10444,7 @@
         <v>427</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>1549</v>
+        <v>1534</v>
       </c>
       <c r="F225" s="2" t="s">
         <v>428</v>
@@ -10536,7 +10513,7 @@
         <v>7</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>1593</v>
+        <v>1567</v>
       </c>
       <c r="F228" s="2" t="s">
         <v>100</v>
@@ -10582,7 +10559,7 @@
         <v>7</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>1594</v>
+        <v>1568</v>
       </c>
       <c r="F230" s="2" t="s">
         <v>9</v>
@@ -10651,7 +10628,7 @@
         <v>7</v>
       </c>
       <c r="E233" s="2" t="s">
-        <v>1497</v>
+        <v>1589</v>
       </c>
       <c r="F233" s="2" t="s">
         <v>9</v>
@@ -10812,7 +10789,7 @@
         <v>7</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
       <c r="F240" s="2" t="s">
         <v>265</v>
@@ -10835,7 +10812,7 @@
         <v>7</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>211</v>
+        <v>104</v>
       </c>
       <c r="F241" s="2" t="s">
         <v>9</v>
@@ -10872,16 +10849,16 @@
         <v>4</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>1550</v>
+        <v>1535</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>1551</v>
+        <v>1536</v>
       </c>
       <c r="D243" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>1194</v>
+        <v>431</v>
       </c>
       <c r="F243" s="2" t="s">
         <v>528</v>
@@ -10904,7 +10881,7 @@
         <v>7</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="F244" s="2" t="s">
         <v>9</v>
@@ -10927,7 +10904,7 @@
         <v>19</v>
       </c>
       <c r="E245" s="2" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="F245" s="2" t="s">
         <v>9</v>
@@ -10950,7 +10927,7 @@
         <v>7</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>1595</v>
+        <v>1569</v>
       </c>
       <c r="F246" s="2" t="s">
         <v>9</v>
@@ -10987,10 +10964,10 @@
         <v>4</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>1459</v>
+        <v>1455</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>1460</v>
+        <v>1456</v>
       </c>
       <c r="D248" s="2" t="s">
         <v>7</v>
@@ -11010,10 +10987,10 @@
         <v>4</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>1552</v>
+        <v>1537</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>1553</v>
+        <v>1538</v>
       </c>
       <c r="D249" s="2" t="s">
         <v>7</v>
@@ -11088,7 +11065,7 @@
         <v>7</v>
       </c>
       <c r="E252" s="2" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="F252" s="2" t="s">
         <v>9</v>
@@ -11249,7 +11226,7 @@
         <v>33</v>
       </c>
       <c r="E259" s="2" t="s">
-        <v>1560</v>
+        <v>1590</v>
       </c>
       <c r="F259" s="2" t="s">
         <v>9</v>
@@ -11295,7 +11272,7 @@
         <v>7</v>
       </c>
       <c r="E261" s="2" t="s">
-        <v>1500</v>
+        <v>1193</v>
       </c>
       <c r="F261" s="2" t="s">
         <v>9</v>
@@ -11318,7 +11295,7 @@
         <v>19</v>
       </c>
       <c r="E262" s="2" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="F262" s="2" t="s">
         <v>9</v>
@@ -11341,7 +11318,7 @@
         <v>7</v>
       </c>
       <c r="E263" s="2" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="F263" s="2" t="s">
         <v>9</v>
@@ -11433,7 +11410,7 @@
         <v>7</v>
       </c>
       <c r="E267" s="2" t="s">
-        <v>1404</v>
+        <v>23</v>
       </c>
       <c r="F267" s="2" t="s">
         <v>9</v>
@@ -11456,7 +11433,7 @@
         <v>7</v>
       </c>
       <c r="E268" s="2" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="F268" s="2" t="s">
         <v>9</v>
@@ -11516,10 +11493,10 @@
         <v>4</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>1461</v>
+        <v>1457</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>1462</v>
+        <v>1458</v>
       </c>
       <c r="D271" s="2" t="s">
         <v>7</v>
@@ -11548,7 +11525,7 @@
         <v>7</v>
       </c>
       <c r="E272" s="2" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
       <c r="F272" s="2" t="s">
         <v>9</v>
@@ -11562,16 +11539,16 @@
         <v>4</v>
       </c>
       <c r="B273" s="2" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C273" s="2" t="s">
         <v>1359</v>
       </c>
-      <c r="C273" s="2" t="s">
-        <v>1360</v>
-      </c>
       <c r="D273" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="F273" s="2" t="s">
         <v>9</v>
@@ -11815,10 +11792,10 @@
         <v>4</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>1463</v>
+        <v>1459</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>1464</v>
+        <v>1460</v>
       </c>
       <c r="D284" s="2" t="s">
         <v>7</v>
@@ -11884,16 +11861,16 @@
         <v>4</v>
       </c>
       <c r="B287" s="2" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C287" s="2" t="s">
         <v>1361</v>
       </c>
-      <c r="C287" s="2" t="s">
-        <v>1362</v>
-      </c>
       <c r="D287" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E287" s="2" t="s">
-        <v>23</v>
+        <v>1402</v>
       </c>
       <c r="F287" s="2" t="s">
         <v>9</v>
@@ -11962,7 +11939,7 @@
         <v>7</v>
       </c>
       <c r="E290" s="2" t="s">
-        <v>1596</v>
+        <v>1570</v>
       </c>
       <c r="F290" s="2" t="s">
         <v>100</v>
@@ -11976,10 +11953,10 @@
         <v>4</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>1554</v>
+        <v>1539</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>1555</v>
+        <v>1540</v>
       </c>
       <c r="D291" s="2" t="s">
         <v>7</v>
@@ -12031,7 +12008,7 @@
         <v>7</v>
       </c>
       <c r="E293" s="2" t="s">
-        <v>1556</v>
+        <v>1591</v>
       </c>
       <c r="F293" s="2" t="s">
         <v>9</v>
@@ -12123,7 +12100,7 @@
         <v>7</v>
       </c>
       <c r="E297" s="2" t="s">
-        <v>1597</v>
+        <v>1565</v>
       </c>
       <c r="F297" s="2" t="s">
         <v>9</v>
@@ -12192,7 +12169,7 @@
         <v>7</v>
       </c>
       <c r="E300" s="2" t="s">
-        <v>1525</v>
+        <v>1515</v>
       </c>
       <c r="F300" s="2" t="s">
         <v>9</v>
@@ -12215,7 +12192,7 @@
         <v>7</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>1505</v>
+        <v>1495</v>
       </c>
       <c r="F301" s="2" t="s">
         <v>9</v>
@@ -12238,7 +12215,7 @@
         <v>7</v>
       </c>
       <c r="E302" s="2" t="s">
-        <v>1376</v>
+        <v>1406</v>
       </c>
       <c r="F302" s="2" t="s">
         <v>9</v>
@@ -12284,7 +12261,7 @@
         <v>7</v>
       </c>
       <c r="E304" s="2" t="s">
-        <v>211</v>
+        <v>235</v>
       </c>
       <c r="F304" s="2" t="s">
         <v>9</v>
@@ -12445,7 +12422,7 @@
         <v>7</v>
       </c>
       <c r="E311" s="2" t="s">
-        <v>1598</v>
+        <v>1592</v>
       </c>
       <c r="F311" s="2" t="s">
         <v>9</v>
@@ -12560,7 +12537,7 @@
         <v>7</v>
       </c>
       <c r="E316" s="2" t="s">
-        <v>1599</v>
+        <v>1593</v>
       </c>
       <c r="F316" s="2" t="s">
         <v>9</v>
@@ -12583,7 +12560,7 @@
         <v>7</v>
       </c>
       <c r="E317" s="2" t="s">
-        <v>146</v>
+        <v>42</v>
       </c>
       <c r="F317" s="2" t="s">
         <v>9</v>
@@ -12597,10 +12574,10 @@
         <v>4</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>1492</v>
+        <v>1486</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>1493</v>
+        <v>1487</v>
       </c>
       <c r="D318" s="2" t="s">
         <v>33</v>
@@ -12643,16 +12620,16 @@
         <v>4</v>
       </c>
       <c r="B320" s="2" t="s">
+        <v>1428</v>
+      </c>
+      <c r="C320" s="2" t="s">
         <v>1429</v>
       </c>
-      <c r="C320" s="2" t="s">
-        <v>1430</v>
-      </c>
       <c r="D320" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E320" s="2" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="F320" s="2" t="s">
         <v>100</v>
@@ -12698,7 +12675,7 @@
         <v>7</v>
       </c>
       <c r="E322" s="2" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="F322" s="2" t="s">
         <v>9</v>
@@ -12721,7 +12698,7 @@
         <v>7</v>
       </c>
       <c r="E323" s="2" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="F323" s="2" t="s">
         <v>9</v>
@@ -12744,7 +12721,7 @@
         <v>7</v>
       </c>
       <c r="E324" s="2" t="s">
-        <v>1504</v>
+        <v>1525</v>
       </c>
       <c r="F324" s="2" t="s">
         <v>9</v>
@@ -12813,7 +12790,7 @@
         <v>7</v>
       </c>
       <c r="E327" s="2" t="s">
-        <v>1600</v>
+        <v>1594</v>
       </c>
       <c r="F327" s="2" t="s">
         <v>9</v>
@@ -12836,7 +12813,7 @@
         <v>19</v>
       </c>
       <c r="E328" s="2" t="s">
-        <v>1494</v>
+        <v>1488</v>
       </c>
       <c r="F328" s="2" t="s">
         <v>9</v>
@@ -12896,10 +12873,10 @@
         <v>4</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>1466</v>
+        <v>1461</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>1467</v>
+        <v>1462</v>
       </c>
       <c r="D331" s="2" t="s">
         <v>7</v>
@@ -12951,7 +12928,7 @@
         <v>7</v>
       </c>
       <c r="E333" s="2" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="F333" s="2" t="s">
         <v>9</v>
@@ -12974,7 +12951,7 @@
         <v>7</v>
       </c>
       <c r="E334" s="2" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="F334" s="2" t="s">
         <v>9</v>
@@ -12988,10 +12965,10 @@
         <v>4</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>1468</v>
+        <v>1463</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>1469</v>
+        <v>1464</v>
       </c>
       <c r="D335" s="2" t="s">
         <v>7</v>
@@ -13158,7 +13135,7 @@
         <v>7</v>
       </c>
       <c r="E342" s="2" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="F342" s="2" t="s">
         <v>100</v>
@@ -13204,7 +13181,7 @@
         <v>7</v>
       </c>
       <c r="E344" s="2" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="F344" s="2" t="s">
         <v>9</v>
@@ -13218,16 +13195,16 @@
         <v>4</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>1470</v>
+        <v>1465</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>1471</v>
+        <v>1466</v>
       </c>
       <c r="D345" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E345" s="2" t="s">
-        <v>1558</v>
+        <v>1542</v>
       </c>
       <c r="F345" s="2" t="s">
         <v>9</v>
@@ -13250,7 +13227,7 @@
         <v>7</v>
       </c>
       <c r="E346" s="2" t="s">
-        <v>1601</v>
+        <v>1571</v>
       </c>
       <c r="F346" s="2" t="s">
         <v>9</v>
@@ -13273,7 +13250,7 @@
         <v>7</v>
       </c>
       <c r="E347" s="2" t="s">
-        <v>1501</v>
+        <v>1493</v>
       </c>
       <c r="F347" s="2" t="s">
         <v>9</v>
@@ -13287,16 +13264,16 @@
         <v>4</v>
       </c>
       <c r="B348" s="2" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C348" s="2" t="s">
         <v>1356</v>
       </c>
-      <c r="C348" s="2" t="s">
-        <v>1357</v>
-      </c>
       <c r="D348" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E348" s="2" t="s">
-        <v>1602</v>
+        <v>1595</v>
       </c>
       <c r="F348" s="2" t="s">
         <v>9</v>
@@ -13365,7 +13342,7 @@
         <v>7</v>
       </c>
       <c r="E351" s="2" t="s">
-        <v>1559</v>
+        <v>1596</v>
       </c>
       <c r="F351" s="2" t="s">
         <v>9</v>
@@ -13388,7 +13365,7 @@
         <v>7</v>
       </c>
       <c r="E352" s="2" t="s">
-        <v>1603</v>
+        <v>1597</v>
       </c>
       <c r="F352" s="2" t="s">
         <v>9</v>
@@ -13411,7 +13388,7 @@
         <v>7</v>
       </c>
       <c r="E353" s="2" t="s">
-        <v>1604</v>
+        <v>1525</v>
       </c>
       <c r="F353" s="2" t="s">
         <v>9</v>
@@ -13434,7 +13411,7 @@
         <v>7</v>
       </c>
       <c r="E354" s="2" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="F354" s="2" t="s">
         <v>9</v>
@@ -13457,7 +13434,7 @@
         <v>7</v>
       </c>
       <c r="E355" s="2" t="s">
-        <v>1453</v>
+        <v>1598</v>
       </c>
       <c r="F355" s="2" t="s">
         <v>100</v>
@@ -13503,7 +13480,7 @@
         <v>7</v>
       </c>
       <c r="E357" s="2" t="s">
-        <v>1605</v>
+        <v>1349</v>
       </c>
       <c r="F357" s="2" t="s">
         <v>9</v>
@@ -13526,7 +13503,7 @@
         <v>7</v>
       </c>
       <c r="E358" s="2" t="s">
-        <v>1526</v>
+        <v>1599</v>
       </c>
       <c r="F358" s="2" t="s">
         <v>9</v>
@@ -13549,7 +13526,7 @@
         <v>7</v>
       </c>
       <c r="E359" s="2" t="s">
-        <v>211</v>
+        <v>104</v>
       </c>
       <c r="F359" s="2" t="s">
         <v>9</v>
@@ -13572,7 +13549,7 @@
         <v>7</v>
       </c>
       <c r="E360" s="2" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="F360" s="2" t="s">
         <v>9</v>
@@ -13595,7 +13572,7 @@
         <v>7</v>
       </c>
       <c r="E361" s="2" t="s">
-        <v>1606</v>
+        <v>1600</v>
       </c>
       <c r="F361" s="2" t="s">
         <v>9</v>
@@ -13618,7 +13595,7 @@
         <v>19</v>
       </c>
       <c r="E362" s="2" t="s">
-        <v>1506</v>
+        <v>1496</v>
       </c>
       <c r="F362" s="2" t="s">
         <v>9</v>
@@ -13641,7 +13618,7 @@
         <v>7</v>
       </c>
       <c r="E363" s="2" t="s">
-        <v>1515</v>
+        <v>1505</v>
       </c>
       <c r="F363" s="2" t="s">
         <v>9</v>
@@ -13687,7 +13664,7 @@
         <v>7</v>
       </c>
       <c r="E365" s="2" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="F365" s="2" t="s">
         <v>9</v>
@@ -13710,7 +13687,7 @@
         <v>7</v>
       </c>
       <c r="E366" s="2" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="F366" s="2" t="s">
         <v>9</v>
@@ -13793,10 +13770,10 @@
         <v>4</v>
       </c>
       <c r="B370" s="2" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C370" s="2" t="s">
         <v>1431</v>
-      </c>
-      <c r="C370" s="2" t="s">
-        <v>1432</v>
       </c>
       <c r="D370" s="2" t="s">
         <v>7</v>
@@ -14055,7 +14032,7 @@
         <v>7</v>
       </c>
       <c r="E381" s="2" t="s">
-        <v>1518</v>
+        <v>1508</v>
       </c>
       <c r="F381" s="2" t="s">
         <v>100</v>
@@ -14078,7 +14055,7 @@
         <v>7</v>
       </c>
       <c r="E382" s="2" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="F382" s="2" t="s">
         <v>9</v>
@@ -14101,7 +14078,7 @@
         <v>7</v>
       </c>
       <c r="E383" s="2" t="s">
-        <v>1607</v>
+        <v>1572</v>
       </c>
       <c r="F383" s="2" t="s">
         <v>9</v>
@@ -14193,7 +14170,7 @@
         <v>19</v>
       </c>
       <c r="E387" s="2" t="s">
-        <v>1529</v>
+        <v>1517</v>
       </c>
       <c r="F387" s="2" t="s">
         <v>9</v>
@@ -14354,7 +14331,7 @@
         <v>40</v>
       </c>
       <c r="E394" s="2" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="F394" s="2" t="s">
         <v>172</v>
@@ -14377,7 +14354,7 @@
         <v>40</v>
       </c>
       <c r="E395" s="2" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="F395" s="2" t="s">
         <v>172</v>
@@ -14446,7 +14423,7 @@
         <v>40</v>
       </c>
       <c r="E398" s="2" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="F398" s="2" t="s">
         <v>172</v>
@@ -14460,10 +14437,10 @@
         <v>4</v>
       </c>
       <c r="B399" s="2" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C399" s="2" t="s">
         <v>1363</v>
-      </c>
-      <c r="C399" s="2" t="s">
-        <v>1364</v>
       </c>
       <c r="D399" s="2" t="s">
         <v>40</v>
@@ -14538,7 +14515,7 @@
         <v>40</v>
       </c>
       <c r="E402" s="2" t="s">
-        <v>1608</v>
+        <v>1507</v>
       </c>
       <c r="F402" s="2" t="s">
         <v>172</v>
@@ -14713,10 +14690,10 @@
         <v>4</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>1472</v>
+        <v>1467</v>
       </c>
       <c r="C410" s="2" t="s">
-        <v>1473</v>
+        <v>1468</v>
       </c>
       <c r="D410" s="2" t="s">
         <v>7</v>
@@ -14791,7 +14768,7 @@
         <v>7</v>
       </c>
       <c r="E413" s="2" t="s">
-        <v>1609</v>
+        <v>1601</v>
       </c>
       <c r="F413" s="2" t="s">
         <v>265</v>
@@ -14814,7 +14791,7 @@
         <v>7</v>
       </c>
       <c r="E414" s="2" t="s">
-        <v>1561</v>
+        <v>1602</v>
       </c>
       <c r="F414" s="2" t="s">
         <v>265</v>
@@ -14837,7 +14814,7 @@
         <v>19</v>
       </c>
       <c r="E415" s="2" t="s">
-        <v>1465</v>
+        <v>457</v>
       </c>
       <c r="F415" s="2" t="s">
         <v>265</v>
@@ -14860,7 +14837,7 @@
         <v>7</v>
       </c>
       <c r="E416" s="2" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="F416" s="2" t="s">
         <v>9</v>
@@ -14874,10 +14851,10 @@
         <v>4</v>
       </c>
       <c r="B417" s="2" t="s">
+        <v>1432</v>
+      </c>
+      <c r="C417" s="2" t="s">
         <v>1433</v>
-      </c>
-      <c r="C417" s="2" t="s">
-        <v>1434</v>
       </c>
       <c r="D417" s="2" t="s">
         <v>7</v>
@@ -14943,16 +14920,16 @@
         <v>4</v>
       </c>
       <c r="B420" s="2" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C420" s="2" t="s">
         <v>1293</v>
       </c>
-      <c r="C420" s="2" t="s">
-        <v>1294</v>
-      </c>
       <c r="D420" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E420" s="2" t="s">
-        <v>1527</v>
+        <v>1516</v>
       </c>
       <c r="F420" s="2" t="s">
         <v>9</v>
@@ -14975,7 +14952,7 @@
         <v>7</v>
       </c>
       <c r="E421" s="2" t="s">
-        <v>1562</v>
+        <v>1603</v>
       </c>
       <c r="F421" s="2" t="s">
         <v>9</v>
@@ -14998,7 +14975,7 @@
         <v>7</v>
       </c>
       <c r="E422" s="2" t="s">
-        <v>1563</v>
+        <v>1604</v>
       </c>
       <c r="F422" s="2" t="s">
         <v>9</v>
@@ -15012,10 +14989,10 @@
         <v>4</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>1519</v>
+        <v>1509</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>1520</v>
+        <v>1510</v>
       </c>
       <c r="D423" s="2" t="s">
         <v>7</v>
@@ -15150,16 +15127,16 @@
         <v>4</v>
       </c>
       <c r="B429" s="2" t="s">
+        <v>1434</v>
+      </c>
+      <c r="C429" s="2" t="s">
         <v>1435</v>
       </c>
-      <c r="C429" s="2" t="s">
-        <v>1436</v>
-      </c>
       <c r="D429" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E429" s="2" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="F429" s="2" t="s">
         <v>9</v>
@@ -15205,7 +15182,7 @@
         <v>7</v>
       </c>
       <c r="E431" s="2" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="F431" s="2" t="s">
         <v>9</v>
@@ -15228,7 +15205,7 @@
         <v>19</v>
       </c>
       <c r="E432" s="2" t="s">
-        <v>1456</v>
+        <v>1452</v>
       </c>
       <c r="F432" s="2" t="s">
         <v>9</v>
@@ -15274,7 +15251,7 @@
         <v>7</v>
       </c>
       <c r="E434" s="2" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="F434" s="2" t="s">
         <v>9</v>
@@ -15320,7 +15297,7 @@
         <v>7</v>
       </c>
       <c r="E436" s="2" t="s">
-        <v>1564</v>
+        <v>1544</v>
       </c>
       <c r="F436" s="2" t="s">
         <v>9</v>
@@ -15366,7 +15343,7 @@
         <v>40</v>
       </c>
       <c r="E438" s="2" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="F438" s="2" t="s">
         <v>9</v>
@@ -15389,7 +15366,7 @@
         <v>40</v>
       </c>
       <c r="E439" s="2" t="s">
-        <v>1496</v>
+        <v>1545</v>
       </c>
       <c r="F439" s="2" t="s">
         <v>9</v>
@@ -15412,7 +15389,7 @@
         <v>40</v>
       </c>
       <c r="E440" s="2" t="s">
-        <v>1516</v>
+        <v>1506</v>
       </c>
       <c r="F440" s="2" t="s">
         <v>9</v>
@@ -15435,7 +15412,7 @@
         <v>40</v>
       </c>
       <c r="E441" s="2" t="s">
-        <v>1565</v>
+        <v>1605</v>
       </c>
       <c r="F441" s="2" t="s">
         <v>9</v>
@@ -15458,7 +15435,7 @@
         <v>33</v>
       </c>
       <c r="E442" s="2" t="s">
-        <v>1610</v>
+        <v>1573</v>
       </c>
       <c r="F442" s="2" t="s">
         <v>428</v>
@@ -15495,10 +15472,10 @@
         <v>4</v>
       </c>
       <c r="B444" s="2" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C444" s="2" t="s">
         <v>1410</v>
-      </c>
-      <c r="C444" s="2" t="s">
-        <v>1411</v>
       </c>
       <c r="D444" s="2" t="s">
         <v>7</v>
@@ -15849,7 +15826,7 @@
         <v>7</v>
       </c>
       <c r="E459" s="2" t="s">
-        <v>1331</v>
+        <v>1606</v>
       </c>
       <c r="F459" s="2" t="s">
         <v>9</v>
@@ -15895,7 +15872,7 @@
         <v>7</v>
       </c>
       <c r="E461" s="2" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="F461" s="2" t="s">
         <v>100</v>
@@ -15941,7 +15918,7 @@
         <v>7</v>
       </c>
       <c r="E463" s="2" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="F463" s="2" t="s">
         <v>9</v>
@@ -15964,7 +15941,7 @@
         <v>7</v>
       </c>
       <c r="E464" s="2" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="F464" s="2" t="s">
         <v>9</v>
@@ -15987,7 +15964,7 @@
         <v>7</v>
       </c>
       <c r="E465" s="2" t="s">
-        <v>1566</v>
+        <v>1546</v>
       </c>
       <c r="F465" s="2" t="s">
         <v>9</v>
@@ -16010,7 +15987,7 @@
         <v>7</v>
       </c>
       <c r="E466" s="2" t="s">
-        <v>1567</v>
+        <v>1238</v>
       </c>
       <c r="F466" s="2" t="s">
         <v>9</v>
@@ -16033,7 +16010,7 @@
         <v>7</v>
       </c>
       <c r="E467" s="2" t="s">
-        <v>1452</v>
+        <v>1607</v>
       </c>
       <c r="F467" s="2" t="s">
         <v>9</v>
@@ -16079,7 +16056,7 @@
         <v>7</v>
       </c>
       <c r="E469" s="2" t="s">
-        <v>1447</v>
+        <v>1542</v>
       </c>
       <c r="F469" s="2" t="s">
         <v>100</v>
@@ -16102,7 +16079,7 @@
         <v>7</v>
       </c>
       <c r="E470" s="2" t="s">
-        <v>1528</v>
+        <v>1608</v>
       </c>
       <c r="F470" s="2" t="s">
         <v>100</v>
@@ -16162,10 +16139,10 @@
         <v>4</v>
       </c>
       <c r="B473" s="2" t="s">
+        <v>1336</v>
+      </c>
+      <c r="C473" s="2" t="s">
         <v>1337</v>
-      </c>
-      <c r="C473" s="2" t="s">
-        <v>1338</v>
       </c>
       <c r="D473" s="2" t="s">
         <v>7</v>
@@ -16194,7 +16171,7 @@
         <v>7</v>
       </c>
       <c r="E474" s="2" t="s">
-        <v>1568</v>
+        <v>1547</v>
       </c>
       <c r="F474" s="2" t="s">
         <v>9</v>
@@ -16217,7 +16194,7 @@
         <v>7</v>
       </c>
       <c r="E475" s="2" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="F475" s="2" t="s">
         <v>9</v>
@@ -16240,7 +16217,7 @@
         <v>7</v>
       </c>
       <c r="E476" s="2" t="s">
-        <v>1507</v>
+        <v>1497</v>
       </c>
       <c r="F476" s="2" t="s">
         <v>9</v>
@@ -16286,7 +16263,7 @@
         <v>7</v>
       </c>
       <c r="E478" s="2" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="F478" s="2" t="s">
         <v>9</v>
@@ -16300,10 +16277,10 @@
         <v>4</v>
       </c>
       <c r="B479" s="2" t="s">
-        <v>1569</v>
+        <v>1548</v>
       </c>
       <c r="C479" s="2" t="s">
-        <v>1570</v>
+        <v>1549</v>
       </c>
       <c r="D479" s="2" t="s">
         <v>7</v>
@@ -16355,7 +16332,7 @@
         <v>7</v>
       </c>
       <c r="E481" s="2" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="F481" s="2" t="s">
         <v>9</v>
@@ -16369,10 +16346,10 @@
         <v>4</v>
       </c>
       <c r="B482" s="2" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C482" s="2" t="s">
         <v>1396</v>
-      </c>
-      <c r="C482" s="2" t="s">
-        <v>1397</v>
       </c>
       <c r="D482" s="2" t="s">
         <v>7</v>
@@ -16424,7 +16401,7 @@
         <v>7</v>
       </c>
       <c r="E484" s="2" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="F484" s="2" t="s">
         <v>9</v>
@@ -16447,7 +16424,7 @@
         <v>7</v>
       </c>
       <c r="E485" s="2" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="F485" s="2" t="s">
         <v>9</v>
@@ -16470,7 +16447,7 @@
         <v>7</v>
       </c>
       <c r="E486" s="2" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="F486" s="2" t="s">
         <v>9</v>
@@ -16493,7 +16470,7 @@
         <v>7</v>
       </c>
       <c r="E487" s="2" t="s">
-        <v>1571</v>
+        <v>1550</v>
       </c>
       <c r="F487" s="2" t="s">
         <v>9</v>
@@ -16516,7 +16493,7 @@
         <v>7</v>
       </c>
       <c r="E488" s="2" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="F488" s="2" t="s">
         <v>9</v>
@@ -16530,10 +16507,10 @@
         <v>4</v>
       </c>
       <c r="B489" s="2" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C489" s="2" t="s">
         <v>1399</v>
-      </c>
-      <c r="C489" s="2" t="s">
-        <v>1400</v>
       </c>
       <c r="D489" s="2" t="s">
         <v>7</v>
@@ -16562,7 +16539,7 @@
         <v>7</v>
       </c>
       <c r="E490" s="2" t="s">
-        <v>1495</v>
+        <v>1489</v>
       </c>
       <c r="F490" s="2" t="s">
         <v>9</v>
@@ -16576,16 +16553,16 @@
         <v>4</v>
       </c>
       <c r="B491" s="2" t="s">
+        <v>901</v>
+      </c>
+      <c r="C491" s="2" t="s">
         <v>902</v>
       </c>
-      <c r="C491" s="2" t="s">
-        <v>903</v>
-      </c>
       <c r="D491" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E491" s="2" t="s">
-        <v>1572</v>
+        <v>1609</v>
       </c>
       <c r="F491" s="2" t="s">
         <v>9</v>
@@ -16599,16 +16576,16 @@
         <v>4</v>
       </c>
       <c r="B492" s="2" t="s">
+        <v>903</v>
+      </c>
+      <c r="C492" s="2" t="s">
         <v>904</v>
       </c>
-      <c r="C492" s="2" t="s">
-        <v>905</v>
-      </c>
       <c r="D492" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E492" s="2" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="F492" s="2" t="s">
         <v>9</v>
@@ -16622,16 +16599,16 @@
         <v>4</v>
       </c>
       <c r="B493" s="2" t="s">
+        <v>905</v>
+      </c>
+      <c r="C493" s="2" t="s">
         <v>906</v>
       </c>
-      <c r="C493" s="2" t="s">
-        <v>907</v>
-      </c>
       <c r="D493" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E493" s="2" t="s">
-        <v>1573</v>
+        <v>1610</v>
       </c>
       <c r="F493" s="2" t="s">
         <v>9</v>
@@ -16645,16 +16622,16 @@
         <v>4</v>
       </c>
       <c r="B494" s="2" t="s">
+        <v>907</v>
+      </c>
+      <c r="C494" s="2" t="s">
         <v>908</v>
       </c>
-      <c r="C494" s="2" t="s">
-        <v>909</v>
-      </c>
       <c r="D494" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E494" s="2" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="F494" s="2" t="s">
         <v>9</v>
@@ -16668,10 +16645,10 @@
         <v>4</v>
       </c>
       <c r="B495" s="2" t="s">
+        <v>909</v>
+      </c>
+      <c r="C495" s="2" t="s">
         <v>910</v>
-      </c>
-      <c r="C495" s="2" t="s">
-        <v>911</v>
       </c>
       <c r="D495" s="2" t="s">
         <v>7</v>
@@ -16691,16 +16668,16 @@
         <v>4</v>
       </c>
       <c r="B496" s="2" t="s">
+        <v>911</v>
+      </c>
+      <c r="C496" s="2" t="s">
         <v>912</v>
       </c>
-      <c r="C496" s="2" t="s">
-        <v>913</v>
-      </c>
       <c r="D496" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E496" s="2" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="F496" s="2" t="s">
         <v>9</v>
@@ -16714,10 +16691,10 @@
         <v>4</v>
       </c>
       <c r="B497" s="2" t="s">
+        <v>913</v>
+      </c>
+      <c r="C497" s="2" t="s">
         <v>914</v>
-      </c>
-      <c r="C497" s="2" t="s">
-        <v>915</v>
       </c>
       <c r="D497" s="2" t="s">
         <v>7</v>
@@ -16737,16 +16714,16 @@
         <v>4</v>
       </c>
       <c r="B498" s="2" t="s">
+        <v>915</v>
+      </c>
+      <c r="C498" s="2" t="s">
         <v>916</v>
       </c>
-      <c r="C498" s="2" t="s">
-        <v>917</v>
-      </c>
       <c r="D498" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E498" s="2" t="s">
-        <v>1611</v>
+        <v>1574</v>
       </c>
       <c r="F498" s="2" t="s">
         <v>9</v>
@@ -16760,16 +16737,16 @@
         <v>4</v>
       </c>
       <c r="B499" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="C499" s="2" t="s">
         <v>918</v>
       </c>
-      <c r="C499" s="2" t="s">
-        <v>919</v>
-      </c>
       <c r="D499" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E499" s="2" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="F499" s="2" t="s">
         <v>9</v>
@@ -16783,10 +16760,10 @@
         <v>4</v>
       </c>
       <c r="B500" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="C500" s="2" t="s">
         <v>918</v>
-      </c>
-      <c r="C500" s="2" t="s">
-        <v>919</v>
       </c>
       <c r="D500" s="2" t="s">
         <v>19</v>
@@ -16806,10 +16783,10 @@
         <v>4</v>
       </c>
       <c r="B501" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="C501" s="2" t="s">
         <v>920</v>
-      </c>
-      <c r="C501" s="2" t="s">
-        <v>921</v>
       </c>
       <c r="D501" s="2" t="s">
         <v>7</v>
@@ -16829,10 +16806,10 @@
         <v>4</v>
       </c>
       <c r="B502" s="2" t="s">
+        <v>921</v>
+      </c>
+      <c r="C502" s="2" t="s">
         <v>922</v>
-      </c>
-      <c r="C502" s="2" t="s">
-        <v>923</v>
       </c>
       <c r="D502" s="2" t="s">
         <v>7</v>
@@ -16852,10 +16829,10 @@
         <v>4</v>
       </c>
       <c r="B503" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="C503" s="2" t="s">
         <v>924</v>
-      </c>
-      <c r="C503" s="2" t="s">
-        <v>925</v>
       </c>
       <c r="D503" s="2" t="s">
         <v>7</v>
@@ -16875,16 +16852,16 @@
         <v>4</v>
       </c>
       <c r="B504" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="C504" s="2" t="s">
         <v>926</v>
       </c>
-      <c r="C504" s="2" t="s">
-        <v>927</v>
-      </c>
       <c r="D504" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E504" s="2" t="s">
-        <v>1529</v>
+        <v>1342</v>
       </c>
       <c r="F504" s="2" t="s">
         <v>9</v>
@@ -16898,10 +16875,10 @@
         <v>4</v>
       </c>
       <c r="B505" s="2" t="s">
+        <v>927</v>
+      </c>
+      <c r="C505" s="2" t="s">
         <v>928</v>
-      </c>
-      <c r="C505" s="2" t="s">
-        <v>929</v>
       </c>
       <c r="D505" s="2" t="s">
         <v>366</v>
@@ -16921,10 +16898,10 @@
         <v>4</v>
       </c>
       <c r="B506" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="C506" s="2" t="s">
         <v>930</v>
-      </c>
-      <c r="C506" s="2" t="s">
-        <v>931</v>
       </c>
       <c r="D506" s="2" t="s">
         <v>40</v>
@@ -16944,10 +16921,10 @@
         <v>4</v>
       </c>
       <c r="B507" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="C507" s="2" t="s">
         <v>930</v>
-      </c>
-      <c r="C507" s="2" t="s">
-        <v>931</v>
       </c>
       <c r="D507" s="2" t="s">
         <v>19</v>
@@ -16967,10 +16944,10 @@
         <v>4</v>
       </c>
       <c r="B508" s="2" t="s">
+        <v>931</v>
+      </c>
+      <c r="C508" s="2" t="s">
         <v>932</v>
-      </c>
-      <c r="C508" s="2" t="s">
-        <v>933</v>
       </c>
       <c r="D508" s="2" t="s">
         <v>7</v>
@@ -16990,10 +16967,10 @@
         <v>4</v>
       </c>
       <c r="B509" s="2" t="s">
+        <v>933</v>
+      </c>
+      <c r="C509" s="2" t="s">
         <v>934</v>
-      </c>
-      <c r="C509" s="2" t="s">
-        <v>935</v>
       </c>
       <c r="D509" s="2" t="s">
         <v>7</v>
@@ -17013,16 +16990,16 @@
         <v>4</v>
       </c>
       <c r="B510" s="2" t="s">
+        <v>935</v>
+      </c>
+      <c r="C510" s="2" t="s">
         <v>936</v>
       </c>
-      <c r="C510" s="2" t="s">
-        <v>937</v>
-      </c>
       <c r="D510" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E510" s="2" t="s">
-        <v>1508</v>
+        <v>1498</v>
       </c>
       <c r="F510" s="2" t="s">
         <v>9</v>
@@ -17036,10 +17013,10 @@
         <v>4</v>
       </c>
       <c r="B511" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="C511" s="2" t="s">
         <v>938</v>
-      </c>
-      <c r="C511" s="2" t="s">
-        <v>939</v>
       </c>
       <c r="D511" s="2" t="s">
         <v>7</v>
@@ -17059,16 +17036,16 @@
         <v>4</v>
       </c>
       <c r="B512" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="C512" s="2" t="s">
         <v>940</v>
       </c>
-      <c r="C512" s="2" t="s">
-        <v>941</v>
-      </c>
       <c r="D512" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E512" s="2" t="s">
-        <v>195</v>
+        <v>864</v>
       </c>
       <c r="F512" s="2" t="s">
         <v>9</v>
@@ -17082,10 +17059,10 @@
         <v>4</v>
       </c>
       <c r="B513" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="C513" s="2" t="s">
         <v>942</v>
-      </c>
-      <c r="C513" s="2" t="s">
-        <v>943</v>
       </c>
       <c r="D513" s="2" t="s">
         <v>7</v>
@@ -17105,10 +17082,10 @@
         <v>4</v>
       </c>
       <c r="B514" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="C514" s="2" t="s">
         <v>944</v>
-      </c>
-      <c r="C514" s="2" t="s">
-        <v>945</v>
       </c>
       <c r="D514" s="2" t="s">
         <v>7</v>
@@ -17128,16 +17105,16 @@
         <v>4</v>
       </c>
       <c r="B515" s="2" t="s">
+        <v>945</v>
+      </c>
+      <c r="C515" s="2" t="s">
         <v>946</v>
       </c>
-      <c r="C515" s="2" t="s">
-        <v>947</v>
-      </c>
       <c r="D515" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E515" s="2" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="F515" s="2" t="s">
         <v>9</v>
@@ -17151,16 +17128,16 @@
         <v>4</v>
       </c>
       <c r="B516" s="2" t="s">
+        <v>947</v>
+      </c>
+      <c r="C516" s="2" t="s">
         <v>948</v>
       </c>
-      <c r="C516" s="2" t="s">
-        <v>949</v>
-      </c>
       <c r="D516" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E516" s="2" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="F516" s="2" t="s">
         <v>9</v>
@@ -17174,13 +17151,13 @@
         <v>4</v>
       </c>
       <c r="B517" s="2" t="s">
+        <v>949</v>
+      </c>
+      <c r="C517" s="2" t="s">
         <v>950</v>
       </c>
-      <c r="C517" s="2" t="s">
+      <c r="D517" s="2" t="s">
         <v>951</v>
-      </c>
-      <c r="D517" s="2" t="s">
-        <v>952</v>
       </c>
       <c r="E517" s="2" t="s">
         <v>23</v>
@@ -17197,10 +17174,10 @@
         <v>4</v>
       </c>
       <c r="B518" s="2" t="s">
+        <v>952</v>
+      </c>
+      <c r="C518" s="2" t="s">
         <v>953</v>
-      </c>
-      <c r="C518" s="2" t="s">
-        <v>954</v>
       </c>
       <c r="D518" s="2" t="s">
         <v>19</v>
@@ -17220,16 +17197,16 @@
         <v>4</v>
       </c>
       <c r="B519" s="2" t="s">
+        <v>952</v>
+      </c>
+      <c r="C519" s="2" t="s">
         <v>953</v>
       </c>
-      <c r="C519" s="2" t="s">
-        <v>954</v>
-      </c>
       <c r="D519" s="2" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E519" s="2" t="s">
-        <v>1612</v>
+        <v>1575</v>
       </c>
       <c r="F519" s="2" t="s">
         <v>9</v>
@@ -17243,16 +17220,16 @@
         <v>4</v>
       </c>
       <c r="B520" s="2" t="s">
+        <v>1378</v>
+      </c>
+      <c r="C520" s="2" t="s">
         <v>1379</v>
       </c>
-      <c r="C520" s="2" t="s">
-        <v>1380</v>
-      </c>
       <c r="D520" s="2" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E520" s="2" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="F520" s="2" t="s">
         <v>9</v>
@@ -17266,13 +17243,13 @@
         <v>4</v>
       </c>
       <c r="B521" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C521" s="2" t="s">
         <v>1345</v>
       </c>
-      <c r="C521" s="2" t="s">
-        <v>1346</v>
-      </c>
       <c r="D521" s="2" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E521" s="2" t="s">
         <v>30</v>
@@ -17289,16 +17266,16 @@
         <v>4</v>
       </c>
       <c r="B522" s="2" t="s">
-        <v>1509</v>
+        <v>1499</v>
       </c>
       <c r="C522" s="2" t="s">
-        <v>1510</v>
+        <v>1500</v>
       </c>
       <c r="D522" s="2" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E522" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="F522" s="2" t="s">
         <v>9</v>
@@ -17312,16 +17289,16 @@
         <v>4</v>
       </c>
       <c r="B523" s="2" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C523" s="2" t="s">
         <v>1302</v>
       </c>
-      <c r="C523" s="2" t="s">
-        <v>1303</v>
-      </c>
       <c r="D523" s="2" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E523" s="2" t="s">
-        <v>81</v>
+        <v>216</v>
       </c>
       <c r="F523" s="2" t="s">
         <v>9</v>
@@ -17335,13 +17312,13 @@
         <v>4</v>
       </c>
       <c r="B524" s="2" t="s">
+        <v>1331</v>
+      </c>
+      <c r="C524" s="2" t="s">
         <v>1332</v>
       </c>
-      <c r="C524" s="2" t="s">
-        <v>1333</v>
-      </c>
       <c r="D524" s="2" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E524" s="2" t="s">
         <v>580</v>
@@ -17358,13 +17335,13 @@
         <v>4</v>
       </c>
       <c r="B525" s="2" t="s">
-        <v>1575</v>
+        <v>1552</v>
       </c>
       <c r="C525" s="2" t="s">
-        <v>1576</v>
+        <v>1553</v>
       </c>
       <c r="D525" s="2" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E525" s="2" t="s">
         <v>67</v>
@@ -17381,10 +17358,10 @@
         <v>4</v>
       </c>
       <c r="B526" s="2" t="s">
-        <v>1511</v>
+        <v>1501</v>
       </c>
       <c r="C526" s="2" t="s">
-        <v>1512</v>
+        <v>1502</v>
       </c>
       <c r="D526" s="2" t="s">
         <v>7</v>
@@ -17404,10 +17381,10 @@
         <v>4</v>
       </c>
       <c r="B527" s="2" t="s">
-        <v>1511</v>
+        <v>1501</v>
       </c>
       <c r="C527" s="2" t="s">
-        <v>1512</v>
+        <v>1502</v>
       </c>
       <c r="D527" s="2" t="s">
         <v>19</v>
@@ -17427,16 +17404,16 @@
         <v>4</v>
       </c>
       <c r="B528" s="2" t="s">
+        <v>955</v>
+      </c>
+      <c r="C528" s="2" t="s">
         <v>956</v>
       </c>
-      <c r="C528" s="2" t="s">
-        <v>957</v>
-      </c>
       <c r="D528" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E528" s="2" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="F528" s="2" t="s">
         <v>9</v>
@@ -17450,10 +17427,10 @@
         <v>4</v>
       </c>
       <c r="B529" s="2" t="s">
+        <v>957</v>
+      </c>
+      <c r="C529" s="2" t="s">
         <v>958</v>
-      </c>
-      <c r="C529" s="2" t="s">
-        <v>959</v>
       </c>
       <c r="D529" s="2" t="s">
         <v>7</v>
@@ -17473,16 +17450,16 @@
         <v>4</v>
       </c>
       <c r="B530" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="C530" s="2" t="s">
         <v>960</v>
       </c>
-      <c r="C530" s="2" t="s">
-        <v>961</v>
-      </c>
       <c r="D530" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E530" s="2" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="F530" s="2" t="s">
         <v>100</v>
@@ -17496,16 +17473,16 @@
         <v>4</v>
       </c>
       <c r="B531" s="2" t="s">
+        <v>961</v>
+      </c>
+      <c r="C531" s="2" t="s">
         <v>962</v>
       </c>
-      <c r="C531" s="2" t="s">
+      <c r="D531" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E531" s="2" t="s">
         <v>963</v>
-      </c>
-      <c r="D531" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E531" s="2" t="s">
-        <v>964</v>
       </c>
       <c r="F531" s="2" t="s">
         <v>100</v>
@@ -17519,10 +17496,10 @@
         <v>4</v>
       </c>
       <c r="B532" s="2" t="s">
+        <v>964</v>
+      </c>
+      <c r="C532" s="2" t="s">
         <v>965</v>
-      </c>
-      <c r="C532" s="2" t="s">
-        <v>966</v>
       </c>
       <c r="D532" s="2" t="s">
         <v>7</v>
@@ -17542,10 +17519,10 @@
         <v>4</v>
       </c>
       <c r="B533" s="2" t="s">
+        <v>966</v>
+      </c>
+      <c r="C533" s="2" t="s">
         <v>967</v>
-      </c>
-      <c r="C533" s="2" t="s">
-        <v>968</v>
       </c>
       <c r="D533" s="2" t="s">
         <v>7</v>
@@ -17565,16 +17542,16 @@
         <v>4</v>
       </c>
       <c r="B534" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="C534" s="2" t="s">
         <v>969</v>
       </c>
-      <c r="C534" s="2" t="s">
-        <v>970</v>
-      </c>
       <c r="D534" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E534" s="2" t="s">
-        <v>1577</v>
+        <v>1554</v>
       </c>
       <c r="F534" s="2" t="s">
         <v>9</v>
@@ -17588,10 +17565,10 @@
         <v>4</v>
       </c>
       <c r="B535" s="2" t="s">
+        <v>970</v>
+      </c>
+      <c r="C535" s="2" t="s">
         <v>971</v>
-      </c>
-      <c r="C535" s="2" t="s">
-        <v>972</v>
       </c>
       <c r="D535" s="2" t="s">
         <v>7</v>
@@ -17611,16 +17588,16 @@
         <v>4</v>
       </c>
       <c r="B536" s="2" t="s">
+        <v>972</v>
+      </c>
+      <c r="C536" s="2" t="s">
         <v>973</v>
       </c>
-      <c r="C536" s="2" t="s">
-        <v>974</v>
-      </c>
       <c r="D536" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E536" s="2" t="s">
-        <v>1427</v>
+        <v>211</v>
       </c>
       <c r="F536" s="2" t="s">
         <v>9</v>
@@ -17634,16 +17611,16 @@
         <v>4</v>
       </c>
       <c r="B537" s="2" t="s">
+        <v>974</v>
+      </c>
+      <c r="C537" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C537" s="2" t="s">
-        <v>976</v>
-      </c>
       <c r="D537" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E537" s="2" t="s">
-        <v>1578</v>
+        <v>1611</v>
       </c>
       <c r="F537" s="2" t="s">
         <v>9</v>
@@ -17657,10 +17634,10 @@
         <v>4</v>
       </c>
       <c r="B538" s="2" t="s">
+        <v>976</v>
+      </c>
+      <c r="C538" s="2" t="s">
         <v>977</v>
-      </c>
-      <c r="C538" s="2" t="s">
-        <v>978</v>
       </c>
       <c r="D538" s="2" t="s">
         <v>7</v>
@@ -17680,16 +17657,16 @@
         <v>4</v>
       </c>
       <c r="B539" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="C539" s="2" t="s">
         <v>979</v>
       </c>
-      <c r="C539" s="2" t="s">
-        <v>980</v>
-      </c>
       <c r="D539" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E539" s="2" t="s">
-        <v>1475</v>
+        <v>1470</v>
       </c>
       <c r="F539" s="2" t="s">
         <v>9</v>
@@ -17703,16 +17680,16 @@
         <v>4</v>
       </c>
       <c r="B540" s="2" t="s">
+        <v>980</v>
+      </c>
+      <c r="C540" s="2" t="s">
         <v>981</v>
       </c>
-      <c r="C540" s="2" t="s">
-        <v>982</v>
-      </c>
       <c r="D540" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E540" s="2" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="F540" s="2" t="s">
         <v>9</v>
@@ -17726,16 +17703,16 @@
         <v>4</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>1513</v>
+        <v>1503</v>
       </c>
       <c r="C541" s="2" t="s">
-        <v>1514</v>
+        <v>1504</v>
       </c>
       <c r="D541" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E541" s="2" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="F541" s="2" t="s">
         <v>9</v>
@@ -17749,10 +17726,10 @@
         <v>4</v>
       </c>
       <c r="B542" s="2" t="s">
+        <v>982</v>
+      </c>
+      <c r="C542" s="2" t="s">
         <v>983</v>
-      </c>
-      <c r="C542" s="2" t="s">
-        <v>984</v>
       </c>
       <c r="D542" s="2" t="s">
         <v>7</v>
@@ -17772,16 +17749,16 @@
         <v>4</v>
       </c>
       <c r="B543" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="C543" s="2" t="s">
         <v>985</v>
       </c>
-      <c r="C543" s="2" t="s">
-        <v>986</v>
-      </c>
       <c r="D543" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E543" s="2" t="s">
-        <v>1613</v>
+        <v>1397</v>
       </c>
       <c r="F543" s="2" t="s">
         <v>9</v>
@@ -17795,16 +17772,16 @@
         <v>4</v>
       </c>
       <c r="B544" s="2" t="s">
+        <v>986</v>
+      </c>
+      <c r="C544" s="2" t="s">
         <v>987</v>
       </c>
-      <c r="C544" s="2" t="s">
-        <v>988</v>
-      </c>
       <c r="D544" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E544" s="2" t="s">
-        <v>1614</v>
+        <v>1576</v>
       </c>
       <c r="F544" s="2" t="s">
         <v>9</v>
@@ -17818,16 +17795,16 @@
         <v>4</v>
       </c>
       <c r="B545" s="2" t="s">
+        <v>988</v>
+      </c>
+      <c r="C545" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="C545" s="2" t="s">
-        <v>990</v>
-      </c>
       <c r="D545" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E545" s="2" t="s">
-        <v>1615</v>
+        <v>1577</v>
       </c>
       <c r="F545" s="2" t="s">
         <v>9</v>
@@ -17841,16 +17818,16 @@
         <v>4</v>
       </c>
       <c r="B546" s="2" t="s">
+        <v>990</v>
+      </c>
+      <c r="C546" s="2" t="s">
         <v>991</v>
       </c>
-      <c r="C546" s="2" t="s">
-        <v>992</v>
-      </c>
       <c r="D546" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E546" s="2" t="s">
-        <v>1497</v>
+        <v>1490</v>
       </c>
       <c r="F546" s="2" t="s">
         <v>100</v>
@@ -17864,16 +17841,16 @@
         <v>4</v>
       </c>
       <c r="B547" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="C547" s="2" t="s">
         <v>993</v>
       </c>
-      <c r="C547" s="2" t="s">
-        <v>994</v>
-      </c>
       <c r="D547" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E547" s="2" t="s">
-        <v>1579</v>
+        <v>1555</v>
       </c>
       <c r="F547" s="2" t="s">
         <v>9</v>
@@ -17887,10 +17864,10 @@
         <v>4</v>
       </c>
       <c r="B548" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="C548" s="2" t="s">
         <v>995</v>
-      </c>
-      <c r="C548" s="2" t="s">
-        <v>996</v>
       </c>
       <c r="D548" s="2" t="s">
         <v>7</v>
@@ -17910,10 +17887,10 @@
         <v>4</v>
       </c>
       <c r="B549" s="2" t="s">
+        <v>996</v>
+      </c>
+      <c r="C549" s="2" t="s">
         <v>997</v>
-      </c>
-      <c r="C549" s="2" t="s">
-        <v>998</v>
       </c>
       <c r="D549" s="2" t="s">
         <v>7</v>
@@ -17933,10 +17910,10 @@
         <v>4</v>
       </c>
       <c r="B550" s="2" t="s">
+        <v>998</v>
+      </c>
+      <c r="C550" s="2" t="s">
         <v>999</v>
-      </c>
-      <c r="C550" s="2" t="s">
-        <v>1000</v>
       </c>
       <c r="D550" s="2" t="s">
         <v>7</v>
@@ -17956,16 +17933,16 @@
         <v>4</v>
       </c>
       <c r="B551" s="2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C551" s="2" t="s">
         <v>1001</v>
       </c>
-      <c r="C551" s="2" t="s">
-        <v>1002</v>
-      </c>
       <c r="D551" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E551" s="2" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="F551" s="2" t="s">
         <v>9</v>
@@ -17979,10 +17956,10 @@
         <v>4</v>
       </c>
       <c r="B552" s="2" t="s">
-        <v>1498</v>
+        <v>1491</v>
       </c>
       <c r="C552" s="2" t="s">
-        <v>1499</v>
+        <v>1492</v>
       </c>
       <c r="D552" s="2" t="s">
         <v>40</v>
@@ -18002,16 +17979,16 @@
         <v>4</v>
       </c>
       <c r="B553" s="2" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C553" s="2" t="s">
         <v>1003</v>
-      </c>
-      <c r="C553" s="2" t="s">
-        <v>1004</v>
       </c>
       <c r="D553" s="2" t="s">
         <v>40</v>
       </c>
       <c r="E553" s="2" t="s">
-        <v>1545</v>
+        <v>1590</v>
       </c>
       <c r="F553" s="2" t="s">
         <v>9</v>
@@ -18025,10 +18002,10 @@
         <v>4</v>
       </c>
       <c r="B554" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C554" s="2" t="s">
         <v>1005</v>
-      </c>
-      <c r="C554" s="2" t="s">
-        <v>1006</v>
       </c>
       <c r="D554" s="2" t="s">
         <v>40</v>
@@ -18048,16 +18025,16 @@
         <v>4</v>
       </c>
       <c r="B555" s="2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C555" s="2" t="s">
         <v>1007</v>
       </c>
-      <c r="C555" s="2" t="s">
-        <v>1008</v>
-      </c>
       <c r="D555" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E555" s="2" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="F555" s="2" t="s">
         <v>9</v>
@@ -18071,16 +18048,16 @@
         <v>4</v>
       </c>
       <c r="B556" s="2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C556" s="2" t="s">
         <v>1007</v>
-      </c>
-      <c r="C556" s="2" t="s">
-        <v>1008</v>
       </c>
       <c r="D556" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E556" s="2" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="F556" s="2" t="s">
         <v>9</v>
@@ -18094,10 +18071,10 @@
         <v>4</v>
       </c>
       <c r="B557" s="2" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C557" s="2" t="s">
         <v>1009</v>
-      </c>
-      <c r="C557" s="2" t="s">
-        <v>1010</v>
       </c>
       <c r="D557" s="2" t="s">
         <v>40</v>
@@ -18117,16 +18094,16 @@
         <v>4</v>
       </c>
       <c r="B558" s="2" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C558" s="2" t="s">
         <v>1011</v>
-      </c>
-      <c r="C558" s="2" t="s">
-        <v>1012</v>
       </c>
       <c r="D558" s="2" t="s">
         <v>427</v>
       </c>
       <c r="E558" s="2" t="s">
-        <v>1580</v>
+        <v>1556</v>
       </c>
       <c r="F558" s="2" t="s">
         <v>428</v>
@@ -18140,16 +18117,16 @@
         <v>4</v>
       </c>
       <c r="B559" s="2" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C559" s="2" t="s">
         <v>1013</v>
       </c>
-      <c r="C559" s="2" t="s">
-        <v>1014</v>
-      </c>
       <c r="D559" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E559" s="2" t="s">
-        <v>1616</v>
+        <v>1578</v>
       </c>
       <c r="F559" s="2" t="s">
         <v>9</v>
@@ -18163,10 +18140,10 @@
         <v>4</v>
       </c>
       <c r="B560" s="2" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C560" s="2" t="s">
         <v>1015</v>
-      </c>
-      <c r="C560" s="2" t="s">
-        <v>1016</v>
       </c>
       <c r="D560" s="2" t="s">
         <v>7</v>
@@ -18186,10 +18163,10 @@
         <v>4</v>
       </c>
       <c r="B561" s="2" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C561" s="2" t="s">
         <v>1017</v>
-      </c>
-      <c r="C561" s="2" t="s">
-        <v>1018</v>
       </c>
       <c r="D561" s="2" t="s">
         <v>7</v>
@@ -18209,10 +18186,10 @@
         <v>4</v>
       </c>
       <c r="B562" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C562" s="2" t="s">
         <v>1019</v>
-      </c>
-      <c r="C562" s="2" t="s">
-        <v>1020</v>
       </c>
       <c r="D562" s="2" t="s">
         <v>7</v>
@@ -18232,10 +18209,10 @@
         <v>4</v>
       </c>
       <c r="B563" s="2" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C563" s="2" t="s">
         <v>1022</v>
-      </c>
-      <c r="C563" s="2" t="s">
-        <v>1023</v>
       </c>
       <c r="D563" s="2" t="s">
         <v>7</v>
@@ -18255,10 +18232,10 @@
         <v>4</v>
       </c>
       <c r="B564" s="2" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C564" s="2" t="s">
         <v>1024</v>
-      </c>
-      <c r="C564" s="2" t="s">
-        <v>1025</v>
       </c>
       <c r="D564" s="2" t="s">
         <v>7</v>
@@ -18278,10 +18255,10 @@
         <v>4</v>
       </c>
       <c r="B565" s="2" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C565" s="2" t="s">
         <v>1026</v>
-      </c>
-      <c r="C565" s="2" t="s">
-        <v>1027</v>
       </c>
       <c r="D565" s="2" t="s">
         <v>7</v>
@@ -18301,16 +18278,16 @@
         <v>4</v>
       </c>
       <c r="B566" s="2" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C566" s="2" t="s">
         <v>1028</v>
       </c>
-      <c r="C566" s="2" t="s">
-        <v>1029</v>
-      </c>
       <c r="D566" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E566" s="2" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="F566" s="2" t="s">
         <v>9</v>
@@ -18324,10 +18301,10 @@
         <v>4</v>
       </c>
       <c r="B567" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C567" s="2" t="s">
         <v>1030</v>
-      </c>
-      <c r="C567" s="2" t="s">
-        <v>1031</v>
       </c>
       <c r="D567" s="2" t="s">
         <v>7</v>
@@ -18347,16 +18324,16 @@
         <v>4</v>
       </c>
       <c r="B568" s="2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C568" s="2" t="s">
         <v>1032</v>
       </c>
-      <c r="C568" s="2" t="s">
-        <v>1033</v>
-      </c>
       <c r="D568" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E568" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="F568" s="2" t="s">
         <v>9</v>
@@ -18370,10 +18347,10 @@
         <v>4</v>
       </c>
       <c r="B569" s="2" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C569" s="2" t="s">
         <v>1034</v>
-      </c>
-      <c r="C569" s="2" t="s">
-        <v>1035</v>
       </c>
       <c r="D569" s="2" t="s">
         <v>7</v>
@@ -18393,10 +18370,10 @@
         <v>4</v>
       </c>
       <c r="B570" s="2" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C570" s="2" t="s">
         <v>1036</v>
-      </c>
-      <c r="C570" s="2" t="s">
-        <v>1037</v>
       </c>
       <c r="D570" s="2" t="s">
         <v>40</v>
@@ -18416,10 +18393,10 @@
         <v>4</v>
       </c>
       <c r="B571" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C571" s="2" t="s">
         <v>1038</v>
-      </c>
-      <c r="C571" s="2" t="s">
-        <v>1039</v>
       </c>
       <c r="D571" s="2" t="s">
         <v>7</v>
@@ -18439,10 +18416,10 @@
         <v>4</v>
       </c>
       <c r="B572" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C572" s="2" t="s">
         <v>1040</v>
-      </c>
-      <c r="C572" s="2" t="s">
-        <v>1041</v>
       </c>
       <c r="D572" s="2" t="s">
         <v>7</v>
@@ -18462,16 +18439,16 @@
         <v>4</v>
       </c>
       <c r="B573" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C573" s="2" t="s">
         <v>1042</v>
       </c>
-      <c r="C573" s="2" t="s">
-        <v>1043</v>
-      </c>
       <c r="D573" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E573" s="2" t="s">
-        <v>1530</v>
+        <v>1518</v>
       </c>
       <c r="F573" s="2" t="s">
         <v>100</v>
@@ -18485,10 +18462,10 @@
         <v>4</v>
       </c>
       <c r="B574" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C574" s="2" t="s">
         <v>1044</v>
-      </c>
-      <c r="C574" s="2" t="s">
-        <v>1045</v>
       </c>
       <c r="D574" s="2" t="s">
         <v>7</v>
@@ -18508,10 +18485,10 @@
         <v>4</v>
       </c>
       <c r="B575" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C575" s="2" t="s">
         <v>1046</v>
-      </c>
-      <c r="C575" s="2" t="s">
-        <v>1047</v>
       </c>
       <c r="D575" s="2" t="s">
         <v>7</v>
@@ -18531,10 +18508,10 @@
         <v>4</v>
       </c>
       <c r="B576" s="2" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C576" s="2" t="s">
         <v>1048</v>
-      </c>
-      <c r="C576" s="2" t="s">
-        <v>1049</v>
       </c>
       <c r="D576" s="2" t="s">
         <v>40</v>
@@ -18554,16 +18531,16 @@
         <v>4</v>
       </c>
       <c r="B577" s="2" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C577" s="2" t="s">
         <v>1368</v>
-      </c>
-      <c r="C577" s="2" t="s">
-        <v>1369</v>
       </c>
       <c r="D577" s="2" t="s">
         <v>40</v>
       </c>
       <c r="E577" s="2" t="s">
-        <v>1194</v>
+        <v>1566</v>
       </c>
       <c r="F577" s="2" t="s">
         <v>9</v>
@@ -18577,16 +18554,16 @@
         <v>4</v>
       </c>
       <c r="B578" s="2" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C578" s="2" t="s">
         <v>1368</v>
-      </c>
-      <c r="C578" s="2" t="s">
-        <v>1369</v>
       </c>
       <c r="D578" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E578" s="2" t="s">
-        <v>1476</v>
+        <v>1471</v>
       </c>
       <c r="F578" s="2" t="s">
         <v>9</v>
@@ -18600,16 +18577,16 @@
         <v>4</v>
       </c>
       <c r="B579" s="2" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C579" s="2" t="s">
         <v>1050</v>
       </c>
-      <c r="C579" s="2" t="s">
-        <v>1051</v>
-      </c>
       <c r="D579" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E579" s="2" t="s">
-        <v>1560</v>
+        <v>1543</v>
       </c>
       <c r="F579" s="2" t="s">
         <v>9</v>
@@ -18623,16 +18600,16 @@
         <v>4</v>
       </c>
       <c r="B580" s="2" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C580" s="2" t="s">
         <v>1050</v>
-      </c>
-      <c r="C580" s="2" t="s">
-        <v>1051</v>
       </c>
       <c r="D580" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E580" s="2" t="s">
-        <v>1581</v>
+        <v>1557</v>
       </c>
       <c r="F580" s="2" t="s">
         <v>9</v>
@@ -18646,16 +18623,16 @@
         <v>4</v>
       </c>
       <c r="B581" s="2" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C581" s="2" t="s">
         <v>1052</v>
       </c>
-      <c r="C581" s="2" t="s">
-        <v>1053</v>
-      </c>
       <c r="D581" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E581" s="2" t="s">
-        <v>1295</v>
+        <v>1446</v>
       </c>
       <c r="F581" s="2" t="s">
         <v>9</v>
@@ -18669,16 +18646,16 @@
         <v>4</v>
       </c>
       <c r="B582" s="2" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C582" s="2" t="s">
         <v>1054</v>
       </c>
-      <c r="C582" s="2" t="s">
-        <v>1055</v>
-      </c>
       <c r="D582" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E582" s="2" t="s">
-        <v>1343</v>
+        <v>27</v>
       </c>
       <c r="F582" s="2" t="s">
         <v>9</v>
@@ -18692,10 +18669,10 @@
         <v>4</v>
       </c>
       <c r="B583" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C583" s="2" t="s">
         <v>1056</v>
-      </c>
-      <c r="C583" s="2" t="s">
-        <v>1057</v>
       </c>
       <c r="D583" s="2" t="s">
         <v>7</v>
@@ -18715,10 +18692,10 @@
         <v>4</v>
       </c>
       <c r="B584" s="2" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C584" s="2" t="s">
         <v>1058</v>
-      </c>
-      <c r="C584" s="2" t="s">
-        <v>1059</v>
       </c>
       <c r="D584" s="2" t="s">
         <v>7</v>
@@ -18738,10 +18715,10 @@
         <v>4</v>
       </c>
       <c r="B585" s="2" t="s">
-        <v>1477</v>
+        <v>1472</v>
       </c>
       <c r="C585" s="2" t="s">
-        <v>1478</v>
+        <v>1473</v>
       </c>
       <c r="D585" s="2" t="s">
         <v>7</v>
@@ -18761,10 +18738,10 @@
         <v>4</v>
       </c>
       <c r="B586" s="2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C586" s="2" t="s">
         <v>1060</v>
-      </c>
-      <c r="C586" s="2" t="s">
-        <v>1061</v>
       </c>
       <c r="D586" s="2" t="s">
         <v>7</v>
@@ -18784,16 +18761,16 @@
         <v>4</v>
       </c>
       <c r="B587" s="2" t="s">
-        <v>1479</v>
+        <v>1474</v>
       </c>
       <c r="C587" s="2" t="s">
-        <v>1480</v>
+        <v>1475</v>
       </c>
       <c r="D587" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E587" s="2" t="s">
-        <v>1474</v>
+        <v>1469</v>
       </c>
       <c r="F587" s="2" t="s">
         <v>9</v>
@@ -18807,10 +18784,10 @@
         <v>4</v>
       </c>
       <c r="B588" s="2" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C588" s="2" t="s">
         <v>1062</v>
-      </c>
-      <c r="C588" s="2" t="s">
-        <v>1063</v>
       </c>
       <c r="D588" s="2" t="s">
         <v>7</v>
@@ -18830,16 +18807,16 @@
         <v>4</v>
       </c>
       <c r="B589" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C589" s="2" t="s">
         <v>1065</v>
       </c>
-      <c r="C589" s="2" t="s">
-        <v>1066</v>
-      </c>
       <c r="D589" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E589" s="2" t="s">
-        <v>1617</v>
+        <v>1579</v>
       </c>
       <c r="F589" s="2" t="s">
         <v>9</v>
@@ -18853,10 +18830,10 @@
         <v>4</v>
       </c>
       <c r="B590" s="2" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C590" s="2" t="s">
         <v>1067</v>
-      </c>
-      <c r="C590" s="2" t="s">
-        <v>1068</v>
       </c>
       <c r="D590" s="2" t="s">
         <v>7</v>
@@ -18876,10 +18853,10 @@
         <v>4</v>
       </c>
       <c r="B591" s="2" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C591" s="2" t="s">
         <v>1069</v>
-      </c>
-      <c r="C591" s="2" t="s">
-        <v>1070</v>
       </c>
       <c r="D591" s="2" t="s">
         <v>40</v>
@@ -18899,10 +18876,10 @@
         <v>4</v>
       </c>
       <c r="B592" s="2" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C592" s="2" t="s">
         <v>1071</v>
-      </c>
-      <c r="C592" s="2" t="s">
-        <v>1072</v>
       </c>
       <c r="D592" s="2" t="s">
         <v>40</v>
@@ -18922,10 +18899,10 @@
         <v>4</v>
       </c>
       <c r="B593" s="2" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C593" s="2" t="s">
         <v>1073</v>
-      </c>
-      <c r="C593" s="2" t="s">
-        <v>1074</v>
       </c>
       <c r="D593" s="2" t="s">
         <v>40</v>
@@ -18948,7 +18925,7 @@
         <v>194</v>
       </c>
       <c r="C594" s="2" t="s">
-        <v>1481</v>
+        <v>1476</v>
       </c>
       <c r="D594" s="2" t="s">
         <v>40</v>
@@ -18971,7 +18948,7 @@
         <v>198</v>
       </c>
       <c r="C595" s="2" t="s">
-        <v>1481</v>
+        <v>1476</v>
       </c>
       <c r="D595" s="2" t="s">
         <v>40</v>
@@ -18994,7 +18971,7 @@
         <v>198</v>
       </c>
       <c r="C596" s="2" t="s">
-        <v>1481</v>
+        <v>1476</v>
       </c>
       <c r="D596" s="2" t="s">
         <v>19</v>
@@ -19017,13 +18994,13 @@
         <v>199</v>
       </c>
       <c r="C597" s="2" t="s">
-        <v>1481</v>
+        <v>1476</v>
       </c>
       <c r="D597" s="2" t="s">
         <v>40</v>
       </c>
       <c r="E597" s="2" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="F597" s="2" t="s">
         <v>172</v>
@@ -19040,13 +19017,13 @@
         <v>203</v>
       </c>
       <c r="C598" s="2" t="s">
-        <v>1481</v>
+        <v>1476</v>
       </c>
       <c r="D598" s="2" t="s">
         <v>40</v>
       </c>
       <c r="E598" s="2" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="F598" s="2" t="s">
         <v>172</v>
@@ -19063,7 +19040,7 @@
         <v>205</v>
       </c>
       <c r="C599" s="2" t="s">
-        <v>1481</v>
+        <v>1476</v>
       </c>
       <c r="D599" s="2" t="s">
         <v>40</v>
@@ -19086,13 +19063,13 @@
         <v>202</v>
       </c>
       <c r="C600" s="2" t="s">
-        <v>1481</v>
+        <v>1476</v>
       </c>
       <c r="D600" s="2" t="s">
         <v>40</v>
       </c>
       <c r="E600" s="2" t="s">
-        <v>134</v>
+        <v>37</v>
       </c>
       <c r="F600" s="2" t="s">
         <v>172</v>
@@ -19109,7 +19086,7 @@
         <v>202</v>
       </c>
       <c r="C601" s="2" t="s">
-        <v>1481</v>
+        <v>1476</v>
       </c>
       <c r="D601" s="2" t="s">
         <v>19</v>
@@ -19132,7 +19109,7 @@
         <v>204</v>
       </c>
       <c r="C602" s="2" t="s">
-        <v>1481</v>
+        <v>1476</v>
       </c>
       <c r="D602" s="2" t="s">
         <v>40</v>
@@ -19155,7 +19132,7 @@
         <v>196</v>
       </c>
       <c r="C603" s="2" t="s">
-        <v>1481</v>
+        <v>1476</v>
       </c>
       <c r="D603" s="2" t="s">
         <v>40</v>
@@ -19178,7 +19155,7 @@
         <v>197</v>
       </c>
       <c r="C604" s="2" t="s">
-        <v>1481</v>
+        <v>1476</v>
       </c>
       <c r="D604" s="2" t="s">
         <v>40</v>
@@ -19201,13 +19178,13 @@
         <v>201</v>
       </c>
       <c r="C605" s="2" t="s">
-        <v>1481</v>
+        <v>1476</v>
       </c>
       <c r="D605" s="2" t="s">
         <v>40</v>
       </c>
       <c r="E605" s="2" t="s">
-        <v>103</v>
+        <v>143</v>
       </c>
       <c r="F605" s="2" t="s">
         <v>172</v>
@@ -19224,7 +19201,7 @@
         <v>206</v>
       </c>
       <c r="C606" s="2" t="s">
-        <v>1481</v>
+        <v>1476</v>
       </c>
       <c r="D606" s="2" t="s">
         <v>40</v>
@@ -19247,7 +19224,7 @@
         <v>193</v>
       </c>
       <c r="C607" s="2" t="s">
-        <v>1481</v>
+        <v>1476</v>
       </c>
       <c r="D607" s="2" t="s">
         <v>40</v>
@@ -19267,16 +19244,16 @@
         <v>4</v>
       </c>
       <c r="B608" s="2" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C608" s="2" t="s">
         <v>1075</v>
       </c>
-      <c r="C608" s="2" t="s">
+      <c r="D608" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E608" s="2" t="s">
         <v>1076</v>
-      </c>
-      <c r="D608" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E608" s="2" t="s">
-        <v>1077</v>
       </c>
       <c r="F608" s="2" t="s">
         <v>9</v>
@@ -19290,10 +19267,10 @@
         <v>4</v>
       </c>
       <c r="B609" s="2" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C609" s="2" t="s">
         <v>1078</v>
-      </c>
-      <c r="C609" s="2" t="s">
-        <v>1079</v>
       </c>
       <c r="D609" s="2" t="s">
         <v>7</v>
@@ -19313,10 +19290,10 @@
         <v>4</v>
       </c>
       <c r="B610" s="2" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C610" s="2" t="s">
         <v>1080</v>
-      </c>
-      <c r="C610" s="2" t="s">
-        <v>1081</v>
       </c>
       <c r="D610" s="2" t="s">
         <v>7</v>
@@ -19336,10 +19313,10 @@
         <v>4</v>
       </c>
       <c r="B611" s="2" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C611" s="2" t="s">
         <v>1082</v>
-      </c>
-      <c r="C611" s="2" t="s">
-        <v>1083</v>
       </c>
       <c r="D611" s="2" t="s">
         <v>7</v>
@@ -19359,13 +19336,13 @@
         <v>4</v>
       </c>
       <c r="B612" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C612" s="2" t="s">
         <v>1084</v>
       </c>
-      <c r="C612" s="2" t="s">
-        <v>1085</v>
-      </c>
       <c r="D612" s="2" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="E612" s="2" t="s">
         <v>42</v>
@@ -19382,10 +19359,10 @@
         <v>4</v>
       </c>
       <c r="B613" s="2" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C613" s="2" t="s">
         <v>1086</v>
-      </c>
-      <c r="C613" s="2" t="s">
-        <v>1087</v>
       </c>
       <c r="D613" s="2" t="s">
         <v>7</v>
@@ -19405,10 +19382,10 @@
         <v>4</v>
       </c>
       <c r="B614" s="2" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C614" s="2" t="s">
         <v>1088</v>
-      </c>
-      <c r="C614" s="2" t="s">
-        <v>1089</v>
       </c>
       <c r="D614" s="2" t="s">
         <v>7</v>
@@ -19428,10 +19405,10 @@
         <v>4</v>
       </c>
       <c r="B615" s="2" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C615" s="2" t="s">
         <v>1090</v>
-      </c>
-      <c r="C615" s="2" t="s">
-        <v>1091</v>
       </c>
       <c r="D615" s="2" t="s">
         <v>7</v>
@@ -19451,10 +19428,10 @@
         <v>4</v>
       </c>
       <c r="B616" s="2" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C616" s="2" t="s">
         <v>1092</v>
-      </c>
-      <c r="C616" s="2" t="s">
-        <v>1093</v>
       </c>
       <c r="D616" s="2" t="s">
         <v>7</v>
@@ -19474,10 +19451,10 @@
         <v>4</v>
       </c>
       <c r="B617" s="2" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C617" s="2" t="s">
         <v>1094</v>
-      </c>
-      <c r="C617" s="2" t="s">
-        <v>1095</v>
       </c>
       <c r="D617" s="2" t="s">
         <v>7</v>
@@ -19497,10 +19474,10 @@
         <v>4</v>
       </c>
       <c r="B618" s="2" t="s">
+        <v>1415</v>
+      </c>
+      <c r="C618" s="2" t="s">
         <v>1416</v>
-      </c>
-      <c r="C618" s="2" t="s">
-        <v>1417</v>
       </c>
       <c r="D618" s="2" t="s">
         <v>7</v>
@@ -19520,10 +19497,10 @@
         <v>4</v>
       </c>
       <c r="B619" s="2" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C619" s="2" t="s">
         <v>1096</v>
-      </c>
-      <c r="C619" s="2" t="s">
-        <v>1097</v>
       </c>
       <c r="D619" s="2" t="s">
         <v>7</v>
@@ -19543,10 +19520,10 @@
         <v>4</v>
       </c>
       <c r="B620" s="2" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C620" s="2" t="s">
         <v>1098</v>
-      </c>
-      <c r="C620" s="2" t="s">
-        <v>1099</v>
       </c>
       <c r="D620" s="2" t="s">
         <v>7</v>
@@ -19566,10 +19543,10 @@
         <v>4</v>
       </c>
       <c r="B621" s="2" t="s">
+        <v>1438</v>
+      </c>
+      <c r="C621" s="2" t="s">
         <v>1439</v>
-      </c>
-      <c r="C621" s="2" t="s">
-        <v>1440</v>
       </c>
       <c r="D621" s="2" t="s">
         <v>7</v>
@@ -19589,10 +19566,10 @@
         <v>4</v>
       </c>
       <c r="B622" s="2" t="s">
-        <v>1531</v>
+        <v>1519</v>
       </c>
       <c r="C622" s="2" t="s">
-        <v>1532</v>
+        <v>1520</v>
       </c>
       <c r="D622" s="2" t="s">
         <v>7</v>
@@ -19612,10 +19589,10 @@
         <v>4</v>
       </c>
       <c r="B623" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C623" s="2" t="s">
         <v>1100</v>
-      </c>
-      <c r="C623" s="2" t="s">
-        <v>1101</v>
       </c>
       <c r="D623" s="2" t="s">
         <v>7</v>
@@ -19635,16 +19612,16 @@
         <v>4</v>
       </c>
       <c r="B624" s="2" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C624" s="2" t="s">
         <v>1102</v>
       </c>
-      <c r="C624" s="2" t="s">
+      <c r="D624" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E624" s="2" t="s">
         <v>1103</v>
-      </c>
-      <c r="D624" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E624" s="2" t="s">
-        <v>1104</v>
       </c>
       <c r="F624" s="2" t="s">
         <v>9</v>
@@ -19658,10 +19635,10 @@
         <v>4</v>
       </c>
       <c r="B625" s="2" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C625" s="2" t="s">
         <v>1105</v>
-      </c>
-      <c r="C625" s="2" t="s">
-        <v>1106</v>
       </c>
       <c r="D625" s="2" t="s">
         <v>7</v>
@@ -19681,16 +19658,16 @@
         <v>4</v>
       </c>
       <c r="B626" s="2" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C626" s="2" t="s">
         <v>1107</v>
       </c>
-      <c r="C626" s="2" t="s">
-        <v>1108</v>
-      </c>
       <c r="D626" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E626" s="2" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="F626" s="2" t="s">
         <v>9</v>
@@ -19704,10 +19681,10 @@
         <v>4</v>
       </c>
       <c r="B627" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C627" s="2" t="s">
         <v>1109</v>
-      </c>
-      <c r="C627" s="2" t="s">
-        <v>1110</v>
       </c>
       <c r="D627" s="2" t="s">
         <v>7</v>
@@ -19727,10 +19704,10 @@
         <v>4</v>
       </c>
       <c r="B628" s="2" t="s">
+        <v>1369</v>
+      </c>
+      <c r="C628" s="2" t="s">
         <v>1370</v>
-      </c>
-      <c r="C628" s="2" t="s">
-        <v>1371</v>
       </c>
       <c r="D628" s="2" t="s">
         <v>7</v>
@@ -19750,10 +19727,10 @@
         <v>4</v>
       </c>
       <c r="B629" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C629" s="2" t="s">
         <v>1111</v>
-      </c>
-      <c r="C629" s="2" t="s">
-        <v>1112</v>
       </c>
       <c r="D629" s="2" t="s">
         <v>7</v>
@@ -19773,16 +19750,16 @@
         <v>4</v>
       </c>
       <c r="B630" s="2" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C630" s="2" t="s">
         <v>1113</v>
       </c>
-      <c r="C630" s="2" t="s">
-        <v>1114</v>
-      </c>
       <c r="D630" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E630" s="2" t="s">
-        <v>1314</v>
+        <v>1563</v>
       </c>
       <c r="F630" s="2" t="s">
         <v>9</v>
@@ -19796,16 +19773,16 @@
         <v>4</v>
       </c>
       <c r="B631" s="2" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C631" s="2" t="s">
         <v>1115</v>
       </c>
-      <c r="C631" s="2" t="s">
-        <v>1116</v>
-      </c>
       <c r="D631" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E631" s="2" t="s">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="F631" s="2" t="s">
         <v>9</v>
@@ -19819,16 +19796,16 @@
         <v>4</v>
       </c>
       <c r="B632" s="2" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C632" s="2" t="s">
         <v>1115</v>
-      </c>
-      <c r="C632" s="2" t="s">
-        <v>1116</v>
       </c>
       <c r="D632" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E632" s="2" t="s">
-        <v>104</v>
+        <v>216</v>
       </c>
       <c r="F632" s="2" t="s">
         <v>9</v>
@@ -19842,10 +19819,10 @@
         <v>4</v>
       </c>
       <c r="B633" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C633" s="2" t="s">
         <v>1117</v>
-      </c>
-      <c r="C633" s="2" t="s">
-        <v>1118</v>
       </c>
       <c r="D633" s="2" t="s">
         <v>7</v>
@@ -19865,10 +19842,10 @@
         <v>4</v>
       </c>
       <c r="B634" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C634" s="2" t="s">
         <v>1119</v>
-      </c>
-      <c r="C634" s="2" t="s">
-        <v>1120</v>
       </c>
       <c r="D634" s="2" t="s">
         <v>7</v>
@@ -19888,10 +19865,10 @@
         <v>4</v>
       </c>
       <c r="B635" s="2" t="s">
+        <v>1371</v>
+      </c>
+      <c r="C635" s="2" t="s">
         <v>1372</v>
-      </c>
-      <c r="C635" s="2" t="s">
-        <v>1373</v>
       </c>
       <c r="D635" s="2" t="s">
         <v>7</v>
@@ -19911,16 +19888,16 @@
         <v>4</v>
       </c>
       <c r="B636" s="2" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C636" s="2" t="s">
         <v>1304</v>
       </c>
-      <c r="C636" s="2" t="s">
-        <v>1305</v>
-      </c>
       <c r="D636" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E636" s="2" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="F636" s="2" t="s">
         <v>9</v>
@@ -19934,10 +19911,10 @@
         <v>4</v>
       </c>
       <c r="B637" s="2" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C637" s="2" t="s">
         <v>1121</v>
-      </c>
-      <c r="C637" s="2" t="s">
-        <v>1122</v>
       </c>
       <c r="D637" s="2" t="s">
         <v>7</v>
@@ -19957,10 +19934,10 @@
         <v>4</v>
       </c>
       <c r="B638" s="2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C638" s="2" t="s">
         <v>1123</v>
-      </c>
-      <c r="C638" s="2" t="s">
-        <v>1124</v>
       </c>
       <c r="D638" s="2" t="s">
         <v>7</v>
@@ -19980,10 +19957,10 @@
         <v>4</v>
       </c>
       <c r="B639" s="2" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C639" s="2" t="s">
         <v>1125</v>
-      </c>
-      <c r="C639" s="2" t="s">
-        <v>1126</v>
       </c>
       <c r="D639" s="2" t="s">
         <v>7</v>
@@ -20003,10 +19980,10 @@
         <v>4</v>
       </c>
       <c r="B640" s="2" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C640" s="2" t="s">
         <v>1127</v>
-      </c>
-      <c r="C640" s="2" t="s">
-        <v>1128</v>
       </c>
       <c r="D640" s="2" t="s">
         <v>7</v>
@@ -20026,10 +20003,10 @@
         <v>4</v>
       </c>
       <c r="B641" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C641" s="2" t="s">
         <v>1129</v>
-      </c>
-      <c r="C641" s="2" t="s">
-        <v>1130</v>
       </c>
       <c r="D641" s="2" t="s">
         <v>7</v>
@@ -20049,10 +20026,10 @@
         <v>4</v>
       </c>
       <c r="B642" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C642" s="2" t="s">
         <v>1131</v>
-      </c>
-      <c r="C642" s="2" t="s">
-        <v>1132</v>
       </c>
       <c r="D642" s="2" t="s">
         <v>7</v>
@@ -20072,16 +20049,16 @@
         <v>4</v>
       </c>
       <c r="B643" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C643" s="2" t="s">
         <v>1133</v>
-      </c>
-      <c r="C643" s="2" t="s">
-        <v>1134</v>
       </c>
       <c r="D643" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E643" s="2" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="F643" s="2" t="s">
         <v>9</v>
@@ -20095,10 +20072,10 @@
         <v>4</v>
       </c>
       <c r="B644" s="2" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C644" s="2" t="s">
         <v>1135</v>
-      </c>
-      <c r="C644" s="2" t="s">
-        <v>1136</v>
       </c>
       <c r="D644" s="2" t="s">
         <v>40</v>
@@ -20118,10 +20095,10 @@
         <v>4</v>
       </c>
       <c r="B645" s="2" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C645" s="2" t="s">
         <v>1347</v>
-      </c>
-      <c r="C645" s="2" t="s">
-        <v>1348</v>
       </c>
       <c r="D645" s="2" t="s">
         <v>7</v>
@@ -20141,10 +20118,10 @@
         <v>4</v>
       </c>
       <c r="B646" s="2" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C646" s="2" t="s">
         <v>1137</v>
-      </c>
-      <c r="C646" s="2" t="s">
-        <v>1138</v>
       </c>
       <c r="D646" s="2" t="s">
         <v>7</v>
@@ -20164,10 +20141,10 @@
         <v>4</v>
       </c>
       <c r="B647" s="2" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C647" s="2" t="s">
         <v>1139</v>
-      </c>
-      <c r="C647" s="2" t="s">
-        <v>1140</v>
       </c>
       <c r="D647" s="2" t="s">
         <v>7</v>
@@ -20187,10 +20164,10 @@
         <v>4</v>
       </c>
       <c r="B648" s="2" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C648" s="2" t="s">
         <v>1141</v>
-      </c>
-      <c r="C648" s="2" t="s">
-        <v>1142</v>
       </c>
       <c r="D648" s="2" t="s">
         <v>7</v>
@@ -20210,10 +20187,10 @@
         <v>4</v>
       </c>
       <c r="B649" s="2" t="s">
-        <v>1521</v>
+        <v>1511</v>
       </c>
       <c r="C649" s="2" t="s">
-        <v>1522</v>
+        <v>1512</v>
       </c>
       <c r="D649" s="2" t="s">
         <v>7</v>
@@ -20233,10 +20210,10 @@
         <v>4</v>
       </c>
       <c r="B650" s="2" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C650" s="2" t="s">
         <v>1143</v>
-      </c>
-      <c r="C650" s="2" t="s">
-        <v>1144</v>
       </c>
       <c r="D650" s="2" t="s">
         <v>7</v>
@@ -20256,10 +20233,10 @@
         <v>4</v>
       </c>
       <c r="B651" s="2" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C651" s="2" t="s">
         <v>1145</v>
-      </c>
-      <c r="C651" s="2" t="s">
-        <v>1146</v>
       </c>
       <c r="D651" s="2" t="s">
         <v>7</v>
@@ -20279,10 +20256,10 @@
         <v>4</v>
       </c>
       <c r="B652" s="2" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C652" s="2" t="s">
         <v>1147</v>
-      </c>
-      <c r="C652" s="2" t="s">
-        <v>1148</v>
       </c>
       <c r="D652" s="2" t="s">
         <v>7</v>
@@ -20302,10 +20279,10 @@
         <v>4</v>
       </c>
       <c r="B653" s="2" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C653" s="2" t="s">
         <v>1353</v>
-      </c>
-      <c r="C653" s="2" t="s">
-        <v>1354</v>
       </c>
       <c r="D653" s="2" t="s">
         <v>7</v>
@@ -20325,10 +20302,10 @@
         <v>4</v>
       </c>
       <c r="B654" s="2" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C654" s="2" t="s">
         <v>1149</v>
-      </c>
-      <c r="C654" s="2" t="s">
-        <v>1150</v>
       </c>
       <c r="D654" s="2" t="s">
         <v>7</v>
@@ -20348,10 +20325,10 @@
         <v>4</v>
       </c>
       <c r="B655" s="2" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C655" s="2" t="s">
         <v>1151</v>
-      </c>
-      <c r="C655" s="2" t="s">
-        <v>1152</v>
       </c>
       <c r="D655" s="2" t="s">
         <v>7</v>
@@ -20371,16 +20348,16 @@
         <v>4</v>
       </c>
       <c r="B656" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C656" s="2" t="s">
         <v>1153</v>
       </c>
-      <c r="C656" s="2" t="s">
-        <v>1154</v>
-      </c>
       <c r="D656" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E656" s="2" t="s">
-        <v>1501</v>
+        <v>1493</v>
       </c>
       <c r="F656" s="2" t="s">
         <v>9</v>
@@ -20394,16 +20371,16 @@
         <v>4</v>
       </c>
       <c r="B657" s="2" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C657" s="2" t="s">
         <v>1155</v>
       </c>
-      <c r="C657" s="2" t="s">
-        <v>1156</v>
-      </c>
       <c r="D657" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E657" s="2" t="s">
-        <v>1582</v>
+        <v>1558</v>
       </c>
       <c r="F657" s="2" t="s">
         <v>9</v>
@@ -20417,10 +20394,10 @@
         <v>4</v>
       </c>
       <c r="B658" s="2" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C658" s="2" t="s">
         <v>1157</v>
-      </c>
-      <c r="C658" s="2" t="s">
-        <v>1158</v>
       </c>
       <c r="D658" s="2" t="s">
         <v>7</v>
@@ -20440,10 +20417,10 @@
         <v>4</v>
       </c>
       <c r="B659" s="2" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C659" s="2" t="s">
         <v>1159</v>
-      </c>
-      <c r="C659" s="2" t="s">
-        <v>1160</v>
       </c>
       <c r="D659" s="2" t="s">
         <v>7</v>
@@ -20463,16 +20440,16 @@
         <v>4</v>
       </c>
       <c r="B660" s="2" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C660" s="2" t="s">
         <v>1161</v>
       </c>
-      <c r="C660" s="2" t="s">
-        <v>1162</v>
-      </c>
       <c r="D660" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E660" s="2" t="s">
-        <v>1583</v>
+        <v>1559</v>
       </c>
       <c r="F660" s="2" t="s">
         <v>9</v>
@@ -20486,16 +20463,16 @@
         <v>4</v>
       </c>
       <c r="B661" s="2" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C661" s="2" t="s">
         <v>1163</v>
       </c>
-      <c r="C661" s="2" t="s">
+      <c r="D661" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E661" s="2" t="s">
         <v>1164</v>
-      </c>
-      <c r="D661" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E661" s="2" t="s">
-        <v>1165</v>
       </c>
       <c r="F661" s="2" t="s">
         <v>9</v>
@@ -20509,10 +20486,10 @@
         <v>4</v>
       </c>
       <c r="B662" s="2" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C662" s="2" t="s">
         <v>1166</v>
-      </c>
-      <c r="C662" s="2" t="s">
-        <v>1167</v>
       </c>
       <c r="D662" s="2" t="s">
         <v>7</v>
@@ -20532,16 +20509,16 @@
         <v>4</v>
       </c>
       <c r="B663" s="2" t="s">
+        <v>1440</v>
+      </c>
+      <c r="C663" s="2" t="s">
         <v>1441</v>
       </c>
-      <c r="C663" s="2" t="s">
-        <v>1442</v>
-      </c>
       <c r="D663" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E663" s="2" t="s">
-        <v>1574</v>
+        <v>1551</v>
       </c>
       <c r="F663" s="2" t="s">
         <v>9</v>
@@ -20555,16 +20532,16 @@
         <v>4</v>
       </c>
       <c r="B664" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C664" s="2" t="s">
         <v>1168</v>
       </c>
-      <c r="C664" s="2" t="s">
-        <v>1169</v>
-      </c>
       <c r="D664" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E664" s="2" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="F664" s="2" t="s">
         <v>9</v>
@@ -20578,10 +20555,10 @@
         <v>4</v>
       </c>
       <c r="B665" s="2" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C665" s="2" t="s">
         <v>1170</v>
-      </c>
-      <c r="C665" s="2" t="s">
-        <v>1171</v>
       </c>
       <c r="D665" s="2" t="s">
         <v>7</v>
@@ -20601,10 +20578,10 @@
         <v>4</v>
       </c>
       <c r="B666" s="2" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C666" s="2" t="s">
         <v>1170</v>
-      </c>
-      <c r="C666" s="2" t="s">
-        <v>1171</v>
       </c>
       <c r="D666" s="2" t="s">
         <v>19</v>
@@ -20624,10 +20601,10 @@
         <v>4</v>
       </c>
       <c r="B667" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C667" s="2" t="s">
         <v>1172</v>
-      </c>
-      <c r="C667" s="2" t="s">
-        <v>1173</v>
       </c>
       <c r="D667" s="2" t="s">
         <v>7</v>
@@ -20647,10 +20624,10 @@
         <v>4</v>
       </c>
       <c r="B668" s="2" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C668" s="2" t="s">
         <v>1174</v>
-      </c>
-      <c r="C668" s="2" t="s">
-        <v>1175</v>
       </c>
       <c r="D668" s="2" t="s">
         <v>7</v>
@@ -20670,10 +20647,10 @@
         <v>4</v>
       </c>
       <c r="B669" s="2" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C669" s="2" t="s">
         <v>1176</v>
-      </c>
-      <c r="C669" s="2" t="s">
-        <v>1177</v>
       </c>
       <c r="D669" s="2" t="s">
         <v>7</v>
@@ -20693,16 +20670,16 @@
         <v>4</v>
       </c>
       <c r="B670" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C670" s="2" t="s">
         <v>1178</v>
       </c>
-      <c r="C670" s="2" t="s">
-        <v>1179</v>
-      </c>
       <c r="D670" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E670" s="2" t="s">
-        <v>1618</v>
+        <v>1580</v>
       </c>
       <c r="F670" s="2" t="s">
         <v>9</v>
@@ -20716,10 +20693,10 @@
         <v>4</v>
       </c>
       <c r="B671" s="2" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C671" s="2" t="s">
         <v>1180</v>
-      </c>
-      <c r="C671" s="2" t="s">
-        <v>1181</v>
       </c>
       <c r="D671" s="2" t="s">
         <v>7</v>
@@ -20739,16 +20716,16 @@
         <v>4</v>
       </c>
       <c r="B672" s="2" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C672" s="2" t="s">
         <v>1182</v>
       </c>
-      <c r="C672" s="2" t="s">
-        <v>1183</v>
-      </c>
       <c r="D672" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E672" s="2" t="s">
-        <v>1584</v>
+        <v>1560</v>
       </c>
       <c r="F672" s="2" t="s">
         <v>9</v>
@@ -20762,16 +20739,16 @@
         <v>4</v>
       </c>
       <c r="B673" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C673" s="2" t="s">
         <v>1184</v>
       </c>
-      <c r="C673" s="2" t="s">
-        <v>1185</v>
-      </c>
       <c r="D673" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E673" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="F673" s="2" t="s">
         <v>9</v>
@@ -20785,10 +20762,10 @@
         <v>4</v>
       </c>
       <c r="B674" s="2" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C674" s="2" t="s">
         <v>1186</v>
-      </c>
-      <c r="C674" s="2" t="s">
-        <v>1187</v>
       </c>
       <c r="D674" s="2" t="s">
         <v>7</v>
@@ -20808,10 +20785,10 @@
         <v>4</v>
       </c>
       <c r="B675" s="2" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C675" s="2" t="s">
         <v>1188</v>
-      </c>
-      <c r="C675" s="2" t="s">
-        <v>1189</v>
       </c>
       <c r="D675" s="2" t="s">
         <v>7</v>
@@ -20831,16 +20808,16 @@
         <v>4</v>
       </c>
       <c r="B676" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C676" s="2" t="s">
         <v>1190</v>
       </c>
-      <c r="C676" s="2" t="s">
-        <v>1191</v>
-      </c>
       <c r="D676" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E676" s="2" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F676" s="2" t="s">
         <v>9</v>
@@ -20854,16 +20831,16 @@
         <v>4</v>
       </c>
       <c r="B677" s="2" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C677" s="2" t="s">
         <v>1192</v>
       </c>
-      <c r="C677" s="2" t="s">
+      <c r="D677" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E677" s="2" t="s">
         <v>1193</v>
-      </c>
-      <c r="D677" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E677" s="2" t="s">
-        <v>1194</v>
       </c>
       <c r="F677" s="2" t="s">
         <v>9</v>
@@ -20877,10 +20854,10 @@
         <v>4</v>
       </c>
       <c r="B678" s="2" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C678" s="2" t="s">
         <v>1195</v>
-      </c>
-      <c r="C678" s="2" t="s">
-        <v>1196</v>
       </c>
       <c r="D678" s="2" t="s">
         <v>7</v>
@@ -20900,16 +20877,16 @@
         <v>4</v>
       </c>
       <c r="B679" s="2" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C679" s="2" t="s">
         <v>1197</v>
       </c>
-      <c r="C679" s="2" t="s">
-        <v>1198</v>
-      </c>
       <c r="D679" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E679" s="2" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="F679" s="2" t="s">
         <v>9</v>
@@ -20923,10 +20900,10 @@
         <v>4</v>
       </c>
       <c r="B680" s="2" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C680" s="2" t="s">
         <v>1199</v>
-      </c>
-      <c r="C680" s="2" t="s">
-        <v>1200</v>
       </c>
       <c r="D680" s="2" t="s">
         <v>7</v>
@@ -20946,10 +20923,10 @@
         <v>4</v>
       </c>
       <c r="B681" s="2" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C681" s="2" t="s">
         <v>1201</v>
-      </c>
-      <c r="C681" s="2" t="s">
-        <v>1202</v>
       </c>
       <c r="D681" s="2" t="s">
         <v>7</v>
@@ -20969,10 +20946,10 @@
         <v>4</v>
       </c>
       <c r="B682" s="2" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C682" s="2" t="s">
         <v>1418</v>
-      </c>
-      <c r="C682" s="2" t="s">
-        <v>1419</v>
       </c>
       <c r="D682" s="2" t="s">
         <v>7</v>
@@ -20992,16 +20969,16 @@
         <v>4</v>
       </c>
       <c r="B683" s="2" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C683" s="2" t="s">
         <v>1203</v>
       </c>
-      <c r="C683" s="2" t="s">
+      <c r="D683" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E683" s="2" t="s">
         <v>1204</v>
-      </c>
-      <c r="D683" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E683" s="2" t="s">
-        <v>1205</v>
       </c>
       <c r="F683" s="2" t="s">
         <v>9</v>
@@ -21015,13 +20992,13 @@
         <v>4</v>
       </c>
       <c r="B684" s="2" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C684" s="2" t="s">
         <v>1206</v>
       </c>
-      <c r="C684" s="2" t="s">
+      <c r="D684" s="2" t="s">
         <v>1207</v>
-      </c>
-      <c r="D684" s="2" t="s">
-        <v>1208</v>
       </c>
       <c r="E684" s="2" t="s">
         <v>134</v>
@@ -21038,16 +21015,16 @@
         <v>4</v>
       </c>
       <c r="B685" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C685" s="2" t="s">
         <v>1209</v>
       </c>
-      <c r="C685" s="2" t="s">
-        <v>1210</v>
-      </c>
       <c r="D685" s="2" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="E685" s="2" t="s">
-        <v>1021</v>
+        <v>1342</v>
       </c>
       <c r="F685" s="2" t="s">
         <v>9</v>
@@ -21061,16 +21038,16 @@
         <v>4</v>
       </c>
       <c r="B686" s="2" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C686" s="2" t="s">
         <v>1211</v>
       </c>
-      <c r="C686" s="2" t="s">
-        <v>1212</v>
-      </c>
       <c r="D686" s="2" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="E686" s="2" t="s">
-        <v>1585</v>
+        <v>1561</v>
       </c>
       <c r="F686" s="2" t="s">
         <v>9</v>
@@ -21084,13 +21061,13 @@
         <v>4</v>
       </c>
       <c r="B687" s="2" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C687" s="2" t="s">
         <v>1213</v>
       </c>
-      <c r="C687" s="2" t="s">
-        <v>1214</v>
-      </c>
       <c r="D687" s="2" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="E687" s="2" t="s">
         <v>42</v>
@@ -21107,13 +21084,13 @@
         <v>4</v>
       </c>
       <c r="B688" s="2" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C688" s="2" t="s">
         <v>1215</v>
       </c>
-      <c r="C688" s="2" t="s">
-        <v>1216</v>
-      </c>
       <c r="D688" s="2" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="E688" s="2" t="s">
         <v>59</v>
@@ -21130,16 +21107,16 @@
         <v>4</v>
       </c>
       <c r="B689" s="2" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C689" s="2" t="s">
         <v>1217</v>
       </c>
-      <c r="C689" s="2" t="s">
-        <v>1218</v>
-      </c>
       <c r="D689" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E689" s="2" t="s">
-        <v>523</v>
+        <v>216</v>
       </c>
       <c r="F689" s="2" t="s">
         <v>9</v>
@@ -21153,10 +21130,10 @@
         <v>4</v>
       </c>
       <c r="B690" s="2" t="s">
+        <v>1338</v>
+      </c>
+      <c r="C690" s="2" t="s">
         <v>1339</v>
-      </c>
-      <c r="C690" s="2" t="s">
-        <v>1340</v>
       </c>
       <c r="D690" s="2" t="s">
         <v>7</v>
@@ -21176,10 +21153,10 @@
         <v>4</v>
       </c>
       <c r="B691" s="2" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C691" s="2" t="s">
         <v>1219</v>
-      </c>
-      <c r="C691" s="2" t="s">
-        <v>1220</v>
       </c>
       <c r="D691" s="2" t="s">
         <v>7</v>
@@ -21199,16 +21176,16 @@
         <v>4</v>
       </c>
       <c r="B692" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C692" s="2" t="s">
         <v>1221</v>
       </c>
-      <c r="C692" s="2" t="s">
-        <v>1222</v>
-      </c>
       <c r="D692" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E692" s="2" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="F692" s="2" t="s">
         <v>9</v>
@@ -21222,10 +21199,10 @@
         <v>4</v>
       </c>
       <c r="B693" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C693" s="2" t="s">
         <v>1221</v>
-      </c>
-      <c r="C693" s="2" t="s">
-        <v>1222</v>
       </c>
       <c r="D693" s="2" t="s">
         <v>19</v>
@@ -21245,16 +21222,16 @@
         <v>4</v>
       </c>
       <c r="B694" s="2" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C694" s="2" t="s">
         <v>1223</v>
       </c>
-      <c r="C694" s="2" t="s">
-        <v>1224</v>
-      </c>
       <c r="D694" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E694" s="2" t="s">
-        <v>1404</v>
+        <v>571</v>
       </c>
       <c r="F694" s="2" t="s">
         <v>9</v>
@@ -21268,16 +21245,16 @@
         <v>4</v>
       </c>
       <c r="B695" s="2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C695" s="2" t="s">
         <v>1225</v>
       </c>
-      <c r="C695" s="2" t="s">
-        <v>1226</v>
-      </c>
       <c r="D695" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E695" s="2" t="s">
-        <v>1619</v>
+        <v>1581</v>
       </c>
       <c r="F695" s="2" t="s">
         <v>9</v>
@@ -21291,16 +21268,16 @@
         <v>4</v>
       </c>
       <c r="B696" s="2" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C696" s="2" t="s">
         <v>1227</v>
       </c>
-      <c r="C696" s="2" t="s">
-        <v>1228</v>
-      </c>
       <c r="D696" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E696" s="2" t="s">
-        <v>1446</v>
+        <v>1612</v>
       </c>
       <c r="F696" s="2" t="s">
         <v>9</v>
@@ -21314,16 +21291,16 @@
         <v>4</v>
       </c>
       <c r="B697" s="2" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C697" s="2" t="s">
         <v>1229</v>
       </c>
-      <c r="C697" s="2" t="s">
-        <v>1230</v>
-      </c>
       <c r="D697" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E697" s="2" t="s">
-        <v>1620</v>
+        <v>1582</v>
       </c>
       <c r="F697" s="2" t="s">
         <v>9</v>
@@ -21337,16 +21314,16 @@
         <v>4</v>
       </c>
       <c r="B698" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C698" s="2" t="s">
         <v>1231</v>
       </c>
-      <c r="C698" s="2" t="s">
-        <v>1232</v>
-      </c>
       <c r="D698" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E698" s="2" t="s">
-        <v>1621</v>
+        <v>1583</v>
       </c>
       <c r="F698" s="2" t="s">
         <v>100</v>
@@ -21360,16 +21337,16 @@
         <v>4</v>
       </c>
       <c r="B699" s="2" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C699" s="2" t="s">
         <v>1233</v>
       </c>
-      <c r="C699" s="2" t="s">
-        <v>1234</v>
-      </c>
       <c r="D699" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E699" s="2" t="s">
-        <v>195</v>
+        <v>292</v>
       </c>
       <c r="F699" s="2" t="s">
         <v>9</v>
@@ -21383,16 +21360,16 @@
         <v>4</v>
       </c>
       <c r="B700" s="2" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C700" s="2" t="s">
         <v>1235</v>
       </c>
-      <c r="C700" s="2" t="s">
-        <v>1236</v>
-      </c>
       <c r="D700" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E700" s="2" t="s">
-        <v>1537</v>
+        <v>1525</v>
       </c>
       <c r="F700" s="2" t="s">
         <v>9</v>
@@ -21406,16 +21383,16 @@
         <v>4</v>
       </c>
       <c r="B701" s="2" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C701" s="2" t="s">
         <v>1237</v>
       </c>
-      <c r="C701" s="2" t="s">
+      <c r="D701" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E701" s="2" t="s">
         <v>1238</v>
-      </c>
-      <c r="D701" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E701" s="2" t="s">
-        <v>1239</v>
       </c>
       <c r="F701" s="2" t="s">
         <v>9</v>
@@ -21429,16 +21406,16 @@
         <v>4</v>
       </c>
       <c r="B702" s="2" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C702" s="2" t="s">
         <v>1374</v>
       </c>
-      <c r="C702" s="2" t="s">
-        <v>1375</v>
-      </c>
       <c r="D702" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E702" s="2" t="s">
-        <v>1482</v>
+        <v>1490</v>
       </c>
       <c r="F702" s="2" t="s">
         <v>100</v>
@@ -21452,10 +21429,10 @@
         <v>4</v>
       </c>
       <c r="B703" s="2" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C703" s="2" t="s">
         <v>1240</v>
-      </c>
-      <c r="C703" s="2" t="s">
-        <v>1241</v>
       </c>
       <c r="D703" s="2" t="s">
         <v>7</v>
@@ -21475,10 +21452,10 @@
         <v>4</v>
       </c>
       <c r="B704" s="2" t="s">
+        <v>1442</v>
+      </c>
+      <c r="C704" s="2" t="s">
         <v>1443</v>
-      </c>
-      <c r="C704" s="2" t="s">
-        <v>1444</v>
       </c>
       <c r="D704" s="2" t="s">
         <v>7</v>
@@ -21498,10 +21475,10 @@
         <v>4</v>
       </c>
       <c r="B705" s="2" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C705" s="2" t="s">
         <v>1242</v>
-      </c>
-      <c r="C705" s="2" t="s">
-        <v>1243</v>
       </c>
       <c r="D705" s="2" t="s">
         <v>7</v>
@@ -21521,16 +21498,16 @@
         <v>4</v>
       </c>
       <c r="B706" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C706" s="2" t="s">
         <v>1244</v>
       </c>
-      <c r="C706" s="2" t="s">
-        <v>1245</v>
-      </c>
       <c r="D706" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E706" s="2" t="s">
-        <v>1104</v>
+        <v>86</v>
       </c>
       <c r="F706" s="2" t="s">
         <v>9</v>
@@ -21544,16 +21521,16 @@
         <v>4</v>
       </c>
       <c r="B707" s="2" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C707" s="2" t="s">
         <v>1246</v>
       </c>
-      <c r="C707" s="2" t="s">
-        <v>1247</v>
-      </c>
       <c r="D707" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E707" s="2" t="s">
-        <v>1517</v>
+        <v>1507</v>
       </c>
       <c r="F707" s="2" t="s">
         <v>265</v>
@@ -21567,16 +21544,16 @@
         <v>4</v>
       </c>
       <c r="B708" s="2" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C708" s="2" t="s">
         <v>1248</v>
       </c>
-      <c r="C708" s="2" t="s">
+      <c r="D708" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E708" s="2" t="s">
         <v>1249</v>
-      </c>
-      <c r="D708" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E708" s="2" t="s">
-        <v>1250</v>
       </c>
       <c r="F708" s="2" t="s">
         <v>265</v>
@@ -21590,10 +21567,10 @@
         <v>4</v>
       </c>
       <c r="B709" s="2" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C709" s="2" t="s">
         <v>1251</v>
-      </c>
-      <c r="C709" s="2" t="s">
-        <v>1252</v>
       </c>
       <c r="D709" s="2" t="s">
         <v>7</v>
@@ -21613,16 +21590,16 @@
         <v>4</v>
       </c>
       <c r="B710" s="2" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C710" s="2" t="s">
         <v>1253</v>
       </c>
-      <c r="C710" s="2" t="s">
-        <v>1254</v>
-      </c>
       <c r="D710" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E710" s="2" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="F710" s="2" t="s">
         <v>100</v>
@@ -21636,10 +21613,10 @@
         <v>4</v>
       </c>
       <c r="B711" s="2" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C711" s="2" t="s">
         <v>1256</v>
-      </c>
-      <c r="C711" s="2" t="s">
-        <v>1257</v>
       </c>
       <c r="D711" s="2" t="s">
         <v>7</v>
@@ -21659,16 +21636,16 @@
         <v>4</v>
       </c>
       <c r="B712" s="2" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C712" s="2" t="s">
         <v>1381</v>
       </c>
-      <c r="C712" s="2" t="s">
-        <v>1382</v>
-      </c>
       <c r="D712" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E712" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="F712" s="2" t="s">
         <v>9</v>
@@ -21682,10 +21659,10 @@
         <v>4</v>
       </c>
       <c r="B713" s="2" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C713" s="2" t="s">
         <v>1258</v>
-      </c>
-      <c r="C713" s="2" t="s">
-        <v>1259</v>
       </c>
       <c r="D713" s="2" t="s">
         <v>7</v>
@@ -21705,10 +21682,10 @@
         <v>4</v>
       </c>
       <c r="B714" s="2" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C714" s="2" t="s">
         <v>1260</v>
-      </c>
-      <c r="C714" s="2" t="s">
-        <v>1261</v>
       </c>
       <c r="D714" s="2" t="s">
         <v>7</v>
@@ -21728,10 +21705,10 @@
         <v>4</v>
       </c>
       <c r="B715" s="2" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C715" s="2" t="s">
         <v>1262</v>
-      </c>
-      <c r="C715" s="2" t="s">
-        <v>1263</v>
       </c>
       <c r="D715" s="2" t="s">
         <v>7</v>
@@ -21751,16 +21728,16 @@
         <v>4</v>
       </c>
       <c r="B716" s="2" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C716" s="2" t="s">
         <v>1262</v>
-      </c>
-      <c r="C716" s="2" t="s">
-        <v>1263</v>
       </c>
       <c r="D716" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E716" s="2" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="F716" s="2" t="s">
         <v>9</v>
@@ -21774,10 +21751,10 @@
         <v>4</v>
       </c>
       <c r="B717" s="2" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C717" s="2" t="s">
         <v>1420</v>
-      </c>
-      <c r="C717" s="2" t="s">
-        <v>1421</v>
       </c>
       <c r="D717" s="2" t="s">
         <v>7</v>
@@ -21797,10 +21774,10 @@
         <v>4</v>
       </c>
       <c r="B718" s="2" t="s">
+        <v>1421</v>
+      </c>
+      <c r="C718" s="2" t="s">
         <v>1422</v>
-      </c>
-      <c r="C718" s="2" t="s">
-        <v>1423</v>
       </c>
       <c r="D718" s="2" t="s">
         <v>7</v>
@@ -21820,10 +21797,10 @@
         <v>4</v>
       </c>
       <c r="B719" s="2" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C719" s="2" t="s">
         <v>1265</v>
-      </c>
-      <c r="C719" s="2" t="s">
-        <v>1266</v>
       </c>
       <c r="D719" s="2" t="s">
         <v>7</v>
@@ -21843,10 +21820,10 @@
         <v>4</v>
       </c>
       <c r="B720" s="2" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C720" s="2" t="s">
         <v>1267</v>
-      </c>
-      <c r="C720" s="2" t="s">
-        <v>1268</v>
       </c>
       <c r="D720" s="2" t="s">
         <v>7</v>
@@ -21866,16 +21843,16 @@
         <v>4</v>
       </c>
       <c r="B721" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C721" s="2" t="s">
         <v>1269</v>
       </c>
-      <c r="C721" s="2" t="s">
-        <v>1270</v>
-      </c>
       <c r="D721" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E721" s="2" t="s">
-        <v>1495</v>
+        <v>1489</v>
       </c>
       <c r="F721" s="2" t="s">
         <v>9</v>
@@ -21889,16 +21866,16 @@
         <v>4</v>
       </c>
       <c r="B722" s="2" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C722" s="2" t="s">
         <v>1271</v>
       </c>
-      <c r="C722" s="2" t="s">
-        <v>1272</v>
-      </c>
       <c r="D722" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E722" s="2" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="F722" s="2" t="s">
         <v>9</v>
@@ -21912,10 +21889,10 @@
         <v>4</v>
       </c>
       <c r="B723" s="2" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C723" s="2" t="s">
         <v>1273</v>
-      </c>
-      <c r="C723" s="2" t="s">
-        <v>1274</v>
       </c>
       <c r="D723" s="2" t="s">
         <v>7</v>
@@ -21935,16 +21912,16 @@
         <v>4</v>
       </c>
       <c r="B724" s="2" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C724" s="2" t="s">
         <v>1275</v>
       </c>
-      <c r="C724" s="2" t="s">
-        <v>1276</v>
-      </c>
       <c r="D724" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E724" s="2" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="F724" s="2" t="s">
         <v>9</v>
@@ -21958,10 +21935,10 @@
         <v>4</v>
       </c>
       <c r="B725" s="2" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C725" s="2" t="s">
         <v>1277</v>
-      </c>
-      <c r="C725" s="2" t="s">
-        <v>1278</v>
       </c>
       <c r="D725" s="2" t="s">
         <v>7</v>
@@ -21981,10 +21958,10 @@
         <v>4</v>
       </c>
       <c r="B726" s="2" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C726" s="2" t="s">
         <v>1277</v>
-      </c>
-      <c r="C726" s="2" t="s">
-        <v>1278</v>
       </c>
       <c r="D726" s="2" t="s">
         <v>19</v>
@@ -22004,10 +21981,10 @@
         <v>4</v>
       </c>
       <c r="B727" s="2" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C727" s="2" t="s">
         <v>1279</v>
-      </c>
-      <c r="C727" s="2" t="s">
-        <v>1280</v>
       </c>
       <c r="D727" s="2" t="s">
         <v>7</v>
@@ -22027,10 +22004,10 @@
         <v>4</v>
       </c>
       <c r="B728" s="2" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C728" s="2" t="s">
         <v>1279</v>
-      </c>
-      <c r="C728" s="2" t="s">
-        <v>1280</v>
       </c>
       <c r="D728" s="2" t="s">
         <v>19</v>
@@ -22050,10 +22027,10 @@
         <v>4</v>
       </c>
       <c r="B729" s="2" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C729" s="2" t="s">
         <v>1281</v>
-      </c>
-      <c r="C729" s="2" t="s">
-        <v>1282</v>
       </c>
       <c r="D729" s="2" t="s">
         <v>7</v>
@@ -22073,10 +22050,10 @@
         <v>4</v>
       </c>
       <c r="B730" s="2" t="s">
+        <v>1334</v>
+      </c>
+      <c r="C730" s="2" t="s">
         <v>1335</v>
-      </c>
-      <c r="C730" s="2" t="s">
-        <v>1336</v>
       </c>
       <c r="D730" s="2" t="s">
         <v>7</v>
@@ -22096,10 +22073,10 @@
         <v>4</v>
       </c>
       <c r="B731" s="2" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C731" s="2" t="s">
         <v>1283</v>
-      </c>
-      <c r="C731" s="2" t="s">
-        <v>1284</v>
       </c>
       <c r="D731" s="2" t="s">
         <v>7</v>
@@ -22119,10 +22096,10 @@
         <v>4</v>
       </c>
       <c r="B732" s="2" t="s">
+        <v>1404</v>
+      </c>
+      <c r="C732" s="2" t="s">
         <v>1405</v>
-      </c>
-      <c r="C732" s="2" t="s">
-        <v>1406</v>
       </c>
       <c r="D732" s="2" t="s">
         <v>7</v>
@@ -22142,16 +22119,16 @@
         <v>4</v>
       </c>
       <c r="B733" s="2" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C733" s="2" t="s">
         <v>1285</v>
       </c>
-      <c r="C733" s="2" t="s">
-        <v>1286</v>
-      </c>
       <c r="D733" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E733" s="2" t="s">
-        <v>1064</v>
+        <v>86</v>
       </c>
       <c r="F733" s="2" t="s">
         <v>9</v>
@@ -22197,7 +22174,7 @@
         <v>0</v>
       </c>
       <c r="E735" s="2" t="s">
-        <v>1586</v>
+        <v>1613</v>
       </c>
       <c r="F735" s="2" t="s">
         <v>528</v>
@@ -22220,7 +22197,7 @@
         <v>0</v>
       </c>
       <c r="E736" s="2" t="s">
-        <v>1622</v>
+        <v>1584</v>
       </c>
       <c r="F736" s="2" t="s">
         <v>428</v>
@@ -22243,7 +22220,7 @@
         <v>0</v>
       </c>
       <c r="E737" s="2" t="s">
-        <v>1623</v>
+        <v>1614</v>
       </c>
       <c r="F737" s="2" t="s">
         <v>265</v>
@@ -22266,13 +22243,13 @@
         <v>0</v>
       </c>
       <c r="E738" s="2" t="s">
-        <v>1624</v>
+        <v>1615</v>
       </c>
       <c r="F738" s="2" t="s">
         <v>172</v>
       </c>
       <c r="G738" s="2" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="739" spans="1:7" x14ac:dyDescent="0.2">
@@ -22289,7 +22266,7 @@
         <v>0</v>
       </c>
       <c r="E739" s="2" t="s">
-        <v>1625</v>
+        <v>1616</v>
       </c>
       <c r="F739" s="2" t="s">
         <v>100</v>
@@ -22312,7 +22289,7 @@
         <v>0</v>
       </c>
       <c r="E740" s="2" t="s">
-        <v>1626</v>
+        <v>1617</v>
       </c>
       <c r="F740" s="2" t="s">
         <v>9</v>
@@ -22335,7 +22312,7 @@
         <v>0</v>
       </c>
       <c r="E741" s="2" t="s">
-        <v>1587</v>
+        <v>1562</v>
       </c>
       <c r="F741" s="2" t="s">
         <v>9</v>

--- a/dados-catalago-pcm-interno/relatorio.xlsx
+++ b/dados-catalago-pcm-interno/relatorio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amaggicombr-my.sharepoint.com/personal/hiago_andre_amaggi_com_br/Documents/Área de Trabalho/codigos/catalogoPecasPCM/dados-catalago-pcm-interno/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="64" documentId="11_FD86FE4AC4094E4AB971B8A5A011EE841C83CB4A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7582CB10-7780-4BA6-BD4C-BE6677DADB7C}"/>
+  <xr:revisionPtr revIDLastSave="68" documentId="11_FD86FE4AC4094E4AB971B8A5A011EE841C83CB4A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6E0419C-BC24-4978-8425-39581DB8E83B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5187" uniqueCount="1621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5186" uniqueCount="1621">
   <si>
     <t>Cen.</t>
   </si>
@@ -5334,8 +5334,8 @@
       <c r="D2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>11</v>
+      <c r="E2" s="2">
+        <v>50</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>12</v>

--- a/dados-catalago-pcm-interno/relatorio.xlsx
+++ b/dados-catalago-pcm-interno/relatorio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amaggicombr-my.sharepoint.com/personal/hiago_andre_amaggi_com_br/Documents/Área de Trabalho/codigos/catalogoPecasPCM/dados-catalago-pcm-interno/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="94" documentId="11_FD86FE4AC4094E4AB971B8A5A011EE841C83CB4A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{869E974E-B2AC-49C0-9F31-0FD11043F8F9}"/>
+  <xr:revisionPtr revIDLastSave="96" documentId="11_FD86FE4AC4094E4AB971B8A5A011EE841C83CB4A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CC4A115-0099-4438-A400-337CC54FB6B3}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5184" uniqueCount="1621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5184" uniqueCount="1622">
   <si>
     <t>Cen.</t>
   </si>
@@ -1736,12 +1736,6 @@
     <t>DIFUSOR SCANIA: 2184703</t>
   </si>
   <si>
-    <t>1040017773</t>
-  </si>
-  <si>
-    <t>DIFUSOR SCANIA: 2184704</t>
-  </si>
-  <si>
     <t>1010028655</t>
   </si>
   <si>
@@ -4544,9 +4538,6 @@
     <t>191</t>
   </si>
   <si>
-    <t>225</t>
-  </si>
-  <si>
     <t>223</t>
   </si>
   <si>
@@ -4607,9 +4598,6 @@
     <t>106,100</t>
   </si>
   <si>
-    <t>355</t>
-  </si>
-  <si>
     <t>145</t>
   </si>
   <si>
@@ -4721,15 +4709,9 @@
     <t>210</t>
   </si>
   <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>600</t>
   </si>
   <si>
-    <t>67</t>
-  </si>
-  <si>
     <t>147</t>
   </si>
   <si>
@@ -4760,9 +4742,6 @@
     <t>248</t>
   </si>
   <si>
-    <t>468</t>
-  </si>
-  <si>
     <t>348</t>
   </si>
   <si>
@@ -4772,9 +4751,6 @@
     <t>365</t>
   </si>
   <si>
-    <t>807</t>
-  </si>
-  <si>
     <t>57</t>
   </si>
   <si>
@@ -4814,18 +4790,12 @@
     <t>99</t>
   </si>
   <si>
-    <t>289</t>
-  </si>
-  <si>
     <t>562</t>
   </si>
   <si>
     <t>354</t>
   </si>
   <si>
-    <t>1.460</t>
-  </si>
-  <si>
     <t>284</t>
   </si>
   <si>
@@ -4850,12 +4820,6 @@
     <t>103</t>
   </si>
   <si>
-    <t>118</t>
-  </si>
-  <si>
-    <t>830</t>
-  </si>
-  <si>
     <t>188</t>
   </si>
   <si>
@@ -4880,25 +4844,64 @@
     <t>360</t>
   </si>
   <si>
-    <t>91</t>
-  </si>
-  <si>
     <t>950</t>
   </si>
   <si>
     <t>417</t>
   </si>
   <si>
-    <t>247.136,910</t>
-  </si>
-  <si>
-    <t>1.383</t>
-  </si>
-  <si>
-    <t>8.326</t>
-  </si>
-  <si>
-    <t>112.617</t>
+    <t>452</t>
+  </si>
+  <si>
+    <t>797</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>1.420</t>
+  </si>
+  <si>
+    <t>586</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>1030000489</t>
+  </si>
+  <si>
+    <t>PNEU 295/80 R22.5 BANDA VL110LA REC</t>
+  </si>
+  <si>
+    <t>1030000490</t>
+  </si>
+  <si>
+    <t>PNEU 295/80 R22.5 BANDA VL130 REC</t>
+  </si>
+  <si>
+    <t>814</t>
+  </si>
+  <si>
+    <t>299</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>247.096,910</t>
+  </si>
+  <si>
+    <t>1.380</t>
+  </si>
+  <si>
+    <t>8.322</t>
+  </si>
+  <si>
+    <t>112.548</t>
   </si>
 </sst>
 </file>
@@ -5336,7 +5339,7 @@
         <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>11</v>
+        <v>703</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>12</v>
@@ -5359,7 +5362,7 @@
         <v>10</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1569</v>
+        <v>1563</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>12</v>
@@ -5603,10 +5606,10 @@
         <v>7</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>138</v>
@@ -5728,7 +5731,7 @@
         <v>10</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>1570</v>
+        <v>1564</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>12</v>
@@ -5811,10 +5814,10 @@
         <v>7</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>10</v>
@@ -5843,7 +5846,7 @@
         <v>10</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>12</v>
@@ -6004,7 +6007,7 @@
         <v>10</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>92</v>
+        <v>837</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>12</v>
@@ -6027,7 +6030,7 @@
         <v>10</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>12</v>
@@ -6050,7 +6053,7 @@
         <v>10</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>12</v>
@@ -6073,7 +6076,7 @@
         <v>10</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>1475</v>
+        <v>1473</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>12</v>
@@ -6096,7 +6099,7 @@
         <v>10</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>12</v>
@@ -6119,7 +6122,7 @@
         <v>10</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>1571</v>
+        <v>1565</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>12</v>
@@ -6142,7 +6145,7 @@
         <v>10</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>1572</v>
+        <v>1566</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>12</v>
@@ -6165,7 +6168,7 @@
         <v>10</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>11</v>
+        <v>703</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>12</v>
@@ -6211,7 +6214,7 @@
         <v>10</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>12</v>
@@ -6280,7 +6283,7 @@
         <v>10</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>1573</v>
+        <v>1567</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>12</v>
@@ -6303,7 +6306,7 @@
         <v>10</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>1574</v>
+        <v>1604</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>12</v>
@@ -6349,7 +6352,7 @@
         <v>10</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>1575</v>
+        <v>1568</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>12</v>
@@ -6372,7 +6375,7 @@
         <v>10</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>1576</v>
+        <v>1569</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>12</v>
@@ -6395,7 +6398,7 @@
         <v>10</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>1577</v>
+        <v>1570</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>12</v>
@@ -6464,7 +6467,7 @@
         <v>10</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>1578</v>
+        <v>1605</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>12</v>
@@ -6800,10 +6803,10 @@
         <v>7</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1477</v>
+        <v>1475</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>10</v>
@@ -6924,7 +6927,7 @@
         <v>22</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>1475</v>
+        <v>1473</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>12</v>
@@ -7858,10 +7861,10 @@
         <v>7</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>1513</v>
+        <v>1510</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>1514</v>
+        <v>1511</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>10</v>
@@ -7936,7 +7939,7 @@
         <v>10</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>1542</v>
+        <v>1538</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>12</v>
@@ -7959,7 +7962,7 @@
         <v>10</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>12</v>
@@ -8005,7 +8008,7 @@
         <v>10</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>1543</v>
+        <v>1539</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>12</v>
@@ -8028,7 +8031,7 @@
         <v>22</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>1544</v>
+        <v>1540</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>12</v>
@@ -8097,7 +8100,7 @@
         <v>10</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>12</v>
@@ -8350,7 +8353,7 @@
         <v>10</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>109</v>
+        <v>164</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>12</v>
@@ -8557,7 +8560,7 @@
         <v>10</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="F142" s="2" t="s">
         <v>12</v>
@@ -8856,7 +8859,7 @@
         <v>299</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
       <c r="F155" s="2" t="s">
         <v>12</v>
@@ -9178,7 +9181,7 @@
         <v>299</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>1545</v>
+        <v>1541</v>
       </c>
       <c r="F169" s="2" t="s">
         <v>12</v>
@@ -9201,7 +9204,7 @@
         <v>299</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
       <c r="F170" s="2" t="s">
         <v>12</v>
@@ -9247,7 +9250,7 @@
         <v>299</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>1516</v>
+        <v>1513</v>
       </c>
       <c r="F172" s="2" t="s">
         <v>12</v>
@@ -9293,7 +9296,7 @@
         <v>299</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>1579</v>
+        <v>1571</v>
       </c>
       <c r="F174" s="2" t="s">
         <v>12</v>
@@ -9500,7 +9503,7 @@
         <v>299</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>1580</v>
+        <v>1572</v>
       </c>
       <c r="F183" s="2" t="s">
         <v>12</v>
@@ -9583,10 +9586,10 @@
         <v>7</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>1504</v>
+        <v>1501</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>1505</v>
+        <v>1502</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>10</v>
@@ -9684,7 +9687,7 @@
         <v>10</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>1547</v>
+        <v>1543</v>
       </c>
       <c r="F191" s="2" t="s">
         <v>12</v>
@@ -9730,7 +9733,7 @@
         <v>138</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="F193" s="2" t="s">
         <v>12</v>
@@ -10029,7 +10032,7 @@
         <v>10</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>1581</v>
+        <v>1573</v>
       </c>
       <c r="F206" s="2" t="s">
         <v>12</v>
@@ -10052,7 +10055,7 @@
         <v>10</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>1582</v>
+        <v>1574</v>
       </c>
       <c r="F207" s="2" t="s">
         <v>12</v>
@@ -10282,7 +10285,7 @@
         <v>10</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="F217" s="2" t="s">
         <v>12</v>
@@ -10443,7 +10446,7 @@
         <v>10</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="F224" s="2" t="s">
         <v>12</v>
@@ -10466,7 +10469,7 @@
         <v>484</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>1506</v>
+        <v>1503</v>
       </c>
       <c r="F225" s="2" t="s">
         <v>40</v>
@@ -10627,7 +10630,7 @@
         <v>10</v>
       </c>
       <c r="E232" s="2" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="F232" s="2" t="s">
         <v>12</v>
@@ -10650,7 +10653,7 @@
         <v>10</v>
       </c>
       <c r="E233" s="2" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="F233" s="2" t="s">
         <v>12</v>
@@ -10857,7 +10860,7 @@
         <v>10</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>551</v>
+        <v>427</v>
       </c>
       <c r="F242" s="2" t="s">
         <v>12</v>
@@ -10903,7 +10906,7 @@
         <v>10</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>1467</v>
+        <v>1465</v>
       </c>
       <c r="F244" s="2" t="s">
         <v>12</v>
@@ -10949,7 +10952,7 @@
         <v>10</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="F246" s="2" t="s">
         <v>12</v>
@@ -11179,7 +11182,7 @@
         <v>10</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="F256" s="2" t="s">
         <v>12</v>
@@ -11225,7 +11228,7 @@
         <v>35</v>
       </c>
       <c r="E258" s="2" t="s">
-        <v>26</v>
+        <v>1606</v>
       </c>
       <c r="F258" s="2" t="s">
         <v>12</v>
@@ -11248,7 +11251,7 @@
         <v>10</v>
       </c>
       <c r="E259" s="2" t="s">
-        <v>1475</v>
+        <v>1473</v>
       </c>
       <c r="F259" s="2" t="s">
         <v>12</v>
@@ -11271,7 +11274,7 @@
         <v>10</v>
       </c>
       <c r="E260" s="2" t="s">
-        <v>1583</v>
+        <v>1575</v>
       </c>
       <c r="F260" s="2" t="s">
         <v>12</v>
@@ -11294,7 +11297,7 @@
         <v>22</v>
       </c>
       <c r="E261" s="2" t="s">
-        <v>1584</v>
+        <v>1576</v>
       </c>
       <c r="F261" s="2" t="s">
         <v>12</v>
@@ -11363,7 +11366,7 @@
         <v>10</v>
       </c>
       <c r="E264" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F264" s="2" t="s">
         <v>12</v>
@@ -11386,7 +11389,7 @@
         <v>10</v>
       </c>
       <c r="E265" s="2" t="s">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="F265" s="2" t="s">
         <v>12</v>
@@ -11409,7 +11412,7 @@
         <v>10</v>
       </c>
       <c r="E266" s="2" t="s">
-        <v>45</v>
+        <v>1545</v>
       </c>
       <c r="F266" s="2" t="s">
         <v>12</v>
@@ -11432,7 +11435,7 @@
         <v>10</v>
       </c>
       <c r="E267" s="2" t="s">
-        <v>1549</v>
+        <v>54</v>
       </c>
       <c r="F267" s="2" t="s">
         <v>12</v>
@@ -11455,7 +11458,7 @@
         <v>10</v>
       </c>
       <c r="E268" s="2" t="s">
-        <v>54</v>
+        <v>254</v>
       </c>
       <c r="F268" s="2" t="s">
         <v>12</v>
@@ -11478,7 +11481,7 @@
         <v>10</v>
       </c>
       <c r="E269" s="2" t="s">
-        <v>254</v>
+        <v>72</v>
       </c>
       <c r="F269" s="2" t="s">
         <v>12</v>
@@ -11501,7 +11504,7 @@
         <v>10</v>
       </c>
       <c r="E270" s="2" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="F270" s="2" t="s">
         <v>12</v>
@@ -11524,7 +11527,7 @@
         <v>10</v>
       </c>
       <c r="E271" s="2" t="s">
-        <v>62</v>
+        <v>367</v>
       </c>
       <c r="F271" s="2" t="s">
         <v>12</v>
@@ -11547,7 +11550,7 @@
         <v>10</v>
       </c>
       <c r="E272" s="2" t="s">
-        <v>367</v>
+        <v>247</v>
       </c>
       <c r="F272" s="2" t="s">
         <v>12</v>
@@ -11570,7 +11573,7 @@
         <v>10</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>247</v>
+        <v>141</v>
       </c>
       <c r="F273" s="2" t="s">
         <v>12</v>
@@ -11593,10 +11596,10 @@
         <v>10</v>
       </c>
       <c r="E274" s="2" t="s">
-        <v>141</v>
+        <v>487</v>
       </c>
       <c r="F274" s="2" t="s">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="G274" s="2" t="s">
         <v>13</v>
@@ -11616,10 +11619,10 @@
         <v>10</v>
       </c>
       <c r="E275" s="2" t="s">
-        <v>487</v>
+        <v>588</v>
       </c>
       <c r="F275" s="2" t="s">
-        <v>114</v>
+        <v>12</v>
       </c>
       <c r="G275" s="2" t="s">
         <v>13</v>
@@ -11630,16 +11633,16 @@
         <v>7</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D276" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E276" s="2" t="s">
-        <v>590</v>
+        <v>51</v>
       </c>
       <c r="F276" s="2" t="s">
         <v>12</v>
@@ -11662,7 +11665,7 @@
         <v>10</v>
       </c>
       <c r="E277" s="2" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="F277" s="2" t="s">
         <v>12</v>
@@ -11685,7 +11688,7 @@
         <v>10</v>
       </c>
       <c r="E278" s="2" t="s">
-        <v>32</v>
+        <v>164</v>
       </c>
       <c r="F278" s="2" t="s">
         <v>12</v>
@@ -11708,10 +11711,10 @@
         <v>10</v>
       </c>
       <c r="E279" s="2" t="s">
-        <v>164</v>
+        <v>261</v>
       </c>
       <c r="F279" s="2" t="s">
-        <v>12</v>
+        <v>525</v>
       </c>
       <c r="G279" s="2" t="s">
         <v>13</v>
@@ -11731,7 +11734,7 @@
         <v>10</v>
       </c>
       <c r="E280" s="2" t="s">
-        <v>261</v>
+        <v>164</v>
       </c>
       <c r="F280" s="2" t="s">
         <v>525</v>
@@ -11754,10 +11757,10 @@
         <v>10</v>
       </c>
       <c r="E281" s="2" t="s">
-        <v>164</v>
+        <v>264</v>
       </c>
       <c r="F281" s="2" t="s">
-        <v>525</v>
+        <v>12</v>
       </c>
       <c r="G281" s="2" t="s">
         <v>13</v>
@@ -11777,7 +11780,7 @@
         <v>10</v>
       </c>
       <c r="E282" s="2" t="s">
-        <v>264</v>
+        <v>48</v>
       </c>
       <c r="F282" s="2" t="s">
         <v>12</v>
@@ -11800,7 +11803,7 @@
         <v>10</v>
       </c>
       <c r="E283" s="2" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="F283" s="2" t="s">
         <v>12</v>
@@ -11823,7 +11826,7 @@
         <v>10</v>
       </c>
       <c r="E284" s="2" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="F284" s="2" t="s">
         <v>12</v>
@@ -11846,7 +11849,7 @@
         <v>10</v>
       </c>
       <c r="E285" s="2" t="s">
-        <v>21</v>
+        <v>1577</v>
       </c>
       <c r="F285" s="2" t="s">
         <v>12</v>
@@ -11869,7 +11872,7 @@
         <v>10</v>
       </c>
       <c r="E286" s="2" t="s">
-        <v>1585</v>
+        <v>45</v>
       </c>
       <c r="F286" s="2" t="s">
         <v>12</v>
@@ -11892,7 +11895,7 @@
         <v>10</v>
       </c>
       <c r="E287" s="2" t="s">
-        <v>45</v>
+        <v>613</v>
       </c>
       <c r="F287" s="2" t="s">
         <v>12</v>
@@ -11906,19 +11909,19 @@
         <v>7</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D288" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E288" s="2" t="s">
-        <v>615</v>
+        <v>1546</v>
       </c>
       <c r="F288" s="2" t="s">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="G288" s="2" t="s">
         <v>13</v>
@@ -11938,10 +11941,10 @@
         <v>10</v>
       </c>
       <c r="E289" s="2" t="s">
-        <v>1550</v>
+        <v>21</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>114</v>
+        <v>12</v>
       </c>
       <c r="G289" s="2" t="s">
         <v>13</v>
@@ -11961,7 +11964,7 @@
         <v>10</v>
       </c>
       <c r="E290" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F290" s="2" t="s">
         <v>12</v>
@@ -11984,7 +11987,7 @@
         <v>10</v>
       </c>
       <c r="E291" s="2" t="s">
-        <v>32</v>
+        <v>1514</v>
       </c>
       <c r="F291" s="2" t="s">
         <v>12</v>
@@ -12007,7 +12010,7 @@
         <v>10</v>
       </c>
       <c r="E292" s="2" t="s">
-        <v>1517</v>
+        <v>48</v>
       </c>
       <c r="F292" s="2" t="s">
         <v>12</v>
@@ -12030,10 +12033,10 @@
         <v>10</v>
       </c>
       <c r="E293" s="2" t="s">
-        <v>48</v>
+        <v>626</v>
       </c>
       <c r="F293" s="2" t="s">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="G293" s="2" t="s">
         <v>13</v>
@@ -12044,19 +12047,19 @@
         <v>7</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D294" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E294" s="2" t="s">
-        <v>628</v>
+        <v>155</v>
       </c>
       <c r="F294" s="2" t="s">
-        <v>114</v>
+        <v>12</v>
       </c>
       <c r="G294" s="2" t="s">
         <v>13</v>
@@ -12076,7 +12079,7 @@
         <v>10</v>
       </c>
       <c r="E295" s="2" t="s">
-        <v>155</v>
+        <v>1494</v>
       </c>
       <c r="F295" s="2" t="s">
         <v>12</v>
@@ -12096,10 +12099,10 @@
         <v>632</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E296" s="2" t="s">
-        <v>1496</v>
+        <v>21</v>
       </c>
       <c r="F296" s="2" t="s">
         <v>12</v>
@@ -12119,10 +12122,10 @@
         <v>634</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E297" s="2" t="s">
-        <v>21</v>
+        <v>635</v>
       </c>
       <c r="F297" s="2" t="s">
         <v>12</v>
@@ -12136,16 +12139,16 @@
         <v>7</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="D298" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E298" s="2" t="s">
-        <v>637</v>
+        <v>1479</v>
       </c>
       <c r="F298" s="2" t="s">
         <v>12</v>
@@ -12168,7 +12171,7 @@
         <v>10</v>
       </c>
       <c r="E299" s="2" t="s">
-        <v>1481</v>
+        <v>1547</v>
       </c>
       <c r="F299" s="2" t="s">
         <v>12</v>
@@ -12191,7 +12194,7 @@
         <v>10</v>
       </c>
       <c r="E300" s="2" t="s">
-        <v>1551</v>
+        <v>1509</v>
       </c>
       <c r="F300" s="2" t="s">
         <v>12</v>
@@ -12205,16 +12208,16 @@
         <v>7</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D301" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>1512</v>
+        <v>57</v>
       </c>
       <c r="F301" s="2" t="s">
         <v>12</v>
@@ -12237,7 +12240,7 @@
         <v>10</v>
       </c>
       <c r="E302" s="2" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="F302" s="2" t="s">
         <v>12</v>
@@ -12260,7 +12263,7 @@
         <v>10</v>
       </c>
       <c r="E303" s="2" t="s">
-        <v>72</v>
+        <v>178</v>
       </c>
       <c r="F303" s="2" t="s">
         <v>12</v>
@@ -12283,7 +12286,7 @@
         <v>10</v>
       </c>
       <c r="E304" s="2" t="s">
-        <v>178</v>
+        <v>45</v>
       </c>
       <c r="F304" s="2" t="s">
         <v>12</v>
@@ -12306,7 +12309,7 @@
         <v>10</v>
       </c>
       <c r="E305" s="2" t="s">
-        <v>45</v>
+        <v>254</v>
       </c>
       <c r="F305" s="2" t="s">
         <v>12</v>
@@ -12329,7 +12332,7 @@
         <v>10</v>
       </c>
       <c r="E306" s="2" t="s">
-        <v>254</v>
+        <v>716</v>
       </c>
       <c r="F306" s="2" t="s">
         <v>12</v>
@@ -12343,16 +12346,16 @@
         <v>7</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>655</v>
+        <v>1480</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>656</v>
+        <v>1481</v>
       </c>
       <c r="D307" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E307" s="2" t="s">
-        <v>718</v>
+        <v>427</v>
       </c>
       <c r="F307" s="2" t="s">
         <v>12</v>
@@ -12366,16 +12369,16 @@
         <v>7</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>1482</v>
+        <v>655</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>1483</v>
+        <v>656</v>
       </c>
       <c r="D308" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E308" s="2" t="s">
-        <v>427</v>
+        <v>54</v>
       </c>
       <c r="F308" s="2" t="s">
         <v>12</v>
@@ -12398,7 +12401,7 @@
         <v>10</v>
       </c>
       <c r="E309" s="2" t="s">
-        <v>54</v>
+        <v>178</v>
       </c>
       <c r="F309" s="2" t="s">
         <v>12</v>
@@ -12421,7 +12424,7 @@
         <v>10</v>
       </c>
       <c r="E310" s="2" t="s">
-        <v>45</v>
+        <v>1548</v>
       </c>
       <c r="F310" s="2" t="s">
         <v>12</v>
@@ -12444,7 +12447,7 @@
         <v>10</v>
       </c>
       <c r="E311" s="2" t="s">
-        <v>1552</v>
+        <v>551</v>
       </c>
       <c r="F311" s="2" t="s">
         <v>12</v>
@@ -12467,7 +12470,7 @@
         <v>10</v>
       </c>
       <c r="E312" s="2" t="s">
-        <v>551</v>
+        <v>226</v>
       </c>
       <c r="F312" s="2" t="s">
         <v>12</v>
@@ -12490,7 +12493,7 @@
         <v>10</v>
       </c>
       <c r="E313" s="2" t="s">
-        <v>226</v>
+        <v>21</v>
       </c>
       <c r="F313" s="2" t="s">
         <v>12</v>
@@ -12513,7 +12516,7 @@
         <v>10</v>
       </c>
       <c r="E314" s="2" t="s">
-        <v>21</v>
+        <v>487</v>
       </c>
       <c r="F314" s="2" t="s">
         <v>12</v>
@@ -12536,7 +12539,7 @@
         <v>10</v>
       </c>
       <c r="E315" s="2" t="s">
-        <v>487</v>
+        <v>1578</v>
       </c>
       <c r="F315" s="2" t="s">
         <v>12</v>
@@ -12559,7 +12562,7 @@
         <v>10</v>
       </c>
       <c r="E316" s="2" t="s">
-        <v>1586</v>
+        <v>21</v>
       </c>
       <c r="F316" s="2" t="s">
         <v>12</v>
@@ -12579,13 +12582,13 @@
         <v>674</v>
       </c>
       <c r="D317" s="2" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="E317" s="2" t="s">
-        <v>48</v>
+        <v>191</v>
       </c>
       <c r="F317" s="2" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="G317" s="2" t="s">
         <v>13</v>
@@ -12602,13 +12605,13 @@
         <v>676</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E318" s="2" t="s">
-        <v>191</v>
+        <v>100</v>
       </c>
       <c r="F318" s="2" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="G318" s="2" t="s">
         <v>13</v>
@@ -12628,10 +12631,10 @@
         <v>10</v>
       </c>
       <c r="E319" s="2" t="s">
-        <v>100</v>
+        <v>1182</v>
       </c>
       <c r="F319" s="2" t="s">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="G319" s="2" t="s">
         <v>13</v>
@@ -12648,13 +12651,13 @@
         <v>680</v>
       </c>
       <c r="D320" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E320" s="2" t="s">
-        <v>1184</v>
+        <v>72</v>
       </c>
       <c r="F320" s="2" t="s">
-        <v>114</v>
+        <v>12</v>
       </c>
       <c r="G320" s="2" t="s">
         <v>13</v>
@@ -12671,10 +12674,10 @@
         <v>682</v>
       </c>
       <c r="D321" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E321" s="2" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="F321" s="2" t="s">
         <v>12</v>
@@ -12697,7 +12700,7 @@
         <v>10</v>
       </c>
       <c r="E322" s="2" t="s">
-        <v>51</v>
+        <v>685</v>
       </c>
       <c r="F322" s="2" t="s">
         <v>12</v>
@@ -12711,16 +12714,16 @@
         <v>7</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D323" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E323" s="2" t="s">
-        <v>687</v>
+        <v>1515</v>
       </c>
       <c r="F323" s="2" t="s">
         <v>12</v>
@@ -12743,7 +12746,7 @@
         <v>10</v>
       </c>
       <c r="E324" s="2" t="s">
-        <v>1518</v>
+        <v>223</v>
       </c>
       <c r="F324" s="2" t="s">
         <v>12</v>
@@ -12766,7 +12769,7 @@
         <v>10</v>
       </c>
       <c r="E325" s="2" t="s">
-        <v>223</v>
+        <v>382</v>
       </c>
       <c r="F325" s="2" t="s">
         <v>12</v>
@@ -12789,7 +12792,7 @@
         <v>10</v>
       </c>
       <c r="E326" s="2" t="s">
-        <v>382</v>
+        <v>1579</v>
       </c>
       <c r="F326" s="2" t="s">
         <v>12</v>
@@ -12803,16 +12806,16 @@
         <v>7</v>
       </c>
       <c r="B327" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="C327" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="D327" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E327" s="2" t="s">
         <v>694</v>
-      </c>
-      <c r="C327" s="2" t="s">
-        <v>695</v>
-      </c>
-      <c r="D327" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E327" s="2" t="s">
-        <v>1587</v>
       </c>
       <c r="F327" s="2" t="s">
         <v>12</v>
@@ -12826,16 +12829,16 @@
         <v>7</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E328" s="2" t="s">
-        <v>696</v>
+        <v>45</v>
       </c>
       <c r="F328" s="2" t="s">
         <v>12</v>
@@ -12858,7 +12861,7 @@
         <v>10</v>
       </c>
       <c r="E329" s="2" t="s">
-        <v>45</v>
+        <v>191</v>
       </c>
       <c r="F329" s="2" t="s">
         <v>12</v>
@@ -12881,7 +12884,7 @@
         <v>10</v>
       </c>
       <c r="E330" s="2" t="s">
-        <v>191</v>
+        <v>72</v>
       </c>
       <c r="F330" s="2" t="s">
         <v>12</v>
@@ -12904,7 +12907,7 @@
         <v>10</v>
       </c>
       <c r="E331" s="2" t="s">
-        <v>72</v>
+        <v>703</v>
       </c>
       <c r="F331" s="2" t="s">
         <v>12</v>
@@ -12918,16 +12921,16 @@
         <v>7</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D332" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E332" s="2" t="s">
-        <v>705</v>
+        <v>745</v>
       </c>
       <c r="F332" s="2" t="s">
         <v>12</v>
@@ -12950,7 +12953,7 @@
         <v>10</v>
       </c>
       <c r="E333" s="2" t="s">
-        <v>747</v>
+        <v>1489</v>
       </c>
       <c r="F333" s="2" t="s">
         <v>12</v>
@@ -12973,7 +12976,7 @@
         <v>10</v>
       </c>
       <c r="E334" s="2" t="s">
-        <v>1491</v>
+        <v>89</v>
       </c>
       <c r="F334" s="2" t="s">
         <v>12</v>
@@ -12993,10 +12996,10 @@
         <v>711</v>
       </c>
       <c r="D335" s="2" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="E335" s="2" t="s">
-        <v>89</v>
+        <v>551</v>
       </c>
       <c r="F335" s="2" t="s">
         <v>12</v>
@@ -13010,19 +13013,19 @@
         <v>7</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>712</v>
+        <v>1516</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>713</v>
+        <v>1517</v>
       </c>
       <c r="D336" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E336" s="2" t="s">
-        <v>551</v>
+        <v>1518</v>
       </c>
       <c r="F336" s="2" t="s">
-        <v>12</v>
+        <v>525</v>
       </c>
       <c r="G336" s="2" t="s">
         <v>13</v>
@@ -13033,19 +13036,19 @@
         <v>7</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>1519</v>
+        <v>712</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>1520</v>
+        <v>713</v>
       </c>
       <c r="D337" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E337" s="2" t="s">
-        <v>1521</v>
+        <v>81</v>
       </c>
       <c r="F337" s="2" t="s">
-        <v>525</v>
+        <v>12</v>
       </c>
       <c r="G337" s="2" t="s">
         <v>13</v>
@@ -13062,10 +13065,10 @@
         <v>715</v>
       </c>
       <c r="D338" s="2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E338" s="2" t="s">
-        <v>81</v>
+        <v>1473</v>
       </c>
       <c r="F338" s="2" t="s">
         <v>12</v>
@@ -13079,16 +13082,16 @@
         <v>7</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="D339" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E339" s="2" t="s">
-        <v>1475</v>
+        <v>418</v>
       </c>
       <c r="F339" s="2" t="s">
         <v>12</v>
@@ -13111,7 +13114,7 @@
         <v>10</v>
       </c>
       <c r="E340" s="2" t="s">
-        <v>418</v>
+        <v>109</v>
       </c>
       <c r="F340" s="2" t="s">
         <v>12</v>
@@ -13134,7 +13137,7 @@
         <v>10</v>
       </c>
       <c r="E341" s="2" t="s">
-        <v>109</v>
+        <v>723</v>
       </c>
       <c r="F341" s="2" t="s">
         <v>12</v>
@@ -13148,19 +13151,19 @@
         <v>7</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="D342" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E342" s="2" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
       <c r="F342" s="2" t="s">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="G342" s="2" t="s">
         <v>13</v>
@@ -13180,10 +13183,10 @@
         <v>10</v>
       </c>
       <c r="E343" s="2" t="s">
-        <v>644</v>
+        <v>728</v>
       </c>
       <c r="F343" s="2" t="s">
-        <v>114</v>
+        <v>12</v>
       </c>
       <c r="G343" s="2" t="s">
         <v>13</v>
@@ -13194,16 +13197,16 @@
         <v>7</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="D344" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E344" s="2" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="F344" s="2" t="s">
         <v>12</v>
@@ -13217,16 +13220,16 @@
         <v>7</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D345" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E345" s="2" t="s">
-        <v>733</v>
+        <v>1493</v>
       </c>
       <c r="F345" s="2" t="s">
         <v>12</v>
@@ -13240,16 +13243,16 @@
         <v>7</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="D346" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E346" s="2" t="s">
-        <v>1495</v>
+        <v>1580</v>
       </c>
       <c r="F346" s="2" t="s">
         <v>12</v>
@@ -13272,7 +13275,7 @@
         <v>10</v>
       </c>
       <c r="E347" s="2" t="s">
-        <v>1588</v>
+        <v>282</v>
       </c>
       <c r="F347" s="2" t="s">
         <v>12</v>
@@ -13295,7 +13298,7 @@
         <v>10</v>
       </c>
       <c r="E348" s="2" t="s">
-        <v>282</v>
+        <v>731</v>
       </c>
       <c r="F348" s="2" t="s">
         <v>12</v>
@@ -13318,7 +13321,7 @@
         <v>10</v>
       </c>
       <c r="E349" s="2" t="s">
-        <v>733</v>
+        <v>152</v>
       </c>
       <c r="F349" s="2" t="s">
         <v>12</v>
@@ -13338,10 +13341,10 @@
         <v>744</v>
       </c>
       <c r="D350" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E350" s="2" t="s">
-        <v>152</v>
+        <v>745</v>
       </c>
       <c r="F350" s="2" t="s">
         <v>12</v>
@@ -13355,16 +13358,16 @@
         <v>7</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D351" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E351" s="2" t="s">
-        <v>747</v>
+        <v>1514</v>
       </c>
       <c r="F351" s="2" t="s">
         <v>12</v>
@@ -13387,7 +13390,7 @@
         <v>10</v>
       </c>
       <c r="E352" s="2" t="s">
-        <v>1517</v>
+        <v>75</v>
       </c>
       <c r="F352" s="2" t="s">
         <v>12</v>
@@ -13410,7 +13413,7 @@
         <v>10</v>
       </c>
       <c r="E353" s="2" t="s">
-        <v>75</v>
+        <v>734</v>
       </c>
       <c r="F353" s="2" t="s">
         <v>12</v>
@@ -13433,7 +13436,7 @@
         <v>10</v>
       </c>
       <c r="E354" s="2" t="s">
-        <v>736</v>
+        <v>1496</v>
       </c>
       <c r="F354" s="2" t="s">
         <v>12</v>
@@ -13447,19 +13450,19 @@
         <v>7</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="D355" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E355" s="2" t="s">
-        <v>1498</v>
+        <v>1581</v>
       </c>
       <c r="F355" s="2" t="s">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="G355" s="2" t="s">
         <v>13</v>
@@ -13470,16 +13473,16 @@
         <v>7</v>
       </c>
       <c r="B356" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="C356" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="D356" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E356" s="2" t="s">
         <v>757</v>
-      </c>
-      <c r="C356" s="2" t="s">
-        <v>758</v>
-      </c>
-      <c r="D356" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E356" s="2" t="s">
-        <v>1589</v>
       </c>
       <c r="F356" s="2" t="s">
         <v>114</v>
@@ -13493,19 +13496,19 @@
         <v>7</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="D357" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E357" s="2" t="s">
-        <v>759</v>
+        <v>1582</v>
       </c>
       <c r="F357" s="2" t="s">
-        <v>114</v>
+        <v>12</v>
       </c>
       <c r="G357" s="2" t="s">
         <v>13</v>
@@ -13525,7 +13528,7 @@
         <v>10</v>
       </c>
       <c r="E358" s="2" t="s">
-        <v>1590</v>
+        <v>1514</v>
       </c>
       <c r="F358" s="2" t="s">
         <v>12</v>
@@ -13548,7 +13551,7 @@
         <v>10</v>
       </c>
       <c r="E359" s="2" t="s">
-        <v>1517</v>
+        <v>1474</v>
       </c>
       <c r="F359" s="2" t="s">
         <v>12</v>
@@ -13562,16 +13565,16 @@
         <v>7</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D360" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E360" s="2" t="s">
-        <v>1476</v>
+        <v>1549</v>
       </c>
       <c r="F360" s="2" t="s">
         <v>12</v>
@@ -13585,16 +13588,16 @@
         <v>7</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="D361" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E361" s="2" t="s">
-        <v>1553</v>
+        <v>1583</v>
       </c>
       <c r="F361" s="2" t="s">
         <v>12</v>
@@ -13608,16 +13611,16 @@
         <v>7</v>
       </c>
       <c r="B362" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="C362" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="D362" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E362" s="2" t="s">
         <v>767</v>
-      </c>
-      <c r="C362" s="2" t="s">
-        <v>768</v>
-      </c>
-      <c r="D362" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E362" s="2" t="s">
-        <v>1591</v>
       </c>
       <c r="F362" s="2" t="s">
         <v>12</v>
@@ -13631,16 +13634,16 @@
         <v>7</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="D363" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E363" s="2" t="s">
-        <v>769</v>
+        <v>1550</v>
       </c>
       <c r="F363" s="2" t="s">
         <v>12</v>
@@ -13663,7 +13666,7 @@
         <v>10</v>
       </c>
       <c r="E364" s="2" t="s">
-        <v>1554</v>
+        <v>223</v>
       </c>
       <c r="F364" s="2" t="s">
         <v>12</v>
@@ -13686,7 +13689,7 @@
         <v>10</v>
       </c>
       <c r="E365" s="2" t="s">
-        <v>223</v>
+        <v>1495</v>
       </c>
       <c r="F365" s="2" t="s">
         <v>12</v>
@@ -13709,7 +13712,7 @@
         <v>10</v>
       </c>
       <c r="E366" s="2" t="s">
-        <v>1497</v>
+        <v>364</v>
       </c>
       <c r="F366" s="2" t="s">
         <v>12</v>
@@ -13732,7 +13735,7 @@
         <v>10</v>
       </c>
       <c r="E367" s="2" t="s">
-        <v>364</v>
+        <v>226</v>
       </c>
       <c r="F367" s="2" t="s">
         <v>12</v>
@@ -13755,7 +13758,7 @@
         <v>10</v>
       </c>
       <c r="E368" s="2" t="s">
-        <v>226</v>
+        <v>32</v>
       </c>
       <c r="F368" s="2" t="s">
         <v>12</v>
@@ -13801,7 +13804,7 @@
         <v>10</v>
       </c>
       <c r="E370" s="2" t="s">
-        <v>32</v>
+        <v>226</v>
       </c>
       <c r="F370" s="2" t="s">
         <v>12</v>
@@ -13824,7 +13827,7 @@
         <v>10</v>
       </c>
       <c r="E371" s="2" t="s">
-        <v>226</v>
+        <v>84</v>
       </c>
       <c r="F371" s="2" t="s">
         <v>12</v>
@@ -13847,7 +13850,7 @@
         <v>10</v>
       </c>
       <c r="E372" s="2" t="s">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="F372" s="2" t="s">
         <v>12</v>
@@ -13870,7 +13873,7 @@
         <v>10</v>
       </c>
       <c r="E373" s="2" t="s">
-        <v>36</v>
+        <v>92</v>
       </c>
       <c r="F373" s="2" t="s">
         <v>12</v>
@@ -13893,7 +13896,7 @@
         <v>10</v>
       </c>
       <c r="E374" s="2" t="s">
-        <v>92</v>
+        <v>141</v>
       </c>
       <c r="F374" s="2" t="s">
         <v>12</v>
@@ -13913,10 +13916,10 @@
         <v>793</v>
       </c>
       <c r="D375" s="2" t="s">
-        <v>10</v>
+        <v>138</v>
       </c>
       <c r="E375" s="2" t="s">
-        <v>141</v>
+        <v>72</v>
       </c>
       <c r="F375" s="2" t="s">
         <v>12</v>
@@ -13939,7 +13942,7 @@
         <v>138</v>
       </c>
       <c r="E376" s="2" t="s">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="F376" s="2" t="s">
         <v>12</v>
@@ -13959,10 +13962,10 @@
         <v>797</v>
       </c>
       <c r="D377" s="2" t="s">
-        <v>138</v>
+        <v>10</v>
       </c>
       <c r="E377" s="2" t="s">
-        <v>36</v>
+        <v>109</v>
       </c>
       <c r="F377" s="2" t="s">
         <v>12</v>
@@ -13985,7 +13988,7 @@
         <v>10</v>
       </c>
       <c r="E378" s="2" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="F378" s="2" t="s">
         <v>12</v>
@@ -14008,7 +14011,7 @@
         <v>10</v>
       </c>
       <c r="E379" s="2" t="s">
-        <v>57</v>
+        <v>152</v>
       </c>
       <c r="F379" s="2" t="s">
         <v>12</v>
@@ -14031,10 +14034,10 @@
         <v>10</v>
       </c>
       <c r="E380" s="2" t="s">
-        <v>361</v>
+        <v>1041</v>
       </c>
       <c r="F380" s="2" t="s">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="G380" s="2" t="s">
         <v>13</v>
@@ -14054,10 +14057,10 @@
         <v>10</v>
       </c>
       <c r="E381" s="2" t="s">
-        <v>1043</v>
+        <v>806</v>
       </c>
       <c r="F381" s="2" t="s">
-        <v>114</v>
+        <v>12</v>
       </c>
       <c r="G381" s="2" t="s">
         <v>13</v>
@@ -14068,16 +14071,16 @@
         <v>7</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D382" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E382" s="2" t="s">
-        <v>808</v>
+        <v>1483</v>
       </c>
       <c r="F382" s="2" t="s">
         <v>12</v>
@@ -14100,7 +14103,7 @@
         <v>10</v>
       </c>
       <c r="E383" s="2" t="s">
-        <v>1485</v>
+        <v>57</v>
       </c>
       <c r="F383" s="2" t="s">
         <v>12</v>
@@ -14120,10 +14123,10 @@
         <v>812</v>
       </c>
       <c r="D384" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E384" s="2" t="s">
-        <v>57</v>
+        <v>264</v>
       </c>
       <c r="F384" s="2" t="s">
         <v>12</v>
@@ -14143,10 +14146,10 @@
         <v>814</v>
       </c>
       <c r="D385" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E385" s="2" t="s">
-        <v>264</v>
+        <v>72</v>
       </c>
       <c r="F385" s="2" t="s">
         <v>12</v>
@@ -14160,16 +14163,16 @@
         <v>7</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="D386" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E386" s="2" t="s">
-        <v>72</v>
+        <v>312</v>
       </c>
       <c r="F386" s="2" t="s">
         <v>12</v>
@@ -14183,19 +14186,19 @@
         <v>7</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D387" s="2" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E387" s="2" t="s">
-        <v>312</v>
+        <v>21</v>
       </c>
       <c r="F387" s="2" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="G387" s="2" t="s">
         <v>13</v>
@@ -14206,16 +14209,16 @@
         <v>7</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="D388" s="2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E388" s="2" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="F388" s="2" t="s">
         <v>40</v>
@@ -14238,10 +14241,10 @@
         <v>10</v>
       </c>
       <c r="E389" s="2" t="s">
-        <v>81</v>
+        <v>487</v>
       </c>
       <c r="F389" s="2" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="G389" s="2" t="s">
         <v>13</v>
@@ -14258,13 +14261,13 @@
         <v>821</v>
       </c>
       <c r="D390" s="2" t="s">
-        <v>10</v>
+        <v>138</v>
       </c>
       <c r="E390" s="2" t="s">
-        <v>487</v>
+        <v>57</v>
       </c>
       <c r="F390" s="2" t="s">
-        <v>12</v>
+        <v>192</v>
       </c>
       <c r="G390" s="2" t="s">
         <v>13</v>
@@ -14284,7 +14287,7 @@
         <v>138</v>
       </c>
       <c r="E391" s="2" t="s">
-        <v>57</v>
+        <v>220</v>
       </c>
       <c r="F391" s="2" t="s">
         <v>192</v>
@@ -14307,7 +14310,7 @@
         <v>138</v>
       </c>
       <c r="E392" s="2" t="s">
-        <v>220</v>
+        <v>95</v>
       </c>
       <c r="F392" s="2" t="s">
         <v>192</v>
@@ -14344,16 +14347,16 @@
         <v>7</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C394" s="2" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D394" s="2" t="s">
         <v>138</v>
       </c>
       <c r="E394" s="2" t="s">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="F394" s="2" t="s">
         <v>192</v>
@@ -14376,7 +14379,7 @@
         <v>138</v>
       </c>
       <c r="E395" s="2" t="s">
-        <v>500</v>
+        <v>51</v>
       </c>
       <c r="F395" s="2" t="s">
         <v>192</v>
@@ -14399,7 +14402,7 @@
         <v>138</v>
       </c>
       <c r="E396" s="2" t="s">
-        <v>51</v>
+        <v>247</v>
       </c>
       <c r="F396" s="2" t="s">
         <v>192</v>
@@ -14422,7 +14425,7 @@
         <v>138</v>
       </c>
       <c r="E397" s="2" t="s">
-        <v>247</v>
+        <v>418</v>
       </c>
       <c r="F397" s="2" t="s">
         <v>192</v>
@@ -14436,16 +14439,16 @@
         <v>7</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C398" s="2" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D398" s="2" t="s">
         <v>138</v>
       </c>
       <c r="E398" s="2" t="s">
-        <v>418</v>
+        <v>538</v>
       </c>
       <c r="F398" s="2" t="s">
         <v>192</v>
@@ -14468,7 +14471,7 @@
         <v>138</v>
       </c>
       <c r="E399" s="2" t="s">
-        <v>538</v>
+        <v>57</v>
       </c>
       <c r="F399" s="2" t="s">
         <v>192</v>
@@ -14491,7 +14494,7 @@
         <v>138</v>
       </c>
       <c r="E400" s="2" t="s">
-        <v>57</v>
+        <v>191</v>
       </c>
       <c r="F400" s="2" t="s">
         <v>192</v>
@@ -14514,7 +14517,7 @@
         <v>138</v>
       </c>
       <c r="E401" s="2" t="s">
-        <v>191</v>
+        <v>906</v>
       </c>
       <c r="F401" s="2" t="s">
         <v>192</v>
@@ -14528,19 +14531,19 @@
         <v>7</v>
       </c>
       <c r="B402" s="2" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C402" s="2" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="D402" s="2" t="s">
         <v>138</v>
       </c>
       <c r="E402" s="2" t="s">
-        <v>1592</v>
+        <v>21</v>
       </c>
       <c r="F402" s="2" t="s">
-        <v>192</v>
+        <v>12</v>
       </c>
       <c r="G402" s="2" t="s">
         <v>13</v>
@@ -14560,7 +14563,7 @@
         <v>138</v>
       </c>
       <c r="E403" s="2" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="F403" s="2" t="s">
         <v>12</v>
@@ -14583,7 +14586,7 @@
         <v>138</v>
       </c>
       <c r="E404" s="2" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="F404" s="2" t="s">
         <v>12</v>
@@ -14606,7 +14609,7 @@
         <v>138</v>
       </c>
       <c r="E405" s="2" t="s">
-        <v>72</v>
+        <v>21</v>
       </c>
       <c r="F405" s="2" t="s">
         <v>12</v>
@@ -14649,10 +14652,10 @@
         <v>858</v>
       </c>
       <c r="D407" s="2" t="s">
-        <v>138</v>
+        <v>10</v>
       </c>
       <c r="E407" s="2" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="F407" s="2" t="s">
         <v>12</v>
@@ -14675,7 +14678,7 @@
         <v>10</v>
       </c>
       <c r="E408" s="2" t="s">
-        <v>54</v>
+        <v>418</v>
       </c>
       <c r="F408" s="2" t="s">
         <v>12</v>
@@ -14698,7 +14701,7 @@
         <v>10</v>
       </c>
       <c r="E409" s="2" t="s">
-        <v>418</v>
+        <v>48</v>
       </c>
       <c r="F409" s="2" t="s">
         <v>12</v>
@@ -14718,10 +14721,10 @@
         <v>864</v>
       </c>
       <c r="D410" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E410" s="2" t="s">
-        <v>48</v>
+        <v>865</v>
       </c>
       <c r="F410" s="2" t="s">
         <v>12</v>
@@ -14735,16 +14738,16 @@
         <v>7</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C411" s="2" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="D411" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E411" s="2" t="s">
-        <v>867</v>
+        <v>191</v>
       </c>
       <c r="F411" s="2" t="s">
         <v>12</v>
@@ -14767,10 +14770,10 @@
         <v>10</v>
       </c>
       <c r="E412" s="2" t="s">
-        <v>191</v>
+        <v>870</v>
       </c>
       <c r="F412" s="2" t="s">
-        <v>12</v>
+        <v>285</v>
       </c>
       <c r="G412" s="2" t="s">
         <v>13</v>
@@ -14781,16 +14784,16 @@
         <v>7</v>
       </c>
       <c r="B413" s="2" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="C413" s="2" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="D413" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E413" s="2" t="s">
-        <v>872</v>
+        <v>1519</v>
       </c>
       <c r="F413" s="2" t="s">
         <v>285</v>
@@ -14804,16 +14807,16 @@
         <v>7</v>
       </c>
       <c r="B414" s="2" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="C414" s="2" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="D414" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E414" s="2" t="s">
-        <v>1522</v>
+        <v>1551</v>
       </c>
       <c r="F414" s="2" t="s">
         <v>285</v>
@@ -14833,13 +14836,13 @@
         <v>874</v>
       </c>
       <c r="D415" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E415" s="2" t="s">
-        <v>1555</v>
+        <v>875</v>
       </c>
       <c r="F415" s="2" t="s">
-        <v>285</v>
+        <v>12</v>
       </c>
       <c r="G415" s="2" t="s">
         <v>13</v>
@@ -14850,16 +14853,16 @@
         <v>7</v>
       </c>
       <c r="B416" s="2" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C416" s="2" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="D416" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E416" s="2" t="s">
-        <v>877</v>
+        <v>538</v>
       </c>
       <c r="F416" s="2" t="s">
         <v>12</v>
@@ -14882,7 +14885,7 @@
         <v>10</v>
       </c>
       <c r="E417" s="2" t="s">
-        <v>538</v>
+        <v>1473</v>
       </c>
       <c r="F417" s="2" t="s">
         <v>12</v>
@@ -14896,16 +14899,16 @@
         <v>7</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>880</v>
+        <v>1471</v>
       </c>
       <c r="C418" s="2" t="s">
-        <v>881</v>
+        <v>1472</v>
       </c>
       <c r="D418" s="2" t="s">
-        <v>10</v>
+        <v>138</v>
       </c>
       <c r="E418" s="2" t="s">
-        <v>1475</v>
+        <v>81</v>
       </c>
       <c r="F418" s="2" t="s">
         <v>12</v>
@@ -14919,16 +14922,16 @@
         <v>7</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>1473</v>
+        <v>880</v>
       </c>
       <c r="C419" s="2" t="s">
-        <v>1474</v>
+        <v>881</v>
       </c>
       <c r="D419" s="2" t="s">
-        <v>138</v>
+        <v>10</v>
       </c>
       <c r="E419" s="2" t="s">
-        <v>81</v>
+        <v>223</v>
       </c>
       <c r="F419" s="2" t="s">
         <v>12</v>
@@ -14951,7 +14954,7 @@
         <v>10</v>
       </c>
       <c r="E420" s="2" t="s">
-        <v>223</v>
+        <v>1463</v>
       </c>
       <c r="F420" s="2" t="s">
         <v>12</v>
@@ -14974,7 +14977,7 @@
         <v>10</v>
       </c>
       <c r="E421" s="2" t="s">
-        <v>1465</v>
+        <v>1584</v>
       </c>
       <c r="F421" s="2" t="s">
         <v>12</v>
@@ -14997,7 +15000,7 @@
         <v>10</v>
       </c>
       <c r="E422" s="2" t="s">
-        <v>1593</v>
+        <v>72</v>
       </c>
       <c r="F422" s="2" t="s">
         <v>12</v>
@@ -15020,7 +15023,7 @@
         <v>10</v>
       </c>
       <c r="E423" s="2" t="s">
-        <v>72</v>
+        <v>1473</v>
       </c>
       <c r="F423" s="2" t="s">
         <v>12</v>
@@ -15043,7 +15046,7 @@
         <v>10</v>
       </c>
       <c r="E424" s="2" t="s">
-        <v>361</v>
+        <v>1464</v>
       </c>
       <c r="F424" s="2" t="s">
         <v>12</v>
@@ -15066,7 +15069,7 @@
         <v>10</v>
       </c>
       <c r="E425" s="2" t="s">
-        <v>1466</v>
+        <v>191</v>
       </c>
       <c r="F425" s="2" t="s">
         <v>12</v>
@@ -15089,7 +15092,7 @@
         <v>10</v>
       </c>
       <c r="E426" s="2" t="s">
-        <v>191</v>
+        <v>164</v>
       </c>
       <c r="F426" s="2" t="s">
         <v>12</v>
@@ -15112,7 +15115,7 @@
         <v>10</v>
       </c>
       <c r="E427" s="2" t="s">
-        <v>164</v>
+        <v>48</v>
       </c>
       <c r="F427" s="2" t="s">
         <v>12</v>
@@ -15135,7 +15138,7 @@
         <v>10</v>
       </c>
       <c r="E428" s="2" t="s">
-        <v>48</v>
+        <v>220</v>
       </c>
       <c r="F428" s="2" t="s">
         <v>12</v>
@@ -15158,7 +15161,7 @@
         <v>10</v>
       </c>
       <c r="E429" s="2" t="s">
-        <v>220</v>
+        <v>89</v>
       </c>
       <c r="F429" s="2" t="s">
         <v>12</v>
@@ -15181,7 +15184,7 @@
         <v>10</v>
       </c>
       <c r="E430" s="2" t="s">
-        <v>89</v>
+        <v>716</v>
       </c>
       <c r="F430" s="2" t="s">
         <v>12</v>
@@ -15204,7 +15207,7 @@
         <v>10</v>
       </c>
       <c r="E431" s="2" t="s">
-        <v>718</v>
+        <v>1464</v>
       </c>
       <c r="F431" s="2" t="s">
         <v>12</v>
@@ -15218,16 +15221,16 @@
         <v>7</v>
       </c>
       <c r="B432" s="2" t="s">
+        <v>904</v>
+      </c>
+      <c r="C432" s="2" t="s">
+        <v>905</v>
+      </c>
+      <c r="D432" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E432" s="2" t="s">
         <v>906</v>
-      </c>
-      <c r="C432" s="2" t="s">
-        <v>907</v>
-      </c>
-      <c r="D432" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E432" s="2" t="s">
-        <v>1466</v>
       </c>
       <c r="F432" s="2" t="s">
         <v>12</v>
@@ -15241,19 +15244,19 @@
         <v>7</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C433" s="2" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="D433" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E433" s="2" t="s">
-        <v>908</v>
+        <v>167</v>
       </c>
       <c r="F433" s="2" t="s">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="G433" s="2" t="s">
         <v>13</v>
@@ -15273,10 +15276,10 @@
         <v>10</v>
       </c>
       <c r="E434" s="2" t="s">
-        <v>167</v>
+        <v>837</v>
       </c>
       <c r="F434" s="2" t="s">
-        <v>114</v>
+        <v>12</v>
       </c>
       <c r="G434" s="2" t="s">
         <v>13</v>
@@ -15287,16 +15290,16 @@
         <v>7</v>
       </c>
       <c r="B435" s="2" t="s">
+        <v>909</v>
+      </c>
+      <c r="C435" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="D435" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E435" s="2" t="s">
         <v>911</v>
-      </c>
-      <c r="C435" s="2" t="s">
-        <v>912</v>
-      </c>
-      <c r="D435" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E435" s="2" t="s">
-        <v>839</v>
       </c>
       <c r="F435" s="2" t="s">
         <v>12</v>
@@ -15310,16 +15313,16 @@
         <v>7</v>
       </c>
       <c r="B436" s="2" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="C436" s="2" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="D436" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E436" s="2" t="s">
-        <v>913</v>
+        <v>1504</v>
       </c>
       <c r="F436" s="2" t="s">
         <v>12</v>
@@ -15339,10 +15342,10 @@
         <v>915</v>
       </c>
       <c r="D437" s="2" t="s">
-        <v>10</v>
+        <v>138</v>
       </c>
       <c r="E437" s="2" t="s">
-        <v>1507</v>
+        <v>191</v>
       </c>
       <c r="F437" s="2" t="s">
         <v>12</v>
@@ -15365,7 +15368,7 @@
         <v>138</v>
       </c>
       <c r="E438" s="2" t="s">
-        <v>191</v>
+        <v>1554</v>
       </c>
       <c r="F438" s="2" t="s">
         <v>12</v>
@@ -15388,7 +15391,7 @@
         <v>138</v>
       </c>
       <c r="E439" s="2" t="s">
-        <v>1558</v>
+        <v>1585</v>
       </c>
       <c r="F439" s="2" t="s">
         <v>12</v>
@@ -15411,7 +15414,7 @@
         <v>138</v>
       </c>
       <c r="E440" s="2" t="s">
-        <v>1594</v>
+        <v>1512</v>
       </c>
       <c r="F440" s="2" t="s">
         <v>12</v>
@@ -15434,7 +15437,7 @@
         <v>138</v>
       </c>
       <c r="E441" s="2" t="s">
-        <v>1515</v>
+        <v>1585</v>
       </c>
       <c r="F441" s="2" t="s">
         <v>12</v>
@@ -15454,13 +15457,13 @@
         <v>925</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>138</v>
+        <v>35</v>
       </c>
       <c r="E442" s="2" t="s">
-        <v>1523</v>
+        <v>1607</v>
       </c>
       <c r="F442" s="2" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="G442" s="2" t="s">
         <v>13</v>
@@ -15480,7 +15483,7 @@
         <v>35</v>
       </c>
       <c r="E443" s="2" t="s">
-        <v>1595</v>
+        <v>65</v>
       </c>
       <c r="F443" s="2" t="s">
         <v>40</v>
@@ -15500,13 +15503,13 @@
         <v>929</v>
       </c>
       <c r="D444" s="2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E444" s="2" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="F444" s="2" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="G444" s="2" t="s">
         <v>13</v>
@@ -15526,7 +15529,7 @@
         <v>10</v>
       </c>
       <c r="E445" s="2" t="s">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="F445" s="2" t="s">
         <v>12</v>
@@ -15549,7 +15552,7 @@
         <v>10</v>
       </c>
       <c r="E446" s="2" t="s">
-        <v>54</v>
+        <v>226</v>
       </c>
       <c r="F446" s="2" t="s">
         <v>12</v>
@@ -15572,7 +15575,7 @@
         <v>10</v>
       </c>
       <c r="E447" s="2" t="s">
-        <v>226</v>
+        <v>81</v>
       </c>
       <c r="F447" s="2" t="s">
         <v>12</v>
@@ -15595,7 +15598,7 @@
         <v>10</v>
       </c>
       <c r="E448" s="2" t="s">
-        <v>81</v>
+        <v>418</v>
       </c>
       <c r="F448" s="2" t="s">
         <v>12</v>
@@ -15609,16 +15612,16 @@
         <v>7</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="C449" s="2" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="D449" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E449" s="2" t="s">
-        <v>418</v>
+        <v>155</v>
       </c>
       <c r="F449" s="2" t="s">
         <v>12</v>
@@ -15638,10 +15641,10 @@
         <v>939</v>
       </c>
       <c r="D450" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E450" s="2" t="s">
-        <v>155</v>
+        <v>723</v>
       </c>
       <c r="F450" s="2" t="s">
         <v>12</v>
@@ -15664,7 +15667,7 @@
         <v>10</v>
       </c>
       <c r="E451" s="2" t="s">
-        <v>725</v>
+        <v>155</v>
       </c>
       <c r="F451" s="2" t="s">
         <v>12</v>
@@ -15687,7 +15690,7 @@
         <v>10</v>
       </c>
       <c r="E452" s="2" t="s">
-        <v>155</v>
+        <v>361</v>
       </c>
       <c r="F452" s="2" t="s">
         <v>12</v>
@@ -15707,10 +15710,10 @@
         <v>945</v>
       </c>
       <c r="D453" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E453" s="2" t="s">
-        <v>1475</v>
+        <v>65</v>
       </c>
       <c r="F453" s="2" t="s">
         <v>12</v>
@@ -15730,10 +15733,10 @@
         <v>947</v>
       </c>
       <c r="D454" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E454" s="2" t="s">
-        <v>65</v>
+        <v>109</v>
       </c>
       <c r="F454" s="2" t="s">
         <v>12</v>
@@ -15756,7 +15759,7 @@
         <v>10</v>
       </c>
       <c r="E455" s="2" t="s">
-        <v>164</v>
+        <v>141</v>
       </c>
       <c r="F455" s="2" t="s">
         <v>12</v>
@@ -15779,7 +15782,7 @@
         <v>10</v>
       </c>
       <c r="E456" s="2" t="s">
-        <v>141</v>
+        <v>223</v>
       </c>
       <c r="F456" s="2" t="s">
         <v>12</v>
@@ -15802,7 +15805,7 @@
         <v>10</v>
       </c>
       <c r="E457" s="2" t="s">
-        <v>223</v>
+        <v>954</v>
       </c>
       <c r="F457" s="2" t="s">
         <v>12</v>
@@ -15816,19 +15819,19 @@
         <v>7</v>
       </c>
       <c r="B458" s="2" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C458" s="2" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="D458" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E458" s="2" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="F458" s="2" t="s">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="G458" s="2" t="s">
         <v>13</v>
@@ -15839,19 +15842,19 @@
         <v>7</v>
       </c>
       <c r="B459" s="2" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="C459" s="2" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="D459" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E459" s="2" t="s">
-        <v>959</v>
+        <v>1586</v>
       </c>
       <c r="F459" s="2" t="s">
-        <v>114</v>
+        <v>12</v>
       </c>
       <c r="G459" s="2" t="s">
         <v>13</v>
@@ -15871,7 +15874,7 @@
         <v>10</v>
       </c>
       <c r="E460" s="2" t="s">
-        <v>1596</v>
+        <v>500</v>
       </c>
       <c r="F460" s="2" t="s">
         <v>12</v>
@@ -15894,10 +15897,10 @@
         <v>10</v>
       </c>
       <c r="E461" s="2" t="s">
-        <v>500</v>
+        <v>1587</v>
       </c>
       <c r="F461" s="2" t="s">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="G461" s="2" t="s">
         <v>13</v>
@@ -15917,10 +15920,10 @@
         <v>10</v>
       </c>
       <c r="E462" s="2" t="s">
-        <v>1597</v>
+        <v>95</v>
       </c>
       <c r="F462" s="2" t="s">
-        <v>114</v>
+        <v>12</v>
       </c>
       <c r="G462" s="2" t="s">
         <v>13</v>
@@ -15940,7 +15943,7 @@
         <v>10</v>
       </c>
       <c r="E463" s="2" t="s">
-        <v>95</v>
+        <v>968</v>
       </c>
       <c r="F463" s="2" t="s">
         <v>12</v>
@@ -15954,16 +15957,16 @@
         <v>7</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C464" s="2" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="D464" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E464" s="2" t="s">
-        <v>970</v>
+        <v>1482</v>
       </c>
       <c r="F464" s="2" t="s">
         <v>12</v>
@@ -15986,7 +15989,7 @@
         <v>10</v>
       </c>
       <c r="E465" s="2" t="s">
-        <v>1484</v>
+        <v>1552</v>
       </c>
       <c r="F465" s="2" t="s">
         <v>12</v>
@@ -16009,7 +16012,7 @@
         <v>10</v>
       </c>
       <c r="E466" s="2" t="s">
-        <v>1556</v>
+        <v>1506</v>
       </c>
       <c r="F466" s="2" t="s">
         <v>12</v>
@@ -16032,7 +16035,7 @@
         <v>10</v>
       </c>
       <c r="E467" s="2" t="s">
-        <v>1509</v>
+        <v>1608</v>
       </c>
       <c r="F467" s="2" t="s">
         <v>12</v>
@@ -16055,7 +16058,7 @@
         <v>10</v>
       </c>
       <c r="E468" s="2" t="s">
-        <v>1562</v>
+        <v>364</v>
       </c>
       <c r="F468" s="2" t="s">
         <v>12</v>
@@ -16078,10 +16081,10 @@
         <v>10</v>
       </c>
       <c r="E469" s="2" t="s">
-        <v>364</v>
+        <v>734</v>
       </c>
       <c r="F469" s="2" t="s">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="G469" s="2" t="s">
         <v>13</v>
@@ -16101,7 +16104,7 @@
         <v>10</v>
       </c>
       <c r="E470" s="2" t="s">
-        <v>736</v>
+        <v>1588</v>
       </c>
       <c r="F470" s="2" t="s">
         <v>114</v>
@@ -16124,10 +16127,10 @@
         <v>10</v>
       </c>
       <c r="E471" s="2" t="s">
-        <v>1598</v>
+        <v>152</v>
       </c>
       <c r="F471" s="2" t="s">
-        <v>114</v>
+        <v>12</v>
       </c>
       <c r="G471" s="2" t="s">
         <v>13</v>
@@ -16147,7 +16150,7 @@
         <v>10</v>
       </c>
       <c r="E472" s="2" t="s">
-        <v>152</v>
+        <v>1520</v>
       </c>
       <c r="F472" s="2" t="s">
         <v>12</v>
@@ -16170,7 +16173,7 @@
         <v>10</v>
       </c>
       <c r="E473" s="2" t="s">
-        <v>1524</v>
+        <v>1473</v>
       </c>
       <c r="F473" s="2" t="s">
         <v>12</v>
@@ -16193,7 +16196,7 @@
         <v>10</v>
       </c>
       <c r="E474" s="2" t="s">
-        <v>1475</v>
+        <v>1521</v>
       </c>
       <c r="F474" s="2" t="s">
         <v>12</v>
@@ -16207,16 +16210,16 @@
         <v>7</v>
       </c>
       <c r="B475" s="2" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="C475" s="2" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="D475" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E475" s="2" t="s">
-        <v>1525</v>
+        <v>994</v>
       </c>
       <c r="F475" s="2" t="s">
         <v>12</v>
@@ -16230,16 +16233,16 @@
         <v>7</v>
       </c>
       <c r="B476" s="2" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="C476" s="2" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="D476" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E476" s="2" t="s">
-        <v>996</v>
+        <v>1553</v>
       </c>
       <c r="F476" s="2" t="s">
         <v>12</v>
@@ -16262,7 +16265,7 @@
         <v>10</v>
       </c>
       <c r="E477" s="2" t="s">
-        <v>1557</v>
+        <v>11</v>
       </c>
       <c r="F477" s="2" t="s">
         <v>12</v>
@@ -16285,7 +16288,7 @@
         <v>10</v>
       </c>
       <c r="E478" s="2" t="s">
-        <v>11</v>
+        <v>1001</v>
       </c>
       <c r="F478" s="2" t="s">
         <v>12</v>
@@ -16299,16 +16302,16 @@
         <v>7</v>
       </c>
       <c r="B479" s="2" t="s">
-        <v>1001</v>
+        <v>1497</v>
       </c>
       <c r="C479" s="2" t="s">
-        <v>1002</v>
+        <v>1498</v>
       </c>
       <c r="D479" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E479" s="2" t="s">
-        <v>1003</v>
+        <v>828</v>
       </c>
       <c r="F479" s="2" t="s">
         <v>12</v>
@@ -16322,16 +16325,16 @@
         <v>7</v>
       </c>
       <c r="B480" s="2" t="s">
-        <v>1499</v>
+        <v>1002</v>
       </c>
       <c r="C480" s="2" t="s">
-        <v>1500</v>
+        <v>1003</v>
       </c>
       <c r="D480" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E480" s="2" t="s">
-        <v>830</v>
+        <v>89</v>
       </c>
       <c r="F480" s="2" t="s">
         <v>12</v>
@@ -16354,7 +16357,7 @@
         <v>10</v>
       </c>
       <c r="E481" s="2" t="s">
-        <v>89</v>
+        <v>372</v>
       </c>
       <c r="F481" s="2" t="s">
         <v>12</v>
@@ -16377,7 +16380,7 @@
         <v>10</v>
       </c>
       <c r="E482" s="2" t="s">
-        <v>372</v>
+        <v>487</v>
       </c>
       <c r="F482" s="2" t="s">
         <v>12</v>
@@ -16400,7 +16403,7 @@
         <v>10</v>
       </c>
       <c r="E483" s="2" t="s">
-        <v>487</v>
+        <v>1500</v>
       </c>
       <c r="F483" s="2" t="s">
         <v>12</v>
@@ -16423,7 +16426,7 @@
         <v>10</v>
       </c>
       <c r="E484" s="2" t="s">
-        <v>1502</v>
+        <v>1529</v>
       </c>
       <c r="F484" s="2" t="s">
         <v>12</v>
@@ -16446,7 +16449,7 @@
         <v>10</v>
       </c>
       <c r="E485" s="2" t="s">
-        <v>1533</v>
+        <v>1014</v>
       </c>
       <c r="F485" s="2" t="s">
         <v>12</v>
@@ -16460,16 +16463,16 @@
         <v>7</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="C486" s="2" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="D486" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E486" s="2" t="s">
-        <v>1016</v>
+        <v>1589</v>
       </c>
       <c r="F486" s="2" t="s">
         <v>12</v>
@@ -16492,7 +16495,7 @@
         <v>10</v>
       </c>
       <c r="E487" s="2" t="s">
-        <v>1599</v>
+        <v>1340</v>
       </c>
       <c r="F487" s="2" t="s">
         <v>12</v>
@@ -16515,7 +16518,7 @@
         <v>10</v>
       </c>
       <c r="E488" s="2" t="s">
-        <v>1342</v>
+        <v>164</v>
       </c>
       <c r="F488" s="2" t="s">
         <v>12</v>
@@ -16538,7 +16541,7 @@
         <v>10</v>
       </c>
       <c r="E489" s="2" t="s">
-        <v>427</v>
+        <v>100</v>
       </c>
       <c r="F489" s="2" t="s">
         <v>12</v>
@@ -16561,7 +16564,7 @@
         <v>10</v>
       </c>
       <c r="E490" s="2" t="s">
-        <v>100</v>
+        <v>1590</v>
       </c>
       <c r="F490" s="2" t="s">
         <v>12</v>
@@ -16584,7 +16587,7 @@
         <v>10</v>
       </c>
       <c r="E491" s="2" t="s">
-        <v>1600</v>
+        <v>837</v>
       </c>
       <c r="F491" s="2" t="s">
         <v>12</v>
@@ -16607,7 +16610,7 @@
         <v>10</v>
       </c>
       <c r="E492" s="2" t="s">
-        <v>839</v>
+        <v>1591</v>
       </c>
       <c r="F492" s="2" t="s">
         <v>12</v>
@@ -16630,7 +16633,7 @@
         <v>10</v>
       </c>
       <c r="E493" s="2" t="s">
-        <v>1601</v>
+        <v>528</v>
       </c>
       <c r="F493" s="2" t="s">
         <v>12</v>
@@ -16653,7 +16656,7 @@
         <v>10</v>
       </c>
       <c r="E494" s="2" t="s">
-        <v>528</v>
+        <v>141</v>
       </c>
       <c r="F494" s="2" t="s">
         <v>12</v>
@@ -16676,7 +16679,7 @@
         <v>10</v>
       </c>
       <c r="E495" s="2" t="s">
-        <v>141</v>
+        <v>438</v>
       </c>
       <c r="F495" s="2" t="s">
         <v>12</v>
@@ -16699,7 +16702,7 @@
         <v>10</v>
       </c>
       <c r="E496" s="2" t="s">
-        <v>438</v>
+        <v>164</v>
       </c>
       <c r="F496" s="2" t="s">
         <v>12</v>
@@ -16722,7 +16725,7 @@
         <v>10</v>
       </c>
       <c r="E497" s="2" t="s">
-        <v>164</v>
+        <v>1592</v>
       </c>
       <c r="F497" s="2" t="s">
         <v>12</v>
@@ -16745,7 +16748,7 @@
         <v>10</v>
       </c>
       <c r="E498" s="2" t="s">
-        <v>1602</v>
+        <v>141</v>
       </c>
       <c r="F498" s="2" t="s">
         <v>12</v>
@@ -16759,16 +16762,16 @@
         <v>7</v>
       </c>
       <c r="B499" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C499" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D499" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E499" s="2" t="s">
         <v>1041</v>
-      </c>
-      <c r="C499" s="2" t="s">
-        <v>1042</v>
-      </c>
-      <c r="D499" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E499" s="2" t="s">
-        <v>141</v>
       </c>
       <c r="F499" s="2" t="s">
         <v>12</v>
@@ -16782,16 +16785,16 @@
         <v>7</v>
       </c>
       <c r="B500" s="2" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C500" s="2" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="D500" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E500" s="2" t="s">
-        <v>1043</v>
+        <v>220</v>
       </c>
       <c r="F500" s="2" t="s">
         <v>12</v>
@@ -16814,7 +16817,7 @@
         <v>10</v>
       </c>
       <c r="E501" s="2" t="s">
-        <v>220</v>
+        <v>703</v>
       </c>
       <c r="F501" s="2" t="s">
         <v>12</v>
@@ -16828,16 +16831,16 @@
         <v>7</v>
       </c>
       <c r="B502" s="2" t="s">
-        <v>1046</v>
+        <v>1522</v>
       </c>
       <c r="C502" s="2" t="s">
-        <v>1047</v>
+        <v>1523</v>
       </c>
       <c r="D502" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E502" s="2" t="s">
-        <v>705</v>
+        <v>81</v>
       </c>
       <c r="F502" s="2" t="s">
         <v>12</v>
@@ -16851,16 +16854,16 @@
         <v>7</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>1526</v>
+        <v>1046</v>
       </c>
       <c r="C503" s="2" t="s">
-        <v>1527</v>
+        <v>1047</v>
       </c>
       <c r="D503" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E503" s="2" t="s">
-        <v>81</v>
+        <v>1593</v>
       </c>
       <c r="F503" s="2" t="s">
         <v>12</v>
@@ -16880,10 +16883,10 @@
         <v>1049</v>
       </c>
       <c r="D504" s="2" t="s">
-        <v>10</v>
+        <v>417</v>
       </c>
       <c r="E504" s="2" t="s">
-        <v>1603</v>
+        <v>427</v>
       </c>
       <c r="F504" s="2" t="s">
         <v>12</v>
@@ -16903,13 +16906,13 @@
         <v>1051</v>
       </c>
       <c r="D505" s="2" t="s">
-        <v>417</v>
+        <v>138</v>
       </c>
       <c r="E505" s="2" t="s">
-        <v>427</v>
+        <v>72</v>
       </c>
       <c r="F505" s="2" t="s">
-        <v>12</v>
+        <v>192</v>
       </c>
       <c r="G505" s="2" t="s">
         <v>13</v>
@@ -16920,16 +16923,16 @@
         <v>7</v>
       </c>
       <c r="B506" s="2" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="C506" s="2" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D506" s="2" t="s">
-        <v>138</v>
+        <v>22</v>
       </c>
       <c r="E506" s="2" t="s">
-        <v>72</v>
+        <v>261</v>
       </c>
       <c r="F506" s="2" t="s">
         <v>192</v>
@@ -16949,13 +16952,13 @@
         <v>1053</v>
       </c>
       <c r="D507" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E507" s="2" t="s">
-        <v>261</v>
+        <v>226</v>
       </c>
       <c r="F507" s="2" t="s">
-        <v>192</v>
+        <v>12</v>
       </c>
       <c r="G507" s="2" t="s">
         <v>13</v>
@@ -16975,7 +16978,7 @@
         <v>10</v>
       </c>
       <c r="E508" s="2" t="s">
-        <v>226</v>
+        <v>21</v>
       </c>
       <c r="F508" s="2" t="s">
         <v>12</v>
@@ -16998,7 +17001,7 @@
         <v>10</v>
       </c>
       <c r="E509" s="2" t="s">
-        <v>21</v>
+        <v>1524</v>
       </c>
       <c r="F509" s="2" t="s">
         <v>12</v>
@@ -17021,7 +17024,7 @@
         <v>10</v>
       </c>
       <c r="E510" s="2" t="s">
-        <v>1528</v>
+        <v>84</v>
       </c>
       <c r="F510" s="2" t="s">
         <v>12</v>
@@ -17044,7 +17047,7 @@
         <v>10</v>
       </c>
       <c r="E511" s="2" t="s">
-        <v>84</v>
+        <v>226</v>
       </c>
       <c r="F511" s="2" t="s">
         <v>12</v>
@@ -17067,7 +17070,7 @@
         <v>10</v>
       </c>
       <c r="E512" s="2" t="s">
-        <v>226</v>
+        <v>1473</v>
       </c>
       <c r="F512" s="2" t="s">
         <v>12</v>
@@ -17090,7 +17093,7 @@
         <v>10</v>
       </c>
       <c r="E513" s="2" t="s">
-        <v>1475</v>
+        <v>191</v>
       </c>
       <c r="F513" s="2" t="s">
         <v>12</v>
@@ -17113,7 +17116,7 @@
         <v>10</v>
       </c>
       <c r="E514" s="2" t="s">
-        <v>191</v>
+        <v>764</v>
       </c>
       <c r="F514" s="2" t="s">
         <v>12</v>
@@ -17127,16 +17130,16 @@
         <v>7</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>1068</v>
+        <v>1525</v>
       </c>
       <c r="C515" s="2" t="s">
-        <v>1069</v>
+        <v>1526</v>
       </c>
       <c r="D515" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E515" s="2" t="s">
-        <v>766</v>
+        <v>164</v>
       </c>
       <c r="F515" s="2" t="s">
         <v>12</v>
@@ -17150,16 +17153,16 @@
         <v>7</v>
       </c>
       <c r="B516" s="2" t="s">
-        <v>1529</v>
+        <v>1068</v>
       </c>
       <c r="C516" s="2" t="s">
-        <v>1530</v>
+        <v>1069</v>
       </c>
       <c r="D516" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E516" s="2" t="s">
-        <v>164</v>
+        <v>1527</v>
       </c>
       <c r="F516" s="2" t="s">
         <v>12</v>
@@ -17179,10 +17182,10 @@
         <v>1071</v>
       </c>
       <c r="D517" s="2" t="s">
-        <v>10</v>
+        <v>1072</v>
       </c>
       <c r="E517" s="2" t="s">
-        <v>1531</v>
+        <v>1513</v>
       </c>
       <c r="F517" s="2" t="s">
         <v>12</v>
@@ -17196,16 +17199,16 @@
         <v>7</v>
       </c>
       <c r="B518" s="2" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="C518" s="2" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="D518" s="2" t="s">
-        <v>1074</v>
+        <v>22</v>
       </c>
       <c r="E518" s="2" t="s">
-        <v>1604</v>
+        <v>515</v>
       </c>
       <c r="F518" s="2" t="s">
         <v>12</v>
@@ -17219,16 +17222,16 @@
         <v>7</v>
       </c>
       <c r="B519" s="2" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="C519" s="2" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="D519" s="2" t="s">
-        <v>22</v>
+        <v>1072</v>
       </c>
       <c r="E519" s="2" t="s">
-        <v>515</v>
+        <v>1609</v>
       </c>
       <c r="F519" s="2" t="s">
         <v>12</v>
@@ -17248,10 +17251,10 @@
         <v>1076</v>
       </c>
       <c r="D520" s="2" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="E520" s="2" t="s">
-        <v>1558</v>
+        <v>65</v>
       </c>
       <c r="F520" s="2" t="s">
         <v>12</v>
@@ -17265,16 +17268,16 @@
         <v>7</v>
       </c>
       <c r="B521" s="2" t="s">
+        <v>1507</v>
+      </c>
+      <c r="C521" s="2" t="s">
+        <v>1508</v>
+      </c>
+      <c r="D521" s="2" t="s">
         <v>1077</v>
       </c>
-      <c r="C521" s="2" t="s">
-        <v>1078</v>
-      </c>
-      <c r="D521" s="2" t="s">
-        <v>1079</v>
-      </c>
       <c r="E521" s="2" t="s">
-        <v>72</v>
+        <v>271</v>
       </c>
       <c r="F521" s="2" t="s">
         <v>12</v>
@@ -17288,16 +17291,16 @@
         <v>7</v>
       </c>
       <c r="B522" s="2" t="s">
-        <v>1510</v>
+        <v>1610</v>
       </c>
       <c r="C522" s="2" t="s">
-        <v>1511</v>
+        <v>1611</v>
       </c>
       <c r="D522" s="2" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="E522" s="2" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="F522" s="2" t="s">
         <v>12</v>
@@ -17311,13 +17314,13 @@
         <v>7</v>
       </c>
       <c r="B523" s="2" t="s">
-        <v>1080</v>
+        <v>1612</v>
       </c>
       <c r="C523" s="2" t="s">
-        <v>1081</v>
+        <v>1613</v>
       </c>
       <c r="D523" s="2" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="E523" s="2" t="s">
         <v>81</v>
@@ -17334,16 +17337,16 @@
         <v>7</v>
       </c>
       <c r="B524" s="2" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
       <c r="C524" s="2" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="D524" s="2" t="s">
-        <v>22</v>
+        <v>1077</v>
       </c>
       <c r="E524" s="2" t="s">
-        <v>254</v>
+        <v>81</v>
       </c>
       <c r="F524" s="2" t="s">
         <v>12</v>
@@ -17357,16 +17360,16 @@
         <v>7</v>
       </c>
       <c r="B525" s="2" t="s">
-        <v>1084</v>
+        <v>1080</v>
       </c>
       <c r="C525" s="2" t="s">
-        <v>1085</v>
+        <v>1081</v>
       </c>
       <c r="D525" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E525" s="2" t="s">
-        <v>725</v>
+        <v>254</v>
       </c>
       <c r="F525" s="2" t="s">
         <v>12</v>
@@ -17380,16 +17383,16 @@
         <v>7</v>
       </c>
       <c r="B526" s="2" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="C526" s="2" t="s">
-        <v>1087</v>
+        <v>1083</v>
       </c>
       <c r="D526" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E526" s="2" t="s">
-        <v>563</v>
+        <v>723</v>
       </c>
       <c r="F526" s="2" t="s">
         <v>12</v>
@@ -17403,19 +17406,19 @@
         <v>7</v>
       </c>
       <c r="B527" s="2" t="s">
-        <v>1088</v>
+        <v>1084</v>
       </c>
       <c r="C527" s="2" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="D527" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E527" s="2" t="s">
-        <v>1486</v>
+        <v>563</v>
       </c>
       <c r="F527" s="2" t="s">
-        <v>114</v>
+        <v>12</v>
       </c>
       <c r="G527" s="2" t="s">
         <v>13</v>
@@ -17426,16 +17429,16 @@
         <v>7</v>
       </c>
       <c r="B528" s="2" t="s">
-        <v>1090</v>
+        <v>1086</v>
       </c>
       <c r="C528" s="2" t="s">
-        <v>1091</v>
+        <v>1087</v>
       </c>
       <c r="D528" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E528" s="2" t="s">
-        <v>1532</v>
+        <v>1484</v>
       </c>
       <c r="F528" s="2" t="s">
         <v>114</v>
@@ -17449,19 +17452,19 @@
         <v>7</v>
       </c>
       <c r="B529" s="2" t="s">
-        <v>1092</v>
+        <v>1088</v>
       </c>
       <c r="C529" s="2" t="s">
-        <v>1093</v>
+        <v>1089</v>
       </c>
       <c r="D529" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E529" s="2" t="s">
-        <v>92</v>
+        <v>1528</v>
       </c>
       <c r="F529" s="2" t="s">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="G529" s="2" t="s">
         <v>13</v>
@@ -17472,16 +17475,16 @@
         <v>7</v>
       </c>
       <c r="B530" s="2" t="s">
-        <v>1094</v>
+        <v>1090</v>
       </c>
       <c r="C530" s="2" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="D530" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E530" s="2" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="F530" s="2" t="s">
         <v>12</v>
@@ -17495,16 +17498,16 @@
         <v>7</v>
       </c>
       <c r="B531" s="2" t="s">
-        <v>1096</v>
+        <v>1092</v>
       </c>
       <c r="C531" s="2" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="D531" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E531" s="2" t="s">
-        <v>1559</v>
+        <v>48</v>
       </c>
       <c r="F531" s="2" t="s">
         <v>12</v>
@@ -17518,16 +17521,16 @@
         <v>7</v>
       </c>
       <c r="B532" s="2" t="s">
-        <v>1098</v>
+        <v>1094</v>
       </c>
       <c r="C532" s="2" t="s">
-        <v>1099</v>
+        <v>1095</v>
       </c>
       <c r="D532" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E532" s="2" t="s">
-        <v>223</v>
+        <v>1555</v>
       </c>
       <c r="F532" s="2" t="s">
         <v>12</v>
@@ -17541,16 +17544,16 @@
         <v>7</v>
       </c>
       <c r="B533" s="2" t="s">
-        <v>1100</v>
+        <v>1096</v>
       </c>
       <c r="C533" s="2" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="D533" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E533" s="2" t="s">
-        <v>1605</v>
+        <v>223</v>
       </c>
       <c r="F533" s="2" t="s">
         <v>12</v>
@@ -17564,16 +17567,16 @@
         <v>7</v>
       </c>
       <c r="B534" s="2" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
       <c r="C534" s="2" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="D534" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E534" s="2" t="s">
-        <v>141</v>
+        <v>1614</v>
       </c>
       <c r="F534" s="2" t="s">
         <v>12</v>
@@ -17587,16 +17590,16 @@
         <v>7</v>
       </c>
       <c r="B535" s="2" t="s">
-        <v>1104</v>
+        <v>1100</v>
       </c>
       <c r="C535" s="2" t="s">
-        <v>1105</v>
+        <v>1101</v>
       </c>
       <c r="D535" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E535" s="2" t="s">
-        <v>438</v>
+        <v>141</v>
       </c>
       <c r="F535" s="2" t="s">
         <v>12</v>
@@ -17610,16 +17613,16 @@
         <v>7</v>
       </c>
       <c r="B536" s="2" t="s">
-        <v>1106</v>
+        <v>1102</v>
       </c>
       <c r="C536" s="2" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="D536" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E536" s="2" t="s">
-        <v>1560</v>
+        <v>438</v>
       </c>
       <c r="F536" s="2" t="s">
         <v>12</v>
@@ -17633,16 +17636,16 @@
         <v>7</v>
       </c>
       <c r="B537" s="2" t="s">
-        <v>1108</v>
+        <v>1104</v>
       </c>
       <c r="C537" s="2" t="s">
-        <v>1109</v>
+        <v>1105</v>
       </c>
       <c r="D537" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E537" s="2" t="s">
-        <v>89</v>
+        <v>1556</v>
       </c>
       <c r="F537" s="2" t="s">
         <v>12</v>
@@ -17656,16 +17659,16 @@
         <v>7</v>
       </c>
       <c r="B538" s="2" t="s">
-        <v>1110</v>
+        <v>1106</v>
       </c>
       <c r="C538" s="2" t="s">
-        <v>1111</v>
+        <v>1107</v>
       </c>
       <c r="D538" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E538" s="2" t="s">
-        <v>1606</v>
+        <v>89</v>
       </c>
       <c r="F538" s="2" t="s">
         <v>12</v>
@@ -17679,16 +17682,16 @@
         <v>7</v>
       </c>
       <c r="B539" s="2" t="s">
-        <v>1112</v>
+        <v>1108</v>
       </c>
       <c r="C539" s="2" t="s">
-        <v>1113</v>
+        <v>1109</v>
       </c>
       <c r="D539" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E539" s="2" t="s">
-        <v>1561</v>
+        <v>1594</v>
       </c>
       <c r="F539" s="2" t="s">
         <v>12</v>
@@ -17702,16 +17705,16 @@
         <v>7</v>
       </c>
       <c r="B540" s="2" t="s">
-        <v>1114</v>
+        <v>1110</v>
       </c>
       <c r="C540" s="2" t="s">
-        <v>1115</v>
+        <v>1111</v>
       </c>
       <c r="D540" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E540" s="2" t="s">
-        <v>1501</v>
+        <v>1615</v>
       </c>
       <c r="F540" s="2" t="s">
         <v>12</v>
@@ -17725,16 +17728,16 @@
         <v>7</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>1116</v>
+        <v>1112</v>
       </c>
       <c r="C541" s="2" t="s">
-        <v>1117</v>
+        <v>1113</v>
       </c>
       <c r="D541" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E541" s="2" t="s">
-        <v>1607</v>
+        <v>1499</v>
       </c>
       <c r="F541" s="2" t="s">
         <v>12</v>
@@ -17748,16 +17751,16 @@
         <v>7</v>
       </c>
       <c r="B542" s="2" t="s">
-        <v>1118</v>
+        <v>1114</v>
       </c>
       <c r="C542" s="2" t="s">
-        <v>1119</v>
+        <v>1115</v>
       </c>
       <c r="D542" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E542" s="2" t="s">
-        <v>1608</v>
+        <v>1595</v>
       </c>
       <c r="F542" s="2" t="s">
         <v>12</v>
@@ -17771,16 +17774,16 @@
         <v>7</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>1120</v>
+        <v>1116</v>
       </c>
       <c r="C543" s="2" t="s">
-        <v>1121</v>
+        <v>1117</v>
       </c>
       <c r="D543" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E543" s="2" t="s">
-        <v>109</v>
+        <v>1596</v>
       </c>
       <c r="F543" s="2" t="s">
         <v>12</v>
@@ -17794,16 +17797,16 @@
         <v>7</v>
       </c>
       <c r="B544" s="2" t="s">
-        <v>1122</v>
+        <v>1118</v>
       </c>
       <c r="C544" s="2" t="s">
-        <v>1123</v>
+        <v>1119</v>
       </c>
       <c r="D544" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E544" s="2" t="s">
-        <v>141</v>
+        <v>109</v>
       </c>
       <c r="F544" s="2" t="s">
         <v>12</v>
@@ -17817,16 +17820,16 @@
         <v>7</v>
       </c>
       <c r="B545" s="2" t="s">
-        <v>1124</v>
+        <v>1120</v>
       </c>
       <c r="C545" s="2" t="s">
-        <v>1125</v>
+        <v>1121</v>
       </c>
       <c r="D545" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E545" s="2" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="F545" s="2" t="s">
         <v>12</v>
@@ -17840,16 +17843,16 @@
         <v>7</v>
       </c>
       <c r="B546" s="2" t="s">
-        <v>1126</v>
+        <v>1122</v>
       </c>
       <c r="C546" s="2" t="s">
-        <v>1127</v>
+        <v>1123</v>
       </c>
       <c r="D546" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E546" s="2" t="s">
-        <v>438</v>
+        <v>109</v>
       </c>
       <c r="F546" s="2" t="s">
         <v>12</v>
@@ -17863,16 +17866,16 @@
         <v>7</v>
       </c>
       <c r="B547" s="2" t="s">
-        <v>1128</v>
+        <v>1124</v>
       </c>
       <c r="C547" s="2" t="s">
-        <v>1129</v>
+        <v>1125</v>
       </c>
       <c r="D547" s="2" t="s">
-        <v>138</v>
+        <v>10</v>
       </c>
       <c r="E547" s="2" t="s">
-        <v>164</v>
+        <v>438</v>
       </c>
       <c r="F547" s="2" t="s">
         <v>12</v>
@@ -17886,16 +17889,16 @@
         <v>7</v>
       </c>
       <c r="B548" s="2" t="s">
-        <v>1130</v>
+        <v>1126</v>
       </c>
       <c r="C548" s="2" t="s">
-        <v>1131</v>
+        <v>1127</v>
       </c>
       <c r="D548" s="2" t="s">
         <v>138</v>
       </c>
       <c r="E548" s="2" t="s">
-        <v>1583</v>
+        <v>164</v>
       </c>
       <c r="F548" s="2" t="s">
         <v>12</v>
@@ -17909,16 +17912,16 @@
         <v>7</v>
       </c>
       <c r="B549" s="2" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="C549" s="2" t="s">
-        <v>1133</v>
+        <v>1129</v>
       </c>
       <c r="D549" s="2" t="s">
         <v>138</v>
       </c>
       <c r="E549" s="2" t="s">
-        <v>178</v>
+        <v>1575</v>
       </c>
       <c r="F549" s="2" t="s">
         <v>12</v>
@@ -17932,16 +17935,16 @@
         <v>7</v>
       </c>
       <c r="B550" s="2" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
       <c r="C550" s="2" t="s">
-        <v>1135</v>
+        <v>1131</v>
       </c>
       <c r="D550" s="2" t="s">
-        <v>10</v>
+        <v>138</v>
       </c>
       <c r="E550" s="2" t="s">
-        <v>32</v>
+        <v>178</v>
       </c>
       <c r="F550" s="2" t="s">
         <v>12</v>
@@ -17955,16 +17958,16 @@
         <v>7</v>
       </c>
       <c r="B551" s="2" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="C551" s="2" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="D551" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E551" s="2" t="s">
-        <v>830</v>
+        <v>32</v>
       </c>
       <c r="F551" s="2" t="s">
         <v>12</v>
@@ -17978,16 +17981,16 @@
         <v>7</v>
       </c>
       <c r="B552" s="2" t="s">
-        <v>1136</v>
+        <v>1132</v>
       </c>
       <c r="C552" s="2" t="s">
-        <v>1137</v>
+        <v>1133</v>
       </c>
       <c r="D552" s="2" t="s">
-        <v>138</v>
+        <v>22</v>
       </c>
       <c r="E552" s="2" t="s">
-        <v>84</v>
+        <v>828</v>
       </c>
       <c r="F552" s="2" t="s">
         <v>12</v>
@@ -18001,19 +18004,19 @@
         <v>7</v>
       </c>
       <c r="B553" s="2" t="s">
-        <v>1138</v>
+        <v>1134</v>
       </c>
       <c r="C553" s="2" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
       <c r="D553" s="2" t="s">
-        <v>484</v>
+        <v>138</v>
       </c>
       <c r="E553" s="2" t="s">
-        <v>1534</v>
+        <v>84</v>
       </c>
       <c r="F553" s="2" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="G553" s="2" t="s">
         <v>13</v>
@@ -18024,19 +18027,19 @@
         <v>7</v>
       </c>
       <c r="B554" s="2" t="s">
-        <v>1140</v>
+        <v>1136</v>
       </c>
       <c r="C554" s="2" t="s">
-        <v>1141</v>
+        <v>1137</v>
       </c>
       <c r="D554" s="2" t="s">
-        <v>10</v>
+        <v>484</v>
       </c>
       <c r="E554" s="2" t="s">
-        <v>1609</v>
+        <v>1530</v>
       </c>
       <c r="F554" s="2" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="G554" s="2" t="s">
         <v>13</v>
@@ -18047,16 +18050,16 @@
         <v>7</v>
       </c>
       <c r="B555" s="2" t="s">
-        <v>1142</v>
+        <v>1138</v>
       </c>
       <c r="C555" s="2" t="s">
-        <v>1143</v>
+        <v>1139</v>
       </c>
       <c r="D555" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E555" s="2" t="s">
-        <v>11</v>
+        <v>1597</v>
       </c>
       <c r="F555" s="2" t="s">
         <v>12</v>
@@ -18070,16 +18073,16 @@
         <v>7</v>
       </c>
       <c r="B556" s="2" t="s">
-        <v>1144</v>
+        <v>1140</v>
       </c>
       <c r="C556" s="2" t="s">
-        <v>1145</v>
+        <v>1141</v>
       </c>
       <c r="D556" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E556" s="2" t="s">
-        <v>223</v>
+        <v>11</v>
       </c>
       <c r="F556" s="2" t="s">
         <v>12</v>
@@ -18093,16 +18096,16 @@
         <v>7</v>
       </c>
       <c r="B557" s="2" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
       <c r="C557" s="2" t="s">
-        <v>1147</v>
+        <v>1143</v>
       </c>
       <c r="D557" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E557" s="2" t="s">
-        <v>1487</v>
+        <v>223</v>
       </c>
       <c r="F557" s="2" t="s">
         <v>12</v>
@@ -18116,16 +18119,16 @@
         <v>7</v>
       </c>
       <c r="B558" s="2" t="s">
-        <v>1148</v>
+        <v>1144</v>
       </c>
       <c r="C558" s="2" t="s">
-        <v>1149</v>
+        <v>1145</v>
       </c>
       <c r="D558" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E558" s="2" t="s">
-        <v>164</v>
+        <v>1485</v>
       </c>
       <c r="F558" s="2" t="s">
         <v>12</v>
@@ -18139,16 +18142,16 @@
         <v>7</v>
       </c>
       <c r="B559" s="2" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="C559" s="2" t="s">
-        <v>1151</v>
+        <v>1147</v>
       </c>
       <c r="D559" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E559" s="2" t="s">
-        <v>1491</v>
+        <v>164</v>
       </c>
       <c r="F559" s="2" t="s">
         <v>12</v>
@@ -18162,19 +18165,19 @@
         <v>7</v>
       </c>
       <c r="B560" s="2" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="C560" s="2" t="s">
-        <v>1153</v>
+        <v>1149</v>
       </c>
       <c r="D560" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E560" s="2" t="s">
-        <v>48</v>
+        <v>1489</v>
       </c>
       <c r="F560" s="2" t="s">
-        <v>114</v>
+        <v>12</v>
       </c>
       <c r="G560" s="2" t="s">
         <v>13</v>
@@ -18185,19 +18188,19 @@
         <v>7</v>
       </c>
       <c r="B561" s="2" t="s">
-        <v>1154</v>
+        <v>1150</v>
       </c>
       <c r="C561" s="2" t="s">
-        <v>1155</v>
+        <v>1151</v>
       </c>
       <c r="D561" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E561" s="2" t="s">
-        <v>1156</v>
+        <v>48</v>
       </c>
       <c r="F561" s="2" t="s">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="G561" s="2" t="s">
         <v>13</v>
@@ -18208,16 +18211,16 @@
         <v>7</v>
       </c>
       <c r="B562" s="2" t="s">
-        <v>1157</v>
+        <v>1152</v>
       </c>
       <c r="C562" s="2" t="s">
-        <v>1158</v>
+        <v>1153</v>
       </c>
       <c r="D562" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E562" s="2" t="s">
-        <v>178</v>
+        <v>1154</v>
       </c>
       <c r="F562" s="2" t="s">
         <v>12</v>
@@ -18231,16 +18234,16 @@
         <v>7</v>
       </c>
       <c r="B563" s="2" t="s">
-        <v>1159</v>
+        <v>1155</v>
       </c>
       <c r="C563" s="2" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
       <c r="D563" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E563" s="2" t="s">
-        <v>1161</v>
+        <v>178</v>
       </c>
       <c r="F563" s="2" t="s">
         <v>12</v>
@@ -18254,16 +18257,16 @@
         <v>7</v>
       </c>
       <c r="B564" s="2" t="s">
-        <v>1162</v>
+        <v>1157</v>
       </c>
       <c r="C564" s="2" t="s">
-        <v>1163</v>
+        <v>1158</v>
       </c>
       <c r="D564" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E564" s="2" t="s">
-        <v>167</v>
+        <v>1159</v>
       </c>
       <c r="F564" s="2" t="s">
         <v>12</v>
@@ -18277,16 +18280,16 @@
         <v>7</v>
       </c>
       <c r="B565" s="2" t="s">
-        <v>1164</v>
+        <v>1160</v>
       </c>
       <c r="C565" s="2" t="s">
-        <v>1165</v>
+        <v>1161</v>
       </c>
       <c r="D565" s="2" t="s">
-        <v>138</v>
+        <v>10</v>
       </c>
       <c r="E565" s="2" t="s">
-        <v>72</v>
+        <v>167</v>
       </c>
       <c r="F565" s="2" t="s">
         <v>12</v>
@@ -18300,16 +18303,16 @@
         <v>7</v>
       </c>
       <c r="B566" s="2" t="s">
-        <v>1166</v>
+        <v>1162</v>
       </c>
       <c r="C566" s="2" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="D566" s="2" t="s">
-        <v>10</v>
+        <v>138</v>
       </c>
       <c r="E566" s="2" t="s">
-        <v>254</v>
+        <v>72</v>
       </c>
       <c r="F566" s="2" t="s">
         <v>12</v>
@@ -18323,16 +18326,16 @@
         <v>7</v>
       </c>
       <c r="B567" s="2" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="C567" s="2" t="s">
-        <v>1169</v>
+        <v>1165</v>
       </c>
       <c r="D567" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E567" s="2" t="s">
-        <v>628</v>
+        <v>254</v>
       </c>
       <c r="F567" s="2" t="s">
         <v>12</v>
@@ -18346,19 +18349,19 @@
         <v>7</v>
       </c>
       <c r="B568" s="2" t="s">
-        <v>1170</v>
+        <v>1166</v>
       </c>
       <c r="C568" s="2" t="s">
-        <v>1171</v>
+        <v>1167</v>
       </c>
       <c r="D568" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E568" s="2" t="s">
-        <v>1535</v>
+        <v>626</v>
       </c>
       <c r="F568" s="2" t="s">
-        <v>114</v>
+        <v>12</v>
       </c>
       <c r="G568" s="2" t="s">
         <v>13</v>
@@ -18369,19 +18372,19 @@
         <v>7</v>
       </c>
       <c r="B569" s="2" t="s">
-        <v>1172</v>
+        <v>1168</v>
       </c>
       <c r="C569" s="2" t="s">
-        <v>1173</v>
+        <v>1169</v>
       </c>
       <c r="D569" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E569" s="2" t="s">
-        <v>427</v>
+        <v>1531</v>
       </c>
       <c r="F569" s="2" t="s">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="G569" s="2" t="s">
         <v>13</v>
@@ -18392,16 +18395,16 @@
         <v>7</v>
       </c>
       <c r="B570" s="2" t="s">
-        <v>1468</v>
+        <v>1170</v>
       </c>
       <c r="C570" s="2" t="s">
-        <v>1469</v>
+        <v>1171</v>
       </c>
       <c r="D570" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E570" s="2" t="s">
-        <v>81</v>
+        <v>427</v>
       </c>
       <c r="F570" s="2" t="s">
         <v>12</v>
@@ -18415,16 +18418,16 @@
         <v>7</v>
       </c>
       <c r="B571" s="2" t="s">
-        <v>1174</v>
+        <v>1466</v>
       </c>
       <c r="C571" s="2" t="s">
-        <v>1175</v>
+        <v>1467</v>
       </c>
       <c r="D571" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E571" s="2" t="s">
-        <v>418</v>
+        <v>81</v>
       </c>
       <c r="F571" s="2" t="s">
         <v>12</v>
@@ -18438,16 +18441,16 @@
         <v>7</v>
       </c>
       <c r="B572" s="2" t="s">
-        <v>1176</v>
+        <v>1172</v>
       </c>
       <c r="C572" s="2" t="s">
-        <v>1177</v>
+        <v>1173</v>
       </c>
       <c r="D572" s="2" t="s">
-        <v>138</v>
+        <v>10</v>
       </c>
       <c r="E572" s="2" t="s">
-        <v>21</v>
+        <v>418</v>
       </c>
       <c r="F572" s="2" t="s">
         <v>12</v>
@@ -18461,16 +18464,16 @@
         <v>7</v>
       </c>
       <c r="B573" s="2" t="s">
-        <v>1178</v>
+        <v>1174</v>
       </c>
       <c r="C573" s="2" t="s">
-        <v>1179</v>
+        <v>1175</v>
       </c>
       <c r="D573" s="2" t="s">
         <v>138</v>
       </c>
       <c r="E573" s="2" t="s">
-        <v>1610</v>
+        <v>21</v>
       </c>
       <c r="F573" s="2" t="s">
         <v>12</v>
@@ -18484,16 +18487,16 @@
         <v>7</v>
       </c>
       <c r="B574" s="2" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="C574" s="2" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="D574" s="2" t="s">
-        <v>22</v>
+        <v>138</v>
       </c>
       <c r="E574" s="2" t="s">
-        <v>1562</v>
+        <v>1598</v>
       </c>
       <c r="F574" s="2" t="s">
         <v>12</v>
@@ -18507,16 +18510,16 @@
         <v>7</v>
       </c>
       <c r="B575" s="2" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="C575" s="2" t="s">
-        <v>1181</v>
+        <v>1177</v>
       </c>
       <c r="D575" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E575" s="2" t="s">
-        <v>1606</v>
+        <v>1557</v>
       </c>
       <c r="F575" s="2" t="s">
         <v>12</v>
@@ -18530,16 +18533,16 @@
         <v>7</v>
       </c>
       <c r="B576" s="2" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="C576" s="2" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="D576" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E576" s="2" t="s">
-        <v>1611</v>
+        <v>1594</v>
       </c>
       <c r="F576" s="2" t="s">
         <v>12</v>
@@ -18553,16 +18556,16 @@
         <v>7</v>
       </c>
       <c r="B577" s="2" t="s">
-        <v>1182</v>
+        <v>1178</v>
       </c>
       <c r="C577" s="2" t="s">
-        <v>1183</v>
+        <v>1179</v>
       </c>
       <c r="D577" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E577" s="2" t="s">
-        <v>264</v>
+        <v>1599</v>
       </c>
       <c r="F577" s="2" t="s">
         <v>12</v>
@@ -18576,16 +18579,16 @@
         <v>7</v>
       </c>
       <c r="B578" s="2" t="s">
-        <v>1185</v>
+        <v>1180</v>
       </c>
       <c r="C578" s="2" t="s">
-        <v>1186</v>
+        <v>1181</v>
       </c>
       <c r="D578" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E578" s="2" t="s">
-        <v>254</v>
+        <v>1616</v>
       </c>
       <c r="F578" s="2" t="s">
         <v>12</v>
@@ -18599,16 +18602,16 @@
         <v>7</v>
       </c>
       <c r="B579" s="2" t="s">
-        <v>1187</v>
+        <v>1183</v>
       </c>
       <c r="C579" s="2" t="s">
-        <v>1188</v>
+        <v>1184</v>
       </c>
       <c r="D579" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E579" s="2" t="s">
-        <v>538</v>
+        <v>254</v>
       </c>
       <c r="F579" s="2" t="s">
         <v>12</v>
@@ -18622,10 +18625,10 @@
         <v>7</v>
       </c>
       <c r="B580" s="2" t="s">
-        <v>1189</v>
+        <v>1185</v>
       </c>
       <c r="C580" s="2" t="s">
-        <v>1190</v>
+        <v>1186</v>
       </c>
       <c r="D580" s="2" t="s">
         <v>10</v>
@@ -18645,16 +18648,16 @@
         <v>7</v>
       </c>
       <c r="B581" s="2" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="C581" s="2" t="s">
-        <v>1192</v>
+        <v>1188</v>
       </c>
       <c r="D581" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E581" s="2" t="s">
-        <v>48</v>
+        <v>538</v>
       </c>
       <c r="F581" s="2" t="s">
         <v>12</v>
@@ -18668,16 +18671,16 @@
         <v>7</v>
       </c>
       <c r="B582" s="2" t="s">
-        <v>1193</v>
+        <v>1189</v>
       </c>
       <c r="C582" s="2" t="s">
-        <v>1194</v>
+        <v>1190</v>
       </c>
       <c r="D582" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E582" s="2" t="s">
-        <v>1612</v>
+        <v>48</v>
       </c>
       <c r="F582" s="2" t="s">
         <v>12</v>
@@ -18691,16 +18694,16 @@
         <v>7</v>
       </c>
       <c r="B583" s="2" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="C583" s="2" t="s">
-        <v>1196</v>
+        <v>1192</v>
       </c>
       <c r="D583" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E583" s="2" t="s">
-        <v>993</v>
+        <v>1600</v>
       </c>
       <c r="F583" s="2" t="s">
         <v>12</v>
@@ -18714,16 +18717,16 @@
         <v>7</v>
       </c>
       <c r="B584" s="2" t="s">
-        <v>1197</v>
+        <v>1193</v>
       </c>
       <c r="C584" s="2" t="s">
-        <v>1198</v>
+        <v>1194</v>
       </c>
       <c r="D584" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E584" s="2" t="s">
-        <v>364</v>
+        <v>991</v>
       </c>
       <c r="F584" s="2" t="s">
         <v>12</v>
@@ -18737,16 +18740,16 @@
         <v>7</v>
       </c>
       <c r="B585" s="2" t="s">
-        <v>1199</v>
+        <v>1195</v>
       </c>
       <c r="C585" s="2" t="s">
-        <v>1200</v>
+        <v>1196</v>
       </c>
       <c r="D585" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E585" s="2" t="s">
-        <v>1613</v>
+        <v>364</v>
       </c>
       <c r="F585" s="2" t="s">
         <v>12</v>
@@ -18760,16 +18763,16 @@
         <v>7</v>
       </c>
       <c r="B586" s="2" t="s">
-        <v>1201</v>
+        <v>1197</v>
       </c>
       <c r="C586" s="2" t="s">
-        <v>1202</v>
+        <v>1198</v>
       </c>
       <c r="D586" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E586" s="2" t="s">
-        <v>45</v>
+        <v>1601</v>
       </c>
       <c r="F586" s="2" t="s">
         <v>12</v>
@@ -18783,19 +18786,19 @@
         <v>7</v>
       </c>
       <c r="B587" s="2" t="s">
-        <v>1203</v>
+        <v>1199</v>
       </c>
       <c r="C587" s="2" t="s">
-        <v>1204</v>
+        <v>1200</v>
       </c>
       <c r="D587" s="2" t="s">
-        <v>138</v>
+        <v>10</v>
       </c>
       <c r="E587" s="2" t="s">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="F587" s="2" t="s">
-        <v>192</v>
+        <v>12</v>
       </c>
       <c r="G587" s="2" t="s">
         <v>13</v>
@@ -18806,16 +18809,16 @@
         <v>7</v>
       </c>
       <c r="B588" s="2" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="C588" s="2" t="s">
-        <v>1206</v>
+        <v>1202</v>
       </c>
       <c r="D588" s="2" t="s">
         <v>138</v>
       </c>
       <c r="E588" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="F588" s="2" t="s">
         <v>192</v>
@@ -18829,16 +18832,16 @@
         <v>7</v>
       </c>
       <c r="B589" s="2" t="s">
-        <v>1207</v>
+        <v>1203</v>
       </c>
       <c r="C589" s="2" t="s">
-        <v>1208</v>
+        <v>1204</v>
       </c>
       <c r="D589" s="2" t="s">
         <v>138</v>
       </c>
       <c r="E589" s="2" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="F589" s="2" t="s">
         <v>192</v>
@@ -18852,16 +18855,16 @@
         <v>7</v>
       </c>
       <c r="B590" s="2" t="s">
-        <v>1209</v>
+        <v>1205</v>
       </c>
       <c r="C590" s="2" t="s">
-        <v>1210</v>
+        <v>1206</v>
       </c>
       <c r="D590" s="2" t="s">
         <v>138</v>
       </c>
       <c r="E590" s="2" t="s">
-        <v>418</v>
+        <v>72</v>
       </c>
       <c r="F590" s="2" t="s">
         <v>192</v>
@@ -18875,16 +18878,16 @@
         <v>7</v>
       </c>
       <c r="B591" s="2" t="s">
-        <v>1211</v>
+        <v>1207</v>
       </c>
       <c r="C591" s="2" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="D591" s="2" t="s">
         <v>138</v>
       </c>
       <c r="E591" s="2" t="s">
-        <v>141</v>
+        <v>418</v>
       </c>
       <c r="F591" s="2" t="s">
         <v>192</v>
@@ -18898,16 +18901,16 @@
         <v>7</v>
       </c>
       <c r="B592" s="2" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="C592" s="2" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="D592" s="2" t="s">
-        <v>22</v>
+        <v>138</v>
       </c>
       <c r="E592" s="2" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="F592" s="2" t="s">
         <v>192</v>
@@ -18921,16 +18924,16 @@
         <v>7</v>
       </c>
       <c r="B593" s="2" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="C593" s="2" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="D593" s="2" t="s">
-        <v>138</v>
+        <v>22</v>
       </c>
       <c r="E593" s="2" t="s">
-        <v>26</v>
+        <v>155</v>
       </c>
       <c r="F593" s="2" t="s">
         <v>192</v>
@@ -18944,16 +18947,16 @@
         <v>7</v>
       </c>
       <c r="B594" s="2" t="s">
-        <v>1213</v>
+        <v>1210</v>
       </c>
       <c r="C594" s="2" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="D594" s="2" t="s">
         <v>138</v>
       </c>
       <c r="E594" s="2" t="s">
-        <v>89</v>
+        <v>1606</v>
       </c>
       <c r="F594" s="2" t="s">
         <v>192</v>
@@ -18967,16 +18970,16 @@
         <v>7</v>
       </c>
       <c r="B595" s="2" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="C595" s="2" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="D595" s="2" t="s">
         <v>138</v>
       </c>
       <c r="E595" s="2" t="s">
-        <v>418</v>
+        <v>89</v>
       </c>
       <c r="F595" s="2" t="s">
         <v>192</v>
@@ -18990,16 +18993,16 @@
         <v>7</v>
       </c>
       <c r="B596" s="2" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="C596" s="2" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="D596" s="2" t="s">
         <v>138</v>
       </c>
       <c r="E596" s="2" t="s">
-        <v>361</v>
+        <v>418</v>
       </c>
       <c r="F596" s="2" t="s">
         <v>192</v>
@@ -19013,16 +19016,16 @@
         <v>7</v>
       </c>
       <c r="B597" s="2" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="C597" s="2" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="D597" s="2" t="s">
-        <v>22</v>
+        <v>138</v>
       </c>
       <c r="E597" s="2" t="s">
-        <v>226</v>
+        <v>361</v>
       </c>
       <c r="F597" s="2" t="s">
         <v>192</v>
@@ -19036,16 +19039,16 @@
         <v>7</v>
       </c>
       <c r="B598" s="2" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="C598" s="2" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="D598" s="2" t="s">
-        <v>138</v>
+        <v>22</v>
       </c>
       <c r="E598" s="2" t="s">
-        <v>590</v>
+        <v>226</v>
       </c>
       <c r="F598" s="2" t="s">
         <v>192</v>
@@ -19059,16 +19062,16 @@
         <v>7</v>
       </c>
       <c r="B599" s="2" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="C599" s="2" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="D599" s="2" t="s">
         <v>138</v>
       </c>
       <c r="E599" s="2" t="s">
-        <v>615</v>
+        <v>588</v>
       </c>
       <c r="F599" s="2" t="s">
         <v>192</v>
@@ -19082,16 +19085,16 @@
         <v>7</v>
       </c>
       <c r="B600" s="2" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
       <c r="C600" s="2" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="D600" s="2" t="s">
         <v>138</v>
       </c>
       <c r="E600" s="2" t="s">
-        <v>551</v>
+        <v>613</v>
       </c>
       <c r="F600" s="2" t="s">
         <v>192</v>
@@ -19105,16 +19108,16 @@
         <v>7</v>
       </c>
       <c r="B601" s="2" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="C601" s="2" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="D601" s="2" t="s">
         <v>138</v>
       </c>
       <c r="E601" s="2" t="s">
-        <v>1563</v>
+        <v>551</v>
       </c>
       <c r="F601" s="2" t="s">
         <v>192</v>
@@ -19128,16 +19131,16 @@
         <v>7</v>
       </c>
       <c r="B602" s="2" t="s">
-        <v>1220</v>
+        <v>1217</v>
       </c>
       <c r="C602" s="2" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="D602" s="2" t="s">
         <v>138</v>
       </c>
       <c r="E602" s="2" t="s">
-        <v>247</v>
+        <v>1617</v>
       </c>
       <c r="F602" s="2" t="s">
         <v>192</v>
@@ -19151,16 +19154,16 @@
         <v>7</v>
       </c>
       <c r="B603" s="2" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="C603" s="2" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="D603" s="2" t="s">
         <v>138</v>
       </c>
       <c r="E603" s="2" t="s">
-        <v>32</v>
+        <v>247</v>
       </c>
       <c r="F603" s="2" t="s">
         <v>192</v>
@@ -19174,19 +19177,19 @@
         <v>7</v>
       </c>
       <c r="B604" s="2" t="s">
-        <v>1222</v>
+        <v>1219</v>
       </c>
       <c r="C604" s="2" t="s">
-        <v>1223</v>
+        <v>1208</v>
       </c>
       <c r="D604" s="2" t="s">
-        <v>10</v>
+        <v>138</v>
       </c>
       <c r="E604" s="2" t="s">
-        <v>1224</v>
+        <v>32</v>
       </c>
       <c r="F604" s="2" t="s">
-        <v>12</v>
+        <v>192</v>
       </c>
       <c r="G604" s="2" t="s">
         <v>13</v>
@@ -19197,16 +19200,16 @@
         <v>7</v>
       </c>
       <c r="B605" s="2" t="s">
-        <v>1225</v>
+        <v>1220</v>
       </c>
       <c r="C605" s="2" t="s">
-        <v>1226</v>
+        <v>1221</v>
       </c>
       <c r="D605" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E605" s="2" t="s">
-        <v>155</v>
+        <v>1222</v>
       </c>
       <c r="F605" s="2" t="s">
         <v>12</v>
@@ -19220,19 +19223,19 @@
         <v>7</v>
       </c>
       <c r="B606" s="2" t="s">
-        <v>1227</v>
+        <v>1223</v>
       </c>
       <c r="C606" s="2" t="s">
-        <v>1228</v>
+        <v>1224</v>
       </c>
       <c r="D606" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E606" s="2" t="s">
-        <v>65</v>
+        <v>155</v>
       </c>
       <c r="F606" s="2" t="s">
-        <v>114</v>
+        <v>12</v>
       </c>
       <c r="G606" s="2" t="s">
         <v>13</v>
@@ -19243,19 +19246,19 @@
         <v>7</v>
       </c>
       <c r="B607" s="2" t="s">
-        <v>1229</v>
+        <v>1225</v>
       </c>
       <c r="C607" s="2" t="s">
-        <v>1230</v>
+        <v>1226</v>
       </c>
       <c r="D607" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E607" s="2" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="F607" s="2" t="s">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="G607" s="2" t="s">
         <v>13</v>
@@ -19266,16 +19269,16 @@
         <v>7</v>
       </c>
       <c r="B608" s="2" t="s">
-        <v>1231</v>
+        <v>1227</v>
       </c>
       <c r="C608" s="2" t="s">
-        <v>1232</v>
+        <v>1228</v>
       </c>
       <c r="D608" s="2" t="s">
-        <v>1233</v>
+        <v>10</v>
       </c>
       <c r="E608" s="2" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="F608" s="2" t="s">
         <v>12</v>
@@ -19289,16 +19292,16 @@
         <v>7</v>
       </c>
       <c r="B609" s="2" t="s">
-        <v>1234</v>
+        <v>1229</v>
       </c>
       <c r="C609" s="2" t="s">
-        <v>1235</v>
+        <v>1230</v>
       </c>
       <c r="D609" s="2" t="s">
-        <v>10</v>
+        <v>1231</v>
       </c>
       <c r="E609" s="2" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="F609" s="2" t="s">
         <v>12</v>
@@ -19312,16 +19315,16 @@
         <v>7</v>
       </c>
       <c r="B610" s="2" t="s">
-        <v>1236</v>
+        <v>1232</v>
       </c>
       <c r="C610" s="2" t="s">
-        <v>1237</v>
+        <v>1233</v>
       </c>
       <c r="D610" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E610" s="2" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="F610" s="2" t="s">
         <v>12</v>
@@ -19335,16 +19338,16 @@
         <v>7</v>
       </c>
       <c r="B611" s="2" t="s">
-        <v>1238</v>
+        <v>1234</v>
       </c>
       <c r="C611" s="2" t="s">
-        <v>1239</v>
+        <v>1235</v>
       </c>
       <c r="D611" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E611" s="2" t="s">
-        <v>167</v>
+        <v>81</v>
       </c>
       <c r="F611" s="2" t="s">
         <v>12</v>
@@ -19358,16 +19361,16 @@
         <v>7</v>
       </c>
       <c r="B612" s="2" t="s">
-        <v>1488</v>
+        <v>1236</v>
       </c>
       <c r="C612" s="2" t="s">
-        <v>1489</v>
+        <v>1237</v>
       </c>
       <c r="D612" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E612" s="2" t="s">
-        <v>427</v>
+        <v>167</v>
       </c>
       <c r="F612" s="2" t="s">
         <v>12</v>
@@ -19381,16 +19384,16 @@
         <v>7</v>
       </c>
       <c r="B613" s="2" t="s">
-        <v>1240</v>
+        <v>1486</v>
       </c>
       <c r="C613" s="2" t="s">
-        <v>1241</v>
+        <v>1487</v>
       </c>
       <c r="D613" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E613" s="2" t="s">
-        <v>500</v>
+        <v>427</v>
       </c>
       <c r="F613" s="2" t="s">
         <v>12</v>
@@ -19404,16 +19407,16 @@
         <v>7</v>
       </c>
       <c r="B614" s="2" t="s">
-        <v>1242</v>
+        <v>1238</v>
       </c>
       <c r="C614" s="2" t="s">
-        <v>1243</v>
+        <v>1239</v>
       </c>
       <c r="D614" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E614" s="2" t="s">
-        <v>141</v>
+        <v>500</v>
       </c>
       <c r="F614" s="2" t="s">
         <v>12</v>
@@ -19427,16 +19430,16 @@
         <v>7</v>
       </c>
       <c r="B615" s="2" t="s">
-        <v>1244</v>
+        <v>1240</v>
       </c>
       <c r="C615" s="2" t="s">
-        <v>1245</v>
+        <v>1241</v>
       </c>
       <c r="D615" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E615" s="2" t="s">
-        <v>223</v>
+        <v>141</v>
       </c>
       <c r="F615" s="2" t="s">
         <v>12</v>
@@ -19450,16 +19453,16 @@
         <v>7</v>
       </c>
       <c r="B616" s="2" t="s">
-        <v>1246</v>
+        <v>1242</v>
       </c>
       <c r="C616" s="2" t="s">
-        <v>1247</v>
+        <v>1243</v>
       </c>
       <c r="D616" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E616" s="2" t="s">
-        <v>551</v>
+        <v>223</v>
       </c>
       <c r="F616" s="2" t="s">
         <v>12</v>
@@ -19473,16 +19476,16 @@
         <v>7</v>
       </c>
       <c r="B617" s="2" t="s">
-        <v>1248</v>
+        <v>1244</v>
       </c>
       <c r="C617" s="2" t="s">
-        <v>1249</v>
+        <v>1245</v>
       </c>
       <c r="D617" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E617" s="2" t="s">
-        <v>364</v>
+        <v>551</v>
       </c>
       <c r="F617" s="2" t="s">
         <v>12</v>
@@ -19496,16 +19499,16 @@
         <v>7</v>
       </c>
       <c r="B618" s="2" t="s">
-        <v>1250</v>
+        <v>1246</v>
       </c>
       <c r="C618" s="2" t="s">
-        <v>1251</v>
+        <v>1247</v>
       </c>
       <c r="D618" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E618" s="2" t="s">
-        <v>220</v>
+        <v>364</v>
       </c>
       <c r="F618" s="2" t="s">
         <v>12</v>
@@ -19519,16 +19522,16 @@
         <v>7</v>
       </c>
       <c r="B619" s="2" t="s">
-        <v>1252</v>
+        <v>1248</v>
       </c>
       <c r="C619" s="2" t="s">
-        <v>1253</v>
+        <v>1249</v>
       </c>
       <c r="D619" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E619" s="2" t="s">
-        <v>191</v>
+        <v>220</v>
       </c>
       <c r="F619" s="2" t="s">
         <v>12</v>
@@ -19542,16 +19545,16 @@
         <v>7</v>
       </c>
       <c r="B620" s="2" t="s">
-        <v>1254</v>
+        <v>1250</v>
       </c>
       <c r="C620" s="2" t="s">
-        <v>1255</v>
+        <v>1251</v>
       </c>
       <c r="D620" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E620" s="2" t="s">
-        <v>839</v>
+        <v>191</v>
       </c>
       <c r="F620" s="2" t="s">
         <v>12</v>
@@ -19565,16 +19568,16 @@
         <v>7</v>
       </c>
       <c r="B621" s="2" t="s">
-        <v>1256</v>
+        <v>1252</v>
       </c>
       <c r="C621" s="2" t="s">
-        <v>1257</v>
+        <v>1253</v>
       </c>
       <c r="D621" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E621" s="2" t="s">
-        <v>467</v>
+        <v>837</v>
       </c>
       <c r="F621" s="2" t="s">
         <v>12</v>
@@ -19588,16 +19591,16 @@
         <v>7</v>
       </c>
       <c r="B622" s="2" t="s">
-        <v>1258</v>
+        <v>1254</v>
       </c>
       <c r="C622" s="2" t="s">
-        <v>1259</v>
+        <v>1255</v>
       </c>
       <c r="D622" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E622" s="2" t="s">
-        <v>220</v>
+        <v>467</v>
       </c>
       <c r="F622" s="2" t="s">
         <v>12</v>
@@ -19611,16 +19614,16 @@
         <v>7</v>
       </c>
       <c r="B623" s="2" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="C623" s="2" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="D623" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E623" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F623" s="2" t="s">
         <v>12</v>
@@ -19634,16 +19637,16 @@
         <v>7</v>
       </c>
       <c r="B624" s="2" t="s">
-        <v>1260</v>
+        <v>1256</v>
       </c>
       <c r="C624" s="2" t="s">
-        <v>1261</v>
+        <v>1257</v>
       </c>
       <c r="D624" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E624" s="2" t="s">
-        <v>590</v>
+        <v>223</v>
       </c>
       <c r="F624" s="2" t="s">
         <v>12</v>
@@ -19657,16 +19660,16 @@
         <v>7</v>
       </c>
       <c r="B625" s="2" t="s">
-        <v>1262</v>
+        <v>1258</v>
       </c>
       <c r="C625" s="2" t="s">
-        <v>1263</v>
+        <v>1259</v>
       </c>
       <c r="D625" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E625" s="2" t="s">
-        <v>65</v>
+        <v>588</v>
       </c>
       <c r="F625" s="2" t="s">
         <v>12</v>
@@ -19680,16 +19683,16 @@
         <v>7</v>
       </c>
       <c r="B626" s="2" t="s">
-        <v>1264</v>
+        <v>1260</v>
       </c>
       <c r="C626" s="2" t="s">
-        <v>1265</v>
+        <v>1261</v>
       </c>
       <c r="D626" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E626" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F626" s="2" t="s">
         <v>12</v>
@@ -19703,16 +19706,16 @@
         <v>7</v>
       </c>
       <c r="B627" s="2" t="s">
-        <v>1266</v>
+        <v>1262</v>
       </c>
       <c r="C627" s="2" t="s">
-        <v>1267</v>
+        <v>1263</v>
       </c>
       <c r="D627" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E627" s="2" t="s">
-        <v>191</v>
+        <v>11</v>
       </c>
       <c r="F627" s="2" t="s">
         <v>12</v>
@@ -19726,16 +19729,16 @@
         <v>7</v>
       </c>
       <c r="B628" s="2" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="C628" s="2" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="D628" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E628" s="2" t="s">
-        <v>109</v>
+        <v>191</v>
       </c>
       <c r="F628" s="2" t="s">
         <v>12</v>
@@ -19749,16 +19752,16 @@
         <v>7</v>
       </c>
       <c r="B629" s="2" t="s">
-        <v>1268</v>
+        <v>1264</v>
       </c>
       <c r="C629" s="2" t="s">
-        <v>1269</v>
+        <v>1265</v>
       </c>
       <c r="D629" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E629" s="2" t="s">
-        <v>26</v>
+        <v>109</v>
       </c>
       <c r="F629" s="2" t="s">
         <v>12</v>
@@ -19772,16 +19775,16 @@
         <v>7</v>
       </c>
       <c r="B630" s="2" t="s">
-        <v>1270</v>
+        <v>1266</v>
       </c>
       <c r="C630" s="2" t="s">
-        <v>1271</v>
+        <v>1267</v>
       </c>
       <c r="D630" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E630" s="2" t="s">
-        <v>109</v>
+        <v>26</v>
       </c>
       <c r="F630" s="2" t="s">
         <v>12</v>
@@ -19795,16 +19798,16 @@
         <v>7</v>
       </c>
       <c r="B631" s="2" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="C631" s="2" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="D631" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E631" s="2" t="s">
-        <v>65</v>
+        <v>109</v>
       </c>
       <c r="F631" s="2" t="s">
         <v>12</v>
@@ -19818,16 +19821,16 @@
         <v>7</v>
       </c>
       <c r="B632" s="2" t="s">
-        <v>1274</v>
+        <v>1270</v>
       </c>
       <c r="C632" s="2" t="s">
-        <v>1275</v>
+        <v>1271</v>
       </c>
       <c r="D632" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E632" s="2" t="s">
-        <v>538</v>
+        <v>65</v>
       </c>
       <c r="F632" s="2" t="s">
         <v>12</v>
@@ -19841,16 +19844,16 @@
         <v>7</v>
       </c>
       <c r="B633" s="2" t="s">
-        <v>1276</v>
+        <v>1272</v>
       </c>
       <c r="C633" s="2" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="D633" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E633" s="2" t="s">
-        <v>178</v>
+        <v>538</v>
       </c>
       <c r="F633" s="2" t="s">
         <v>12</v>
@@ -19864,16 +19867,16 @@
         <v>7</v>
       </c>
       <c r="B634" s="2" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="C634" s="2" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="D634" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E634" s="2" t="s">
-        <v>54</v>
+        <v>178</v>
       </c>
       <c r="F634" s="2" t="s">
         <v>12</v>
@@ -19887,16 +19890,16 @@
         <v>7</v>
       </c>
       <c r="B635" s="2" t="s">
-        <v>1280</v>
+        <v>1276</v>
       </c>
       <c r="C635" s="2" t="s">
-        <v>1281</v>
+        <v>1277</v>
       </c>
       <c r="D635" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E635" s="2" t="s">
-        <v>95</v>
+        <v>54</v>
       </c>
       <c r="F635" s="2" t="s">
         <v>12</v>
@@ -19910,16 +19913,16 @@
         <v>7</v>
       </c>
       <c r="B636" s="2" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="C636" s="2" t="s">
-        <v>1283</v>
+        <v>1279</v>
       </c>
       <c r="D636" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E636" s="2" t="s">
-        <v>48</v>
+        <v>815</v>
       </c>
       <c r="F636" s="2" t="s">
         <v>12</v>
@@ -19933,16 +19936,16 @@
         <v>7</v>
       </c>
       <c r="B637" s="2" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
       <c r="C637" s="2" t="s">
-        <v>1285</v>
+        <v>1281</v>
       </c>
       <c r="D637" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E637" s="2" t="s">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="F637" s="2" t="s">
         <v>12</v>
@@ -19956,16 +19959,16 @@
         <v>7</v>
       </c>
       <c r="B638" s="2" t="s">
-        <v>1286</v>
+        <v>1282</v>
       </c>
       <c r="C638" s="2" t="s">
-        <v>1287</v>
+        <v>1283</v>
       </c>
       <c r="D638" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E638" s="2" t="s">
-        <v>1184</v>
+        <v>89</v>
       </c>
       <c r="F638" s="2" t="s">
         <v>12</v>
@@ -19979,16 +19982,16 @@
         <v>7</v>
       </c>
       <c r="B639" s="2" t="s">
-        <v>1288</v>
+        <v>1284</v>
       </c>
       <c r="C639" s="2" t="s">
-        <v>1289</v>
+        <v>1285</v>
       </c>
       <c r="D639" s="2" t="s">
-        <v>138</v>
+        <v>22</v>
       </c>
       <c r="E639" s="2" t="s">
-        <v>72</v>
+        <v>1182</v>
       </c>
       <c r="F639" s="2" t="s">
         <v>12</v>
@@ -20002,16 +20005,16 @@
         <v>7</v>
       </c>
       <c r="B640" s="2" t="s">
-        <v>1290</v>
+        <v>1286</v>
       </c>
       <c r="C640" s="2" t="s">
-        <v>1291</v>
+        <v>1287</v>
       </c>
       <c r="D640" s="2" t="s">
-        <v>10</v>
+        <v>138</v>
       </c>
       <c r="E640" s="2" t="s">
-        <v>718</v>
+        <v>72</v>
       </c>
       <c r="F640" s="2" t="s">
         <v>12</v>
@@ -20025,16 +20028,16 @@
         <v>7</v>
       </c>
       <c r="B641" s="2" t="s">
-        <v>1292</v>
+        <v>1288</v>
       </c>
       <c r="C641" s="2" t="s">
-        <v>1293</v>
+        <v>1289</v>
       </c>
       <c r="D641" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E641" s="2" t="s">
-        <v>109</v>
+        <v>716</v>
       </c>
       <c r="F641" s="2" t="s">
         <v>12</v>
@@ -20048,16 +20051,16 @@
         <v>7</v>
       </c>
       <c r="B642" s="2" t="s">
-        <v>1294</v>
+        <v>1290</v>
       </c>
       <c r="C642" s="2" t="s">
-        <v>1295</v>
+        <v>1291</v>
       </c>
       <c r="D642" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E642" s="2" t="s">
-        <v>164</v>
+        <v>109</v>
       </c>
       <c r="F642" s="2" t="s">
         <v>12</v>
@@ -20071,16 +20074,16 @@
         <v>7</v>
       </c>
       <c r="B643" s="2" t="s">
-        <v>1296</v>
+        <v>1292</v>
       </c>
       <c r="C643" s="2" t="s">
-        <v>1297</v>
+        <v>1293</v>
       </c>
       <c r="D643" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E643" s="2" t="s">
-        <v>551</v>
+        <v>164</v>
       </c>
       <c r="F643" s="2" t="s">
         <v>12</v>
@@ -20094,16 +20097,16 @@
         <v>7</v>
       </c>
       <c r="B644" s="2" t="s">
-        <v>1298</v>
+        <v>1294</v>
       </c>
       <c r="C644" s="2" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="D644" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E644" s="2" t="s">
-        <v>21</v>
+        <v>551</v>
       </c>
       <c r="F644" s="2" t="s">
         <v>12</v>
@@ -20117,16 +20120,16 @@
         <v>7</v>
       </c>
       <c r="B645" s="2" t="s">
-        <v>1300</v>
+        <v>1296</v>
       </c>
       <c r="C645" s="2" t="s">
-        <v>1301</v>
+        <v>1297</v>
       </c>
       <c r="D645" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E645" s="2" t="s">
-        <v>551</v>
+        <v>21</v>
       </c>
       <c r="F645" s="2" t="s">
         <v>12</v>
@@ -20140,16 +20143,16 @@
         <v>7</v>
       </c>
       <c r="B646" s="2" t="s">
-        <v>1302</v>
+        <v>1298</v>
       </c>
       <c r="C646" s="2" t="s">
-        <v>1303</v>
+        <v>1299</v>
       </c>
       <c r="D646" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E646" s="2" t="s">
-        <v>615</v>
+        <v>551</v>
       </c>
       <c r="F646" s="2" t="s">
         <v>12</v>
@@ -20163,16 +20166,16 @@
         <v>7</v>
       </c>
       <c r="B647" s="2" t="s">
-        <v>1304</v>
+        <v>1300</v>
       </c>
       <c r="C647" s="2" t="s">
-        <v>1305</v>
+        <v>1301</v>
       </c>
       <c r="D647" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E647" s="2" t="s">
-        <v>109</v>
+        <v>613</v>
       </c>
       <c r="F647" s="2" t="s">
         <v>12</v>
@@ -20186,16 +20189,16 @@
         <v>7</v>
       </c>
       <c r="B648" s="2" t="s">
-        <v>1306</v>
+        <v>1302</v>
       </c>
       <c r="C648" s="2" t="s">
-        <v>1307</v>
+        <v>1303</v>
       </c>
       <c r="D648" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E648" s="2" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="F648" s="2" t="s">
         <v>12</v>
@@ -20209,16 +20212,16 @@
         <v>7</v>
       </c>
       <c r="B649" s="2" t="s">
-        <v>1308</v>
+        <v>1304</v>
       </c>
       <c r="C649" s="2" t="s">
-        <v>1309</v>
+        <v>1305</v>
       </c>
       <c r="D649" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E649" s="2" t="s">
-        <v>164</v>
+        <v>54</v>
       </c>
       <c r="F649" s="2" t="s">
         <v>12</v>
@@ -20232,16 +20235,16 @@
         <v>7</v>
       </c>
       <c r="B650" s="2" t="s">
-        <v>1310</v>
+        <v>1306</v>
       </c>
       <c r="C650" s="2" t="s">
-        <v>1311</v>
+        <v>1307</v>
       </c>
       <c r="D650" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E650" s="2" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="F650" s="2" t="s">
         <v>12</v>
@@ -20255,16 +20258,16 @@
         <v>7</v>
       </c>
       <c r="B651" s="2" t="s">
-        <v>1312</v>
+        <v>1308</v>
       </c>
       <c r="C651" s="2" t="s">
-        <v>1313</v>
+        <v>1309</v>
       </c>
       <c r="D651" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E651" s="2" t="s">
-        <v>1536</v>
+        <v>178</v>
       </c>
       <c r="F651" s="2" t="s">
         <v>12</v>
@@ -20278,16 +20281,16 @@
         <v>7</v>
       </c>
       <c r="B652" s="2" t="s">
-        <v>1314</v>
+        <v>1310</v>
       </c>
       <c r="C652" s="2" t="s">
-        <v>1315</v>
+        <v>1311</v>
       </c>
       <c r="D652" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E652" s="2" t="s">
-        <v>1537</v>
+        <v>1532</v>
       </c>
       <c r="F652" s="2" t="s">
         <v>12</v>
@@ -20301,16 +20304,16 @@
         <v>7</v>
       </c>
       <c r="B653" s="2" t="s">
-        <v>1316</v>
+        <v>1312</v>
       </c>
       <c r="C653" s="2" t="s">
-        <v>1317</v>
+        <v>1313</v>
       </c>
       <c r="D653" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E653" s="2" t="s">
-        <v>725</v>
+        <v>1533</v>
       </c>
       <c r="F653" s="2" t="s">
         <v>12</v>
@@ -20324,16 +20327,16 @@
         <v>7</v>
       </c>
       <c r="B654" s="2" t="s">
-        <v>1318</v>
+        <v>1314</v>
       </c>
       <c r="C654" s="2" t="s">
-        <v>1319</v>
+        <v>1315</v>
       </c>
       <c r="D654" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E654" s="2" t="s">
-        <v>164</v>
+        <v>723</v>
       </c>
       <c r="F654" s="2" t="s">
         <v>12</v>
@@ -20347,16 +20350,16 @@
         <v>7</v>
       </c>
       <c r="B655" s="2" t="s">
-        <v>1320</v>
+        <v>1316</v>
       </c>
       <c r="C655" s="2" t="s">
-        <v>1321</v>
+        <v>1317</v>
       </c>
       <c r="D655" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E655" s="2" t="s">
-        <v>1490</v>
+        <v>164</v>
       </c>
       <c r="F655" s="2" t="s">
         <v>12</v>
@@ -20370,16 +20373,16 @@
         <v>7</v>
       </c>
       <c r="B656" s="2" t="s">
-        <v>1322</v>
+        <v>1318</v>
       </c>
       <c r="C656" s="2" t="s">
-        <v>1323</v>
+        <v>1319</v>
       </c>
       <c r="D656" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E656" s="2" t="s">
-        <v>1324</v>
+        <v>1488</v>
       </c>
       <c r="F656" s="2" t="s">
         <v>12</v>
@@ -20393,16 +20396,16 @@
         <v>7</v>
       </c>
       <c r="B657" s="2" t="s">
-        <v>1325</v>
+        <v>1320</v>
       </c>
       <c r="C657" s="2" t="s">
-        <v>1326</v>
+        <v>1321</v>
       </c>
       <c r="D657" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E657" s="2" t="s">
-        <v>48</v>
+        <v>1322</v>
       </c>
       <c r="F657" s="2" t="s">
         <v>12</v>
@@ -20416,16 +20419,16 @@
         <v>7</v>
       </c>
       <c r="B658" s="2" t="s">
-        <v>1327</v>
+        <v>1323</v>
       </c>
       <c r="C658" s="2" t="s">
-        <v>1328</v>
+        <v>1324</v>
       </c>
       <c r="D658" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E658" s="2" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="F658" s="2" t="s">
         <v>12</v>
@@ -20439,16 +20442,16 @@
         <v>7</v>
       </c>
       <c r="B659" s="2" t="s">
-        <v>1329</v>
+        <v>1325</v>
       </c>
       <c r="C659" s="2" t="s">
-        <v>1330</v>
+        <v>1326</v>
       </c>
       <c r="D659" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E659" s="2" t="s">
-        <v>877</v>
+        <v>84</v>
       </c>
       <c r="F659" s="2" t="s">
         <v>12</v>
@@ -20462,16 +20465,16 @@
         <v>7</v>
       </c>
       <c r="B660" s="2" t="s">
-        <v>1331</v>
+        <v>1327</v>
       </c>
       <c r="C660" s="2" t="s">
-        <v>1332</v>
+        <v>1328</v>
       </c>
       <c r="D660" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E660" s="2" t="s">
-        <v>261</v>
+        <v>875</v>
       </c>
       <c r="F660" s="2" t="s">
         <v>12</v>
@@ -20485,16 +20488,16 @@
         <v>7</v>
       </c>
       <c r="B661" s="2" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="C661" s="2" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="D661" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E661" s="2" t="s">
-        <v>1333</v>
+        <v>261</v>
       </c>
       <c r="F661" s="2" t="s">
         <v>12</v>
@@ -20508,19 +20511,19 @@
         <v>7</v>
       </c>
       <c r="B662" s="2" t="s">
-        <v>1334</v>
+        <v>1329</v>
       </c>
       <c r="C662" s="2" t="s">
-        <v>1335</v>
+        <v>1330</v>
       </c>
       <c r="D662" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E662" s="2" t="s">
-        <v>487</v>
+        <v>1331</v>
       </c>
       <c r="F662" s="2" t="s">
-        <v>114</v>
+        <v>12</v>
       </c>
       <c r="G662" s="2" t="s">
         <v>13</v>
@@ -20531,16 +20534,16 @@
         <v>7</v>
       </c>
       <c r="B663" s="2" t="s">
-        <v>1336</v>
+        <v>1332</v>
       </c>
       <c r="C663" s="2" t="s">
-        <v>1337</v>
+        <v>1333</v>
       </c>
       <c r="D663" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E663" s="2" t="s">
-        <v>223</v>
+        <v>487</v>
       </c>
       <c r="F663" s="2" t="s">
         <v>114</v>
@@ -20554,19 +20557,19 @@
         <v>7</v>
       </c>
       <c r="B664" s="2" t="s">
-        <v>1338</v>
+        <v>1334</v>
       </c>
       <c r="C664" s="2" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="D664" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E664" s="2" t="s">
-        <v>32</v>
+        <v>223</v>
       </c>
       <c r="F664" s="2" t="s">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="G664" s="2" t="s">
         <v>13</v>
@@ -20577,16 +20580,16 @@
         <v>7</v>
       </c>
       <c r="B665" s="2" t="s">
-        <v>1340</v>
+        <v>1336</v>
       </c>
       <c r="C665" s="2" t="s">
-        <v>1341</v>
+        <v>1337</v>
       </c>
       <c r="D665" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E665" s="2" t="s">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="F665" s="2" t="s">
         <v>12</v>
@@ -20600,16 +20603,16 @@
         <v>7</v>
       </c>
       <c r="B666" s="2" t="s">
-        <v>1343</v>
+        <v>1338</v>
       </c>
       <c r="C666" s="2" t="s">
-        <v>1344</v>
+        <v>1339</v>
       </c>
       <c r="D666" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E666" s="2" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="F666" s="2" t="s">
         <v>12</v>
@@ -20623,16 +20626,16 @@
         <v>7</v>
       </c>
       <c r="B667" s="2" t="s">
-        <v>1345</v>
+        <v>1341</v>
       </c>
       <c r="C667" s="2" t="s">
-        <v>1346</v>
+        <v>1342</v>
       </c>
       <c r="D667" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E667" s="2" t="s">
-        <v>1538</v>
+        <v>191</v>
       </c>
       <c r="F667" s="2" t="s">
         <v>12</v>
@@ -20646,16 +20649,16 @@
         <v>7</v>
       </c>
       <c r="B668" s="2" t="s">
-        <v>1347</v>
+        <v>1343</v>
       </c>
       <c r="C668" s="2" t="s">
-        <v>1348</v>
+        <v>1344</v>
       </c>
       <c r="D668" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E668" s="2" t="s">
-        <v>1161</v>
+        <v>1534</v>
       </c>
       <c r="F668" s="2" t="s">
         <v>12</v>
@@ -20669,16 +20672,16 @@
         <v>7</v>
       </c>
       <c r="B669" s="2" t="s">
-        <v>1349</v>
+        <v>1345</v>
       </c>
       <c r="C669" s="2" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
       <c r="D669" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E669" s="2" t="s">
-        <v>487</v>
+        <v>1159</v>
       </c>
       <c r="F669" s="2" t="s">
         <v>12</v>
@@ -20692,16 +20695,16 @@
         <v>7</v>
       </c>
       <c r="B670" s="2" t="s">
-        <v>1351</v>
+        <v>1347</v>
       </c>
       <c r="C670" s="2" t="s">
-        <v>1352</v>
+        <v>1348</v>
       </c>
       <c r="D670" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E670" s="2" t="s">
-        <v>1353</v>
+        <v>487</v>
       </c>
       <c r="F670" s="2" t="s">
         <v>12</v>
@@ -20715,16 +20718,16 @@
         <v>7</v>
       </c>
       <c r="B671" s="2" t="s">
-        <v>1354</v>
+        <v>1349</v>
       </c>
       <c r="C671" s="2" t="s">
-        <v>1355</v>
+        <v>1350</v>
       </c>
       <c r="D671" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E671" s="2" t="s">
-        <v>32</v>
+        <v>1351</v>
       </c>
       <c r="F671" s="2" t="s">
         <v>12</v>
@@ -20738,16 +20741,16 @@
         <v>7</v>
       </c>
       <c r="B672" s="2" t="s">
-        <v>1356</v>
+        <v>1352</v>
       </c>
       <c r="C672" s="2" t="s">
-        <v>1357</v>
+        <v>1353</v>
       </c>
       <c r="D672" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E672" s="2" t="s">
-        <v>560</v>
+        <v>32</v>
       </c>
       <c r="F672" s="2" t="s">
         <v>12</v>
@@ -20761,16 +20764,16 @@
         <v>7</v>
       </c>
       <c r="B673" s="2" t="s">
-        <v>1358</v>
+        <v>1354</v>
       </c>
       <c r="C673" s="2" t="s">
-        <v>1359</v>
+        <v>1355</v>
       </c>
       <c r="D673" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E673" s="2" t="s">
-        <v>487</v>
+        <v>560</v>
       </c>
       <c r="F673" s="2" t="s">
         <v>12</v>
@@ -20784,16 +20787,16 @@
         <v>7</v>
       </c>
       <c r="B674" s="2" t="s">
-        <v>1360</v>
+        <v>1356</v>
       </c>
       <c r="C674" s="2" t="s">
-        <v>1361</v>
+        <v>1357</v>
       </c>
       <c r="D674" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E674" s="2" t="s">
-        <v>1539</v>
+        <v>487</v>
       </c>
       <c r="F674" s="2" t="s">
         <v>12</v>
@@ -20807,16 +20810,16 @@
         <v>7</v>
       </c>
       <c r="B675" s="2" t="s">
-        <v>1362</v>
+        <v>1358</v>
       </c>
       <c r="C675" s="2" t="s">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="D675" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E675" s="2" t="s">
-        <v>164</v>
+        <v>1535</v>
       </c>
       <c r="F675" s="2" t="s">
         <v>12</v>
@@ -20830,16 +20833,16 @@
         <v>7</v>
       </c>
       <c r="B676" s="2" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="C676" s="2" t="s">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="D676" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E676" s="2" t="s">
-        <v>226</v>
+        <v>164</v>
       </c>
       <c r="F676" s="2" t="s">
         <v>12</v>
@@ -20853,16 +20856,16 @@
         <v>7</v>
       </c>
       <c r="B677" s="2" t="s">
-        <v>1366</v>
+        <v>1362</v>
       </c>
       <c r="C677" s="2" t="s">
-        <v>1367</v>
+        <v>1363</v>
       </c>
       <c r="D677" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E677" s="2" t="s">
-        <v>1475</v>
+        <v>226</v>
       </c>
       <c r="F677" s="2" t="s">
         <v>12</v>
@@ -20876,16 +20879,16 @@
         <v>7</v>
       </c>
       <c r="B678" s="2" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="C678" s="2" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="D678" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E678" s="2" t="s">
-        <v>756</v>
+        <v>1473</v>
       </c>
       <c r="F678" s="2" t="s">
         <v>12</v>
@@ -20899,16 +20902,16 @@
         <v>7</v>
       </c>
       <c r="B679" s="2" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="C679" s="2" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="D679" s="2" t="s">
-        <v>1233</v>
+        <v>10</v>
       </c>
       <c r="E679" s="2" t="s">
-        <v>427</v>
+        <v>754</v>
       </c>
       <c r="F679" s="2" t="s">
         <v>12</v>
@@ -20922,16 +20925,16 @@
         <v>7</v>
       </c>
       <c r="B680" s="2" t="s">
-        <v>1372</v>
+        <v>1368</v>
       </c>
       <c r="C680" s="2" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="D680" s="2" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="E680" s="2" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="F680" s="2" t="s">
         <v>12</v>
@@ -20945,16 +20948,16 @@
         <v>7</v>
       </c>
       <c r="B681" s="2" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="C681" s="2" t="s">
-        <v>1375</v>
+        <v>1371</v>
       </c>
       <c r="D681" s="2" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="E681" s="2" t="s">
-        <v>1548</v>
+        <v>438</v>
       </c>
       <c r="F681" s="2" t="s">
         <v>12</v>
@@ -20968,16 +20971,16 @@
         <v>7</v>
       </c>
       <c r="B682" s="2" t="s">
-        <v>1376</v>
+        <v>1372</v>
       </c>
       <c r="C682" s="2" t="s">
-        <v>1377</v>
+        <v>1373</v>
       </c>
       <c r="D682" s="2" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="E682" s="2" t="s">
-        <v>48</v>
+        <v>1544</v>
       </c>
       <c r="F682" s="2" t="s">
         <v>12</v>
@@ -20991,16 +20994,16 @@
         <v>7</v>
       </c>
       <c r="B683" s="2" t="s">
-        <v>1378</v>
+        <v>1374</v>
       </c>
       <c r="C683" s="2" t="s">
-        <v>1379</v>
+        <v>1375</v>
       </c>
       <c r="D683" s="2" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="E683" s="2" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="F683" s="2" t="s">
         <v>12</v>
@@ -21014,16 +21017,16 @@
         <v>7</v>
       </c>
       <c r="B684" s="2" t="s">
-        <v>1380</v>
+        <v>1376</v>
       </c>
       <c r="C684" s="2" t="s">
-        <v>1381</v>
+        <v>1377</v>
       </c>
       <c r="D684" s="2" t="s">
-        <v>10</v>
+        <v>1231</v>
       </c>
       <c r="E684" s="2" t="s">
-        <v>178</v>
+        <v>65</v>
       </c>
       <c r="F684" s="2" t="s">
         <v>12</v>
@@ -21037,19 +21040,19 @@
         <v>7</v>
       </c>
       <c r="B685" s="2" t="s">
-        <v>1382</v>
+        <v>1378</v>
       </c>
       <c r="C685" s="2" t="s">
-        <v>1383</v>
+        <v>1379</v>
       </c>
       <c r="D685" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E685" s="2" t="s">
-        <v>54</v>
+        <v>178</v>
       </c>
       <c r="F685" s="2" t="s">
-        <v>114</v>
+        <v>12</v>
       </c>
       <c r="G685" s="2" t="s">
         <v>13</v>
@@ -21060,19 +21063,19 @@
         <v>7</v>
       </c>
       <c r="B686" s="2" t="s">
-        <v>1384</v>
+        <v>1380</v>
       </c>
       <c r="C686" s="2" t="s">
-        <v>1385</v>
+        <v>1381</v>
       </c>
       <c r="D686" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E686" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F686" s="2" t="s">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="G686" s="2" t="s">
         <v>13</v>
@@ -21083,16 +21086,16 @@
         <v>7</v>
       </c>
       <c r="B687" s="2" t="s">
-        <v>1386</v>
+        <v>1382</v>
       </c>
       <c r="C687" s="2" t="s">
-        <v>1387</v>
+        <v>1383</v>
       </c>
       <c r="D687" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E687" s="2" t="s">
-        <v>1614</v>
+        <v>57</v>
       </c>
       <c r="F687" s="2" t="s">
         <v>12</v>
@@ -21106,16 +21109,16 @@
         <v>7</v>
       </c>
       <c r="B688" s="2" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="C688" s="2" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="D688" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E688" s="2" t="s">
-        <v>487</v>
+        <v>1609</v>
       </c>
       <c r="F688" s="2" t="s">
         <v>12</v>
@@ -21129,16 +21132,16 @@
         <v>7</v>
       </c>
       <c r="B689" s="2" t="s">
-        <v>1388</v>
+        <v>1384</v>
       </c>
       <c r="C689" s="2" t="s">
-        <v>1389</v>
+        <v>1385</v>
       </c>
       <c r="D689" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E689" s="2" t="s">
-        <v>89</v>
+        <v>487</v>
       </c>
       <c r="F689" s="2" t="s">
         <v>12</v>
@@ -21152,16 +21155,16 @@
         <v>7</v>
       </c>
       <c r="B690" s="2" t="s">
-        <v>1390</v>
+        <v>1386</v>
       </c>
       <c r="C690" s="2" t="s">
-        <v>1391</v>
+        <v>1387</v>
       </c>
       <c r="D690" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E690" s="2" t="s">
-        <v>1615</v>
+        <v>89</v>
       </c>
       <c r="F690" s="2" t="s">
         <v>12</v>
@@ -21175,16 +21178,16 @@
         <v>7</v>
       </c>
       <c r="B691" s="2" t="s">
-        <v>1392</v>
+        <v>1388</v>
       </c>
       <c r="C691" s="2" t="s">
-        <v>1393</v>
+        <v>1389</v>
       </c>
       <c r="D691" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E691" s="2" t="s">
-        <v>1465</v>
+        <v>1602</v>
       </c>
       <c r="F691" s="2" t="s">
         <v>12</v>
@@ -21198,16 +21201,16 @@
         <v>7</v>
       </c>
       <c r="B692" s="2" t="s">
-        <v>1394</v>
+        <v>1390</v>
       </c>
       <c r="C692" s="2" t="s">
-        <v>1395</v>
+        <v>1391</v>
       </c>
       <c r="D692" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E692" s="2" t="s">
-        <v>1616</v>
+        <v>1463</v>
       </c>
       <c r="F692" s="2" t="s">
         <v>12</v>
@@ -21221,19 +21224,19 @@
         <v>7</v>
       </c>
       <c r="B693" s="2" t="s">
-        <v>1396</v>
+        <v>1392</v>
       </c>
       <c r="C693" s="2" t="s">
-        <v>1397</v>
+        <v>1393</v>
       </c>
       <c r="D693" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E693" s="2" t="s">
-        <v>1558</v>
+        <v>1603</v>
       </c>
       <c r="F693" s="2" t="s">
-        <v>114</v>
+        <v>12</v>
       </c>
       <c r="G693" s="2" t="s">
         <v>13</v>
@@ -21244,19 +21247,19 @@
         <v>7</v>
       </c>
       <c r="B694" s="2" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="C694" s="2" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="D694" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E694" s="2" t="s">
-        <v>220</v>
+        <v>626</v>
       </c>
       <c r="F694" s="2" t="s">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="G694" s="2" t="s">
         <v>13</v>
@@ -21267,16 +21270,16 @@
         <v>7</v>
       </c>
       <c r="B695" s="2" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="C695" s="2" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="D695" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E695" s="2" t="s">
-        <v>1508</v>
+        <v>220</v>
       </c>
       <c r="F695" s="2" t="s">
         <v>12</v>
@@ -21290,16 +21293,16 @@
         <v>7</v>
       </c>
       <c r="B696" s="2" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="C696" s="2" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="D696" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E696" s="2" t="s">
-        <v>687</v>
+        <v>1505</v>
       </c>
       <c r="F696" s="2" t="s">
         <v>12</v>
@@ -21313,19 +21316,19 @@
         <v>7</v>
       </c>
       <c r="B697" s="2" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="C697" s="2" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="D697" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E697" s="2" t="s">
-        <v>1564</v>
+        <v>685</v>
       </c>
       <c r="F697" s="2" t="s">
-        <v>114</v>
+        <v>12</v>
       </c>
       <c r="G697" s="2" t="s">
         <v>13</v>
@@ -21336,19 +21339,19 @@
         <v>7</v>
       </c>
       <c r="B698" s="2" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="C698" s="2" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="D698" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E698" s="2" t="s">
-        <v>65</v>
+        <v>1558</v>
       </c>
       <c r="F698" s="2" t="s">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="G698" s="2" t="s">
         <v>13</v>
@@ -21359,16 +21362,16 @@
         <v>7</v>
       </c>
       <c r="B699" s="2" t="s">
-        <v>1408</v>
+        <v>1404</v>
       </c>
       <c r="C699" s="2" t="s">
-        <v>1409</v>
+        <v>1405</v>
       </c>
       <c r="D699" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E699" s="2" t="s">
-        <v>178</v>
+        <v>65</v>
       </c>
       <c r="F699" s="2" t="s">
         <v>12</v>
@@ -21382,16 +21385,16 @@
         <v>7</v>
       </c>
       <c r="B700" s="2" t="s">
-        <v>1410</v>
+        <v>1406</v>
       </c>
       <c r="C700" s="2" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="D700" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E700" s="2" t="s">
-        <v>839</v>
+        <v>178</v>
       </c>
       <c r="F700" s="2" t="s">
         <v>12</v>
@@ -21405,16 +21408,16 @@
         <v>7</v>
       </c>
       <c r="B701" s="2" t="s">
-        <v>1412</v>
+        <v>1408</v>
       </c>
       <c r="C701" s="2" t="s">
-        <v>1413</v>
+        <v>1409</v>
       </c>
       <c r="D701" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E701" s="2" t="s">
-        <v>155</v>
+        <v>837</v>
       </c>
       <c r="F701" s="2" t="s">
         <v>12</v>
@@ -21428,19 +21431,19 @@
         <v>7</v>
       </c>
       <c r="B702" s="2" t="s">
-        <v>1414</v>
+        <v>1410</v>
       </c>
       <c r="C702" s="2" t="s">
-        <v>1415</v>
+        <v>1411</v>
       </c>
       <c r="D702" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E702" s="2" t="s">
-        <v>848</v>
+        <v>613</v>
       </c>
       <c r="F702" s="2" t="s">
-        <v>285</v>
+        <v>12</v>
       </c>
       <c r="G702" s="2" t="s">
         <v>13</v>
@@ -21451,16 +21454,16 @@
         <v>7</v>
       </c>
       <c r="B703" s="2" t="s">
-        <v>1416</v>
+        <v>1412</v>
       </c>
       <c r="C703" s="2" t="s">
-        <v>1417</v>
+        <v>1413</v>
       </c>
       <c r="D703" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E703" s="2" t="s">
-        <v>1418</v>
+        <v>846</v>
       </c>
       <c r="F703" s="2" t="s">
         <v>285</v>
@@ -21474,19 +21477,19 @@
         <v>7</v>
       </c>
       <c r="B704" s="2" t="s">
-        <v>1419</v>
+        <v>1414</v>
       </c>
       <c r="C704" s="2" t="s">
-        <v>1420</v>
+        <v>1415</v>
       </c>
       <c r="D704" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E704" s="2" t="s">
-        <v>72</v>
+        <v>1416</v>
       </c>
       <c r="F704" s="2" t="s">
-        <v>114</v>
+        <v>285</v>
       </c>
       <c r="G704" s="2" t="s">
         <v>13</v>
@@ -21497,16 +21500,16 @@
         <v>7</v>
       </c>
       <c r="B705" s="2" t="s">
-        <v>1421</v>
+        <v>1417</v>
       </c>
       <c r="C705" s="2" t="s">
-        <v>1422</v>
+        <v>1418</v>
       </c>
       <c r="D705" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E705" s="2" t="s">
-        <v>1156</v>
+        <v>72</v>
       </c>
       <c r="F705" s="2" t="s">
         <v>114</v>
@@ -21520,19 +21523,19 @@
         <v>7</v>
       </c>
       <c r="B706" s="2" t="s">
-        <v>1423</v>
+        <v>1419</v>
       </c>
       <c r="C706" s="2" t="s">
-        <v>1424</v>
+        <v>1420</v>
       </c>
       <c r="D706" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E706" s="2" t="s">
-        <v>492</v>
+        <v>1154</v>
       </c>
       <c r="F706" s="2" t="s">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="G706" s="2" t="s">
         <v>13</v>
@@ -21543,16 +21546,16 @@
         <v>7</v>
       </c>
       <c r="B707" s="2" t="s">
-        <v>1425</v>
+        <v>1421</v>
       </c>
       <c r="C707" s="2" t="s">
-        <v>1426</v>
+        <v>1422</v>
       </c>
       <c r="D707" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E707" s="2" t="s">
-        <v>1161</v>
+        <v>492</v>
       </c>
       <c r="F707" s="2" t="s">
         <v>12</v>
@@ -21566,16 +21569,16 @@
         <v>7</v>
       </c>
       <c r="B708" s="2" t="s">
-        <v>1427</v>
+        <v>1423</v>
       </c>
       <c r="C708" s="2" t="s">
-        <v>1428</v>
+        <v>1424</v>
       </c>
       <c r="D708" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E708" s="2" t="s">
-        <v>427</v>
+        <v>1159</v>
       </c>
       <c r="F708" s="2" t="s">
         <v>12</v>
@@ -21589,16 +21592,16 @@
         <v>7</v>
       </c>
       <c r="B709" s="2" t="s">
-        <v>1429</v>
+        <v>1425</v>
       </c>
       <c r="C709" s="2" t="s">
-        <v>1430</v>
+        <v>1426</v>
       </c>
       <c r="D709" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E709" s="2" t="s">
-        <v>32</v>
+        <v>427</v>
       </c>
       <c r="F709" s="2" t="s">
         <v>12</v>
@@ -21612,16 +21615,16 @@
         <v>7</v>
       </c>
       <c r="B710" s="2" t="s">
-        <v>1431</v>
+        <v>1427</v>
       </c>
       <c r="C710" s="2" t="s">
-        <v>1432</v>
+        <v>1428</v>
       </c>
       <c r="D710" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E710" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F710" s="2" t="s">
         <v>12</v>
@@ -21635,16 +21638,16 @@
         <v>7</v>
       </c>
       <c r="B711" s="2" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="C711" s="2" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="D711" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E711" s="2" t="s">
-        <v>1433</v>
+        <v>21</v>
       </c>
       <c r="F711" s="2" t="s">
         <v>12</v>
@@ -21658,16 +21661,16 @@
         <v>7</v>
       </c>
       <c r="B712" s="2" t="s">
-        <v>1434</v>
+        <v>1429</v>
       </c>
       <c r="C712" s="2" t="s">
-        <v>1435</v>
+        <v>1430</v>
       </c>
       <c r="D712" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E712" s="2" t="s">
-        <v>81</v>
+        <v>1431</v>
       </c>
       <c r="F712" s="2" t="s">
         <v>12</v>
@@ -21681,10 +21684,10 @@
         <v>7</v>
       </c>
       <c r="B713" s="2" t="s">
-        <v>1436</v>
+        <v>1432</v>
       </c>
       <c r="C713" s="2" t="s">
-        <v>1437</v>
+        <v>1433</v>
       </c>
       <c r="D713" s="2" t="s">
         <v>10</v>
@@ -21704,16 +21707,16 @@
         <v>7</v>
       </c>
       <c r="B714" s="2" t="s">
-        <v>1438</v>
+        <v>1434</v>
       </c>
       <c r="C714" s="2" t="s">
-        <v>1439</v>
+        <v>1435</v>
       </c>
       <c r="D714" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E714" s="2" t="s">
-        <v>164</v>
+        <v>81</v>
       </c>
       <c r="F714" s="2" t="s">
         <v>12</v>
@@ -21727,16 +21730,16 @@
         <v>7</v>
       </c>
       <c r="B715" s="2" t="s">
-        <v>1440</v>
+        <v>1436</v>
       </c>
       <c r="C715" s="2" t="s">
-        <v>1441</v>
+        <v>1437</v>
       </c>
       <c r="D715" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E715" s="2" t="s">
-        <v>21</v>
+        <v>164</v>
       </c>
       <c r="F715" s="2" t="s">
         <v>12</v>
@@ -21750,16 +21753,16 @@
         <v>7</v>
       </c>
       <c r="B716" s="2" t="s">
-        <v>1442</v>
+        <v>1438</v>
       </c>
       <c r="C716" s="2" t="s">
-        <v>1443</v>
+        <v>1439</v>
       </c>
       <c r="D716" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E716" s="2" t="s">
-        <v>264</v>
+        <v>21</v>
       </c>
       <c r="F716" s="2" t="s">
         <v>12</v>
@@ -21773,16 +21776,16 @@
         <v>7</v>
       </c>
       <c r="B717" s="2" t="s">
-        <v>1444</v>
+        <v>1440</v>
       </c>
       <c r="C717" s="2" t="s">
-        <v>1445</v>
+        <v>1441</v>
       </c>
       <c r="D717" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E717" s="2" t="s">
-        <v>1503</v>
+        <v>264</v>
       </c>
       <c r="F717" s="2" t="s">
         <v>12</v>
@@ -21796,16 +21799,16 @@
         <v>7</v>
       </c>
       <c r="B718" s="2" t="s">
-        <v>1446</v>
+        <v>1442</v>
       </c>
       <c r="C718" s="2" t="s">
-        <v>1447</v>
+        <v>1443</v>
       </c>
       <c r="D718" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E718" s="2" t="s">
-        <v>81</v>
+        <v>1500</v>
       </c>
       <c r="F718" s="2" t="s">
         <v>12</v>
@@ -21819,16 +21822,16 @@
         <v>7</v>
       </c>
       <c r="B719" s="2" t="s">
-        <v>1448</v>
+        <v>1444</v>
       </c>
       <c r="C719" s="2" t="s">
-        <v>1449</v>
+        <v>1445</v>
       </c>
       <c r="D719" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E719" s="2" t="s">
-        <v>271</v>
+        <v>81</v>
       </c>
       <c r="F719" s="2" t="s">
         <v>12</v>
@@ -21842,16 +21845,16 @@
         <v>7</v>
       </c>
       <c r="B720" s="2" t="s">
-        <v>1450</v>
+        <v>1446</v>
       </c>
       <c r="C720" s="2" t="s">
-        <v>1451</v>
+        <v>1447</v>
       </c>
       <c r="D720" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E720" s="2" t="s">
-        <v>109</v>
+        <v>271</v>
       </c>
       <c r="F720" s="2" t="s">
         <v>12</v>
@@ -21865,16 +21868,16 @@
         <v>7</v>
       </c>
       <c r="B721" s="2" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="C721" s="2" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="D721" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E721" s="2" t="s">
-        <v>254</v>
+        <v>109</v>
       </c>
       <c r="F721" s="2" t="s">
         <v>12</v>
@@ -21888,16 +21891,16 @@
         <v>7</v>
       </c>
       <c r="B722" s="2" t="s">
-        <v>1452</v>
+        <v>1448</v>
       </c>
       <c r="C722" s="2" t="s">
-        <v>1453</v>
+        <v>1449</v>
       </c>
       <c r="D722" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E722" s="2" t="s">
-        <v>45</v>
+        <v>254</v>
       </c>
       <c r="F722" s="2" t="s">
         <v>12</v>
@@ -21911,16 +21914,16 @@
         <v>7</v>
       </c>
       <c r="B723" s="2" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="C723" s="2" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="D723" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E723" s="2" t="s">
-        <v>487</v>
+        <v>45</v>
       </c>
       <c r="F723" s="2" t="s">
         <v>12</v>
@@ -21934,16 +21937,16 @@
         <v>7</v>
       </c>
       <c r="B724" s="2" t="s">
-        <v>1454</v>
+        <v>1450</v>
       </c>
       <c r="C724" s="2" t="s">
-        <v>1455</v>
+        <v>1451</v>
       </c>
       <c r="D724" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E724" s="2" t="s">
-        <v>21</v>
+        <v>487</v>
       </c>
       <c r="F724" s="2" t="s">
         <v>12</v>
@@ -21957,16 +21960,16 @@
         <v>7</v>
       </c>
       <c r="B725" s="2" t="s">
-        <v>1456</v>
+        <v>1452</v>
       </c>
       <c r="C725" s="2" t="s">
-        <v>1457</v>
+        <v>1453</v>
       </c>
       <c r="D725" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E725" s="2" t="s">
-        <v>705</v>
+        <v>21</v>
       </c>
       <c r="F725" s="2" t="s">
         <v>12</v>
@@ -21980,16 +21983,16 @@
         <v>7</v>
       </c>
       <c r="B726" s="2" t="s">
-        <v>1458</v>
+        <v>1454</v>
       </c>
       <c r="C726" s="2" t="s">
-        <v>1459</v>
+        <v>1455</v>
       </c>
       <c r="D726" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E726" s="2" t="s">
-        <v>36</v>
+        <v>703</v>
       </c>
       <c r="F726" s="2" t="s">
         <v>12</v>
@@ -22003,16 +22006,16 @@
         <v>7</v>
       </c>
       <c r="B727" s="2" t="s">
-        <v>1460</v>
+        <v>1456</v>
       </c>
       <c r="C727" s="2" t="s">
-        <v>1461</v>
+        <v>1457</v>
       </c>
       <c r="D727" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E727" s="2" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F727" s="2" t="s">
         <v>12</v>
@@ -22026,16 +22029,16 @@
         <v>7</v>
       </c>
       <c r="B728" s="2" t="s">
-        <v>1462</v>
+        <v>1458</v>
       </c>
       <c r="C728" s="2" t="s">
-        <v>1463</v>
+        <v>1459</v>
       </c>
       <c r="D728" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E728" s="2" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F728" s="2" t="s">
         <v>12</v>
@@ -22046,25 +22049,25 @@
     </row>
     <row r="729" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A729" s="2" t="s">
-        <v>205</v>
+        <v>7</v>
       </c>
       <c r="B729" s="2" t="s">
-        <v>205</v>
+        <v>1460</v>
       </c>
       <c r="C729" s="2" t="s">
-        <v>205</v>
+        <v>1461</v>
       </c>
       <c r="D729" s="2" t="s">
-        <v>205</v>
+        <v>10</v>
       </c>
       <c r="E729" s="2" t="s">
-        <v>205</v>
+        <v>36</v>
       </c>
       <c r="F729" s="2" t="s">
-        <v>205</v>
+        <v>12</v>
       </c>
       <c r="G729" s="2" t="s">
-        <v>205</v>
+        <v>13</v>
       </c>
     </row>
     <row r="730" spans="1:8" x14ac:dyDescent="0.2">
@@ -22081,13 +22084,13 @@
         <v>205</v>
       </c>
       <c r="E730" s="2" t="s">
-        <v>1540</v>
+        <v>205</v>
       </c>
       <c r="F730" s="2" t="s">
-        <v>525</v>
+        <v>205</v>
       </c>
       <c r="G730" s="2" t="s">
-        <v>13</v>
+        <v>205</v>
       </c>
       <c r="H730" s="2"/>
     </row>
@@ -22105,10 +22108,10 @@
         <v>205</v>
       </c>
       <c r="E731" s="2" t="s">
-        <v>1617</v>
+        <v>1536</v>
       </c>
       <c r="F731" s="2" t="s">
-        <v>40</v>
+        <v>525</v>
       </c>
       <c r="G731" s="2" t="s">
         <v>13</v>
@@ -22128,10 +22131,10 @@
         <v>205</v>
       </c>
       <c r="E732" s="2" t="s">
-        <v>1565</v>
+        <v>1618</v>
       </c>
       <c r="F732" s="2" t="s">
-        <v>285</v>
+        <v>40</v>
       </c>
       <c r="G732" s="2" t="s">
         <v>13</v>
@@ -22151,13 +22154,13 @@
         <v>205</v>
       </c>
       <c r="E733" s="2" t="s">
-        <v>1618</v>
+        <v>1559</v>
       </c>
       <c r="F733" s="2" t="s">
-        <v>192</v>
+        <v>285</v>
       </c>
       <c r="G733" s="2" t="s">
-        <v>1464</v>
+        <v>13</v>
       </c>
     </row>
     <row r="734" spans="1:8" x14ac:dyDescent="0.2">
@@ -22177,10 +22180,10 @@
         <v>1619</v>
       </c>
       <c r="F734" s="2" t="s">
-        <v>114</v>
+        <v>192</v>
       </c>
       <c r="G734" s="2" t="s">
-        <v>13</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="735" spans="1:8" x14ac:dyDescent="0.2">
@@ -22200,32 +22203,32 @@
         <v>1620</v>
       </c>
       <c r="F735" s="2" t="s">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="G735" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="736" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A736" t="s">
+      <c r="A736" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="B736" t="s">
+      <c r="B736" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C736" t="s">
+      <c r="C736" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="D736" t="s">
+      <c r="D736" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="E736" t="s">
-        <v>1565</v>
-      </c>
-      <c r="F736" t="s">
-        <v>285</v>
-      </c>
-      <c r="G736" t="s">
+      <c r="E736" s="2" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F736" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G736" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -22243,13 +22246,13 @@
         <v>205</v>
       </c>
       <c r="E737" t="s">
-        <v>1566</v>
+        <v>1560</v>
       </c>
       <c r="F737" t="s">
         <v>192</v>
       </c>
       <c r="G737" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="738" spans="1:7" x14ac:dyDescent="0.2">
@@ -22266,7 +22269,7 @@
         <v>205</v>
       </c>
       <c r="E738" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="F738" t="s">
         <v>114</v>
@@ -22289,7 +22292,7 @@
         <v>205</v>
       </c>
       <c r="E739" t="s">
-        <v>1568</v>
+        <v>1562</v>
       </c>
       <c r="F739" t="s">
         <v>12</v>
@@ -22312,7 +22315,7 @@
         <v>205</v>
       </c>
       <c r="E740" s="2" t="s">
-        <v>1541</v>
+        <v>1537</v>
       </c>
       <c r="F740" s="2" t="s">
         <v>12</v>

--- a/dados-catalago-pcm-interno/relatorio.xlsx
+++ b/dados-catalago-pcm-interno/relatorio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amaggicombr-my.sharepoint.com/personal/hiago_andre_amaggi_com_br/Documents/Área de Trabalho/codigos/catalogoPecasPCM/dados-catalago-pcm-interno/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="100" documentId="11_FD86FE4AC4094E4AB971B8A5A011EE841C83CB4A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{465FFAB4-E263-465E-8F3A-282B80B39EF1}"/>
+  <xr:revisionPtr revIDLastSave="102" documentId="11_FD86FE4AC4094E4AB971B8A5A011EE841C83CB4A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D8D8E7C-68D0-450E-901E-062EEB8D8923}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5215" uniqueCount="1636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5215" uniqueCount="1635">
   <si>
     <t>Cen.</t>
   </si>
@@ -4472,9 +4472,6 @@
     <t>580</t>
   </si>
   <si>
-    <t>94</t>
-  </si>
-  <si>
     <t>1010085360</t>
   </si>
   <si>
@@ -4634,9 +4631,6 @@
     <t>PNEU 295/80 R22.5 BANDA VL130 REC</t>
   </si>
   <si>
-    <t>299</t>
-  </si>
-  <si>
     <t>66</t>
   </si>
   <si>
@@ -4703,15 +4697,6 @@
     <t>279</t>
   </si>
   <si>
-    <t>538</t>
-  </si>
-  <si>
-    <t>3.200</t>
-  </si>
-  <si>
-    <t>142</t>
-  </si>
-  <si>
     <t>352</t>
   </si>
   <si>
@@ -4751,18 +4736,9 @@
     <t>770</t>
   </si>
   <si>
-    <t>186</t>
-  </si>
-  <si>
     <t>302</t>
   </si>
   <si>
-    <t>194</t>
-  </si>
-  <si>
-    <t>126</t>
-  </si>
-  <si>
     <t>78</t>
   </si>
   <si>
@@ -4772,18 +4748,12 @@
     <t>317</t>
   </si>
   <si>
-    <t>332</t>
-  </si>
-  <si>
     <t>0,115</t>
   </si>
   <si>
     <t>4.937</t>
   </si>
   <si>
-    <t>434</t>
-  </si>
-  <si>
     <t>1010049326</t>
   </si>
   <si>
@@ -4802,12 +4772,6 @@
     <t>59</t>
   </si>
   <si>
-    <t>194.934,410</t>
-  </si>
-  <si>
-    <t>134</t>
-  </si>
-  <si>
     <t>140</t>
   </si>
   <si>
@@ -4820,12 +4784,6 @@
     <t>118</t>
   </si>
   <si>
-    <t>421</t>
-  </si>
-  <si>
-    <t>1.493</t>
-  </si>
-  <si>
     <t>153</t>
   </si>
   <si>
@@ -4844,12 +4802,6 @@
     <t>167</t>
   </si>
   <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>89</t>
-  </si>
-  <si>
     <t>1040099488</t>
   </si>
   <si>
@@ -4859,9 +4811,6 @@
     <t>120</t>
   </si>
   <si>
-    <t>281</t>
-  </si>
-  <si>
     <t>1040074827</t>
   </si>
   <si>
@@ -4898,24 +4847,15 @@
     <t>PROTETOR SCANIA: 2560450</t>
   </si>
   <si>
-    <t>13.642,440</t>
-  </si>
-  <si>
     <t>18.070</t>
   </si>
   <si>
-    <t>301</t>
-  </si>
-  <si>
     <t>1010059549</t>
   </si>
   <si>
     <t>SUPORTE DIANT ACO CARR RANDON/301206840R</t>
   </si>
   <si>
-    <t>157</t>
-  </si>
-  <si>
     <t>220</t>
   </si>
   <si>
@@ -4931,19 +4871,76 @@
     <t>67</t>
   </si>
   <si>
-    <t>210.051,850</t>
-  </si>
-  <si>
     <t>10.063,550</t>
   </si>
   <si>
-    <t>1.356</t>
-  </si>
-  <si>
     <t>8.298</t>
   </si>
   <si>
-    <t>110.374</t>
+    <t>447</t>
+  </si>
+  <si>
+    <t>331</t>
+  </si>
+  <si>
+    <t>1010020838</t>
+  </si>
+  <si>
+    <t>CINTA COROTE CARRETA METAL C/COR005</t>
+  </si>
+  <si>
+    <t>246.680,620</t>
+  </si>
+  <si>
+    <t>131</t>
+  </si>
+  <si>
+    <t>419</t>
+  </si>
+  <si>
+    <t>1.473</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>514</t>
+  </si>
+  <si>
+    <t>170</t>
+  </si>
+  <si>
+    <t>3.002</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>178</t>
+  </si>
+  <si>
+    <t>297</t>
+  </si>
+  <si>
+    <t>193</t>
+  </si>
+  <si>
+    <t>13.164,530</t>
+  </si>
+  <si>
+    <t>162</t>
+  </si>
+  <si>
+    <t>347</t>
+  </si>
+  <si>
+    <t>261.320,150</t>
+  </si>
+  <si>
+    <t>1.353</t>
+  </si>
+  <si>
+    <t>110.100</t>
   </si>
 </sst>
 </file>
@@ -5404,7 +5401,7 @@
         <v>10</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1580</v>
+        <v>1571</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>12</v>
@@ -5773,7 +5770,7 @@
         <v>10</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>1506</v>
+        <v>1511</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>12</v>
@@ -5888,7 +5885,7 @@
         <v>10</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1581</v>
+        <v>1613</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>12</v>
@@ -6086,16 +6083,16 @@
         <v>7</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>1582</v>
+        <v>1572</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>1583</v>
+        <v>1573</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>708</v>
+        <v>1462</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>12</v>
@@ -6118,7 +6115,7 @@
         <v>10</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>1584</v>
+        <v>1574</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>12</v>
@@ -6164,7 +6161,7 @@
         <v>10</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>12</v>
@@ -6187,7 +6184,7 @@
         <v>10</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>1534</v>
+        <v>1532</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>12</v>
@@ -6210,7 +6207,7 @@
         <v>10</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>12</v>
@@ -6233,7 +6230,7 @@
         <v>10</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>12</v>
@@ -6348,7 +6345,7 @@
         <v>10</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>12</v>
@@ -6371,7 +6368,7 @@
         <v>10</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>12</v>
@@ -6417,7 +6414,7 @@
         <v>10</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>12</v>
@@ -6440,7 +6437,7 @@
         <v>10</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>12</v>
@@ -6463,7 +6460,7 @@
         <v>10</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>1577</v>
+        <v>1569</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>12</v>
@@ -6532,7 +6529,7 @@
         <v>10</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>12</v>
@@ -6670,7 +6667,7 @@
         <v>10</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>191</v>
+        <v>48</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>12</v>
@@ -7903,10 +7900,10 @@
         <v>7</v>
       </c>
       <c r="B112" s="2" t="s">
+        <v>1487</v>
+      </c>
+      <c r="C112" s="2" t="s">
         <v>1488</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>1489</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>10</v>
@@ -7981,7 +7978,7 @@
         <v>10</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>12</v>
@@ -8050,7 +8047,7 @@
         <v>10</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>12</v>
@@ -8073,7 +8070,7 @@
         <v>22</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>12</v>
@@ -8156,16 +8153,16 @@
         <v>7</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>1540</v>
+        <v>1538</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>1541</v>
+        <v>1614</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>12</v>
@@ -8625,7 +8622,7 @@
         <v>10</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>695</v>
+        <v>1526</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>12</v>
@@ -8924,7 +8921,7 @@
         <v>297</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="F156" s="2" t="s">
         <v>12</v>
@@ -9246,7 +9243,7 @@
         <v>297</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="F170" s="2" t="s">
         <v>12</v>
@@ -9269,7 +9266,7 @@
         <v>297</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="F171" s="2" t="s">
         <v>12</v>
@@ -9315,7 +9312,7 @@
         <v>297</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="F173" s="2" t="s">
         <v>12</v>
@@ -9361,7 +9358,7 @@
         <v>297</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="F175" s="2" t="s">
         <v>12</v>
@@ -9499,7 +9496,7 @@
         <v>297</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="F181" s="2" t="s">
         <v>12</v>
@@ -9519,10 +9516,10 @@
         <v>390</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>22</v>
+        <v>297</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>36</v>
+        <v>495</v>
       </c>
       <c r="F182" s="2" t="s">
         <v>12</v>
@@ -9536,16 +9533,16 @@
         <v>7</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>297</v>
+        <v>22</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>545</v>
+        <v>380</v>
       </c>
       <c r="F183" s="2" t="s">
         <v>12</v>
@@ -9565,10 +9562,10 @@
         <v>392</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>22</v>
+        <v>297</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>380</v>
+        <v>620</v>
       </c>
       <c r="F184" s="2" t="s">
         <v>12</v>
@@ -9582,16 +9579,16 @@
         <v>7</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>297</v>
+        <v>10</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>620</v>
+        <v>48</v>
       </c>
       <c r="F185" s="2" t="s">
         <v>12</v>
@@ -9605,10 +9602,10 @@
         <v>7</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>10</v>
@@ -9628,16 +9625,16 @@
         <v>7</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>48</v>
+        <v>224</v>
       </c>
       <c r="F187" s="2" t="s">
         <v>12</v>
@@ -9651,10 +9648,10 @@
         <v>7</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>397</v>
+        <v>1482</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>398</v>
+        <v>1483</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>10</v>
@@ -9674,16 +9671,16 @@
         <v>7</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>1483</v>
+        <v>399</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>1484</v>
+        <v>400</v>
       </c>
       <c r="D189" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>224</v>
+        <v>380</v>
       </c>
       <c r="F189" s="2" t="s">
         <v>12</v>
@@ -9697,16 +9694,16 @@
         <v>7</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D190" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>380</v>
+        <v>403</v>
       </c>
       <c r="F190" s="2" t="s">
         <v>12</v>
@@ -9720,16 +9717,16 @@
         <v>7</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>403</v>
+        <v>462</v>
       </c>
       <c r="F191" s="2" t="s">
         <v>12</v>
@@ -9743,16 +9740,16 @@
         <v>7</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>462</v>
+        <v>1575</v>
       </c>
       <c r="F192" s="2" t="s">
         <v>12</v>
@@ -9766,16 +9763,16 @@
         <v>7</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D193" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>1585</v>
+        <v>1145</v>
       </c>
       <c r="F193" s="2" t="s">
         <v>12</v>
@@ -9789,16 +9786,16 @@
         <v>7</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>10</v>
+        <v>138</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>1145</v>
+        <v>26</v>
       </c>
       <c r="F194" s="2" t="s">
         <v>12</v>
@@ -9812,16 +9809,16 @@
         <v>7</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>138</v>
+        <v>414</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>26</v>
+        <v>415</v>
       </c>
       <c r="F195" s="2" t="s">
         <v>12</v>
@@ -9835,16 +9832,16 @@
         <v>7</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>414</v>
+        <v>138</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>415</v>
+        <v>81</v>
       </c>
       <c r="F196" s="2" t="s">
         <v>12</v>
@@ -9858,16 +9855,16 @@
         <v>7</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D197" s="2" t="s">
         <v>138</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>81</v>
+        <v>221</v>
       </c>
       <c r="F197" s="2" t="s">
         <v>12</v>
@@ -9881,16 +9878,16 @@
         <v>7</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D198" s="2" t="s">
         <v>138</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>221</v>
+        <v>65</v>
       </c>
       <c r="F198" s="2" t="s">
         <v>12</v>
@@ -9904,16 +9901,16 @@
         <v>7</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D199" s="2" t="s">
         <v>138</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>65</v>
+        <v>424</v>
       </c>
       <c r="F199" s="2" t="s">
         <v>12</v>
@@ -9927,16 +9924,16 @@
         <v>7</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>138</v>
+        <v>10</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>424</v>
+        <v>807</v>
       </c>
       <c r="F200" s="2" t="s">
         <v>12</v>
@@ -9950,16 +9947,16 @@
         <v>7</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>807</v>
+        <v>359</v>
       </c>
       <c r="F201" s="2" t="s">
         <v>12</v>
@@ -9973,16 +9970,16 @@
         <v>7</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>359</v>
+        <v>81</v>
       </c>
       <c r="F202" s="2" t="s">
         <v>12</v>
@@ -9996,16 +9993,16 @@
         <v>7</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D203" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>81</v>
+        <v>164</v>
       </c>
       <c r="F203" s="2" t="s">
         <v>12</v>
@@ -10019,16 +10016,16 @@
         <v>7</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>164</v>
+        <v>435</v>
       </c>
       <c r="F204" s="2" t="s">
         <v>12</v>
@@ -10042,16 +10039,16 @@
         <v>7</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>435</v>
+        <v>164</v>
       </c>
       <c r="F205" s="2" t="s">
         <v>12</v>
@@ -10065,16 +10062,16 @@
         <v>7</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F206" s="2" t="s">
         <v>12</v>
@@ -10088,16 +10085,16 @@
         <v>7</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>167</v>
+        <v>1576</v>
       </c>
       <c r="F207" s="2" t="s">
         <v>12</v>
@@ -10111,16 +10108,16 @@
         <v>7</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D208" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>1586</v>
+        <v>1517</v>
       </c>
       <c r="F208" s="2" t="s">
         <v>12</v>
@@ -10134,16 +10131,16 @@
         <v>7</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>442</v>
+        <v>1615</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>443</v>
+        <v>1616</v>
       </c>
       <c r="D209" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>1518</v>
+        <v>21</v>
       </c>
       <c r="F209" s="2" t="s">
         <v>12</v>
@@ -10419,7 +10416,7 @@
         <v>22</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>1587</v>
+        <v>1577</v>
       </c>
       <c r="F221" s="2" t="s">
         <v>12</v>
@@ -10557,7 +10554,7 @@
         <v>479</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>1588</v>
+        <v>1617</v>
       </c>
       <c r="F227" s="2" t="s">
         <v>40</v>
@@ -10741,7 +10738,7 @@
         <v>10</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>1466</v>
+        <v>1618</v>
       </c>
       <c r="F235" s="2" t="s">
         <v>12</v>
@@ -10902,7 +10899,7 @@
         <v>10</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="F242" s="2" t="s">
         <v>283</v>
@@ -11123,10 +11120,10 @@
         <v>7</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="D252" s="2" t="s">
         <v>10</v>
@@ -11293,7 +11290,7 @@
         <v>10</v>
       </c>
       <c r="E259" s="2" t="s">
-        <v>359</v>
+        <v>708</v>
       </c>
       <c r="F259" s="2" t="s">
         <v>12</v>
@@ -11339,7 +11336,7 @@
         <v>35</v>
       </c>
       <c r="E261" s="2" t="s">
-        <v>607</v>
+        <v>532</v>
       </c>
       <c r="F261" s="2" t="s">
         <v>12</v>
@@ -11385,7 +11382,7 @@
         <v>10</v>
       </c>
       <c r="E263" s="2" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="F263" s="2" t="s">
         <v>12</v>
@@ -11408,7 +11405,7 @@
         <v>22</v>
       </c>
       <c r="E264" s="2" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="F264" s="2" t="s">
         <v>12</v>
@@ -11523,7 +11520,7 @@
         <v>10</v>
       </c>
       <c r="E269" s="2" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="F269" s="2" t="s">
         <v>12</v>
@@ -11960,7 +11957,7 @@
         <v>10</v>
       </c>
       <c r="E288" s="2" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="F288" s="2" t="s">
         <v>12</v>
@@ -12006,7 +12003,7 @@
         <v>10</v>
       </c>
       <c r="E290" s="2" t="s">
-        <v>532</v>
+        <v>155</v>
       </c>
       <c r="F290" s="2" t="s">
         <v>12</v>
@@ -12029,7 +12026,7 @@
         <v>10</v>
       </c>
       <c r="E291" s="2" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="F291" s="2" t="s">
         <v>114</v>
@@ -12098,7 +12095,7 @@
         <v>10</v>
       </c>
       <c r="E294" s="2" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="F294" s="2" t="s">
         <v>12</v>
@@ -12190,7 +12187,7 @@
         <v>10</v>
       </c>
       <c r="E298" s="2" t="s">
-        <v>1589</v>
+        <v>756</v>
       </c>
       <c r="F298" s="2" t="s">
         <v>12</v>
@@ -12259,7 +12256,7 @@
         <v>10</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>1590</v>
+        <v>1578</v>
       </c>
       <c r="F301" s="2" t="s">
         <v>12</v>
@@ -12282,7 +12279,7 @@
         <v>10</v>
       </c>
       <c r="E302" s="2" t="s">
-        <v>1591</v>
+        <v>1579</v>
       </c>
       <c r="F302" s="2" t="s">
         <v>12</v>
@@ -12535,7 +12532,7 @@
         <v>10</v>
       </c>
       <c r="E313" s="2" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="F313" s="2" t="s">
         <v>12</v>
@@ -12650,7 +12647,7 @@
         <v>10</v>
       </c>
       <c r="E318" s="2" t="s">
-        <v>1592</v>
+        <v>1580</v>
       </c>
       <c r="F318" s="2" t="s">
         <v>12</v>
@@ -12719,7 +12716,7 @@
         <v>10</v>
       </c>
       <c r="E321" s="2" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
       <c r="F321" s="2" t="s">
         <v>12</v>
@@ -12788,7 +12785,7 @@
         <v>10</v>
       </c>
       <c r="E324" s="2" t="s">
-        <v>715</v>
+        <v>362</v>
       </c>
       <c r="F324" s="2" t="s">
         <v>12</v>
@@ -12811,7 +12808,7 @@
         <v>10</v>
       </c>
       <c r="E325" s="2" t="s">
-        <v>1593</v>
+        <v>1484</v>
       </c>
       <c r="F325" s="2" t="s">
         <v>12</v>
@@ -12834,7 +12831,7 @@
         <v>10</v>
       </c>
       <c r="E326" s="2" t="s">
-        <v>1594</v>
+        <v>1619</v>
       </c>
       <c r="F326" s="2" t="s">
         <v>12</v>
@@ -12880,7 +12877,7 @@
         <v>10</v>
       </c>
       <c r="E328" s="2" t="s">
-        <v>380</v>
+        <v>1567</v>
       </c>
       <c r="F328" s="2" t="s">
         <v>12</v>
@@ -12903,7 +12900,7 @@
         <v>10</v>
       </c>
       <c r="E329" s="2" t="s">
-        <v>1595</v>
+        <v>1620</v>
       </c>
       <c r="F329" s="2" t="s">
         <v>12</v>
@@ -12926,7 +12923,7 @@
         <v>22</v>
       </c>
       <c r="E330" s="2" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="F330" s="2" t="s">
         <v>12</v>
@@ -13124,16 +13121,16 @@
         <v>7</v>
       </c>
       <c r="B339" s="2" t="s">
+        <v>1490</v>
+      </c>
+      <c r="C339" s="2" t="s">
         <v>1491</v>
-      </c>
-      <c r="C339" s="2" t="s">
-        <v>1492</v>
       </c>
       <c r="D339" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E339" s="2" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="F339" s="2" t="s">
         <v>519</v>
@@ -13248,7 +13245,7 @@
         <v>10</v>
       </c>
       <c r="E344" s="2" t="s">
-        <v>715</v>
+        <v>362</v>
       </c>
       <c r="F344" s="2" t="s">
         <v>12</v>
@@ -13271,7 +13268,7 @@
         <v>10</v>
       </c>
       <c r="E345" s="2" t="s">
-        <v>1596</v>
+        <v>1582</v>
       </c>
       <c r="F345" s="2" t="s">
         <v>114</v>
@@ -13340,7 +13337,7 @@
         <v>10</v>
       </c>
       <c r="E348" s="2" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="F348" s="2" t="s">
         <v>12</v>
@@ -13363,7 +13360,7 @@
         <v>10</v>
       </c>
       <c r="E349" s="2" t="s">
-        <v>1597</v>
+        <v>1583</v>
       </c>
       <c r="F349" s="2" t="s">
         <v>12</v>
@@ -13386,7 +13383,7 @@
         <v>10</v>
       </c>
       <c r="E350" s="2" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="F350" s="2" t="s">
         <v>12</v>
@@ -13478,7 +13475,7 @@
         <v>10</v>
       </c>
       <c r="E354" s="2" t="s">
-        <v>1585</v>
+        <v>1575</v>
       </c>
       <c r="F354" s="2" t="s">
         <v>12</v>
@@ -13501,7 +13498,7 @@
         <v>10</v>
       </c>
       <c r="E355" s="2" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="F355" s="2" t="s">
         <v>12</v>
@@ -13524,7 +13521,7 @@
         <v>10</v>
       </c>
       <c r="E356" s="2" t="s">
-        <v>1598</v>
+        <v>1584</v>
       </c>
       <c r="F356" s="2" t="s">
         <v>12</v>
@@ -13547,7 +13544,7 @@
         <v>10</v>
       </c>
       <c r="E357" s="2" t="s">
-        <v>1599</v>
+        <v>1585</v>
       </c>
       <c r="F357" s="2" t="s">
         <v>12</v>
@@ -13570,7 +13567,7 @@
         <v>10</v>
       </c>
       <c r="E358" s="2" t="s">
-        <v>1553</v>
+        <v>1551</v>
       </c>
       <c r="F358" s="2" t="s">
         <v>114</v>
@@ -13616,7 +13613,7 @@
         <v>10</v>
       </c>
       <c r="E360" s="2" t="s">
-        <v>1600</v>
+        <v>1586</v>
       </c>
       <c r="F360" s="2" t="s">
         <v>12</v>
@@ -13639,7 +13636,7 @@
         <v>10</v>
       </c>
       <c r="E361" s="2" t="s">
-        <v>1601</v>
+        <v>1587</v>
       </c>
       <c r="F361" s="2" t="s">
         <v>12</v>
@@ -13662,7 +13659,7 @@
         <v>10</v>
       </c>
       <c r="E362" s="2" t="s">
-        <v>1602</v>
+        <v>1621</v>
       </c>
       <c r="F362" s="2" t="s">
         <v>12</v>
@@ -13685,7 +13682,7 @@
         <v>22</v>
       </c>
       <c r="E363" s="2" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="F363" s="2" t="s">
         <v>12</v>
@@ -13708,7 +13705,7 @@
         <v>10</v>
       </c>
       <c r="E364" s="2" t="s">
-        <v>1603</v>
+        <v>620</v>
       </c>
       <c r="F364" s="2" t="s">
         <v>12</v>
@@ -13754,7 +13751,7 @@
         <v>10</v>
       </c>
       <c r="E366" s="2" t="s">
-        <v>1554</v>
+        <v>1552</v>
       </c>
       <c r="F366" s="2" t="s">
         <v>12</v>
@@ -13906,10 +13903,10 @@
         <v>7</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>1604</v>
+        <v>1588</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>1605</v>
+        <v>1589</v>
       </c>
       <c r="D373" s="2" t="s">
         <v>10</v>
@@ -14214,7 +14211,7 @@
         <v>10</v>
       </c>
       <c r="E386" s="2" t="s">
-        <v>1606</v>
+        <v>1590</v>
       </c>
       <c r="F386" s="2" t="s">
         <v>12</v>
@@ -14651,7 +14648,7 @@
         <v>138</v>
       </c>
       <c r="E405" s="2" t="s">
-        <v>1607</v>
+        <v>365</v>
       </c>
       <c r="F405" s="2" t="s">
         <v>192</v>
@@ -14665,10 +14662,10 @@
         <v>7</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>1609</v>
+        <v>1592</v>
       </c>
       <c r="D406" s="2" t="s">
         <v>10</v>
@@ -14950,7 +14947,7 @@
         <v>10</v>
       </c>
       <c r="E418" s="2" t="s">
-        <v>1610</v>
+        <v>1593</v>
       </c>
       <c r="F418" s="2" t="s">
         <v>283</v>
@@ -14973,7 +14970,7 @@
         <v>22</v>
       </c>
       <c r="E419" s="2" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="F419" s="2" t="s">
         <v>283</v>
@@ -15134,7 +15131,7 @@
         <v>10</v>
       </c>
       <c r="E426" s="2" t="s">
-        <v>1555</v>
+        <v>1622</v>
       </c>
       <c r="F426" s="2" t="s">
         <v>12</v>
@@ -15157,7 +15154,7 @@
         <v>10</v>
       </c>
       <c r="E427" s="2" t="s">
-        <v>1557</v>
+        <v>1623</v>
       </c>
       <c r="F427" s="2" t="s">
         <v>12</v>
@@ -15318,7 +15315,7 @@
         <v>10</v>
       </c>
       <c r="E434" s="2" t="s">
-        <v>715</v>
+        <v>462</v>
       </c>
       <c r="F434" s="2" t="s">
         <v>12</v>
@@ -15479,7 +15476,7 @@
         <v>10</v>
       </c>
       <c r="E441" s="2" t="s">
-        <v>1556</v>
+        <v>1624</v>
       </c>
       <c r="F441" s="2" t="s">
         <v>12</v>
@@ -15525,7 +15522,7 @@
         <v>138</v>
       </c>
       <c r="E443" s="2" t="s">
-        <v>1611</v>
+        <v>1594</v>
       </c>
       <c r="F443" s="2" t="s">
         <v>12</v>
@@ -15548,7 +15545,7 @@
         <v>138</v>
       </c>
       <c r="E444" s="2" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="F444" s="2" t="s">
         <v>12</v>
@@ -15571,7 +15568,7 @@
         <v>138</v>
       </c>
       <c r="E445" s="2" t="s">
-        <v>1612</v>
+        <v>1595</v>
       </c>
       <c r="F445" s="2" t="s">
         <v>12</v>
@@ -15594,7 +15591,7 @@
         <v>138</v>
       </c>
       <c r="E446" s="2" t="s">
-        <v>1558</v>
+        <v>1553</v>
       </c>
       <c r="F446" s="2" t="s">
         <v>12</v>
@@ -15617,7 +15614,7 @@
         <v>35</v>
       </c>
       <c r="E447" s="2" t="s">
-        <v>1613</v>
+        <v>1596</v>
       </c>
       <c r="F447" s="2" t="s">
         <v>40</v>
@@ -15654,10 +15651,10 @@
         <v>7</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>1614</v>
+        <v>1597</v>
       </c>
       <c r="C449" s="2" t="s">
-        <v>1615</v>
+        <v>1598</v>
       </c>
       <c r="D449" s="2" t="s">
         <v>10</v>
@@ -16031,7 +16028,7 @@
         <v>10</v>
       </c>
       <c r="E465" s="2" t="s">
-        <v>1559</v>
+        <v>1554</v>
       </c>
       <c r="F465" s="2" t="s">
         <v>12</v>
@@ -16077,7 +16074,7 @@
         <v>10</v>
       </c>
       <c r="E467" s="2" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="F467" s="2" t="s">
         <v>114</v>
@@ -16169,7 +16166,7 @@
         <v>10</v>
       </c>
       <c r="E471" s="2" t="s">
-        <v>1616</v>
+        <v>1599</v>
       </c>
       <c r="F471" s="2" t="s">
         <v>12</v>
@@ -16192,7 +16189,7 @@
         <v>10</v>
       </c>
       <c r="E472" s="2" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="F472" s="2" t="s">
         <v>12</v>
@@ -16215,7 +16212,7 @@
         <v>10</v>
       </c>
       <c r="E473" s="2" t="s">
-        <v>1560</v>
+        <v>1555</v>
       </c>
       <c r="F473" s="2" t="s">
         <v>12</v>
@@ -16238,7 +16235,7 @@
         <v>10</v>
       </c>
       <c r="E474" s="2" t="s">
-        <v>362</v>
+        <v>1474</v>
       </c>
       <c r="F474" s="2" t="s">
         <v>12</v>
@@ -16284,7 +16281,7 @@
         <v>10</v>
       </c>
       <c r="E476" s="2" t="s">
-        <v>1561</v>
+        <v>1556</v>
       </c>
       <c r="F476" s="2" t="s">
         <v>114</v>
@@ -16330,7 +16327,7 @@
         <v>10</v>
       </c>
       <c r="E478" s="2" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="F478" s="2" t="s">
         <v>12</v>
@@ -16376,7 +16373,7 @@
         <v>10</v>
       </c>
       <c r="E480" s="2" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="F480" s="2" t="s">
         <v>12</v>
@@ -16422,7 +16419,7 @@
         <v>10</v>
       </c>
       <c r="E482" s="2" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="F482" s="2" t="s">
         <v>12</v>
@@ -16482,10 +16479,10 @@
         <v>7</v>
       </c>
       <c r="B485" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="C485" s="2" t="s">
         <v>1479</v>
-      </c>
-      <c r="C485" s="2" t="s">
-        <v>1480</v>
       </c>
       <c r="D485" s="2" t="s">
         <v>10</v>
@@ -16583,7 +16580,7 @@
         <v>10</v>
       </c>
       <c r="E489" s="2" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="F489" s="2" t="s">
         <v>12</v>
@@ -16606,7 +16603,7 @@
         <v>10</v>
       </c>
       <c r="E490" s="2" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="F490" s="2" t="s">
         <v>12</v>
@@ -16652,7 +16649,7 @@
         <v>10</v>
       </c>
       <c r="E492" s="2" t="s">
-        <v>1562</v>
+        <v>1557</v>
       </c>
       <c r="F492" s="2" t="s">
         <v>12</v>
@@ -16744,7 +16741,7 @@
         <v>10</v>
       </c>
       <c r="E496" s="2" t="s">
-        <v>1563</v>
+        <v>1558</v>
       </c>
       <c r="F496" s="2" t="s">
         <v>12</v>
@@ -16790,7 +16787,7 @@
         <v>10</v>
       </c>
       <c r="E498" s="2" t="s">
-        <v>1564</v>
+        <v>1559</v>
       </c>
       <c r="F498" s="2" t="s">
         <v>12</v>
@@ -16905,7 +16902,7 @@
         <v>10</v>
       </c>
       <c r="E503" s="2" t="s">
-        <v>1565</v>
+        <v>1560</v>
       </c>
       <c r="F503" s="2" t="s">
         <v>12</v>
@@ -17011,10 +17008,10 @@
         <v>7</v>
       </c>
       <c r="B508" s="2" t="s">
+        <v>1494</v>
+      </c>
+      <c r="C508" s="2" t="s">
         <v>1495</v>
-      </c>
-      <c r="C508" s="2" t="s">
-        <v>1496</v>
       </c>
       <c r="D508" s="2" t="s">
         <v>10</v>
@@ -17043,7 +17040,7 @@
         <v>10</v>
       </c>
       <c r="E509" s="2" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="F509" s="2" t="s">
         <v>12</v>
@@ -17158,7 +17155,7 @@
         <v>10</v>
       </c>
       <c r="E514" s="2" t="s">
-        <v>620</v>
+        <v>1625</v>
       </c>
       <c r="F514" s="2" t="s">
         <v>12</v>
@@ -17241,16 +17238,16 @@
         <v>7</v>
       </c>
       <c r="B518" s="2" t="s">
-        <v>1566</v>
+        <v>1561</v>
       </c>
       <c r="C518" s="2" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="D518" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E518" s="2" t="s">
-        <v>582</v>
+        <v>252</v>
       </c>
       <c r="F518" s="2" t="s">
         <v>12</v>
@@ -17310,10 +17307,10 @@
         <v>7</v>
       </c>
       <c r="B521" s="2" t="s">
+        <v>1496</v>
+      </c>
+      <c r="C521" s="2" t="s">
         <v>1497</v>
-      </c>
-      <c r="C521" s="2" t="s">
-        <v>1498</v>
       </c>
       <c r="D521" s="2" t="s">
         <v>10</v>
@@ -17342,7 +17339,7 @@
         <v>10</v>
       </c>
       <c r="E522" s="2" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="F522" s="2" t="s">
         <v>12</v>
@@ -17365,7 +17362,7 @@
         <v>1063</v>
       </c>
       <c r="E523" s="2" t="s">
-        <v>1478</v>
+        <v>1625</v>
       </c>
       <c r="F523" s="2" t="s">
         <v>12</v>
@@ -17411,7 +17408,7 @@
         <v>1063</v>
       </c>
       <c r="E525" s="2" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="F525" s="2" t="s">
         <v>12</v>
@@ -17448,10 +17445,10 @@
         <v>7</v>
       </c>
       <c r="B527" s="2" t="s">
-        <v>1568</v>
+        <v>1563</v>
       </c>
       <c r="C527" s="2" t="s">
-        <v>1569</v>
+        <v>1564</v>
       </c>
       <c r="D527" s="2" t="s">
         <v>1068</v>
@@ -17471,16 +17468,16 @@
         <v>7</v>
       </c>
       <c r="B528" s="2" t="s">
+        <v>1485</v>
+      </c>
+      <c r="C528" s="2" t="s">
         <v>1486</v>
-      </c>
-      <c r="C528" s="2" t="s">
-        <v>1487</v>
       </c>
       <c r="D528" s="2" t="s">
         <v>1068</v>
       </c>
       <c r="E528" s="2" t="s">
-        <v>1173</v>
+        <v>607</v>
       </c>
       <c r="F528" s="2" t="s">
         <v>12</v>
@@ -17494,16 +17491,16 @@
         <v>7</v>
       </c>
       <c r="B529" s="2" t="s">
+        <v>1527</v>
+      </c>
+      <c r="C529" s="2" t="s">
         <v>1528</v>
-      </c>
-      <c r="C529" s="2" t="s">
-        <v>1529</v>
       </c>
       <c r="D529" s="2" t="s">
         <v>1068</v>
       </c>
       <c r="E529" s="2" t="s">
-        <v>32</v>
+        <v>81</v>
       </c>
       <c r="F529" s="2" t="s">
         <v>12</v>
@@ -17517,16 +17514,16 @@
         <v>7</v>
       </c>
       <c r="B530" s="2" t="s">
+        <v>1529</v>
+      </c>
+      <c r="C530" s="2" t="s">
         <v>1530</v>
-      </c>
-      <c r="C530" s="2" t="s">
-        <v>1531</v>
       </c>
       <c r="D530" s="2" t="s">
         <v>1068</v>
       </c>
       <c r="E530" s="2" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="F530" s="2" t="s">
         <v>12</v>
@@ -17664,7 +17661,7 @@
         <v>10</v>
       </c>
       <c r="E536" s="2" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="F536" s="2" t="s">
         <v>114</v>
@@ -17733,7 +17730,7 @@
         <v>10</v>
       </c>
       <c r="E539" s="2" t="s">
-        <v>1617</v>
+        <v>1600</v>
       </c>
       <c r="F539" s="2" t="s">
         <v>12</v>
@@ -17779,7 +17776,7 @@
         <v>10</v>
       </c>
       <c r="E541" s="2" t="s">
-        <v>1570</v>
+        <v>1565</v>
       </c>
       <c r="F541" s="2" t="s">
         <v>12</v>
@@ -17825,7 +17822,7 @@
         <v>10</v>
       </c>
       <c r="E543" s="2" t="s">
-        <v>829</v>
+        <v>715</v>
       </c>
       <c r="F543" s="2" t="s">
         <v>12</v>
@@ -17848,7 +17845,7 @@
         <v>10</v>
       </c>
       <c r="E544" s="2" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="F544" s="2" t="s">
         <v>12</v>
@@ -17871,7 +17868,7 @@
         <v>10</v>
       </c>
       <c r="E545" s="2" t="s">
-        <v>582</v>
+        <v>252</v>
       </c>
       <c r="F545" s="2" t="s">
         <v>12</v>
@@ -17894,7 +17891,7 @@
         <v>10</v>
       </c>
       <c r="E546" s="2" t="s">
-        <v>1571</v>
+        <v>1626</v>
       </c>
       <c r="F546" s="2" t="s">
         <v>12</v>
@@ -17917,7 +17914,7 @@
         <v>10</v>
       </c>
       <c r="E547" s="2" t="s">
-        <v>1532</v>
+        <v>1627</v>
       </c>
       <c r="F547" s="2" t="s">
         <v>12</v>
@@ -17940,7 +17937,7 @@
         <v>10</v>
       </c>
       <c r="E548" s="2" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="F548" s="2" t="s">
         <v>12</v>
@@ -17963,7 +17960,7 @@
         <v>10</v>
       </c>
       <c r="E549" s="2" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="F549" s="2" t="s">
         <v>12</v>
@@ -17986,7 +17983,7 @@
         <v>10</v>
       </c>
       <c r="E550" s="2" t="s">
-        <v>1572</v>
+        <v>1566</v>
       </c>
       <c r="F550" s="2" t="s">
         <v>12</v>
@@ -18124,7 +18121,7 @@
         <v>138</v>
       </c>
       <c r="E556" s="2" t="s">
-        <v>1573</v>
+        <v>1628</v>
       </c>
       <c r="F556" s="2" t="s">
         <v>12</v>
@@ -18230,10 +18227,10 @@
         <v>7</v>
       </c>
       <c r="B561" s="2" t="s">
-        <v>1618</v>
+        <v>1601</v>
       </c>
       <c r="C561" s="2" t="s">
-        <v>1619</v>
+        <v>1602</v>
       </c>
       <c r="D561" s="2" t="s">
         <v>10</v>
@@ -18262,7 +18259,7 @@
         <v>479</v>
       </c>
       <c r="E562" s="2" t="s">
-        <v>1620</v>
+        <v>1629</v>
       </c>
       <c r="F562" s="2" t="s">
         <v>40</v>
@@ -18285,7 +18282,7 @@
         <v>10</v>
       </c>
       <c r="E563" s="2" t="s">
-        <v>1621</v>
+        <v>1603</v>
       </c>
       <c r="F563" s="2" t="s">
         <v>12</v>
@@ -18607,7 +18604,7 @@
         <v>10</v>
       </c>
       <c r="E577" s="2" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="F577" s="2" t="s">
         <v>114</v>
@@ -18722,7 +18719,7 @@
         <v>138</v>
       </c>
       <c r="E582" s="2" t="s">
-        <v>1574</v>
+        <v>1581</v>
       </c>
       <c r="F582" s="2" t="s">
         <v>12</v>
@@ -18745,7 +18742,7 @@
         <v>22</v>
       </c>
       <c r="E583" s="2" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="F583" s="2" t="s">
         <v>12</v>
@@ -18768,7 +18765,7 @@
         <v>10</v>
       </c>
       <c r="E584" s="2" t="s">
-        <v>1584</v>
+        <v>1574</v>
       </c>
       <c r="F584" s="2" t="s">
         <v>12</v>
@@ -18791,7 +18788,7 @@
         <v>22</v>
       </c>
       <c r="E585" s="2" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="F585" s="2" t="s">
         <v>12</v>
@@ -18814,7 +18811,7 @@
         <v>10</v>
       </c>
       <c r="E586" s="2" t="s">
-        <v>1587</v>
+        <v>1577</v>
       </c>
       <c r="F586" s="2" t="s">
         <v>12</v>
@@ -18837,7 +18834,7 @@
         <v>10</v>
       </c>
       <c r="E587" s="2" t="s">
-        <v>435</v>
+        <v>1526</v>
       </c>
       <c r="F587" s="2" t="s">
         <v>12</v>
@@ -18952,7 +18949,7 @@
         <v>10</v>
       </c>
       <c r="E592" s="2" t="s">
-        <v>1575</v>
+        <v>1567</v>
       </c>
       <c r="F592" s="2" t="s">
         <v>12</v>
@@ -18998,7 +18995,7 @@
         <v>10</v>
       </c>
       <c r="E594" s="2" t="s">
-        <v>1622</v>
+        <v>1550</v>
       </c>
       <c r="F594" s="2" t="s">
         <v>12</v>
@@ -19182,7 +19179,7 @@
         <v>138</v>
       </c>
       <c r="E602" s="2" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
       <c r="F602" s="2" t="s">
         <v>192</v>
@@ -19205,7 +19202,7 @@
         <v>138</v>
       </c>
       <c r="E603" s="2" t="s">
-        <v>89</v>
+        <v>362</v>
       </c>
       <c r="F603" s="2" t="s">
         <v>192</v>
@@ -19343,7 +19340,7 @@
         <v>138</v>
       </c>
       <c r="E609" s="2" t="s">
-        <v>545</v>
+        <v>708</v>
       </c>
       <c r="F609" s="2" t="s">
         <v>192</v>
@@ -19366,7 +19363,7 @@
         <v>138</v>
       </c>
       <c r="E610" s="2" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="F610" s="2" t="s">
         <v>192</v>
@@ -19748,10 +19745,10 @@
         <v>7</v>
       </c>
       <c r="B627" s="2" t="s">
-        <v>1623</v>
+        <v>1604</v>
       </c>
       <c r="C627" s="2" t="s">
-        <v>1624</v>
+        <v>1605</v>
       </c>
       <c r="D627" s="2" t="s">
         <v>10</v>
@@ -20539,7 +20536,7 @@
         <v>10</v>
       </c>
       <c r="E661" s="2" t="s">
-        <v>1576</v>
+        <v>1568</v>
       </c>
       <c r="F661" s="2" t="s">
         <v>12</v>
@@ -20562,7 +20559,7 @@
         <v>10</v>
       </c>
       <c r="E662" s="2" t="s">
-        <v>1577</v>
+        <v>1569</v>
       </c>
       <c r="F662" s="2" t="s">
         <v>12</v>
@@ -20631,7 +20628,7 @@
         <v>10</v>
       </c>
       <c r="E665" s="2" t="s">
-        <v>1625</v>
+        <v>1630</v>
       </c>
       <c r="F665" s="2" t="s">
         <v>12</v>
@@ -21068,7 +21065,7 @@
         <v>10</v>
       </c>
       <c r="E684" s="2" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="F684" s="2" t="s">
         <v>12</v>
@@ -21229,7 +21226,7 @@
         <v>1222</v>
       </c>
       <c r="E691" s="2" t="s">
-        <v>1626</v>
+        <v>1606</v>
       </c>
       <c r="F691" s="2" t="s">
         <v>12</v>
@@ -21367,7 +21364,7 @@
         <v>10</v>
       </c>
       <c r="E697" s="2" t="s">
-        <v>1627</v>
+        <v>1607</v>
       </c>
       <c r="F697" s="2" t="s">
         <v>12</v>
@@ -21436,7 +21433,7 @@
         <v>10</v>
       </c>
       <c r="E700" s="2" t="s">
-        <v>1628</v>
+        <v>1608</v>
       </c>
       <c r="F700" s="2" t="s">
         <v>12</v>
@@ -21459,7 +21456,7 @@
         <v>10</v>
       </c>
       <c r="E701" s="2" t="s">
-        <v>1629</v>
+        <v>1609</v>
       </c>
       <c r="F701" s="2" t="s">
         <v>12</v>
@@ -21482,7 +21479,7 @@
         <v>10</v>
       </c>
       <c r="E702" s="2" t="s">
-        <v>131</v>
+        <v>1631</v>
       </c>
       <c r="F702" s="2" t="s">
         <v>12</v>
@@ -21505,7 +21502,7 @@
         <v>10</v>
       </c>
       <c r="E703" s="2" t="s">
-        <v>1630</v>
+        <v>1610</v>
       </c>
       <c r="F703" s="2" t="s">
         <v>114</v>
@@ -21551,7 +21548,7 @@
         <v>10</v>
       </c>
       <c r="E705" s="2" t="s">
-        <v>1578</v>
+        <v>1539</v>
       </c>
       <c r="F705" s="2" t="s">
         <v>12</v>
@@ -21597,7 +21594,7 @@
         <v>10</v>
       </c>
       <c r="E707" s="2" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="F707" s="2" t="s">
         <v>114</v>
@@ -21850,7 +21847,7 @@
         <v>10</v>
       </c>
       <c r="E718" s="2" t="s">
-        <v>1505</v>
+        <v>867</v>
       </c>
       <c r="F718" s="2" t="s">
         <v>12</v>
@@ -22057,7 +22054,7 @@
         <v>10</v>
       </c>
       <c r="E727" s="2" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="F727" s="2" t="s">
         <v>12</v>
@@ -22357,7 +22354,7 @@
         <v>205</v>
       </c>
       <c r="E740" s="2" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="F740" s="2" t="s">
         <v>519</v>
@@ -22380,7 +22377,7 @@
         <v>205</v>
       </c>
       <c r="E741" s="2" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="F741" s="2" t="s">
         <v>40</v>
@@ -22403,7 +22400,7 @@
         <v>205</v>
       </c>
       <c r="E742" s="2" t="s">
-        <v>1632</v>
+        <v>1611</v>
       </c>
       <c r="F742" s="2" t="s">
         <v>283</v>
@@ -22432,7 +22429,7 @@
         <v>192</v>
       </c>
       <c r="G743" s="2" t="s">
-        <v>1579</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="744" spans="1:7" x14ac:dyDescent="0.2">
@@ -22449,7 +22446,7 @@
         <v>205</v>
       </c>
       <c r="E744" s="2" t="s">
-        <v>1634</v>
+        <v>1612</v>
       </c>
       <c r="F744" s="2" t="s">
         <v>114</v>
@@ -22472,7 +22469,7 @@
         <v>205</v>
       </c>
       <c r="E745" s="2" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="F745" s="2" t="s">
         <v>12</v>

--- a/dados-catalago-pcm-interno/relatorio.xlsx
+++ b/dados-catalago-pcm-interno/relatorio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amaggicombr-my.sharepoint.com/personal/hiago_andre_amaggi_com_br/Documents/Área de Trabalho/codigos/catalogoPecasPCM/dados-catalago-pcm-interno/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="105" documentId="11_FD86FE4AC4094E4AB971B8A5A011EE841C83CB4A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7332331C-1B1C-473D-B797-80A20605084C}"/>
+  <xr:revisionPtr revIDLastSave="112" documentId="11_FD86FE4AC4094E4AB971B8A5A011EE841C83CB4A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD067AAD-A9C7-480D-A5E7-304AF873969F}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5456,7 +5456,7 @@
         <v>10</v>
       </c>
       <c r="E2" s="2">
-        <v>4611</v>
+        <v>46</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>11</v>
